--- a/Resultados/Entregable/Reporte_Sen_SinInc_vf_2.xlsx
+++ b/Resultados/Entregable/Reporte_Sen_SinInc_vf_2.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ivan\Desktop\Ivan\Laboral\EstrategiaSur\GitProjects\Proyeccion-electoral-congreso\Resultados\Entregable\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80136817-DFE7-4105-9343-59D72BA35339}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4ADB33C8-D4CB-4DC2-9528-DBB4C5BA16A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="1665" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{85AAF8D7-1A96-46DE-A921-B4694576F524}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{85AAF8D7-1A96-46DE-A921-B4694576F524}"/>
   </bookViews>
   <sheets>
-    <sheet name="Resumen de Pactos" sheetId="33" r:id="rId1"/>
+    <sheet name="Resumen de Pactos" sheetId="34" r:id="rId1"/>
     <sheet name="C15" sheetId="1" r:id="rId2"/>
     <sheet name="C1" sheetId="16" r:id="rId3"/>
     <sheet name="C3" sheetId="17" r:id="rId4"/>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="496" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="600" uniqueCount="67">
   <si>
     <t>Esc</t>
   </si>
@@ -294,6 +294,12 @@
 -  Los resultados presentados son el producto de un modelo mixto que combina variables determinísticas y probabilísticas. Las variables determinísticas están basadas en datos observables y predecibles, mientras que las probabilísticas buscan capturar aquellas dinámicas que no se pueden predecir completamente a partir de mediciones conocidas. Esto permite modelar incertidumbres inherentes al sistema. Aunque los resultados no representan la realidad al 100%, se estima que los resultados reales estarán dentro de un rango cercano, considerando un margen de error razonable.
 </t>
     </r>
+  </si>
+  <si>
+    <t>Personalizado 3 CHV+</t>
+  </si>
+  <si>
+    <t>Personalizado 3 CHV</t>
   </si>
 </sst>
 </file>
@@ -634,7 +640,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -705,12 +711,27 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Porcentaje" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="115">
+  <dxfs count="142">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -728,13 +749,6 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="5" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
           <bgColor rgb="FF7030A0"/>
         </patternFill>
       </fill>
@@ -742,7 +756,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FF00B050"/>
+          <bgColor rgb="FFFFC000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -756,21 +770,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
           <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFABAB"/>
         </patternFill>
       </fill>
     </dxf>
@@ -808,7 +808,21 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="5" tint="-0.499984740745262"/>
+          <bgColor rgb="FFFFABAB"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -822,7 +836,171 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor rgb="FF7030A0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF7030A0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF7030A0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFABAB"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="1"/>
         </patternFill>
       </fill>
     </dxf>
@@ -851,6 +1029,128 @@
       <fill>
         <patternFill>
           <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF7030A0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFABAB"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -892,20 +1192,6 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
           <bgColor theme="2" tint="-0.24994659260841701"/>
         </patternFill>
       </fill>
@@ -913,45 +1199,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="7" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFABAB"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
+          <bgColor rgb="FF7030A0"/>
         </patternFill>
       </fill>
     </dxf>
@@ -965,7 +1213,14 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FF7030A0"/>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
@@ -993,7 +1248,45 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFF0000"/>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFABAB"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1028,13 +1321,6 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
           <bgColor rgb="FF0070C0"/>
         </patternFill>
       </fill>
@@ -1043,107 +1329,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFABAB"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF7030A0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF0070C0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1199,14 +1384,21 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
+          <bgColor rgb="FFFFC000"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFFF00"/>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1237,14 +1429,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FF7030A0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
+          <bgColor rgb="FFFFFF00"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1258,6 +1443,13 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor theme="2" tint="-0.24994659260841701"/>
         </patternFill>
       </fill>
@@ -1265,14 +1457,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
+          <bgColor rgb="FF7030A0"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1286,21 +1471,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF0070C0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF7030A0"/>
+          <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1321,6 +1492,20 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor theme="5" tint="-0.499984740745262"/>
         </patternFill>
       </fill>
@@ -1328,7 +1513,21 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
+          <bgColor rgb="FF7030A0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1356,13 +1555,6 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="7" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
           <bgColor rgb="FFFFABAB"/>
         </patternFill>
       </fill>
@@ -1374,6 +1566,20 @@
       <fill>
         <patternFill>
           <bgColor theme="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="-0.499984740745262"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1415,13 +1621,6 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="5" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
           <bgColor rgb="FFFFC000"/>
         </patternFill>
       </fill>
@@ -1430,6 +1629,13 @@
       <fill>
         <patternFill>
           <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1478,7 +1684,14 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFF0000"/>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF7030A0"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1492,14 +1705,14 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="5" tint="-0.499984740745262"/>
+          <bgColor theme="2" tint="-0.24994659260841701"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
+          <bgColor theme="5" tint="-0.499984740745262"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1513,21 +1726,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FF0070C0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
           <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF7030A0"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1570,7 +1769,7 @@
         <xdr:cNvPr id="2" name="Imagen 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{53E634B5-A1AB-4C88-93B4-BDAA767EB7CF}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FBF3A663-302B-474D-B855-90085DC00537}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1592,8 +1791,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="806451" y="5868213"/>
-          <a:ext cx="4451349" cy="552536"/>
+          <a:off x="809626" y="5950763"/>
+          <a:ext cx="4448174" cy="558886"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1620,7 +1819,7 @@
         <xdr:cNvPr id="3" name="Imagen 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F779E3DC-12E3-4120-A109-3B86636B2AA5}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3BA8F69C-99A1-4B35-89D8-63384514A47C}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1642,8 +1841,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6819901" y="5868213"/>
-          <a:ext cx="4448174" cy="552536"/>
+          <a:off x="6819901" y="5950763"/>
+          <a:ext cx="4444999" cy="558886"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1670,7 +1869,7 @@
         <xdr:cNvPr id="4" name="Imagen 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{92C9E3AD-FF32-43C3-95F7-01F27D5436D9}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{51BEE721-E41E-46AC-B586-4B9E8D0DC345}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1692,8 +1891,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="12836526" y="5868213"/>
-          <a:ext cx="4451349" cy="549361"/>
+          <a:off x="12836526" y="5950763"/>
+          <a:ext cx="4448174" cy="562061"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1720,7 +1919,7 @@
         <xdr:cNvPr id="5" name="Imagen 4">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AC3448B5-0083-4D57-885F-C28B4DCF2F74}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{39BAB4AD-AAB0-4AD0-9BAC-67E54A8A4E6B}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1742,8 +1941,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="18869026" y="5868213"/>
-          <a:ext cx="4444999" cy="549361"/>
+          <a:off x="18865851" y="5950763"/>
+          <a:ext cx="4448174" cy="562061"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1770,7 +1969,7 @@
         <xdr:cNvPr id="6" name="Imagen 5">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F3E13198-CF0B-4D4D-8A13-7AA6F98ED246}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CBC8AB2C-BC0B-4755-9205-1E346D1A9B84}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1792,8 +1991,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="24885651" y="5868213"/>
-          <a:ext cx="4451349" cy="552536"/>
+          <a:off x="24888826" y="5950763"/>
+          <a:ext cx="4448174" cy="558886"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1820,7 +2019,7 @@
         <xdr:cNvPr id="7" name="Imagen 6">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9AB815D9-8258-476B-B6C8-274B36EB566E}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{52164040-A36F-457D-BD3C-3ED19886F1BE}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1842,8 +2041,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="30914976" y="5868213"/>
-          <a:ext cx="4441824" cy="549361"/>
+          <a:off x="30914976" y="5950763"/>
+          <a:ext cx="4441824" cy="562061"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1870,7 +2069,7 @@
         <xdr:cNvPr id="8" name="Imagen 7">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{118EB1F7-4B92-4B12-B1E8-E5E8C698D6BA}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6584FDBB-3074-4F12-9312-DD7D3238B9AE}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1892,8 +2091,108 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="36925251" y="5868213"/>
-          <a:ext cx="4451349" cy="549361"/>
+          <a:off x="36928426" y="5950763"/>
+          <a:ext cx="4448174" cy="562061"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>29</xdr:col>
+      <xdr:colOff>19051</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>172263</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>30</xdr:col>
+      <xdr:colOff>3438525</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>181874</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="Imagen 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{05E8A32D-C928-49DA-867F-D14DC35FFB63}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="42919651" y="5938063"/>
+          <a:ext cx="4448174" cy="562061"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>33</xdr:col>
+      <xdr:colOff>6351</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>172263</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>34</xdr:col>
+      <xdr:colOff>3425825</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>181874</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10" name="Imagen 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00A29697-273B-4312-9E2E-AD51AE431A07}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="48926751" y="5938063"/>
+          <a:ext cx="4448174" cy="562061"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2297,7 +2596,7 @@
       <xxl21:absoluteUrl r:id="rId2"/>
     </xxl21:alternateUrls>
     <sheetNames>
-      <sheetName val="resultados_integracion_partido_"/>
+      <sheetName val="resultados_proyectados_proporci"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0">
@@ -2306,81 +2605,78 @@
             <v>Circunscripcion</v>
           </cell>
           <cell r="B1" t="str">
-            <v>Unnamed: 0</v>
+            <v>AH</v>
           </cell>
           <cell r="C1" t="str">
-            <v>AH</v>
+            <v>AMA</v>
           </cell>
           <cell r="D1" t="str">
-            <v>AMA</v>
+            <v>DEM</v>
           </cell>
           <cell r="E1" t="str">
-            <v>DEM</v>
+            <v>EVO</v>
           </cell>
           <cell r="F1" t="str">
-            <v>EVO</v>
+            <v>FA</v>
           </cell>
           <cell r="G1" t="str">
-            <v>FA</v>
+            <v>FREVS</v>
           </cell>
           <cell r="H1" t="str">
-            <v>FREVS</v>
+            <v>IGU</v>
           </cell>
           <cell r="I1" t="str">
-            <v>IGU</v>
+            <v>IND</v>
           </cell>
           <cell r="J1" t="str">
-            <v>IND</v>
+            <v>PAVP</v>
           </cell>
           <cell r="K1" t="str">
-            <v>PAVP</v>
+            <v>PCCH</v>
           </cell>
           <cell r="L1" t="str">
-            <v>PCCH</v>
+            <v>PDC</v>
           </cell>
           <cell r="M1" t="str">
-            <v>PDC</v>
+            <v>PDG</v>
           </cell>
           <cell r="N1" t="str">
-            <v>PDG</v>
+            <v>PH</v>
           </cell>
           <cell r="O1" t="str">
-            <v>PH</v>
+            <v>PL</v>
           </cell>
           <cell r="P1" t="str">
-            <v>PL</v>
+            <v>POP</v>
           </cell>
           <cell r="Q1" t="str">
-            <v>POP</v>
+            <v>PPD</v>
           </cell>
           <cell r="R1" t="str">
-            <v>PPD</v>
+            <v>PR</v>
           </cell>
           <cell r="S1" t="str">
-            <v>PR</v>
+            <v>PS</v>
           </cell>
           <cell r="T1" t="str">
-            <v>PS</v>
+            <v>PSC</v>
           </cell>
           <cell r="U1" t="str">
-            <v>PSC</v>
+            <v>PTR</v>
           </cell>
           <cell r="V1" t="str">
-            <v>PTR</v>
+            <v>REP</v>
           </cell>
           <cell r="W1" t="str">
-            <v>REP</v>
+            <v>RN</v>
           </cell>
           <cell r="X1" t="str">
-            <v>RN</v>
+            <v>UDI</v>
           </cell>
           <cell r="Y1" t="str">
-            <v>UDI</v>
+            <v>Votos Blancos</v>
           </cell>
           <cell r="Z1" t="str">
-            <v>Votos Blancos</v>
-          </cell>
-          <cell r="AA1" t="str">
             <v>Votos Nulos</v>
           </cell>
         </row>
@@ -2389,82 +2685,79 @@
             <v>1</v>
           </cell>
           <cell r="B2">
-            <v>0</v>
+            <v>2.94921215201552E-2</v>
           </cell>
           <cell r="C2">
             <v>0</v>
           </cell>
           <cell r="D2">
-            <v>0</v>
+            <v>3.8370273754083598E-2</v>
           </cell>
           <cell r="E2">
-            <v>0</v>
+            <v>7.7003860909288504E-3</v>
           </cell>
           <cell r="F2">
-            <v>0</v>
+            <v>3.69628738310364E-2</v>
           </cell>
           <cell r="G2">
-            <v>0</v>
+            <v>3.5904517253661603E-2</v>
           </cell>
           <cell r="H2">
-            <v>0</v>
+            <v>3.7122426783395401E-3</v>
           </cell>
           <cell r="I2">
-            <v>0</v>
+            <v>5.6132701789408403E-4</v>
           </cell>
           <cell r="J2">
             <v>0</v>
           </cell>
           <cell r="K2">
-            <v>0</v>
+            <v>2.64487084885912E-2</v>
           </cell>
           <cell r="L2">
-            <v>0</v>
+            <v>5.6262317300813103E-2</v>
           </cell>
           <cell r="M2">
-            <v>0</v>
+            <v>5.7424774525142802E-2</v>
           </cell>
           <cell r="N2">
-            <v>0</v>
+            <v>5.8452853463370601E-3</v>
           </cell>
           <cell r="O2">
-            <v>0</v>
+            <v>1.8447246997155602E-2</v>
           </cell>
           <cell r="P2">
-            <v>0</v>
+            <v>9.9735904143035594E-3</v>
           </cell>
           <cell r="Q2">
-            <v>0</v>
+            <v>3.4214412632511397E-2</v>
           </cell>
           <cell r="R2">
-            <v>0</v>
+            <v>4.3096647244751797E-2</v>
           </cell>
           <cell r="S2">
-            <v>0</v>
+            <v>2.6841637401117099E-2</v>
           </cell>
           <cell r="T2">
-            <v>0</v>
+            <v>3.7715052035014497E-2</v>
           </cell>
           <cell r="U2">
             <v>0</v>
           </cell>
           <cell r="V2">
-            <v>0</v>
+            <v>0.121981463961274</v>
           </cell>
           <cell r="W2">
-            <v>1</v>
+            <v>9.1851470829876006E-2</v>
           </cell>
           <cell r="X2">
-            <v>1</v>
+            <v>5.8876060015043502E-2</v>
           </cell>
           <cell r="Y2">
-            <v>0</v>
+            <v>0.108846411742552</v>
           </cell>
           <cell r="Z2">
-            <v>0</v>
-          </cell>
-          <cell r="AA2">
-            <v>0</v>
+            <v>0.149471178919414</v>
           </cell>
         </row>
         <row r="3">
@@ -2472,25 +2765,25 @@
             <v>2</v>
           </cell>
           <cell r="B3">
-            <v>0</v>
+            <v>1.19339124020918E-2</v>
           </cell>
           <cell r="C3">
             <v>0</v>
           </cell>
           <cell r="D3">
-            <v>0</v>
+            <v>3.4290097581162103E-2</v>
           </cell>
           <cell r="E3">
-            <v>0</v>
+            <v>3.6409073268422097E-2</v>
           </cell>
           <cell r="F3">
-            <v>0</v>
+            <v>4.0998132428207802E-2</v>
           </cell>
           <cell r="G3">
-            <v>0</v>
+            <v>5.1359296369277399E-2</v>
           </cell>
           <cell r="H3">
-            <v>0</v>
+            <v>2.37788417624217E-3</v>
           </cell>
           <cell r="I3">
             <v>0</v>
@@ -2499,55 +2792,52 @@
             <v>0</v>
           </cell>
           <cell r="K3">
-            <v>0</v>
+            <v>5.2003619358421502E-2</v>
           </cell>
           <cell r="L3">
-            <v>0</v>
+            <v>4.3976920157553598E-2</v>
           </cell>
           <cell r="M3">
-            <v>0</v>
+            <v>5.6756707498804598E-2</v>
           </cell>
           <cell r="N3">
-            <v>1</v>
+            <v>2.2009901775586899E-3</v>
           </cell>
           <cell r="O3">
-            <v>0</v>
+            <v>1.25712668397726E-2</v>
           </cell>
           <cell r="P3">
-            <v>0</v>
+            <v>1.3406420930526699E-3</v>
           </cell>
           <cell r="Q3">
-            <v>0</v>
+            <v>2.0125712668397699E-2</v>
           </cell>
           <cell r="R3">
-            <v>0</v>
+            <v>4.6313529067436202E-2</v>
           </cell>
           <cell r="S3">
-            <v>0</v>
+            <v>3.87097673361479E-2</v>
           </cell>
           <cell r="T3">
-            <v>0</v>
+            <v>3.8379029162851797E-2</v>
           </cell>
           <cell r="U3">
             <v>0</v>
           </cell>
           <cell r="V3">
-            <v>0</v>
+            <v>0.101381702942444</v>
           </cell>
           <cell r="W3">
-            <v>1</v>
+            <v>6.1567688220574998E-2</v>
           </cell>
           <cell r="X3">
-            <v>1</v>
+            <v>4.0977226773817897E-2</v>
           </cell>
           <cell r="Y3">
-            <v>0</v>
+            <v>0.12466202525403</v>
           </cell>
           <cell r="Z3">
-            <v>0</v>
-          </cell>
-          <cell r="AA3">
-            <v>0</v>
+            <v>0.18166477622373101</v>
           </cell>
         </row>
         <row r="4">
@@ -2558,79 +2848,76 @@
             <v>0</v>
           </cell>
           <cell r="C4">
-            <v>0</v>
+            <v>2.2323885276993902E-2</v>
           </cell>
           <cell r="D4">
-            <v>0</v>
+            <v>1.09616450830563E-2</v>
           </cell>
           <cell r="E4">
             <v>0</v>
           </cell>
           <cell r="F4">
-            <v>0</v>
+            <v>3.9417319956760503E-2</v>
           </cell>
           <cell r="G4">
-            <v>0</v>
+            <v>8.7931659300052895E-2</v>
           </cell>
           <cell r="H4">
-            <v>1</v>
+            <v>1.52353479068733E-2</v>
           </cell>
           <cell r="I4">
-            <v>0</v>
+            <v>6.86586981278373E-4</v>
           </cell>
           <cell r="J4">
             <v>0</v>
           </cell>
           <cell r="K4">
-            <v>0</v>
+            <v>7.5657755490372805E-2</v>
           </cell>
           <cell r="L4">
-            <v>0</v>
+            <v>1.94526094951365E-2</v>
           </cell>
           <cell r="M4">
-            <v>0</v>
+            <v>2.72518246178085E-2</v>
           </cell>
           <cell r="N4">
-            <v>0</v>
+            <v>6.0722509762785003E-3</v>
           </cell>
           <cell r="O4">
-            <v>0</v>
+            <v>1.4518475384566101E-2</v>
           </cell>
           <cell r="P4">
-            <v>0</v>
+            <v>1.3000068486621099E-2</v>
           </cell>
           <cell r="Q4">
-            <v>0</v>
+            <v>3.6495453555229901E-2</v>
           </cell>
           <cell r="R4">
-            <v>0</v>
+            <v>4.8074510690623899E-2</v>
           </cell>
           <cell r="S4">
-            <v>0</v>
+            <v>8.2266542358286801E-2</v>
           </cell>
           <cell r="T4">
-            <v>0</v>
+            <v>2.6145025754755202E-2</v>
           </cell>
           <cell r="U4">
             <v>0</v>
           </cell>
           <cell r="V4">
-            <v>0</v>
+            <v>7.9563557821464598E-2</v>
           </cell>
           <cell r="W4">
-            <v>0</v>
+            <v>0.107729110978267</v>
           </cell>
           <cell r="X4">
-            <v>1</v>
+            <v>5.4669875557400202E-2</v>
           </cell>
           <cell r="Y4">
-            <v>0</v>
+            <v>0.100040369249575</v>
           </cell>
           <cell r="Z4">
-            <v>0</v>
-          </cell>
-          <cell r="AA4">
-            <v>0</v>
+            <v>0.13250612507859599</v>
           </cell>
         </row>
         <row r="5">
@@ -2638,82 +2925,79 @@
             <v>4</v>
           </cell>
           <cell r="B5">
-            <v>0</v>
+            <v>8.8372020524635497E-3</v>
           </cell>
           <cell r="C5">
-            <v>0</v>
+            <v>1.30034388339584E-2</v>
           </cell>
           <cell r="D5">
-            <v>0</v>
+            <v>2.93165605128635E-2</v>
           </cell>
           <cell r="E5">
-            <v>0</v>
+            <v>1.2391455540471399E-2</v>
           </cell>
           <cell r="F5">
-            <v>0</v>
+            <v>4.8881840833870802E-2</v>
           </cell>
           <cell r="G5">
-            <v>0</v>
+            <v>2.2119726051189802E-2</v>
           </cell>
           <cell r="H5">
-            <v>0</v>
+            <v>1.85265045548034E-3</v>
           </cell>
           <cell r="I5">
-            <v>0</v>
+            <v>6.85094699682837E-3</v>
           </cell>
           <cell r="J5">
             <v>0</v>
           </cell>
           <cell r="K5">
-            <v>0</v>
+            <v>7.4657879442631303E-2</v>
           </cell>
           <cell r="L5">
-            <v>1</v>
+            <v>6.0643128010278602E-2</v>
           </cell>
           <cell r="M5">
-            <v>0</v>
+            <v>4.1295697412301498E-2</v>
           </cell>
           <cell r="N5">
-            <v>0</v>
+            <v>1.85265045548034E-3</v>
           </cell>
           <cell r="O5">
-            <v>0</v>
+            <v>1.21290709507229E-2</v>
           </cell>
           <cell r="P5">
-            <v>0</v>
+            <v>1.85265045548034E-3</v>
           </cell>
           <cell r="Q5">
-            <v>0</v>
+            <v>2.9622366597662299E-2</v>
           </cell>
           <cell r="R5">
-            <v>0</v>
+            <v>3.3264947571328099E-2</v>
           </cell>
           <cell r="S5">
-            <v>0</v>
+            <v>5.9224692505301497E-2</v>
           </cell>
           <cell r="T5">
-            <v>0</v>
+            <v>2.94965555991832E-2</v>
           </cell>
           <cell r="U5">
             <v>0</v>
           </cell>
           <cell r="V5">
-            <v>0</v>
+            <v>8.8958767393648802E-2</v>
           </cell>
           <cell r="W5">
-            <v>1</v>
+            <v>9.1046710394957403E-2</v>
           </cell>
           <cell r="X5">
-            <v>1</v>
+            <v>6.1780622731041297E-2</v>
           </cell>
           <cell r="Y5">
-            <v>0</v>
+            <v>0.123378281384648</v>
           </cell>
           <cell r="Z5">
-            <v>0</v>
-          </cell>
-          <cell r="AA5">
-            <v>0</v>
+            <v>0.14754215781820701</v>
           </cell>
         </row>
         <row r="6">
@@ -2724,79 +3008,76 @@
             <v>0</v>
           </cell>
           <cell r="C6">
-            <v>0</v>
+            <v>6.4869028679831499E-3</v>
           </cell>
           <cell r="D6">
-            <v>0</v>
+            <v>1.04419722326936E-2</v>
           </cell>
           <cell r="E6">
-            <v>0</v>
+            <v>1.0727601254744401E-2</v>
           </cell>
           <cell r="F6">
-            <v>0</v>
+            <v>7.5344175533315502E-2</v>
           </cell>
           <cell r="G6">
-            <v>1</v>
+            <v>1.99833204552331E-2</v>
           </cell>
           <cell r="H6">
-            <v>0</v>
+            <v>6.0856833510710903E-3</v>
           </cell>
           <cell r="I6">
-            <v>0</v>
+            <v>7.8443845483029892E-3</v>
           </cell>
           <cell r="J6">
             <v>0</v>
           </cell>
           <cell r="K6">
-            <v>0</v>
+            <v>6.1068228740051703E-2</v>
           </cell>
           <cell r="L6">
-            <v>0</v>
+            <v>4.6696923507655301E-2</v>
           </cell>
           <cell r="M6">
-            <v>0</v>
+            <v>2.4516491059365299E-2</v>
           </cell>
           <cell r="N6">
-            <v>0</v>
+            <v>6.0856833510710903E-3</v>
           </cell>
           <cell r="O6">
-            <v>0</v>
+            <v>1.47460445587225E-2</v>
           </cell>
           <cell r="P6">
-            <v>0</v>
+            <v>1.6016498646386199E-2</v>
           </cell>
           <cell r="Q6">
-            <v>0</v>
+            <v>3.3914876005763699E-2</v>
           </cell>
           <cell r="R6">
-            <v>0</v>
+            <v>3.6716123133481202E-2</v>
           </cell>
           <cell r="S6">
-            <v>0</v>
+            <v>4.1651405845219397E-2</v>
           </cell>
           <cell r="T6">
-            <v>0</v>
+            <v>2.4874271162507101E-2</v>
           </cell>
           <cell r="U6">
             <v>0</v>
           </cell>
           <cell r="V6">
-            <v>0</v>
+            <v>0.1371598002144</v>
           </cell>
           <cell r="W6">
-            <v>2</v>
+            <v>0.10626961654006201</v>
           </cell>
           <cell r="X6">
-            <v>1</v>
+            <v>6.4773075180236298E-2</v>
           </cell>
           <cell r="Y6">
-            <v>1</v>
+            <v>9.6271856942704306E-2</v>
           </cell>
           <cell r="Z6">
-            <v>0</v>
-          </cell>
-          <cell r="AA6">
-            <v>0</v>
+            <v>0.152325064869028</v>
           </cell>
         </row>
         <row r="7">
@@ -2807,79 +3088,76 @@
             <v>0</v>
           </cell>
           <cell r="C7">
-            <v>0</v>
+            <v>4.7263351114183901E-3</v>
           </cell>
           <cell r="D7">
-            <v>0</v>
+            <v>2.6360823979780498E-2</v>
           </cell>
           <cell r="E7">
-            <v>0</v>
+            <v>9.9077987891215205E-3</v>
           </cell>
           <cell r="F7">
-            <v>0</v>
+            <v>5.5805300497302701E-2</v>
           </cell>
           <cell r="G7">
-            <v>0</v>
+            <v>3.3050031450937302E-2</v>
           </cell>
           <cell r="H7">
             <v>0</v>
           </cell>
           <cell r="I7">
-            <v>0</v>
+            <v>9.7471242621549794E-3</v>
           </cell>
           <cell r="J7">
-            <v>0</v>
+            <v>1.88666208987711E-2</v>
           </cell>
           <cell r="K7">
-            <v>0</v>
+            <v>4.45717629705265E-2</v>
           </cell>
           <cell r="L7">
-            <v>0</v>
+            <v>5.4940718518863702E-2</v>
           </cell>
           <cell r="M7">
-            <v>0</v>
+            <v>2.3737400786957401E-2</v>
           </cell>
           <cell r="N7">
             <v>0</v>
           </cell>
           <cell r="O7">
-            <v>0</v>
+            <v>5.3864222373545302E-3</v>
           </cell>
           <cell r="P7">
             <v>0</v>
           </cell>
           <cell r="Q7">
-            <v>0</v>
+            <v>4.0499023084964801E-2</v>
           </cell>
           <cell r="R7">
-            <v>0</v>
+            <v>6.3749067658814398E-2</v>
           </cell>
           <cell r="S7">
-            <v>0</v>
+            <v>7.4840710798139698E-2</v>
           </cell>
           <cell r="T7">
-            <v>0</v>
+            <v>1.3509644065348299E-2</v>
           </cell>
           <cell r="U7">
             <v>0</v>
           </cell>
           <cell r="V7">
-            <v>0</v>
+            <v>0.119366798614535</v>
           </cell>
           <cell r="W7">
-            <v>1</v>
+            <v>0.10256552935532801</v>
           </cell>
           <cell r="X7">
-            <v>1</v>
+            <v>0.102845608473042</v>
           </cell>
           <cell r="Y7">
-            <v>1</v>
+            <v>8.2573491207069097E-2</v>
           </cell>
           <cell r="Z7">
-            <v>0</v>
-          </cell>
-          <cell r="AA7">
-            <v>0</v>
+            <v>0.112949787239567</v>
           </cell>
         </row>
         <row r="8">
@@ -2887,82 +3165,79 @@
             <v>7</v>
           </cell>
           <cell r="B8">
-            <v>0</v>
+            <v>4.1725406165982401E-3</v>
           </cell>
           <cell r="C8">
-            <v>0</v>
+            <v>9.3335749926337207E-3</v>
           </cell>
           <cell r="D8">
-            <v>0</v>
+            <v>2.8624667847333099E-2</v>
           </cell>
           <cell r="E8">
-            <v>0</v>
+            <v>3.2152027618441402E-2</v>
           </cell>
           <cell r="F8">
-            <v>0</v>
+            <v>4.3984466997937802E-2</v>
           </cell>
           <cell r="G8">
-            <v>0</v>
+            <v>2.1941509789160499E-2</v>
           </cell>
           <cell r="H8">
             <v>0</v>
           </cell>
           <cell r="I8">
-            <v>0</v>
+            <v>5.0032960101678301E-3</v>
           </cell>
           <cell r="J8">
-            <v>0</v>
+            <v>5.0686594898803096E-3</v>
           </cell>
           <cell r="K8">
-            <v>0</v>
+            <v>3.9371702314506297E-2</v>
           </cell>
           <cell r="L8">
-            <v>0</v>
+            <v>6.1016292826739503E-2</v>
           </cell>
           <cell r="M8">
-            <v>0</v>
+            <v>1.77747426029469E-2</v>
           </cell>
           <cell r="N8">
             <v>0</v>
           </cell>
           <cell r="O8">
-            <v>0</v>
+            <v>8.1075458116546103E-4</v>
           </cell>
           <cell r="P8">
             <v>0</v>
           </cell>
           <cell r="Q8">
-            <v>0</v>
+            <v>4.0684951533082901E-2</v>
           </cell>
           <cell r="R8">
-            <v>0</v>
+            <v>7.4653960171165698E-2</v>
           </cell>
           <cell r="S8">
-            <v>1</v>
+            <v>4.5000590745644699E-2</v>
           </cell>
           <cell r="T8">
-            <v>0</v>
+            <v>2.46896626522768E-2</v>
           </cell>
           <cell r="U8">
             <v>0</v>
           </cell>
           <cell r="V8">
-            <v>0</v>
+            <v>9.6292983446956498E-2</v>
           </cell>
           <cell r="W8">
-            <v>1</v>
+            <v>0.140323225500087</v>
           </cell>
           <cell r="X8">
-            <v>2</v>
+            <v>0.121224717787506</v>
           </cell>
           <cell r="Y8">
-            <v>1</v>
+            <v>8.2100242009830099E-2</v>
           </cell>
           <cell r="Z8">
-            <v>0</v>
-          </cell>
-          <cell r="AA8">
-            <v>0</v>
+            <v>0.105775430465938</v>
           </cell>
         </row>
         <row r="9">
@@ -2973,79 +3248,76 @@
             <v>0</v>
           </cell>
           <cell r="C9">
-            <v>0</v>
+            <v>9.0700278594555601E-3</v>
           </cell>
           <cell r="D9">
-            <v>0</v>
+            <v>4.2950330175467302E-2</v>
           </cell>
           <cell r="E9">
-            <v>0</v>
+            <v>1.84792218255839E-2</v>
           </cell>
           <cell r="F9">
-            <v>0</v>
+            <v>4.3808763337555803E-2</v>
           </cell>
           <cell r="G9">
-            <v>0</v>
+            <v>3.2906604546727697E-2</v>
           </cell>
           <cell r="H9">
-            <v>0</v>
+            <v>2.0465086926803499E-2</v>
           </cell>
           <cell r="I9">
-            <v>0</v>
+            <v>8.0951774440995404E-3</v>
           </cell>
           <cell r="J9">
             <v>0</v>
           </cell>
           <cell r="K9">
-            <v>0</v>
+            <v>4.8370216086559101E-2</v>
           </cell>
           <cell r="L9">
-            <v>0</v>
+            <v>6.4069831909623301E-2</v>
           </cell>
           <cell r="M9">
-            <v>0</v>
+            <v>3.3127480350265998E-2</v>
           </cell>
           <cell r="N9">
-            <v>0</v>
+            <v>5.2503028577553996E-4</v>
           </cell>
           <cell r="O9">
-            <v>0</v>
+            <v>9.4156776002830896E-3</v>
           </cell>
           <cell r="P9">
-            <v>0</v>
+            <v>5.2503028577553996E-4</v>
           </cell>
           <cell r="Q9">
-            <v>0</v>
+            <v>2.6173998840438001E-2</v>
           </cell>
           <cell r="R9">
-            <v>0</v>
+            <v>5.3375293492505999E-2</v>
           </cell>
           <cell r="S9">
-            <v>0</v>
+            <v>4.9824711348607401E-2</v>
           </cell>
           <cell r="T9">
-            <v>0</v>
+            <v>6.72030120947152E-2</v>
           </cell>
           <cell r="U9">
             <v>0</v>
           </cell>
           <cell r="V9">
-            <v>0</v>
+            <v>0.114026088991192</v>
           </cell>
           <cell r="W9">
-            <v>1</v>
+            <v>7.3919336675238506E-2</v>
           </cell>
           <cell r="X9">
-            <v>1</v>
+            <v>8.4178463038674697E-2</v>
           </cell>
           <cell r="Y9">
-            <v>1</v>
+            <v>8.1992757924729903E-2</v>
           </cell>
           <cell r="Z9">
-            <v>0</v>
-          </cell>
-          <cell r="AA9">
-            <v>0</v>
+            <v>0.117497858959921</v>
           </cell>
         </row>
         <row r="10">
@@ -3056,79 +3328,76 @@
             <v>0</v>
           </cell>
           <cell r="C10">
-            <v>0</v>
+            <v>2.6399249382519301E-2</v>
           </cell>
           <cell r="D10">
-            <v>0</v>
+            <v>2.9325182030622999E-2</v>
           </cell>
           <cell r="E10">
-            <v>0</v>
+            <v>3.2077536649405401E-2</v>
           </cell>
           <cell r="F10">
-            <v>0</v>
+            <v>5.3475611494803302E-2</v>
           </cell>
           <cell r="G10">
-            <v>0</v>
+            <v>2.26552142885269E-2</v>
           </cell>
           <cell r="H10">
             <v>0</v>
           </cell>
           <cell r="I10">
-            <v>0</v>
+            <v>1.6837295151900002E-2</v>
           </cell>
           <cell r="J10">
             <v>0</v>
           </cell>
           <cell r="K10">
-            <v>0</v>
+            <v>2.1980138328337201E-2</v>
           </cell>
           <cell r="L10">
-            <v>0</v>
+            <v>4.8912795031730599E-2</v>
           </cell>
           <cell r="M10">
-            <v>0</v>
+            <v>2.29840394209961E-2</v>
           </cell>
           <cell r="N10">
             <v>0</v>
           </cell>
           <cell r="O10">
-            <v>0</v>
+            <v>1.7996669655437399E-2</v>
           </cell>
           <cell r="P10">
             <v>0</v>
           </cell>
           <cell r="Q10">
-            <v>0</v>
+            <v>5.8182133366766503E-2</v>
           </cell>
           <cell r="R10">
-            <v>1</v>
+            <v>4.8732654078223699E-2</v>
           </cell>
           <cell r="S10">
-            <v>0</v>
+            <v>4.0948120763236298E-2</v>
           </cell>
           <cell r="T10">
-            <v>0</v>
+            <v>4.0444359755062602E-2</v>
           </cell>
           <cell r="U10">
             <v>0</v>
           </cell>
           <cell r="V10">
-            <v>0</v>
+            <v>0.10683580604703299</v>
           </cell>
           <cell r="W10">
-            <v>1</v>
+            <v>0.13134470695638201</v>
           </cell>
           <cell r="X10">
-            <v>2</v>
+            <v>8.6972550230132298E-2</v>
           </cell>
           <cell r="Y10">
-            <v>1</v>
+            <v>9.1207673099388403E-2</v>
           </cell>
           <cell r="Z10">
-            <v>0</v>
-          </cell>
-          <cell r="AA10">
-            <v>0</v>
+            <v>0.102688264269494</v>
           </cell>
         </row>
         <row r="11">
@@ -3139,79 +3408,76 @@
             <v>0</v>
           </cell>
           <cell r="C11">
-            <v>0</v>
+            <v>2.0746305758587501E-2</v>
           </cell>
           <cell r="D11">
             <v>0</v>
           </cell>
           <cell r="E11">
-            <v>0</v>
+            <v>1.07363366169312E-2</v>
           </cell>
           <cell r="F11">
-            <v>0</v>
+            <v>5.8270382346815502E-2</v>
           </cell>
           <cell r="G11">
-            <v>0</v>
+            <v>2.23269496028622E-2</v>
           </cell>
           <cell r="H11">
             <v>0</v>
           </cell>
           <cell r="I11">
-            <v>0</v>
+            <v>1.65015392995553E-2</v>
           </cell>
           <cell r="J11">
             <v>0</v>
           </cell>
           <cell r="K11">
-            <v>0</v>
+            <v>2.7072757162768801E-2</v>
           </cell>
           <cell r="L11">
-            <v>0</v>
+            <v>7.4696209917357898E-2</v>
           </cell>
           <cell r="M11">
-            <v>0</v>
+            <v>2.97417894118309E-2</v>
           </cell>
           <cell r="N11">
             <v>0</v>
           </cell>
           <cell r="O11">
-            <v>0</v>
+            <v>2.4352819758022198E-2</v>
           </cell>
           <cell r="P11">
             <v>0</v>
           </cell>
           <cell r="Q11">
-            <v>0</v>
+            <v>3.5278306496583103E-2</v>
           </cell>
           <cell r="R11">
-            <v>0</v>
+            <v>2.7824706416788601E-2</v>
           </cell>
           <cell r="S11">
-            <v>0</v>
+            <v>8.1851097509988494E-2</v>
           </cell>
           <cell r="T11">
-            <v>0</v>
+            <v>2.6434763104976701E-2</v>
           </cell>
           <cell r="U11">
             <v>0</v>
           </cell>
           <cell r="V11">
-            <v>0</v>
+            <v>0.116297350192845</v>
           </cell>
           <cell r="W11">
-            <v>1</v>
+            <v>0.11305983397167101</v>
           </cell>
           <cell r="X11">
-            <v>1</v>
+            <v>0.10099815449430501</v>
           </cell>
           <cell r="Y11">
-            <v>1</v>
+            <v>0.10282195443756</v>
           </cell>
           <cell r="Z11">
-            <v>0</v>
-          </cell>
-          <cell r="AA11">
-            <v>0</v>
+            <v>0.11098874350054801</v>
           </cell>
         </row>
         <row r="12">
@@ -3225,16 +3491,16 @@
             <v>0</v>
           </cell>
           <cell r="D12">
-            <v>0</v>
+            <v>2.5873495822975202E-2</v>
           </cell>
           <cell r="E12">
-            <v>0</v>
+            <v>2.23946073691112E-2</v>
           </cell>
           <cell r="F12">
             <v>0</v>
           </cell>
           <cell r="G12">
-            <v>0</v>
+            <v>2.1793172416070299E-2</v>
           </cell>
           <cell r="H12">
             <v>0</v>
@@ -3246,10 +3512,10 @@
             <v>0</v>
           </cell>
           <cell r="K12">
-            <v>0</v>
+            <v>6.1735529003316102E-2</v>
           </cell>
           <cell r="L12">
-            <v>0</v>
+            <v>9.1977093583278602E-2</v>
           </cell>
           <cell r="M12">
             <v>0</v>
@@ -3264,37 +3530,34 @@
             <v>0</v>
           </cell>
           <cell r="Q12">
-            <v>0</v>
+            <v>5.6615076912916902E-2</v>
           </cell>
           <cell r="R12">
-            <v>0</v>
+            <v>6.3910129108036506E-2</v>
           </cell>
           <cell r="S12">
-            <v>0</v>
+            <v>8.2483855599005604E-2</v>
           </cell>
           <cell r="T12">
-            <v>0</v>
+            <v>2.0326142844339201E-2</v>
           </cell>
           <cell r="U12">
             <v>0</v>
           </cell>
           <cell r="V12">
-            <v>0</v>
+            <v>7.8137013958007998E-2</v>
           </cell>
           <cell r="W12">
-            <v>0</v>
+            <v>0.15242956135343999</v>
           </cell>
           <cell r="X12">
-            <v>1</v>
+            <v>0.153957913704697</v>
           </cell>
           <cell r="Y12">
-            <v>1</v>
+            <v>8.0297462652068705E-2</v>
           </cell>
           <cell r="Z12">
-            <v>0</v>
-          </cell>
-          <cell r="AA12">
-            <v>0</v>
+            <v>8.8068945672734406E-2</v>
           </cell>
         </row>
         <row r="13">
@@ -3311,10 +3574,10 @@
             <v>0</v>
           </cell>
           <cell r="E13">
-            <v>0</v>
+            <v>3.3436155846010097E-2</v>
           </cell>
           <cell r="F13">
-            <v>0</v>
+            <v>7.7490198644765501E-2</v>
           </cell>
           <cell r="G13">
             <v>0</v>
@@ -3323,19 +3586,19 @@
             <v>0</v>
           </cell>
           <cell r="I13">
-            <v>0</v>
+            <v>7.0647097668496998E-3</v>
           </cell>
           <cell r="J13">
             <v>0</v>
           </cell>
           <cell r="K13">
-            <v>0</v>
+            <v>5.9413465485546303E-2</v>
           </cell>
           <cell r="L13">
-            <v>0</v>
+            <v>6.5028050616042596E-2</v>
           </cell>
           <cell r="M13">
-            <v>0</v>
+            <v>1.7749525548965101E-2</v>
           </cell>
           <cell r="N13">
             <v>0</v>
@@ -3347,37 +3610,34 @@
             <v>0</v>
           </cell>
           <cell r="Q13">
-            <v>0</v>
+            <v>4.46564022630868E-2</v>
           </cell>
           <cell r="R13">
-            <v>0</v>
+            <v>8.2639256584309498E-2</v>
           </cell>
           <cell r="S13">
-            <v>0</v>
+            <v>0.100997090826883</v>
           </cell>
           <cell r="T13">
-            <v>1</v>
+            <v>2.8303458286978899E-2</v>
           </cell>
           <cell r="U13">
             <v>0</v>
           </cell>
           <cell r="V13">
-            <v>0</v>
+            <v>0.100134452581668</v>
           </cell>
           <cell r="W13">
-            <v>1</v>
+            <v>8.5927693067363101E-2</v>
           </cell>
           <cell r="X13">
-            <v>0</v>
+            <v>5.2802384451094302E-2</v>
           </cell>
           <cell r="Y13">
-            <v>0</v>
+            <v>0.106982015479894</v>
           </cell>
           <cell r="Z13">
-            <v>0</v>
-          </cell>
-          <cell r="AA13">
-            <v>0</v>
+            <v>0.13737514055054101</v>
           </cell>
         </row>
         <row r="14">
@@ -3385,82 +3645,79 @@
             <v>13</v>
           </cell>
           <cell r="B14">
-            <v>0</v>
+            <v>1.00094875593052E-2</v>
           </cell>
           <cell r="C14">
             <v>0</v>
           </cell>
           <cell r="D14">
-            <v>0</v>
+            <v>1.9071504813614099E-2</v>
           </cell>
           <cell r="E14">
-            <v>0</v>
+            <v>2.78413993776786E-2</v>
           </cell>
           <cell r="F14">
-            <v>0</v>
+            <v>8.9453610220408597E-2</v>
           </cell>
           <cell r="G14">
-            <v>1</v>
+            <v>1.9074218911958599E-2</v>
           </cell>
           <cell r="H14">
-            <v>0</v>
+            <v>2.29636527830656E-3</v>
           </cell>
           <cell r="I14">
-            <v>0</v>
+            <v>5.9786943994187798E-3</v>
           </cell>
           <cell r="J14">
-            <v>0</v>
+            <v>3.3853162922716701E-2</v>
           </cell>
           <cell r="K14">
-            <v>0</v>
+            <v>7.6410903490126802E-2</v>
           </cell>
           <cell r="L14">
-            <v>1</v>
+            <v>3.3713815399815397E-2</v>
           </cell>
           <cell r="M14">
-            <v>0</v>
+            <v>2.18004949872567E-2</v>
           </cell>
           <cell r="N14">
-            <v>0</v>
+            <v>1.53299297825856E-2</v>
           </cell>
           <cell r="O14">
-            <v>0</v>
+            <v>1.50100352000699E-2</v>
           </cell>
           <cell r="P14">
-            <v>0</v>
+            <v>2.29636527830656E-3</v>
           </cell>
           <cell r="Q14">
-            <v>0</v>
+            <v>2.6261187040194599E-2</v>
           </cell>
           <cell r="R14">
-            <v>0</v>
+            <v>2.3235574486946999E-2</v>
           </cell>
           <cell r="S14">
-            <v>0</v>
+            <v>5.2216252356578299E-2</v>
           </cell>
           <cell r="T14">
-            <v>0</v>
+            <v>2.0518440637651601E-2</v>
           </cell>
           <cell r="U14">
             <v>0</v>
           </cell>
           <cell r="V14">
-            <v>0</v>
+            <v>0.124168177961142</v>
           </cell>
           <cell r="W14">
-            <v>1</v>
+            <v>9.3413586840594101E-2</v>
           </cell>
           <cell r="X14">
-            <v>1</v>
+            <v>7.3968536386398706E-2</v>
           </cell>
           <cell r="Y14">
-            <v>1</v>
+            <v>8.5111802817326901E-2</v>
           </cell>
           <cell r="Z14">
-            <v>0</v>
-          </cell>
-          <cell r="AA14">
-            <v>0</v>
+            <v>0.128966453851596</v>
           </cell>
         </row>
         <row r="15">
@@ -3471,37 +3728,37 @@
             <v>0</v>
           </cell>
           <cell r="C15">
-            <v>0</v>
+            <v>1.6540157096204398E-2</v>
           </cell>
           <cell r="D15">
             <v>0</v>
           </cell>
           <cell r="E15">
-            <v>0</v>
+            <v>2.3485385716802198E-2</v>
           </cell>
           <cell r="F15">
-            <v>0</v>
+            <v>7.6254669298487301E-2</v>
           </cell>
           <cell r="G15">
-            <v>0</v>
+            <v>1.72628538391006E-2</v>
           </cell>
           <cell r="H15">
             <v>0</v>
           </cell>
           <cell r="I15">
-            <v>0</v>
+            <v>3.3537645725022899E-3</v>
           </cell>
           <cell r="J15">
             <v>0</v>
           </cell>
           <cell r="K15">
-            <v>0</v>
+            <v>4.1970613343691898E-2</v>
           </cell>
           <cell r="L15">
-            <v>0</v>
+            <v>6.3377116711007098E-2</v>
           </cell>
           <cell r="M15">
-            <v>0</v>
+            <v>1.05299173867285E-2</v>
           </cell>
           <cell r="N15">
             <v>0</v>
@@ -3513,37 +3770,34 @@
             <v>0</v>
           </cell>
           <cell r="Q15">
-            <v>0</v>
+            <v>8.3298704114402794E-2</v>
           </cell>
           <cell r="R15">
-            <v>0</v>
+            <v>3.58756826096579E-2</v>
           </cell>
           <cell r="S15">
-            <v>0</v>
+            <v>9.4074225472350004E-2</v>
           </cell>
           <cell r="T15">
-            <v>1</v>
+            <v>1.34523223408147E-2</v>
           </cell>
           <cell r="U15">
             <v>0</v>
           </cell>
           <cell r="V15">
-            <v>0</v>
+            <v>0.12300298564091899</v>
           </cell>
           <cell r="W15">
-            <v>1</v>
+            <v>0.13955048262591799</v>
           </cell>
           <cell r="X15">
-            <v>1</v>
+            <v>7.1679095545026203E-2</v>
           </cell>
           <cell r="Y15">
-            <v>0</v>
+            <v>8.3471473804501498E-2</v>
           </cell>
           <cell r="Z15">
-            <v>0</v>
-          </cell>
-          <cell r="AA15">
-            <v>0</v>
+            <v>0.10282054988188399</v>
           </cell>
         </row>
         <row r="16">
@@ -3551,25 +3805,25 @@
             <v>15</v>
           </cell>
           <cell r="B16">
-            <v>0</v>
+            <v>2.07625287516554E-2</v>
           </cell>
           <cell r="C16">
             <v>0</v>
           </cell>
           <cell r="D16">
-            <v>0</v>
+            <v>5.2794312399804803E-2</v>
           </cell>
           <cell r="E16">
-            <v>0</v>
+            <v>2.5928765595594899E-3</v>
           </cell>
           <cell r="F16">
-            <v>0</v>
+            <v>2.3508747473339298E-2</v>
           </cell>
           <cell r="G16">
-            <v>0</v>
+            <v>2.98933574963407E-2</v>
           </cell>
           <cell r="H16">
-            <v>0</v>
+            <v>4.9980251388211201E-3</v>
           </cell>
           <cell r="I16">
             <v>0</v>
@@ -3578,55 +3832,52 @@
             <v>0</v>
           </cell>
           <cell r="K16">
-            <v>0</v>
+            <v>4.73004809367812E-2</v>
           </cell>
           <cell r="L16">
-            <v>0</v>
+            <v>3.8865268000278799E-2</v>
           </cell>
           <cell r="M16">
-            <v>0</v>
+            <v>5.07144350735345E-2</v>
           </cell>
           <cell r="N16">
-            <v>0</v>
+            <v>3.9520921911665598E-2</v>
           </cell>
           <cell r="O16">
-            <v>0</v>
+            <v>3.4033595873701798E-2</v>
           </cell>
           <cell r="P16">
-            <v>0</v>
+            <v>9.9258846216398293E-3</v>
           </cell>
           <cell r="Q16">
-            <v>0</v>
+            <v>1.5695267303268898E-2</v>
           </cell>
           <cell r="R16">
-            <v>0</v>
+            <v>3.0262772705095101E-2</v>
           </cell>
           <cell r="S16">
-            <v>0</v>
+            <v>4.2696034014079502E-2</v>
           </cell>
           <cell r="T16">
-            <v>0</v>
+            <v>2.28758625496619E-2</v>
           </cell>
           <cell r="U16">
             <v>0</v>
           </cell>
           <cell r="V16">
-            <v>0</v>
+            <v>0.14930229316233301</v>
           </cell>
           <cell r="W16">
-            <v>1</v>
+            <v>7.8909876629260398E-2</v>
           </cell>
           <cell r="X16">
-            <v>1</v>
+            <v>5.2674426709416598E-2</v>
           </cell>
           <cell r="Y16">
-            <v>0</v>
+            <v>9.8612950442601197E-2</v>
           </cell>
           <cell r="Z16">
-            <v>0</v>
-          </cell>
-          <cell r="AA16">
-            <v>0</v>
+            <v>0.154060082247159</v>
           </cell>
         </row>
         <row r="17">
@@ -3637,79 +3888,76 @@
             <v>0</v>
           </cell>
           <cell r="C17">
-            <v>0</v>
+            <v>1.4190465273089099E-2</v>
           </cell>
           <cell r="D17">
-            <v>0</v>
+            <v>1.9918170656068698E-2</v>
           </cell>
           <cell r="E17">
-            <v>0</v>
+            <v>2.5116735613286301E-2</v>
           </cell>
           <cell r="F17">
-            <v>0</v>
+            <v>2.9529871371803001E-2</v>
           </cell>
           <cell r="G17">
-            <v>0</v>
+            <v>1.20399060797537E-2</v>
           </cell>
           <cell r="H17">
             <v>0</v>
           </cell>
           <cell r="I17">
-            <v>0</v>
+            <v>1.29778881194898E-2</v>
           </cell>
           <cell r="J17">
-            <v>0</v>
+            <v>1.7507399902453299E-2</v>
           </cell>
           <cell r="K17">
-            <v>0</v>
+            <v>3.8783290843734802E-2</v>
           </cell>
           <cell r="L17">
-            <v>0</v>
+            <v>4.94676559645763E-2</v>
           </cell>
           <cell r="M17">
-            <v>0</v>
+            <v>2.2804906273713701E-2</v>
           </cell>
           <cell r="N17">
             <v>0</v>
           </cell>
           <cell r="O17">
-            <v>0</v>
+            <v>1.3598124384612701E-2</v>
           </cell>
           <cell r="P17">
             <v>0</v>
           </cell>
           <cell r="Q17">
-            <v>0</v>
+            <v>4.3662366565298899E-2</v>
           </cell>
           <cell r="R17">
-            <v>0</v>
+            <v>8.3377973200388603E-2</v>
           </cell>
           <cell r="S17">
-            <v>0</v>
+            <v>7.1588253779932498E-2</v>
           </cell>
           <cell r="T17">
-            <v>0</v>
+            <v>2.9990145086469099E-2</v>
           </cell>
           <cell r="U17">
             <v>0</v>
           </cell>
           <cell r="V17">
-            <v>0</v>
+            <v>9.3306112094955804E-2</v>
           </cell>
           <cell r="W17">
-            <v>0</v>
+            <v>9.3854866457422206E-2</v>
           </cell>
           <cell r="X17">
-            <v>1</v>
+            <v>0.145324887426899</v>
           </cell>
           <cell r="Y17">
-            <v>1</v>
+            <v>8.7316887555916003E-2</v>
           </cell>
           <cell r="Z17">
-            <v>0</v>
-          </cell>
-          <cell r="AA17">
-            <v>0</v>
+            <v>9.5644093350134393E-2</v>
           </cell>
         </row>
       </sheetData>
@@ -3850,7 +4098,7 @@
             <v>0</v>
           </cell>
           <cell r="M2">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="N2">
             <v>0</v>
@@ -3883,7 +4131,7 @@
             <v>1</v>
           </cell>
           <cell r="X2">
-            <v>0</v>
+            <v>1</v>
           </cell>
           <cell r="Y2">
             <v>0</v>
@@ -3930,13 +4178,13 @@
             <v>0</v>
           </cell>
           <cell r="L3">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="M3">
             <v>0</v>
           </cell>
           <cell r="N3">
-            <v>0</v>
+            <v>1</v>
           </cell>
           <cell r="O3">
             <v>0</v>
@@ -3951,7 +4199,7 @@
             <v>0</v>
           </cell>
           <cell r="S3">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="T3">
             <v>0</v>
@@ -3966,7 +4214,7 @@
             <v>1</v>
           </cell>
           <cell r="X3">
-            <v>0</v>
+            <v>1</v>
           </cell>
           <cell r="Y3">
             <v>0</v>
@@ -4001,7 +4249,7 @@
             <v>0</v>
           </cell>
           <cell r="H4">
-            <v>0</v>
+            <v>1</v>
           </cell>
           <cell r="I4">
             <v>0</v>
@@ -4037,7 +4285,7 @@
             <v>0</v>
           </cell>
           <cell r="T4">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="U4">
             <v>0</v>
@@ -4099,7 +4347,7 @@
             <v>1</v>
           </cell>
           <cell r="M5">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="N5">
             <v>0</v>
@@ -4129,7 +4377,7 @@
             <v>0</v>
           </cell>
           <cell r="W5">
-            <v>0</v>
+            <v>1</v>
           </cell>
           <cell r="X5">
             <v>1</v>
@@ -4182,7 +4430,7 @@
             <v>0</v>
           </cell>
           <cell r="M6">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="N6">
             <v>0</v>
@@ -4218,7 +4466,7 @@
             <v>1</v>
           </cell>
           <cell r="Y6">
-            <v>0</v>
+            <v>1</v>
           </cell>
           <cell r="Z6">
             <v>0</v>
@@ -4286,7 +4534,7 @@
             <v>0</v>
           </cell>
           <cell r="T7">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="U7">
             <v>0</v>
@@ -4298,7 +4546,7 @@
             <v>1</v>
           </cell>
           <cell r="X7">
-            <v>0</v>
+            <v>1</v>
           </cell>
           <cell r="Y7">
             <v>1</v>
@@ -4348,7 +4596,7 @@
             <v>0</v>
           </cell>
           <cell r="M8">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="N8">
             <v>0</v>
@@ -4381,7 +4629,7 @@
             <v>1</v>
           </cell>
           <cell r="X8">
-            <v>1</v>
+            <v>2</v>
           </cell>
           <cell r="Y8">
             <v>1</v>
@@ -4431,7 +4679,7 @@
             <v>0</v>
           </cell>
           <cell r="M9">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="N9">
             <v>0</v>
@@ -4464,7 +4712,7 @@
             <v>1</v>
           </cell>
           <cell r="X9">
-            <v>0</v>
+            <v>1</v>
           </cell>
           <cell r="Y9">
             <v>1</v>
@@ -4514,7 +4762,7 @@
             <v>0</v>
           </cell>
           <cell r="M10">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="N10">
             <v>0</v>
@@ -4547,7 +4795,7 @@
             <v>1</v>
           </cell>
           <cell r="X10">
-            <v>1</v>
+            <v>2</v>
           </cell>
           <cell r="Y10">
             <v>1</v>
@@ -4618,7 +4866,7 @@
             <v>0</v>
           </cell>
           <cell r="T11">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="U11">
             <v>0</v>
@@ -4633,7 +4881,7 @@
             <v>1</v>
           </cell>
           <cell r="Y11">
-            <v>0</v>
+            <v>1</v>
           </cell>
           <cell r="Z11">
             <v>0</v>
@@ -4680,7 +4928,7 @@
             <v>0</v>
           </cell>
           <cell r="M12">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="N12">
             <v>0</v>
@@ -4713,7 +4961,7 @@
             <v>0</v>
           </cell>
           <cell r="X12">
-            <v>0</v>
+            <v>1</v>
           </cell>
           <cell r="Y12">
             <v>1</v>
@@ -4843,7 +5091,7 @@
             <v>0</v>
           </cell>
           <cell r="L14">
-            <v>0</v>
+            <v>1</v>
           </cell>
           <cell r="M14">
             <v>0</v>
@@ -4867,7 +5115,7 @@
             <v>0</v>
           </cell>
           <cell r="T14">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="U14">
             <v>0</v>
@@ -4988,7 +5236,7 @@
             <v>0</v>
           </cell>
           <cell r="E16">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="F16">
             <v>0</v>
@@ -5045,7 +5293,7 @@
             <v>1</v>
           </cell>
           <cell r="X16">
-            <v>0</v>
+            <v>1</v>
           </cell>
           <cell r="Y16">
             <v>0</v>
@@ -5113,7 +5361,7 @@
             <v>0</v>
           </cell>
           <cell r="S17">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="T17">
             <v>0</v>
@@ -5128,7 +5376,7 @@
             <v>0</v>
           </cell>
           <cell r="X17">
-            <v>0</v>
+            <v>1</v>
           </cell>
           <cell r="Y17">
             <v>1</v>
@@ -6789,7 +7037,7 @@
             <v>1</v>
           </cell>
           <cell r="M3">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="N3">
             <v>0</v>
@@ -6807,7 +7055,7 @@
             <v>0</v>
           </cell>
           <cell r="S3">
-            <v>0</v>
+            <v>1</v>
           </cell>
           <cell r="T3">
             <v>0</v>
@@ -6869,7 +7117,7 @@
             <v>0</v>
           </cell>
           <cell r="L4">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="M4">
             <v>0</v>
@@ -6905,7 +7153,7 @@
             <v>0</v>
           </cell>
           <cell r="X4">
-            <v>0</v>
+            <v>1</v>
           </cell>
           <cell r="Y4">
             <v>0</v>
@@ -7068,13 +7316,13 @@
             <v>0</v>
           </cell>
           <cell r="W6">
-            <v>1</v>
+            <v>2</v>
           </cell>
           <cell r="X6">
             <v>1</v>
           </cell>
           <cell r="Y6">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="Z6">
             <v>0</v>
@@ -7186,7 +7434,7 @@
             <v>0</v>
           </cell>
           <cell r="G8">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="H8">
             <v>0</v>
@@ -7222,7 +7470,7 @@
             <v>0</v>
           </cell>
           <cell r="S8">
-            <v>0</v>
+            <v>1</v>
           </cell>
           <cell r="T8">
             <v>0</v>
@@ -7352,7 +7600,7 @@
             <v>0</v>
           </cell>
           <cell r="G10">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="H10">
             <v>0</v>
@@ -7370,7 +7618,7 @@
             <v>0</v>
           </cell>
           <cell r="M10">
-            <v>0</v>
+            <v>1</v>
           </cell>
           <cell r="N10">
             <v>0</v>
@@ -7601,7 +7849,7 @@
             <v>0</v>
           </cell>
           <cell r="G13">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="H13">
             <v>0</v>
@@ -7649,7 +7897,7 @@
             <v>0</v>
           </cell>
           <cell r="W13">
-            <v>0</v>
+            <v>1</v>
           </cell>
           <cell r="X13">
             <v>0</v>
@@ -7844,7 +8092,7 @@
             <v>0</v>
           </cell>
           <cell r="E16">
-            <v>0</v>
+            <v>1</v>
           </cell>
           <cell r="F16">
             <v>0</v>
@@ -7889,7 +8137,7 @@
             <v>0</v>
           </cell>
           <cell r="T16">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="U16">
             <v>0</v>
@@ -7969,10 +8217,10 @@
             <v>0</v>
           </cell>
           <cell r="S17">
-            <v>0</v>
+            <v>1</v>
           </cell>
           <cell r="T17">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="U17">
             <v>0</v>
@@ -8018,78 +8266,81 @@
             <v>Circunscripcion</v>
           </cell>
           <cell r="B1" t="str">
+            <v>Unnamed: 0</v>
+          </cell>
+          <cell r="C1" t="str">
             <v>AH</v>
           </cell>
-          <cell r="C1" t="str">
+          <cell r="D1" t="str">
             <v>AMA</v>
           </cell>
-          <cell r="D1" t="str">
+          <cell r="E1" t="str">
             <v>DEM</v>
           </cell>
-          <cell r="E1" t="str">
+          <cell r="F1" t="str">
             <v>EVO</v>
           </cell>
-          <cell r="F1" t="str">
+          <cell r="G1" t="str">
             <v>FA</v>
           </cell>
-          <cell r="G1" t="str">
+          <cell r="H1" t="str">
             <v>FREVS</v>
           </cell>
-          <cell r="H1" t="str">
+          <cell r="I1" t="str">
             <v>IGU</v>
           </cell>
-          <cell r="I1" t="str">
+          <cell r="J1" t="str">
             <v>IND</v>
           </cell>
-          <cell r="J1" t="str">
+          <cell r="K1" t="str">
             <v>PAVP</v>
           </cell>
-          <cell r="K1" t="str">
+          <cell r="L1" t="str">
             <v>PCCH</v>
           </cell>
-          <cell r="L1" t="str">
+          <cell r="M1" t="str">
             <v>PDC</v>
           </cell>
-          <cell r="M1" t="str">
+          <cell r="N1" t="str">
             <v>PDG</v>
           </cell>
-          <cell r="N1" t="str">
+          <cell r="O1" t="str">
             <v>PH</v>
           </cell>
-          <cell r="O1" t="str">
+          <cell r="P1" t="str">
             <v>PL</v>
           </cell>
-          <cell r="P1" t="str">
+          <cell r="Q1" t="str">
             <v>POP</v>
           </cell>
-          <cell r="Q1" t="str">
+          <cell r="R1" t="str">
             <v>PPD</v>
           </cell>
-          <cell r="R1" t="str">
+          <cell r="S1" t="str">
             <v>PR</v>
           </cell>
-          <cell r="S1" t="str">
+          <cell r="T1" t="str">
             <v>PS</v>
           </cell>
-          <cell r="T1" t="str">
+          <cell r="U1" t="str">
             <v>PSC</v>
           </cell>
-          <cell r="U1" t="str">
+          <cell r="V1" t="str">
             <v>PTR</v>
           </cell>
-          <cell r="V1" t="str">
+          <cell r="W1" t="str">
             <v>REP</v>
           </cell>
-          <cell r="W1" t="str">
+          <cell r="X1" t="str">
             <v>RN</v>
           </cell>
-          <cell r="X1" t="str">
+          <cell r="Y1" t="str">
             <v>UDI</v>
           </cell>
-          <cell r="Y1" t="str">
+          <cell r="Z1" t="str">
             <v>Votos Blancos</v>
           </cell>
-          <cell r="Z1" t="str">
+          <cell r="AA1" t="str">
             <v>Votos Nulos</v>
           </cell>
         </row>
@@ -8128,10 +8379,10 @@
             <v>0</v>
           </cell>
           <cell r="L2">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="M2">
-            <v>0</v>
+            <v>1</v>
           </cell>
           <cell r="N2">
             <v>0</v>
@@ -8170,6 +8421,9 @@
             <v>0</v>
           </cell>
           <cell r="Z2">
+            <v>0</v>
+          </cell>
+          <cell r="AA2">
             <v>0</v>
           </cell>
         </row>
@@ -8205,13 +8459,13 @@
             <v>0</v>
           </cell>
           <cell r="K3">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="L3">
-            <v>0</v>
+            <v>1</v>
           </cell>
           <cell r="M3">
-            <v>0</v>
+            <v>1</v>
           </cell>
           <cell r="N3">
             <v>0</v>
@@ -8226,7 +8480,7 @@
             <v>0</v>
           </cell>
           <cell r="R3">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="S3">
             <v>0</v>
@@ -8250,6 +8504,9 @@
             <v>0</v>
           </cell>
           <cell r="Z3">
+            <v>0</v>
+          </cell>
+          <cell r="AA3">
             <v>0</v>
           </cell>
         </row>
@@ -8273,7 +8530,7 @@
             <v>0</v>
           </cell>
           <cell r="G4">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="H4">
             <v>0</v>
@@ -8288,7 +8545,7 @@
             <v>0</v>
           </cell>
           <cell r="L4">
-            <v>0</v>
+            <v>1</v>
           </cell>
           <cell r="M4">
             <v>0</v>
@@ -8312,7 +8569,7 @@
             <v>0</v>
           </cell>
           <cell r="T4">
-            <v>0</v>
+            <v>1</v>
           </cell>
           <cell r="U4">
             <v>0</v>
@@ -8321,7 +8578,7 @@
             <v>0</v>
           </cell>
           <cell r="W4">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="X4">
             <v>0</v>
@@ -8330,6 +8587,9 @@
             <v>0</v>
           </cell>
           <cell r="Z4">
+            <v>0</v>
+          </cell>
+          <cell r="AA4">
             <v>0</v>
           </cell>
         </row>
@@ -8365,13 +8625,13 @@
             <v>0</v>
           </cell>
           <cell r="K5">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="L5">
             <v>1</v>
           </cell>
           <cell r="M5">
-            <v>0</v>
+            <v>1</v>
           </cell>
           <cell r="N5">
             <v>0</v>
@@ -8401,15 +8661,18 @@
             <v>0</v>
           </cell>
           <cell r="W5">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="X5">
-            <v>0</v>
+            <v>1</v>
           </cell>
           <cell r="Y5">
             <v>0</v>
           </cell>
           <cell r="Z5">
+            <v>0</v>
+          </cell>
+          <cell r="AA5">
             <v>0</v>
           </cell>
         </row>
@@ -8430,10 +8693,10 @@
             <v>0</v>
           </cell>
           <cell r="F6">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="G6">
-            <v>0</v>
+            <v>1</v>
           </cell>
           <cell r="H6">
             <v>0</v>
@@ -8448,10 +8711,10 @@
             <v>0</v>
           </cell>
           <cell r="L6">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="M6">
-            <v>0</v>
+            <v>1</v>
           </cell>
           <cell r="N6">
             <v>0</v>
@@ -8478,7 +8741,7 @@
             <v>0</v>
           </cell>
           <cell r="V6">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="W6">
             <v>1</v>
@@ -8487,9 +8750,12 @@
             <v>1</v>
           </cell>
           <cell r="Y6">
-            <v>0</v>
+            <v>1</v>
           </cell>
           <cell r="Z6">
+            <v>0</v>
+          </cell>
+          <cell r="AA6">
             <v>0</v>
           </cell>
         </row>
@@ -8510,7 +8776,7 @@
             <v>0</v>
           </cell>
           <cell r="F7">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="G7">
             <v>0</v>
@@ -8549,10 +8815,10 @@
             <v>0</v>
           </cell>
           <cell r="S7">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="T7">
-            <v>0</v>
+            <v>1</v>
           </cell>
           <cell r="U7">
             <v>0</v>
@@ -8561,15 +8827,18 @@
             <v>0</v>
           </cell>
           <cell r="W7">
-            <v>0</v>
+            <v>1</v>
           </cell>
           <cell r="X7">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="Y7">
-            <v>0</v>
+            <v>1</v>
           </cell>
           <cell r="Z7">
+            <v>0</v>
+          </cell>
+          <cell r="AA7">
             <v>0</v>
           </cell>
         </row>
@@ -8593,7 +8862,7 @@
             <v>0</v>
           </cell>
           <cell r="G8">
-            <v>0</v>
+            <v>1</v>
           </cell>
           <cell r="H8">
             <v>0</v>
@@ -8608,10 +8877,10 @@
             <v>0</v>
           </cell>
           <cell r="L8">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="M8">
-            <v>0</v>
+            <v>1</v>
           </cell>
           <cell r="N8">
             <v>0</v>
@@ -8626,7 +8895,7 @@
             <v>0</v>
           </cell>
           <cell r="R8">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="S8">
             <v>0</v>
@@ -8638,7 +8907,7 @@
             <v>0</v>
           </cell>
           <cell r="V8">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="W8">
             <v>1</v>
@@ -8647,9 +8916,12 @@
             <v>1</v>
           </cell>
           <cell r="Y8">
-            <v>0</v>
+            <v>1</v>
           </cell>
           <cell r="Z8">
+            <v>0</v>
+          </cell>
+          <cell r="AA8">
             <v>0</v>
           </cell>
         </row>
@@ -8688,10 +8960,10 @@
             <v>0</v>
           </cell>
           <cell r="L9">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="M9">
-            <v>0</v>
+            <v>1</v>
           </cell>
           <cell r="N9">
             <v>0</v>
@@ -8718,18 +8990,21 @@
             <v>0</v>
           </cell>
           <cell r="V9">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="W9">
-            <v>0</v>
+            <v>1</v>
           </cell>
           <cell r="X9">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="Y9">
-            <v>0</v>
+            <v>1</v>
           </cell>
           <cell r="Z9">
+            <v>0</v>
+          </cell>
+          <cell r="AA9">
             <v>0</v>
           </cell>
         </row>
@@ -8750,10 +9025,10 @@
             <v>0</v>
           </cell>
           <cell r="F10">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="G10">
-            <v>0</v>
+            <v>1</v>
           </cell>
           <cell r="H10">
             <v>0</v>
@@ -8783,10 +9058,10 @@
             <v>0</v>
           </cell>
           <cell r="Q10">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="R10">
-            <v>0</v>
+            <v>1</v>
           </cell>
           <cell r="S10">
             <v>0</v>
@@ -8798,7 +9073,7 @@
             <v>0</v>
           </cell>
           <cell r="V10">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="W10">
             <v>1</v>
@@ -8807,9 +9082,12 @@
             <v>1</v>
           </cell>
           <cell r="Y10">
-            <v>0</v>
+            <v>1</v>
           </cell>
           <cell r="Z10">
+            <v>0</v>
+          </cell>
+          <cell r="AA10">
             <v>0</v>
           </cell>
         </row>
@@ -8869,27 +9147,30 @@
             <v>0</v>
           </cell>
           <cell r="S11">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="T11">
-            <v>0</v>
+            <v>1</v>
           </cell>
           <cell r="U11">
             <v>0</v>
           </cell>
           <cell r="V11">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="W11">
             <v>1</v>
           </cell>
           <cell r="X11">
-            <v>0</v>
+            <v>1</v>
           </cell>
           <cell r="Y11">
             <v>0</v>
           </cell>
           <cell r="Z11">
+            <v>0</v>
+          </cell>
+          <cell r="AA11">
             <v>0</v>
           </cell>
         </row>
@@ -8928,10 +9209,10 @@
             <v>0</v>
           </cell>
           <cell r="L12">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="M12">
-            <v>0</v>
+            <v>1</v>
           </cell>
           <cell r="N12">
             <v>0</v>
@@ -8964,12 +9245,15 @@
             <v>0</v>
           </cell>
           <cell r="X12">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="Y12">
-            <v>0</v>
+            <v>1</v>
           </cell>
           <cell r="Z12">
+            <v>0</v>
+          </cell>
+          <cell r="AA12">
             <v>0</v>
           </cell>
         </row>
@@ -8993,7 +9277,7 @@
             <v>0</v>
           </cell>
           <cell r="G13">
-            <v>0</v>
+            <v>1</v>
           </cell>
           <cell r="H13">
             <v>0</v>
@@ -9029,10 +9313,10 @@
             <v>0</v>
           </cell>
           <cell r="S13">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="T13">
-            <v>0</v>
+            <v>1</v>
           </cell>
           <cell r="U13">
             <v>0</v>
@@ -9041,7 +9325,7 @@
             <v>0</v>
           </cell>
           <cell r="W13">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="X13">
             <v>0</v>
@@ -9050,6 +9334,9 @@
             <v>0</v>
           </cell>
           <cell r="Z13">
+            <v>0</v>
+          </cell>
+          <cell r="AA13">
             <v>0</v>
           </cell>
         </row>
@@ -9070,10 +9357,10 @@
             <v>0</v>
           </cell>
           <cell r="F14">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="G14">
-            <v>0</v>
+            <v>1</v>
           </cell>
           <cell r="H14">
             <v>0</v>
@@ -9109,16 +9396,16 @@
             <v>0</v>
           </cell>
           <cell r="S14">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="T14">
-            <v>0</v>
+            <v>1</v>
           </cell>
           <cell r="U14">
             <v>0</v>
           </cell>
           <cell r="V14">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="W14">
             <v>1</v>
@@ -9127,9 +9414,12 @@
             <v>1</v>
           </cell>
           <cell r="Y14">
-            <v>0</v>
+            <v>1</v>
           </cell>
           <cell r="Z14">
+            <v>0</v>
+          </cell>
+          <cell r="AA14">
             <v>0</v>
           </cell>
         </row>
@@ -9183,16 +9473,16 @@
             <v>0</v>
           </cell>
           <cell r="Q15">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="R15">
             <v>0</v>
           </cell>
           <cell r="S15">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="T15">
-            <v>0</v>
+            <v>1</v>
           </cell>
           <cell r="U15">
             <v>0</v>
@@ -9204,12 +9494,15 @@
             <v>1</v>
           </cell>
           <cell r="X15">
-            <v>0</v>
+            <v>1</v>
           </cell>
           <cell r="Y15">
             <v>0</v>
           </cell>
           <cell r="Z15">
+            <v>0</v>
+          </cell>
+          <cell r="AA15">
             <v>0</v>
           </cell>
         </row>
@@ -9272,13 +9565,13 @@
             <v>0</v>
           </cell>
           <cell r="T16">
-            <v>0</v>
+            <v>1</v>
           </cell>
           <cell r="U16">
             <v>0</v>
           </cell>
           <cell r="V16">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="W16">
             <v>1</v>
@@ -9290,6 +9583,9 @@
             <v>0</v>
           </cell>
           <cell r="Z16">
+            <v>0</v>
+          </cell>
+          <cell r="AA16">
             <v>0</v>
           </cell>
         </row>
@@ -9346,13 +9642,13 @@
             <v>0</v>
           </cell>
           <cell r="R17">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="S17">
             <v>0</v>
           </cell>
           <cell r="T17">
-            <v>0</v>
+            <v>1</v>
           </cell>
           <cell r="U17">
             <v>0</v>
@@ -9364,12 +9660,15 @@
             <v>0</v>
           </cell>
           <cell r="X17">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="Y17">
-            <v>0</v>
+            <v>1</v>
           </cell>
           <cell r="Z17">
+            <v>0</v>
+          </cell>
+          <cell r="AA17">
             <v>0</v>
           </cell>
         </row>
@@ -9535,10 +9834,10 @@
             <v>0</v>
           </cell>
           <cell r="V2">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="W2">
-            <v>0</v>
+            <v>1</v>
           </cell>
           <cell r="X2">
             <v>0</v>
@@ -9615,10 +9914,10 @@
             <v>0</v>
           </cell>
           <cell r="V3">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="W3">
-            <v>0</v>
+            <v>1</v>
           </cell>
           <cell r="X3">
             <v>0</v>
@@ -9686,7 +9985,7 @@
             <v>0</v>
           </cell>
           <cell r="S4">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="T4">
             <v>0</v>
@@ -9698,7 +9997,7 @@
             <v>0</v>
           </cell>
           <cell r="W4">
-            <v>0</v>
+            <v>1</v>
           </cell>
           <cell r="X4">
             <v>0</v>
@@ -10462,7 +10761,7 @@
             <v>0</v>
           </cell>
           <cell r="K14">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="L14">
             <v>0</v>
@@ -10501,7 +10800,7 @@
             <v>1</v>
           </cell>
           <cell r="X14">
-            <v>0</v>
+            <v>1</v>
           </cell>
           <cell r="Y14">
             <v>0</v>
@@ -10622,7 +10921,7 @@
             <v>0</v>
           </cell>
           <cell r="K16">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="L16">
             <v>0</v>
@@ -10658,7 +10957,7 @@
             <v>1</v>
           </cell>
           <cell r="W16">
-            <v>0</v>
+            <v>1</v>
           </cell>
           <cell r="X16">
             <v>0</v>
@@ -10882,7 +11181,7 @@
             <v>0</v>
           </cell>
           <cell r="L2">
-            <v>0</v>
+            <v>1</v>
           </cell>
           <cell r="M2">
             <v>0</v>
@@ -10915,7 +11214,7 @@
             <v>1</v>
           </cell>
           <cell r="W2">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="X2">
             <v>0</v>
@@ -10947,7 +11246,7 @@
             <v>0</v>
           </cell>
           <cell r="G3">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="H3">
             <v>0</v>
@@ -10980,7 +11279,7 @@
             <v>0</v>
           </cell>
           <cell r="R3">
-            <v>0</v>
+            <v>1</v>
           </cell>
           <cell r="S3">
             <v>0</v>
@@ -10992,10 +11291,10 @@
             <v>0</v>
           </cell>
           <cell r="V3">
-            <v>0</v>
+            <v>1</v>
           </cell>
           <cell r="W3">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="X3">
             <v>0</v>
@@ -11027,7 +11326,7 @@
             <v>0</v>
           </cell>
           <cell r="G4">
-            <v>0</v>
+            <v>1</v>
           </cell>
           <cell r="H4">
             <v>0</v>
@@ -11075,7 +11374,7 @@
             <v>0</v>
           </cell>
           <cell r="W4">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="X4">
             <v>0</v>
@@ -11199,7 +11498,7 @@
             <v>0</v>
           </cell>
           <cell r="K6">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="L6">
             <v>1</v>
@@ -11238,7 +11537,7 @@
             <v>1</v>
           </cell>
           <cell r="X6">
-            <v>0</v>
+            <v>1</v>
           </cell>
           <cell r="Y6">
             <v>0</v>
@@ -11264,7 +11563,7 @@
             <v>0</v>
           </cell>
           <cell r="F7">
-            <v>0</v>
+            <v>1</v>
           </cell>
           <cell r="G7">
             <v>0</v>
@@ -11300,7 +11599,7 @@
             <v>0</v>
           </cell>
           <cell r="R7">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="S7">
             <v>1</v>
@@ -11362,7 +11661,7 @@
             <v>0</v>
           </cell>
           <cell r="L8">
-            <v>0</v>
+            <v>1</v>
           </cell>
           <cell r="M8">
             <v>0</v>
@@ -11383,7 +11682,7 @@
             <v>1</v>
           </cell>
           <cell r="S8">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="T8">
             <v>0</v>
@@ -11442,7 +11741,7 @@
             <v>0</v>
           </cell>
           <cell r="L9">
-            <v>0</v>
+            <v>1</v>
           </cell>
           <cell r="M9">
             <v>0</v>
@@ -11463,7 +11762,7 @@
             <v>0</v>
           </cell>
           <cell r="S9">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="T9">
             <v>0</v>
@@ -11504,7 +11803,7 @@
             <v>0</v>
           </cell>
           <cell r="F10">
-            <v>0</v>
+            <v>1</v>
           </cell>
           <cell r="G10">
             <v>0</v>
@@ -11522,7 +11821,7 @@
             <v>0</v>
           </cell>
           <cell r="L10">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="M10">
             <v>0</v>
@@ -11602,7 +11901,7 @@
             <v>0</v>
           </cell>
           <cell r="L11">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="M11">
             <v>0</v>
@@ -11632,7 +11931,7 @@
             <v>0</v>
           </cell>
           <cell r="V11">
-            <v>0</v>
+            <v>1</v>
           </cell>
           <cell r="W11">
             <v>1</v>
@@ -11682,7 +11981,7 @@
             <v>0</v>
           </cell>
           <cell r="L12">
-            <v>0</v>
+            <v>1</v>
           </cell>
           <cell r="M12">
             <v>0</v>
@@ -11703,7 +12002,7 @@
             <v>0</v>
           </cell>
           <cell r="S12">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="T12">
             <v>0</v>
@@ -11863,7 +12162,7 @@
             <v>0</v>
           </cell>
           <cell r="S14">
-            <v>0</v>
+            <v>1</v>
           </cell>
           <cell r="T14">
             <v>0</v>
@@ -11878,7 +12177,7 @@
             <v>1</v>
           </cell>
           <cell r="X14">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="Y14">
             <v>0</v>
@@ -11999,7 +12298,7 @@
             <v>0</v>
           </cell>
           <cell r="K16">
-            <v>0</v>
+            <v>1</v>
           </cell>
           <cell r="L16">
             <v>0</v>
@@ -12035,7 +12334,7 @@
             <v>1</v>
           </cell>
           <cell r="W16">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="X16">
             <v>0</v>
@@ -12100,10 +12399,10 @@
             <v>0</v>
           </cell>
           <cell r="R17">
-            <v>0</v>
+            <v>1</v>
           </cell>
           <cell r="S17">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="T17">
             <v>0</v>
@@ -12369,10 +12668,10 @@
             <v>0</v>
           </cell>
           <cell r="V3">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="W3">
-            <v>0</v>
+            <v>1</v>
           </cell>
           <cell r="X3">
             <v>0</v>
@@ -12404,7 +12703,7 @@
             <v>0</v>
           </cell>
           <cell r="G4">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="H4">
             <v>0</v>
@@ -12452,7 +12751,7 @@
             <v>0</v>
           </cell>
           <cell r="W4">
-            <v>0</v>
+            <v>1</v>
           </cell>
           <cell r="X4">
             <v>0</v>
@@ -13376,7 +13675,7 @@
             <v>0</v>
           </cell>
           <cell r="K16">
-            <v>1</v>
+            <v>0</v>
           </cell>
           <cell r="L16">
             <v>0</v>
@@ -13412,7 +13711,7 @@
             <v>1</v>
           </cell>
           <cell r="W16">
-            <v>0</v>
+            <v>1</v>
           </cell>
           <cell r="X16">
             <v>0</v>
@@ -13517,7 +13816,7 @@
       <xxl21:absoluteUrl r:id="rId2"/>
     </xxl21:alternateUrls>
     <sheetNames>
-      <sheetName val="resultados_proyectados_proporci"/>
+      <sheetName val="resultados_integracion_partido_"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0">
@@ -13606,79 +13905,79 @@
             <v>1</v>
           </cell>
           <cell r="B2">
-            <v>2.94921215201552E-2</v>
+            <v>0</v>
           </cell>
           <cell r="C2">
             <v>0</v>
           </cell>
           <cell r="D2">
-            <v>3.8370273754083598E-2</v>
+            <v>0</v>
           </cell>
           <cell r="E2">
-            <v>7.7003860909288504E-3</v>
+            <v>0</v>
           </cell>
           <cell r="F2">
-            <v>3.69628738310364E-2</v>
+            <v>0</v>
           </cell>
           <cell r="G2">
-            <v>3.5904517253661603E-2</v>
+            <v>0</v>
           </cell>
           <cell r="H2">
-            <v>3.7122426783395401E-3</v>
+            <v>0</v>
           </cell>
           <cell r="I2">
-            <v>5.6132701789408403E-4</v>
+            <v>0</v>
           </cell>
           <cell r="J2">
             <v>0</v>
           </cell>
           <cell r="K2">
-            <v>2.64487084885912E-2</v>
+            <v>0</v>
           </cell>
           <cell r="L2">
-            <v>5.6262317300813103E-2</v>
+            <v>0</v>
           </cell>
           <cell r="M2">
-            <v>5.7424774525142802E-2</v>
+            <v>0</v>
           </cell>
           <cell r="N2">
-            <v>5.8452853463370601E-3</v>
+            <v>0</v>
           </cell>
           <cell r="O2">
-            <v>1.8447246997155602E-2</v>
+            <v>0</v>
           </cell>
           <cell r="P2">
-            <v>9.9735904143035594E-3</v>
+            <v>0</v>
           </cell>
           <cell r="Q2">
-            <v>3.4214412632511397E-2</v>
+            <v>0</v>
           </cell>
           <cell r="R2">
-            <v>4.3096647244751797E-2</v>
+            <v>0</v>
           </cell>
           <cell r="S2">
-            <v>2.6841637401117099E-2</v>
+            <v>0</v>
           </cell>
           <cell r="T2">
-            <v>3.7715052035014497E-2</v>
+            <v>0</v>
           </cell>
           <cell r="U2">
             <v>0</v>
           </cell>
           <cell r="V2">
-            <v>0.121981463961274</v>
+            <v>1</v>
           </cell>
           <cell r="W2">
-            <v>9.1851470829876006E-2</v>
+            <v>1</v>
           </cell>
           <cell r="X2">
-            <v>5.8876060015043502E-2</v>
+            <v>0</v>
           </cell>
           <cell r="Y2">
-            <v>0.108846411742552</v>
+            <v>0</v>
           </cell>
           <cell r="Z2">
-            <v>0.149471178919414</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="3">
@@ -13686,25 +13985,25 @@
             <v>2</v>
           </cell>
           <cell r="B3">
-            <v>1.19339124020918E-2</v>
+            <v>0</v>
           </cell>
           <cell r="C3">
             <v>0</v>
           </cell>
           <cell r="D3">
-            <v>3.4290097581162103E-2</v>
+            <v>0</v>
           </cell>
           <cell r="E3">
-            <v>3.6409073268422097E-2</v>
+            <v>0</v>
           </cell>
           <cell r="F3">
-            <v>4.0998132428207802E-2</v>
+            <v>0</v>
           </cell>
           <cell r="G3">
-            <v>5.1359296369277399E-2</v>
+            <v>1</v>
           </cell>
           <cell r="H3">
-            <v>2.37788417624217E-3</v>
+            <v>0</v>
           </cell>
           <cell r="I3">
             <v>0</v>
@@ -13713,52 +14012,52 @@
             <v>0</v>
           </cell>
           <cell r="K3">
-            <v>5.2003619358421502E-2</v>
+            <v>1</v>
           </cell>
           <cell r="L3">
-            <v>4.3976920157553598E-2</v>
+            <v>0</v>
           </cell>
           <cell r="M3">
-            <v>5.6756707498804598E-2</v>
+            <v>0</v>
           </cell>
           <cell r="N3">
-            <v>2.2009901775586899E-3</v>
+            <v>0</v>
           </cell>
           <cell r="O3">
-            <v>1.25712668397726E-2</v>
+            <v>0</v>
           </cell>
           <cell r="P3">
-            <v>1.3406420930526699E-3</v>
+            <v>0</v>
           </cell>
           <cell r="Q3">
-            <v>2.0125712668397699E-2</v>
+            <v>0</v>
           </cell>
           <cell r="R3">
-            <v>4.6313529067436202E-2</v>
+            <v>0</v>
           </cell>
           <cell r="S3">
-            <v>3.87097673361479E-2</v>
+            <v>0</v>
           </cell>
           <cell r="T3">
-            <v>3.8379029162851797E-2</v>
+            <v>0</v>
           </cell>
           <cell r="U3">
             <v>0</v>
           </cell>
           <cell r="V3">
-            <v>0.101381702942444</v>
+            <v>1</v>
           </cell>
           <cell r="W3">
-            <v>6.1567688220574998E-2</v>
+            <v>0</v>
           </cell>
           <cell r="X3">
-            <v>4.0977226773817897E-2</v>
+            <v>0</v>
           </cell>
           <cell r="Y3">
-            <v>0.12466202525403</v>
+            <v>0</v>
           </cell>
           <cell r="Z3">
-            <v>0.18166477622373101</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="4">
@@ -13769,76 +14068,76 @@
             <v>0</v>
           </cell>
           <cell r="C4">
-            <v>2.2323885276993902E-2</v>
+            <v>0</v>
           </cell>
           <cell r="D4">
-            <v>1.09616450830563E-2</v>
+            <v>0</v>
           </cell>
           <cell r="E4">
             <v>0</v>
           </cell>
           <cell r="F4">
-            <v>3.9417319956760503E-2</v>
+            <v>0</v>
           </cell>
           <cell r="G4">
-            <v>8.7931659300052895E-2</v>
+            <v>1</v>
           </cell>
           <cell r="H4">
-            <v>1.52353479068733E-2</v>
+            <v>0</v>
           </cell>
           <cell r="I4">
-            <v>6.86586981278373E-4</v>
+            <v>0</v>
           </cell>
           <cell r="J4">
             <v>0</v>
           </cell>
           <cell r="K4">
-            <v>7.5657755490372805E-2</v>
+            <v>0</v>
           </cell>
           <cell r="L4">
-            <v>1.94526094951365E-2</v>
+            <v>0</v>
           </cell>
           <cell r="M4">
-            <v>2.72518246178085E-2</v>
+            <v>0</v>
           </cell>
           <cell r="N4">
-            <v>6.0722509762785003E-3</v>
+            <v>0</v>
           </cell>
           <cell r="O4">
-            <v>1.4518475384566101E-2</v>
+            <v>0</v>
           </cell>
           <cell r="P4">
-            <v>1.3000068486621099E-2</v>
+            <v>0</v>
           </cell>
           <cell r="Q4">
-            <v>3.6495453555229901E-2</v>
+            <v>0</v>
           </cell>
           <cell r="R4">
-            <v>4.8074510690623899E-2</v>
+            <v>0</v>
           </cell>
           <cell r="S4">
-            <v>8.2266542358286801E-2</v>
+            <v>1</v>
           </cell>
           <cell r="T4">
-            <v>2.6145025754755202E-2</v>
+            <v>0</v>
           </cell>
           <cell r="U4">
             <v>0</v>
           </cell>
           <cell r="V4">
-            <v>7.9563557821464598E-2</v>
+            <v>0</v>
           </cell>
           <cell r="W4">
-            <v>0.107729110978267</v>
+            <v>0</v>
           </cell>
           <cell r="X4">
-            <v>5.4669875557400202E-2</v>
+            <v>0</v>
           </cell>
           <cell r="Y4">
-            <v>0.100040369249575</v>
+            <v>0</v>
           </cell>
           <cell r="Z4">
-            <v>0.13250612507859599</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="5">
@@ -13846,79 +14145,79 @@
             <v>4</v>
           </cell>
           <cell r="B5">
-            <v>8.8372020524635497E-3</v>
+            <v>0</v>
           </cell>
           <cell r="C5">
-            <v>1.30034388339584E-2</v>
+            <v>0</v>
           </cell>
           <cell r="D5">
-            <v>2.93165605128635E-2</v>
+            <v>0</v>
           </cell>
           <cell r="E5">
-            <v>1.2391455540471399E-2</v>
+            <v>0</v>
           </cell>
           <cell r="F5">
-            <v>4.8881840833870802E-2</v>
+            <v>0</v>
           </cell>
           <cell r="G5">
-            <v>2.2119726051189802E-2</v>
+            <v>0</v>
           </cell>
           <cell r="H5">
-            <v>1.85265045548034E-3</v>
+            <v>0</v>
           </cell>
           <cell r="I5">
-            <v>6.85094699682837E-3</v>
+            <v>0</v>
           </cell>
           <cell r="J5">
             <v>0</v>
           </cell>
           <cell r="K5">
-            <v>7.4657879442631303E-2</v>
+            <v>1</v>
           </cell>
           <cell r="L5">
-            <v>6.0643128010278602E-2</v>
+            <v>1</v>
           </cell>
           <cell r="M5">
-            <v>4.1295697412301498E-2</v>
+            <v>0</v>
           </cell>
           <cell r="N5">
-            <v>1.85265045548034E-3</v>
+            <v>0</v>
           </cell>
           <cell r="O5">
-            <v>1.21290709507229E-2</v>
+            <v>0</v>
           </cell>
           <cell r="P5">
-            <v>1.85265045548034E-3</v>
+            <v>0</v>
           </cell>
           <cell r="Q5">
-            <v>2.9622366597662299E-2</v>
+            <v>0</v>
           </cell>
           <cell r="R5">
-            <v>3.3264947571328099E-2</v>
+            <v>0</v>
           </cell>
           <cell r="S5">
-            <v>5.9224692505301497E-2</v>
+            <v>0</v>
           </cell>
           <cell r="T5">
-            <v>2.94965555991832E-2</v>
+            <v>0</v>
           </cell>
           <cell r="U5">
             <v>0</v>
           </cell>
           <cell r="V5">
-            <v>8.8958767393648802E-2</v>
+            <v>0</v>
           </cell>
           <cell r="W5">
-            <v>9.1046710394957403E-2</v>
+            <v>1</v>
           </cell>
           <cell r="X5">
-            <v>6.1780622731041297E-2</v>
+            <v>0</v>
           </cell>
           <cell r="Y5">
-            <v>0.123378281384648</v>
+            <v>0</v>
           </cell>
           <cell r="Z5">
-            <v>0.14754215781820701</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="6">
@@ -13929,76 +14228,76 @@
             <v>0</v>
           </cell>
           <cell r="C6">
-            <v>6.4869028679831499E-3</v>
+            <v>0</v>
           </cell>
           <cell r="D6">
-            <v>1.04419722326936E-2</v>
+            <v>0</v>
           </cell>
           <cell r="E6">
-            <v>1.0727601254744401E-2</v>
+            <v>0</v>
           </cell>
           <cell r="F6">
-            <v>7.5344175533315502E-2</v>
+            <v>1</v>
           </cell>
           <cell r="G6">
-            <v>1.99833204552331E-2</v>
+            <v>0</v>
           </cell>
           <cell r="H6">
-            <v>6.0856833510710903E-3</v>
+            <v>0</v>
           </cell>
           <cell r="I6">
-            <v>7.8443845483029892E-3</v>
+            <v>0</v>
           </cell>
           <cell r="J6">
             <v>0</v>
           </cell>
           <cell r="K6">
-            <v>6.1068228740051703E-2</v>
+            <v>1</v>
           </cell>
           <cell r="L6">
-            <v>4.6696923507655301E-2</v>
+            <v>1</v>
           </cell>
           <cell r="M6">
-            <v>2.4516491059365299E-2</v>
+            <v>0</v>
           </cell>
           <cell r="N6">
-            <v>6.0856833510710903E-3</v>
+            <v>0</v>
           </cell>
           <cell r="O6">
-            <v>1.47460445587225E-2</v>
+            <v>0</v>
           </cell>
           <cell r="P6">
-            <v>1.6016498646386199E-2</v>
+            <v>0</v>
           </cell>
           <cell r="Q6">
-            <v>3.3914876005763699E-2</v>
+            <v>0</v>
           </cell>
           <cell r="R6">
-            <v>3.6716123133481202E-2</v>
+            <v>0</v>
           </cell>
           <cell r="S6">
-            <v>4.1651405845219397E-2</v>
+            <v>0</v>
           </cell>
           <cell r="T6">
-            <v>2.4874271162507101E-2</v>
+            <v>0</v>
           </cell>
           <cell r="U6">
             <v>0</v>
           </cell>
           <cell r="V6">
-            <v>0.1371598002144</v>
+            <v>1</v>
           </cell>
           <cell r="W6">
-            <v>0.10626961654006201</v>
+            <v>1</v>
           </cell>
           <cell r="X6">
-            <v>6.4773075180236298E-2</v>
+            <v>0</v>
           </cell>
           <cell r="Y6">
-            <v>9.6271856942704306E-2</v>
+            <v>0</v>
           </cell>
           <cell r="Z6">
-            <v>0.152325064869028</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="7">
@@ -14009,76 +14308,76 @@
             <v>0</v>
           </cell>
           <cell r="C7">
-            <v>4.7263351114183901E-3</v>
+            <v>0</v>
           </cell>
           <cell r="D7">
-            <v>2.6360823979780498E-2</v>
+            <v>0</v>
           </cell>
           <cell r="E7">
-            <v>9.9077987891215205E-3</v>
+            <v>0</v>
           </cell>
           <cell r="F7">
-            <v>5.5805300497302701E-2</v>
+            <v>0</v>
           </cell>
           <cell r="G7">
-            <v>3.3050031450937302E-2</v>
+            <v>0</v>
           </cell>
           <cell r="H7">
             <v>0</v>
           </cell>
           <cell r="I7">
-            <v>9.7471242621549794E-3</v>
+            <v>0</v>
           </cell>
           <cell r="J7">
-            <v>1.88666208987711E-2</v>
+            <v>0</v>
           </cell>
           <cell r="K7">
-            <v>4.45717629705265E-2</v>
+            <v>0</v>
           </cell>
           <cell r="L7">
-            <v>5.4940718518863702E-2</v>
+            <v>0</v>
           </cell>
           <cell r="M7">
-            <v>2.3737400786957401E-2</v>
+            <v>0</v>
           </cell>
           <cell r="N7">
             <v>0</v>
           </cell>
           <cell r="O7">
-            <v>5.3864222373545302E-3</v>
+            <v>0</v>
           </cell>
           <cell r="P7">
             <v>0</v>
           </cell>
           <cell r="Q7">
-            <v>4.0499023084964801E-2</v>
+            <v>0</v>
           </cell>
           <cell r="R7">
-            <v>6.3749067658814398E-2</v>
+            <v>1</v>
           </cell>
           <cell r="S7">
-            <v>7.4840710798139698E-2</v>
+            <v>1</v>
           </cell>
           <cell r="T7">
-            <v>1.3509644065348299E-2</v>
+            <v>0</v>
           </cell>
           <cell r="U7">
             <v>0</v>
           </cell>
           <cell r="V7">
-            <v>0.119366798614535</v>
+            <v>0</v>
           </cell>
           <cell r="W7">
-            <v>0.10256552935532801</v>
+            <v>0</v>
           </cell>
           <cell r="X7">
-            <v>0.102845608473042</v>
+            <v>1</v>
           </cell>
           <cell r="Y7">
-            <v>8.2573491207069097E-2</v>
+            <v>0</v>
           </cell>
           <cell r="Z7">
-            <v>0.112949787239567</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="8">
@@ -14086,79 +14385,79 @@
             <v>7</v>
           </cell>
           <cell r="B8">
-            <v>4.1725406165982401E-3</v>
+            <v>0</v>
           </cell>
           <cell r="C8">
-            <v>9.3335749926337207E-3</v>
+            <v>0</v>
           </cell>
           <cell r="D8">
-            <v>2.8624667847333099E-2</v>
+            <v>0</v>
           </cell>
           <cell r="E8">
-            <v>3.2152027618441402E-2</v>
+            <v>0</v>
           </cell>
           <cell r="F8">
-            <v>4.3984466997937802E-2</v>
+            <v>0</v>
           </cell>
           <cell r="G8">
-            <v>2.1941509789160499E-2</v>
+            <v>0</v>
           </cell>
           <cell r="H8">
             <v>0</v>
           </cell>
           <cell r="I8">
-            <v>5.0032960101678301E-3</v>
+            <v>0</v>
           </cell>
           <cell r="J8">
-            <v>5.0686594898803096E-3</v>
+            <v>0</v>
           </cell>
           <cell r="K8">
-            <v>3.9371702314506297E-2</v>
+            <v>0</v>
           </cell>
           <cell r="L8">
-            <v>6.1016292826739503E-2</v>
+            <v>0</v>
           </cell>
           <cell r="M8">
-            <v>1.77747426029469E-2</v>
+            <v>0</v>
           </cell>
           <cell r="N8">
             <v>0</v>
           </cell>
           <cell r="O8">
-            <v>8.1075458116546103E-4</v>
+            <v>0</v>
           </cell>
           <cell r="P8">
             <v>0</v>
           </cell>
           <cell r="Q8">
-            <v>4.0684951533082901E-2</v>
+            <v>0</v>
           </cell>
           <cell r="R8">
-            <v>7.4653960171165698E-2</v>
+            <v>1</v>
           </cell>
           <cell r="S8">
-            <v>4.5000590745644699E-2</v>
+            <v>1</v>
           </cell>
           <cell r="T8">
-            <v>2.46896626522768E-2</v>
+            <v>0</v>
           </cell>
           <cell r="U8">
             <v>0</v>
           </cell>
           <cell r="V8">
-            <v>9.6292983446956498E-2</v>
+            <v>1</v>
           </cell>
           <cell r="W8">
-            <v>0.140323225500087</v>
+            <v>1</v>
           </cell>
           <cell r="X8">
-            <v>0.121224717787506</v>
+            <v>1</v>
           </cell>
           <cell r="Y8">
-            <v>8.2100242009830099E-2</v>
+            <v>0</v>
           </cell>
           <cell r="Z8">
-            <v>0.105775430465938</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="9">
@@ -14169,76 +14468,76 @@
             <v>0</v>
           </cell>
           <cell r="C9">
-            <v>9.0700278594555601E-3</v>
+            <v>0</v>
           </cell>
           <cell r="D9">
-            <v>4.2950330175467302E-2</v>
+            <v>0</v>
           </cell>
           <cell r="E9">
-            <v>1.84792218255839E-2</v>
+            <v>0</v>
           </cell>
           <cell r="F9">
-            <v>4.3808763337555803E-2</v>
+            <v>0</v>
           </cell>
           <cell r="G9">
-            <v>3.2906604546727697E-2</v>
+            <v>0</v>
           </cell>
           <cell r="H9">
-            <v>2.0465086926803499E-2</v>
+            <v>0</v>
           </cell>
           <cell r="I9">
-            <v>8.0951774440995404E-3</v>
+            <v>0</v>
           </cell>
           <cell r="J9">
             <v>0</v>
           </cell>
           <cell r="K9">
-            <v>4.8370216086559101E-2</v>
+            <v>0</v>
           </cell>
           <cell r="L9">
-            <v>6.4069831909623301E-2</v>
+            <v>0</v>
           </cell>
           <cell r="M9">
-            <v>3.3127480350265998E-2</v>
+            <v>0</v>
           </cell>
           <cell r="N9">
-            <v>5.2503028577553996E-4</v>
+            <v>0</v>
           </cell>
           <cell r="O9">
-            <v>9.4156776002830896E-3</v>
+            <v>0</v>
           </cell>
           <cell r="P9">
-            <v>5.2503028577553996E-4</v>
+            <v>0</v>
           </cell>
           <cell r="Q9">
-            <v>2.6173998840438001E-2</v>
+            <v>0</v>
           </cell>
           <cell r="R9">
-            <v>5.3375293492505999E-2</v>
+            <v>0</v>
           </cell>
           <cell r="S9">
-            <v>4.9824711348607401E-2</v>
+            <v>1</v>
           </cell>
           <cell r="T9">
-            <v>6.72030120947152E-2</v>
+            <v>0</v>
           </cell>
           <cell r="U9">
             <v>0</v>
           </cell>
           <cell r="V9">
-            <v>0.114026088991192</v>
+            <v>1</v>
           </cell>
           <cell r="W9">
-            <v>7.3919336675238506E-2</v>
+            <v>0</v>
           </cell>
           <cell r="X9">
-            <v>8.4178463038674697E-2</v>
+            <v>1</v>
           </cell>
           <cell r="Y9">
-            <v>8.1992757924729903E-2</v>
+            <v>0</v>
           </cell>
           <cell r="Z9">
-            <v>0.117497858959921</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="10">
@@ -14249,76 +14548,76 @@
             <v>0</v>
           </cell>
           <cell r="C10">
-            <v>2.6399249382519301E-2</v>
+            <v>0</v>
           </cell>
           <cell r="D10">
-            <v>2.9325182030622999E-2</v>
+            <v>0</v>
           </cell>
           <cell r="E10">
-            <v>3.2077536649405401E-2</v>
+            <v>0</v>
           </cell>
           <cell r="F10">
-            <v>5.3475611494803302E-2</v>
+            <v>0</v>
           </cell>
           <cell r="G10">
-            <v>2.26552142885269E-2</v>
+            <v>0</v>
           </cell>
           <cell r="H10">
             <v>0</v>
           </cell>
           <cell r="I10">
-            <v>1.6837295151900002E-2</v>
+            <v>0</v>
           </cell>
           <cell r="J10">
             <v>0</v>
           </cell>
           <cell r="K10">
-            <v>2.1980138328337201E-2</v>
+            <v>0</v>
           </cell>
           <cell r="L10">
-            <v>4.8912795031730599E-2</v>
+            <v>1</v>
           </cell>
           <cell r="M10">
-            <v>2.29840394209961E-2</v>
+            <v>0</v>
           </cell>
           <cell r="N10">
             <v>0</v>
           </cell>
           <cell r="O10">
-            <v>1.7996669655437399E-2</v>
+            <v>0</v>
           </cell>
           <cell r="P10">
             <v>0</v>
           </cell>
           <cell r="Q10">
-            <v>5.8182133366766503E-2</v>
+            <v>1</v>
           </cell>
           <cell r="R10">
-            <v>4.8732654078223699E-2</v>
+            <v>0</v>
           </cell>
           <cell r="S10">
-            <v>4.0948120763236298E-2</v>
+            <v>0</v>
           </cell>
           <cell r="T10">
-            <v>4.0444359755062602E-2</v>
+            <v>0</v>
           </cell>
           <cell r="U10">
             <v>0</v>
           </cell>
           <cell r="V10">
-            <v>0.10683580604703299</v>
+            <v>1</v>
           </cell>
           <cell r="W10">
-            <v>0.13134470695638201</v>
+            <v>1</v>
           </cell>
           <cell r="X10">
-            <v>8.6972550230132298E-2</v>
+            <v>1</v>
           </cell>
           <cell r="Y10">
-            <v>9.1207673099388403E-2</v>
+            <v>0</v>
           </cell>
           <cell r="Z10">
-            <v>0.102688264269494</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="11">
@@ -14329,76 +14628,76 @@
             <v>0</v>
           </cell>
           <cell r="C11">
-            <v>2.0746305758587501E-2</v>
+            <v>0</v>
           </cell>
           <cell r="D11">
             <v>0</v>
           </cell>
           <cell r="E11">
-            <v>1.07363366169312E-2</v>
+            <v>0</v>
           </cell>
           <cell r="F11">
-            <v>5.8270382346815502E-2</v>
+            <v>0</v>
           </cell>
           <cell r="G11">
-            <v>2.23269496028622E-2</v>
+            <v>0</v>
           </cell>
           <cell r="H11">
             <v>0</v>
           </cell>
           <cell r="I11">
-            <v>1.65015392995553E-2</v>
+            <v>0</v>
           </cell>
           <cell r="J11">
             <v>0</v>
           </cell>
           <cell r="K11">
-            <v>2.7072757162768801E-2</v>
+            <v>0</v>
           </cell>
           <cell r="L11">
-            <v>7.4696209917357898E-2</v>
+            <v>1</v>
           </cell>
           <cell r="M11">
-            <v>2.97417894118309E-2</v>
+            <v>0</v>
           </cell>
           <cell r="N11">
             <v>0</v>
           </cell>
           <cell r="O11">
-            <v>2.4352819758022198E-2</v>
+            <v>0</v>
           </cell>
           <cell r="P11">
             <v>0</v>
           </cell>
           <cell r="Q11">
-            <v>3.5278306496583103E-2</v>
+            <v>0</v>
           </cell>
           <cell r="R11">
-            <v>2.7824706416788601E-2</v>
+            <v>0</v>
           </cell>
           <cell r="S11">
-            <v>8.1851097509988494E-2</v>
+            <v>1</v>
           </cell>
           <cell r="T11">
-            <v>2.6434763104976701E-2</v>
+            <v>0</v>
           </cell>
           <cell r="U11">
             <v>0</v>
           </cell>
           <cell r="V11">
-            <v>0.116297350192845</v>
+            <v>0</v>
           </cell>
           <cell r="W11">
-            <v>0.11305983397167101</v>
+            <v>1</v>
           </cell>
           <cell r="X11">
-            <v>0.10099815449430501</v>
+            <v>0</v>
           </cell>
           <cell r="Y11">
-            <v>0.10282195443756</v>
+            <v>0</v>
           </cell>
           <cell r="Z11">
-            <v>0.11098874350054801</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="12">
@@ -14412,16 +14711,16 @@
             <v>0</v>
           </cell>
           <cell r="D12">
-            <v>2.5873495822975202E-2</v>
+            <v>0</v>
           </cell>
           <cell r="E12">
-            <v>2.23946073691112E-2</v>
+            <v>0</v>
           </cell>
           <cell r="F12">
             <v>0</v>
           </cell>
           <cell r="G12">
-            <v>2.1793172416070299E-2</v>
+            <v>0</v>
           </cell>
           <cell r="H12">
             <v>0</v>
@@ -14433,10 +14732,10 @@
             <v>0</v>
           </cell>
           <cell r="K12">
-            <v>6.1735529003316102E-2</v>
+            <v>0</v>
           </cell>
           <cell r="L12">
-            <v>9.1977093583278602E-2</v>
+            <v>0</v>
           </cell>
           <cell r="M12">
             <v>0</v>
@@ -14451,34 +14750,34 @@
             <v>0</v>
           </cell>
           <cell r="Q12">
-            <v>5.6615076912916902E-2</v>
+            <v>0</v>
           </cell>
           <cell r="R12">
-            <v>6.3910129108036506E-2</v>
+            <v>0</v>
           </cell>
           <cell r="S12">
-            <v>8.2483855599005604E-2</v>
+            <v>1</v>
           </cell>
           <cell r="T12">
-            <v>2.0326142844339201E-2</v>
+            <v>0</v>
           </cell>
           <cell r="U12">
             <v>0</v>
           </cell>
           <cell r="V12">
-            <v>7.8137013958007998E-2</v>
+            <v>0</v>
           </cell>
           <cell r="W12">
-            <v>0.15242956135343999</v>
+            <v>0</v>
           </cell>
           <cell r="X12">
-            <v>0.153957913704697</v>
+            <v>1</v>
           </cell>
           <cell r="Y12">
-            <v>8.0297462652068705E-2</v>
+            <v>0</v>
           </cell>
           <cell r="Z12">
-            <v>8.8068945672734406E-2</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="13">
@@ -14495,10 +14794,10 @@
             <v>0</v>
           </cell>
           <cell r="E13">
-            <v>3.3436155846010097E-2</v>
+            <v>0</v>
           </cell>
           <cell r="F13">
-            <v>7.7490198644765501E-2</v>
+            <v>0</v>
           </cell>
           <cell r="G13">
             <v>0</v>
@@ -14507,19 +14806,19 @@
             <v>0</v>
           </cell>
           <cell r="I13">
-            <v>7.0647097668496998E-3</v>
+            <v>0</v>
           </cell>
           <cell r="J13">
             <v>0</v>
           </cell>
           <cell r="K13">
-            <v>5.9413465485546303E-2</v>
+            <v>0</v>
           </cell>
           <cell r="L13">
-            <v>6.5028050616042596E-2</v>
+            <v>0</v>
           </cell>
           <cell r="M13">
-            <v>1.7749525548965101E-2</v>
+            <v>0</v>
           </cell>
           <cell r="N13">
             <v>0</v>
@@ -14531,34 +14830,34 @@
             <v>0</v>
           </cell>
           <cell r="Q13">
-            <v>4.46564022630868E-2</v>
+            <v>0</v>
           </cell>
           <cell r="R13">
-            <v>8.2639256584309498E-2</v>
+            <v>0</v>
           </cell>
           <cell r="S13">
-            <v>0.100997090826883</v>
+            <v>1</v>
           </cell>
           <cell r="T13">
-            <v>2.8303458286978899E-2</v>
+            <v>0</v>
           </cell>
           <cell r="U13">
             <v>0</v>
           </cell>
           <cell r="V13">
-            <v>0.100134452581668</v>
+            <v>0</v>
           </cell>
           <cell r="W13">
-            <v>8.5927693067363101E-2</v>
+            <v>1</v>
           </cell>
           <cell r="X13">
-            <v>5.2802384451094302E-2</v>
+            <v>0</v>
           </cell>
           <cell r="Y13">
-            <v>0.106982015479894</v>
+            <v>0</v>
           </cell>
           <cell r="Z13">
-            <v>0.13737514055054101</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="14">
@@ -14566,79 +14865,79 @@
             <v>13</v>
           </cell>
           <cell r="B14">
-            <v>1.00094875593052E-2</v>
+            <v>0</v>
           </cell>
           <cell r="C14">
             <v>0</v>
           </cell>
           <cell r="D14">
-            <v>1.9071504813614099E-2</v>
+            <v>0</v>
           </cell>
           <cell r="E14">
-            <v>2.78413993776786E-2</v>
+            <v>0</v>
           </cell>
           <cell r="F14">
-            <v>8.9453610220408597E-2</v>
+            <v>1</v>
           </cell>
           <cell r="G14">
-            <v>1.9074218911958599E-2</v>
+            <v>0</v>
           </cell>
           <cell r="H14">
-            <v>2.29636527830656E-3</v>
+            <v>0</v>
           </cell>
           <cell r="I14">
-            <v>5.9786943994187798E-3</v>
+            <v>0</v>
           </cell>
           <cell r="J14">
-            <v>3.3853162922716701E-2</v>
+            <v>0</v>
           </cell>
           <cell r="K14">
-            <v>7.6410903490126802E-2</v>
+            <v>1</v>
           </cell>
           <cell r="L14">
-            <v>3.3713815399815397E-2</v>
+            <v>0</v>
           </cell>
           <cell r="M14">
-            <v>2.18004949872567E-2</v>
+            <v>0</v>
           </cell>
           <cell r="N14">
-            <v>1.53299297825856E-2</v>
+            <v>0</v>
           </cell>
           <cell r="O14">
-            <v>1.50100352000699E-2</v>
+            <v>0</v>
           </cell>
           <cell r="P14">
-            <v>2.29636527830656E-3</v>
+            <v>0</v>
           </cell>
           <cell r="Q14">
-            <v>2.6261187040194599E-2</v>
+            <v>0</v>
           </cell>
           <cell r="R14">
-            <v>2.3235574486946999E-2</v>
+            <v>0</v>
           </cell>
           <cell r="S14">
-            <v>5.2216252356578299E-2</v>
+            <v>0</v>
           </cell>
           <cell r="T14">
-            <v>2.0518440637651601E-2</v>
+            <v>0</v>
           </cell>
           <cell r="U14">
             <v>0</v>
           </cell>
           <cell r="V14">
-            <v>0.124168177961142</v>
+            <v>1</v>
           </cell>
           <cell r="W14">
-            <v>9.3413586840594101E-2</v>
+            <v>1</v>
           </cell>
           <cell r="X14">
-            <v>7.3968536386398706E-2</v>
+            <v>1</v>
           </cell>
           <cell r="Y14">
-            <v>8.5111802817326901E-2</v>
+            <v>0</v>
           </cell>
           <cell r="Z14">
-            <v>0.128966453851596</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="15">
@@ -14649,37 +14948,37 @@
             <v>0</v>
           </cell>
           <cell r="C15">
-            <v>1.6540157096204398E-2</v>
+            <v>0</v>
           </cell>
           <cell r="D15">
             <v>0</v>
           </cell>
           <cell r="E15">
-            <v>2.3485385716802198E-2</v>
+            <v>0</v>
           </cell>
           <cell r="F15">
-            <v>7.6254669298487301E-2</v>
+            <v>0</v>
           </cell>
           <cell r="G15">
-            <v>1.72628538391006E-2</v>
+            <v>0</v>
           </cell>
           <cell r="H15">
             <v>0</v>
           </cell>
           <cell r="I15">
-            <v>3.3537645725022899E-3</v>
+            <v>0</v>
           </cell>
           <cell r="J15">
             <v>0</v>
           </cell>
           <cell r="K15">
-            <v>4.1970613343691898E-2</v>
+            <v>0</v>
           </cell>
           <cell r="L15">
-            <v>6.3377116711007098E-2</v>
+            <v>0</v>
           </cell>
           <cell r="M15">
-            <v>1.05299173867285E-2</v>
+            <v>0</v>
           </cell>
           <cell r="N15">
             <v>0</v>
@@ -14691,34 +14990,34 @@
             <v>0</v>
           </cell>
           <cell r="Q15">
-            <v>8.3298704114402794E-2</v>
+            <v>1</v>
           </cell>
           <cell r="R15">
-            <v>3.58756826096579E-2</v>
+            <v>0</v>
           </cell>
           <cell r="S15">
-            <v>9.4074225472350004E-2</v>
+            <v>1</v>
           </cell>
           <cell r="T15">
-            <v>1.34523223408147E-2</v>
+            <v>0</v>
           </cell>
           <cell r="U15">
             <v>0</v>
           </cell>
           <cell r="V15">
-            <v>0.12300298564091899</v>
+            <v>0</v>
           </cell>
           <cell r="W15">
-            <v>0.13955048262591799</v>
+            <v>1</v>
           </cell>
           <cell r="X15">
-            <v>7.1679095545026203E-2</v>
+            <v>0</v>
           </cell>
           <cell r="Y15">
-            <v>8.3471473804501498E-2</v>
+            <v>0</v>
           </cell>
           <cell r="Z15">
-            <v>0.10282054988188399</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="16">
@@ -14726,25 +15025,25 @@
             <v>15</v>
           </cell>
           <cell r="B16">
-            <v>2.07625287516554E-2</v>
+            <v>0</v>
           </cell>
           <cell r="C16">
             <v>0</v>
           </cell>
           <cell r="D16">
-            <v>5.2794312399804803E-2</v>
+            <v>0</v>
           </cell>
           <cell r="E16">
-            <v>2.5928765595594899E-3</v>
+            <v>0</v>
           </cell>
           <cell r="F16">
-            <v>2.3508747473339298E-2</v>
+            <v>0</v>
           </cell>
           <cell r="G16">
-            <v>2.98933574963407E-2</v>
+            <v>0</v>
           </cell>
           <cell r="H16">
-            <v>4.9980251388211201E-3</v>
+            <v>0</v>
           </cell>
           <cell r="I16">
             <v>0</v>
@@ -14753,52 +15052,52 @@
             <v>0</v>
           </cell>
           <cell r="K16">
-            <v>4.73004809367812E-2</v>
+            <v>1</v>
           </cell>
           <cell r="L16">
-            <v>3.8865268000278799E-2</v>
+            <v>0</v>
           </cell>
           <cell r="M16">
-            <v>5.07144350735345E-2</v>
+            <v>0</v>
           </cell>
           <cell r="N16">
-            <v>3.9520921911665598E-2</v>
+            <v>0</v>
           </cell>
           <cell r="O16">
-            <v>3.4033595873701798E-2</v>
+            <v>0</v>
           </cell>
           <cell r="P16">
-            <v>9.9258846216398293E-3</v>
+            <v>0</v>
           </cell>
           <cell r="Q16">
-            <v>1.5695267303268898E-2</v>
+            <v>0</v>
           </cell>
           <cell r="R16">
-            <v>3.0262772705095101E-2</v>
+            <v>0</v>
           </cell>
           <cell r="S16">
-            <v>4.2696034014079502E-2</v>
+            <v>0</v>
           </cell>
           <cell r="T16">
-            <v>2.28758625496619E-2</v>
+            <v>0</v>
           </cell>
           <cell r="U16">
             <v>0</v>
           </cell>
           <cell r="V16">
-            <v>0.14930229316233301</v>
+            <v>1</v>
           </cell>
           <cell r="W16">
-            <v>7.8909876629260398E-2</v>
+            <v>0</v>
           </cell>
           <cell r="X16">
-            <v>5.2674426709416598E-2</v>
+            <v>0</v>
           </cell>
           <cell r="Y16">
-            <v>9.8612950442601197E-2</v>
+            <v>0</v>
           </cell>
           <cell r="Z16">
-            <v>0.154060082247159</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="17">
@@ -14809,76 +15108,76 @@
             <v>0</v>
           </cell>
           <cell r="C17">
-            <v>1.4190465273089099E-2</v>
+            <v>0</v>
           </cell>
           <cell r="D17">
-            <v>1.9918170656068698E-2</v>
+            <v>0</v>
           </cell>
           <cell r="E17">
-            <v>2.5116735613286301E-2</v>
+            <v>0</v>
           </cell>
           <cell r="F17">
-            <v>2.9529871371803001E-2</v>
+            <v>0</v>
           </cell>
           <cell r="G17">
-            <v>1.20399060797537E-2</v>
+            <v>0</v>
           </cell>
           <cell r="H17">
             <v>0</v>
           </cell>
           <cell r="I17">
-            <v>1.29778881194898E-2</v>
+            <v>0</v>
           </cell>
           <cell r="J17">
-            <v>1.7507399902453299E-2</v>
+            <v>0</v>
           </cell>
           <cell r="K17">
-            <v>3.8783290843734802E-2</v>
+            <v>0</v>
           </cell>
           <cell r="L17">
-            <v>4.94676559645763E-2</v>
+            <v>0</v>
           </cell>
           <cell r="M17">
-            <v>2.2804906273713701E-2</v>
+            <v>0</v>
           </cell>
           <cell r="N17">
             <v>0</v>
           </cell>
           <cell r="O17">
-            <v>1.3598124384612701E-2</v>
+            <v>0</v>
           </cell>
           <cell r="P17">
             <v>0</v>
           </cell>
           <cell r="Q17">
-            <v>4.3662366565298899E-2</v>
+            <v>0</v>
           </cell>
           <cell r="R17">
-            <v>8.3377973200388603E-2</v>
+            <v>0</v>
           </cell>
           <cell r="S17">
-            <v>7.1588253779932498E-2</v>
+            <v>1</v>
           </cell>
           <cell r="T17">
-            <v>2.9990145086469099E-2</v>
+            <v>0</v>
           </cell>
           <cell r="U17">
             <v>0</v>
           </cell>
           <cell r="V17">
-            <v>9.3306112094955804E-2</v>
+            <v>0</v>
           </cell>
           <cell r="W17">
-            <v>9.3854866457422206E-2</v>
+            <v>0</v>
           </cell>
           <cell r="X17">
-            <v>0.145324887426899</v>
+            <v>1</v>
           </cell>
           <cell r="Y17">
-            <v>8.7316887555916003E-2</v>
+            <v>0</v>
           </cell>
           <cell r="Z17">
-            <v>9.5644093350134393E-2</v>
+            <v>0</v>
           </cell>
         </row>
       </sheetData>
@@ -15203,8 +15502,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{394375BD-82B4-4DEB-BDA6-85DF9A687CB6}">
-  <dimension ref="B2:AA27"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80128DDA-BDA1-4D8D-BF45-A17A3A104BE2}">
+  <dimension ref="B2:AI27"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="14.7265625" customWidth="1"/>
@@ -15221,9 +15520,13 @@
     <col min="23" max="23" width="49.6328125" customWidth="1"/>
     <col min="26" max="26" width="14.7265625" customWidth="1"/>
     <col min="27" max="27" width="49.6328125" customWidth="1"/>
+    <col min="30" max="30" width="14.7265625" customWidth="1"/>
+    <col min="31" max="31" width="49.6328125" customWidth="1"/>
+    <col min="34" max="34" width="14.7265625" customWidth="1"/>
+    <col min="35" max="35" width="49.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:27" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:35" x14ac:dyDescent="0.35">
       <c r="B2" s="2" t="s">
         <v>6</v>
       </c>
@@ -15266,8 +15569,20 @@
       <c r="AA2" s="2" t="s">
         <v>7</v>
       </c>
+      <c r="AD2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="AE2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="AH2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="AI2" s="2" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="3" spans="2:27" ht="77" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:35" ht="77" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B3" s="7" t="s">
         <v>8</v>
       </c>
@@ -15322,8 +15637,20 @@
       <c r="AA3" s="28" t="s">
         <v>36</v>
       </c>
+      <c r="AD3" s="28" t="s">
+        <v>65</v>
+      </c>
+      <c r="AE3" s="28" t="s">
+        <v>36</v>
+      </c>
+      <c r="AH3" s="28" t="s">
+        <v>66</v>
+      </c>
+      <c r="AI3" s="28" t="s">
+        <v>36</v>
+      </c>
     </row>
-    <row r="4" spans="2:27" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:35" x14ac:dyDescent="0.35">
       <c r="B4" s="30" t="s">
         <v>40</v>
       </c>
@@ -15378,8 +15705,20 @@
       <c r="AA4" s="30" t="s">
         <v>41</v>
       </c>
+      <c r="AD4" s="30" t="s">
+        <v>40</v>
+      </c>
+      <c r="AE4" s="30" t="s">
+        <v>41</v>
+      </c>
+      <c r="AH4" s="30" t="s">
+        <v>40</v>
+      </c>
+      <c r="AI4" s="30" t="s">
+        <v>41</v>
+      </c>
     </row>
-    <row r="5" spans="2:27" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:35" x14ac:dyDescent="0.35">
       <c r="B5" s="8" t="s">
         <v>11</v>
       </c>
@@ -15422,8 +15761,20 @@
       <c r="AA5" s="9" t="s">
         <v>42</v>
       </c>
+      <c r="AD5" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="AE5" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="AH5" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="AI5" s="9" t="s">
+        <v>42</v>
+      </c>
     </row>
-    <row r="6" spans="2:27" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:35" x14ac:dyDescent="0.35">
       <c r="B6" s="8" t="s">
         <v>12</v>
       </c>
@@ -15466,8 +15817,20 @@
       <c r="AA6" s="9" t="s">
         <v>42</v>
       </c>
+      <c r="AD6" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="AE6" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="AH6" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="AI6" s="9" t="s">
+        <v>42</v>
+      </c>
     </row>
-    <row r="7" spans="2:27" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:35" x14ac:dyDescent="0.35">
       <c r="B7" s="8" t="s">
         <v>38</v>
       </c>
@@ -15510,8 +15873,20 @@
       <c r="AA7" s="9" t="s">
         <v>42</v>
       </c>
+      <c r="AD7" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="AE7" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="AH7" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="AI7" s="9" t="s">
+        <v>42</v>
+      </c>
     </row>
-    <row r="8" spans="2:27" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:35" x14ac:dyDescent="0.35">
       <c r="B8" s="8" t="s">
         <v>17</v>
       </c>
@@ -15554,8 +15929,20 @@
       <c r="AA8" s="9" t="s">
         <v>42</v>
       </c>
+      <c r="AD8" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="AE8" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="AH8" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="AI8" s="9" t="s">
+        <v>42</v>
+      </c>
     </row>
-    <row r="9" spans="2:27" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:35" x14ac:dyDescent="0.35">
       <c r="B9" s="10" t="s">
         <v>23</v>
       </c>
@@ -15598,8 +15985,20 @@
       <c r="AA9" s="9" t="s">
         <v>42</v>
       </c>
+      <c r="AD9" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="AE9" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="AH9" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="AI9" s="9" t="s">
+        <v>42</v>
+      </c>
     </row>
-    <row r="10" spans="2:27" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:35" x14ac:dyDescent="0.35">
       <c r="B10" s="10" t="s">
         <v>13</v>
       </c>
@@ -15642,8 +16041,20 @@
       <c r="AA10" s="9" t="s">
         <v>43</v>
       </c>
+      <c r="AD10" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="AE10" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="AH10" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="AI10" s="9" t="s">
+        <v>42</v>
+      </c>
     </row>
-    <row r="11" spans="2:27" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:35" x14ac:dyDescent="0.35">
       <c r="B11" s="10" t="s">
         <v>19</v>
       </c>
@@ -15686,8 +16097,20 @@
       <c r="AA11" s="9" t="s">
         <v>43</v>
       </c>
+      <c r="AD11" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="AE11" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="AH11" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="AI11" s="9" t="s">
+        <v>42</v>
+      </c>
     </row>
-    <row r="12" spans="2:27" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:35" x14ac:dyDescent="0.35">
       <c r="B12" s="10" t="s">
         <v>15</v>
       </c>
@@ -15730,8 +16153,20 @@
       <c r="AA12" s="9" t="s">
         <v>43</v>
       </c>
+      <c r="AD12" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="AE12" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="AH12" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="AI12" s="9" t="s">
+        <v>42</v>
+      </c>
     </row>
-    <row r="13" spans="2:27" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:35" x14ac:dyDescent="0.35">
       <c r="B13" s="10" t="s">
         <v>26</v>
       </c>
@@ -15774,8 +16209,20 @@
       <c r="AA13" s="9" t="s">
         <v>43</v>
       </c>
+      <c r="AD13" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="AE13" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="AH13" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="AI13" s="9" t="s">
+        <v>42</v>
+      </c>
     </row>
-    <row r="14" spans="2:27" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:35" x14ac:dyDescent="0.35">
       <c r="B14" s="11" t="s">
         <v>21</v>
       </c>
@@ -15818,8 +16265,20 @@
       <c r="AA14" s="9" t="s">
         <v>44</v>
       </c>
+      <c r="AD14" s="40" t="s">
+        <v>25</v>
+      </c>
+      <c r="AE14" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="AH14" s="40" t="s">
+        <v>25</v>
+      </c>
+      <c r="AI14" s="17" t="s">
+        <v>43</v>
+      </c>
     </row>
-    <row r="15" spans="2:27" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:35" x14ac:dyDescent="0.35">
       <c r="B15" s="11" t="s">
         <v>24</v>
       </c>
@@ -15862,8 +16321,20 @@
       <c r="AA15" s="9" t="s">
         <v>44</v>
       </c>
+      <c r="AD15" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="AE15" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="AH15" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="AI15" s="9" t="s">
+        <v>44</v>
+      </c>
     </row>
-    <row r="16" spans="2:27" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:35" x14ac:dyDescent="0.35">
       <c r="B16" s="11" t="s">
         <v>16</v>
       </c>
@@ -15906,8 +16377,20 @@
       <c r="AA16" s="9" t="s">
         <v>44</v>
       </c>
+      <c r="AD16" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="AE16" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="AH16" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="AI16" s="9" t="s">
+        <v>44</v>
+      </c>
     </row>
-    <row r="17" spans="2:27" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:35" x14ac:dyDescent="0.35">
       <c r="B17" s="11" t="s">
         <v>27</v>
       </c>
@@ -15950,8 +16433,20 @@
       <c r="AA17" s="9" t="s">
         <v>46</v>
       </c>
+      <c r="AD17" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="AE17" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="AH17" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="AI17" s="9" t="s">
+        <v>44</v>
+      </c>
     </row>
-    <row r="18" spans="2:27" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:35" x14ac:dyDescent="0.35">
       <c r="B18" s="11" t="s">
         <v>20</v>
       </c>
@@ -15994,8 +16489,20 @@
       <c r="AA18" s="9" t="s">
         <v>46</v>
       </c>
+      <c r="AD18" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="AE18" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="AH18" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="AI18" s="9" t="s">
+        <v>46</v>
+      </c>
     </row>
-    <row r="19" spans="2:27" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:35" x14ac:dyDescent="0.35">
       <c r="B19" s="11" t="s">
         <v>14</v>
       </c>
@@ -16038,8 +16545,20 @@
       <c r="AA19" s="9" t="s">
         <v>47</v>
       </c>
+      <c r="AD19" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE19" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="AH19" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="AI19" s="9" t="s">
+        <v>46</v>
+      </c>
     </row>
-    <row r="20" spans="2:27" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:35" x14ac:dyDescent="0.35">
       <c r="B20" s="11" t="s">
         <v>22</v>
       </c>
@@ -16082,8 +16601,20 @@
       <c r="AA20" s="9" t="s">
         <v>47</v>
       </c>
+      <c r="AD20" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="AE20" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="AH20" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="AI20" s="9" t="s">
+        <v>47</v>
+      </c>
     </row>
-    <row r="21" spans="2:27" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:35" x14ac:dyDescent="0.35">
       <c r="B21" s="12" t="s">
         <v>45</v>
       </c>
@@ -16126,8 +16657,20 @@
       <c r="AA21" s="9" t="s">
         <v>47</v>
       </c>
+      <c r="AD21" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="AE21" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="AH21" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="AI21" s="9" t="s">
+        <v>47</v>
+      </c>
     </row>
-    <row r="22" spans="2:27" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:35" x14ac:dyDescent="0.35">
       <c r="B22" s="13" t="s">
         <v>18</v>
       </c>
@@ -16170,8 +16713,20 @@
       <c r="AA22" s="9" t="s">
         <v>47</v>
       </c>
+      <c r="AD22" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="AE22" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="AH22" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="AI22" s="9" t="s">
+        <v>47</v>
+      </c>
     </row>
-    <row r="23" spans="2:27" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:35" x14ac:dyDescent="0.35">
       <c r="B23" s="14" t="s">
         <v>25</v>
       </c>
@@ -16214,8 +16769,20 @@
       <c r="AA23" s="9" t="s">
         <v>48</v>
       </c>
+      <c r="AD23" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="AE23" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="AH23" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="AI23" s="9" t="s">
+        <v>47</v>
+      </c>
     </row>
-    <row r="24" spans="2:27" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:35" x14ac:dyDescent="0.35">
       <c r="B24" s="15" t="s">
         <v>49</v>
       </c>
@@ -16258,8 +16825,20 @@
       <c r="AA24" s="9" t="s">
         <v>48</v>
       </c>
+      <c r="AD24" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="AE24" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="AH24" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="AI24" s="9" t="s">
+        <v>48</v>
+      </c>
     </row>
-    <row r="25" spans="2:27" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:35" x14ac:dyDescent="0.35">
       <c r="B25" s="15" t="s">
         <v>39</v>
       </c>
@@ -16302,8 +16881,20 @@
       <c r="AA25" s="9" t="s">
         <v>50</v>
       </c>
+      <c r="AD25" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="AE25" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="AH25" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="AI25" s="9" t="s">
+        <v>48</v>
+      </c>
     </row>
-    <row r="26" spans="2:27" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:35" x14ac:dyDescent="0.35">
       <c r="B26" s="15" t="s">
         <v>51</v>
       </c>
@@ -16346,8 +16937,20 @@
       <c r="AA26" s="9" t="s">
         <v>52</v>
       </c>
+      <c r="AD26" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="AE26" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="AH26" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="AI26" s="9" t="s">
+        <v>50</v>
+      </c>
     </row>
-    <row r="27" spans="2:27" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:35" x14ac:dyDescent="0.35">
       <c r="B27" s="16" t="s">
         <v>37</v>
       </c>
@@ -16389,388 +16992,489 @@
       </c>
       <c r="AA27" s="17" t="s">
         <v>53</v>
+      </c>
+      <c r="AD27" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="AE27" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="AH27" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="AI27" s="9" t="s">
+        <v>52</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4:C27">
-    <cfRule type="cellIs" dxfId="114" priority="113" operator="equal">
+    <cfRule type="cellIs" dxfId="140" priority="136" operator="equal">
+      <formula>"p7"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="138" priority="137" operator="equal">
+      <formula>"p6"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="139" priority="138" operator="equal">
+      <formula>"p5"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="137" priority="139" operator="equal">
+      <formula>"p4"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="136" priority="140" operator="equal">
       <formula>"p3"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="113" priority="115" operator="equal">
-      <formula>"p1"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="112" priority="114" operator="equal">
+    <cfRule type="cellIs" dxfId="135" priority="141" operator="equal">
       <formula>"p2"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="111" priority="109" operator="equal">
-      <formula>"p7"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="110" priority="110" operator="equal">
-      <formula>"p6"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="109" priority="111" operator="equal">
-      <formula>"p5"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="108" priority="112" operator="equal">
-      <formula>"p4"</formula>
+    <cfRule type="cellIs" dxfId="141" priority="142" operator="equal">
+      <formula>"p1"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F4:G27">
-    <cfRule type="cellIs" dxfId="107" priority="73" operator="equal">
-      <formula>"p1"</formula>
+    <cfRule type="cellIs" dxfId="130" priority="94" operator="equal">
+      <formula>"p7"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="106" priority="71" operator="equal">
+    <cfRule type="cellIs" dxfId="131" priority="95" operator="equal">
+      <formula>"p6"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="132" priority="96" operator="equal">
+      <formula>"p5"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="133" priority="97" operator="equal">
+      <formula>"p4"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="134" priority="98" operator="equal">
       <formula>"p3"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="105" priority="70" operator="equal">
-      <formula>"p4"</formula>
+    <cfRule type="cellIs" dxfId="129" priority="99" operator="equal">
+      <formula>"p2"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="104" priority="69" operator="equal">
-      <formula>"p5"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="103" priority="68" operator="equal">
-      <formula>"p6"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="102" priority="67" operator="equal">
-      <formula>"p7"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="101" priority="72" operator="equal">
-      <formula>"p2"</formula>
+    <cfRule type="cellIs" dxfId="128" priority="100" operator="equal">
+      <formula>"p1"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:G27">
-    <cfRule type="cellIs" dxfId="100" priority="66" operator="equal">
+    <cfRule type="cellIs" dxfId="127" priority="93" operator="equal">
       <formula>"p8"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J4:K4">
-    <cfRule type="cellIs" dxfId="99" priority="102" operator="equal">
+    <cfRule type="cellIs" dxfId="126" priority="129" operator="equal">
       <formula>"p7"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="98" priority="104" operator="equal">
+    <cfRule type="cellIs" dxfId="125" priority="130" operator="equal">
+      <formula>"p6"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="120" priority="131" operator="equal">
       <formula>"p5"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="97" priority="103" operator="equal">
-      <formula>"p6"</formula>
+    <cfRule type="cellIs" dxfId="121" priority="132" operator="equal">
+      <formula>"p4"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="96" priority="108" operator="equal">
+    <cfRule type="cellIs" dxfId="122" priority="133" operator="equal">
+      <formula>"p3"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="123" priority="134" operator="equal">
+      <formula>"p2"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="124" priority="135" operator="equal">
       <formula>"p1"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="95" priority="107" operator="equal">
-      <formula>"p2"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="94" priority="106" operator="equal">
-      <formula>"p3"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="93" priority="105" operator="equal">
-      <formula>"p4"</formula>
-    </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J5:K27">
-    <cfRule type="cellIs" dxfId="92" priority="53" operator="equal">
+  <conditionalFormatting sqref="J5:K27 AD5:AE27">
+    <cfRule type="cellIs" dxfId="118" priority="80" operator="equal">
       <formula>"p13"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="91" priority="54" operator="equal">
+    <cfRule type="cellIs" dxfId="117" priority="81" operator="equal">
       <formula>"p12"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="90" priority="55" operator="equal">
+    <cfRule type="cellIs" dxfId="119" priority="82" operator="equal">
       <formula>"p11"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="89" priority="56" operator="equal">
+    <cfRule type="cellIs" dxfId="116" priority="83" operator="equal">
       <formula>"p10"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="88" priority="57" operator="equal">
+    <cfRule type="cellIs" dxfId="115" priority="84" operator="equal">
       <formula>"p9"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K5:K27">
-    <cfRule type="cellIs" dxfId="87" priority="65" operator="equal">
-      <formula>"p1"</formula>
+  <conditionalFormatting sqref="K5:K27 AE5:AE27">
+    <cfRule type="cellIs" dxfId="107" priority="85" operator="equal">
+      <formula>"p8"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="86" priority="60" operator="equal">
+    <cfRule type="cellIs" dxfId="108" priority="86" operator="equal">
+      <formula>"p7"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="109" priority="87" operator="equal">
       <formula>"p6"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="85" priority="61" operator="equal">
+    <cfRule type="cellIs" dxfId="110" priority="88" operator="equal">
       <formula>"p5"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="84" priority="58" operator="equal">
-      <formula>"p8"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="83" priority="62" operator="equal">
+    <cfRule type="cellIs" dxfId="113" priority="89" operator="equal">
       <formula>"p4"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="82" priority="63" operator="equal">
+    <cfRule type="cellIs" dxfId="111" priority="90" operator="equal">
       <formula>"p3"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="81" priority="64" operator="equal">
+    <cfRule type="cellIs" dxfId="112" priority="91" operator="equal">
       <formula>"p2"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="80" priority="59" operator="equal">
-      <formula>"p7"</formula>
+    <cfRule type="cellIs" dxfId="114" priority="92" operator="equal">
+      <formula>"p1"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N4:O4">
-    <cfRule type="cellIs" dxfId="79" priority="100" operator="equal">
+    <cfRule type="cellIs" dxfId="101" priority="122" operator="equal">
+      <formula>"p7"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="102" priority="123" operator="equal">
+      <formula>"p6"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="100" priority="124" operator="equal">
+      <formula>"p5"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="106" priority="125" operator="equal">
+      <formula>"p4"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="103" priority="126" operator="equal">
+      <formula>"p3"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="104" priority="127" operator="equal">
       <formula>"p2"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="78" priority="101" operator="equal">
+    <cfRule type="cellIs" dxfId="105" priority="128" operator="equal">
       <formula>"p1"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="77" priority="95" operator="equal">
-      <formula>"p7"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="76" priority="96" operator="equal">
-      <formula>"p6"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="75" priority="97" operator="equal">
-      <formula>"p5"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="74" priority="98" operator="equal">
-      <formula>"p4"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="73" priority="99" operator="equal">
-      <formula>"p3"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N5:O27">
-    <cfRule type="cellIs" dxfId="72" priority="42" operator="equal">
+    <cfRule type="cellIs" dxfId="96" priority="67" operator="equal">
+      <formula>"p13"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="97" priority="68" operator="equal">
+      <formula>"p12"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="98" priority="69" operator="equal">
       <formula>"p11"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="71" priority="41" operator="equal">
-      <formula>"p12"</formula>
+    <cfRule type="cellIs" dxfId="95" priority="70" operator="equal">
+      <formula>"p10"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="70" priority="40" operator="equal">
-      <formula>"p13"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="69" priority="44" operator="equal">
+    <cfRule type="cellIs" dxfId="99" priority="71" operator="equal">
       <formula>"p9"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="68" priority="43" operator="equal">
-      <formula>"p10"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O5:O27">
-    <cfRule type="cellIs" dxfId="67" priority="47" operator="equal">
+    <cfRule type="cellIs" dxfId="94" priority="72" operator="equal">
+      <formula>"p8"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="93" priority="73" operator="equal">
+      <formula>"p7"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="92" priority="74" operator="equal">
       <formula>"p6"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="66" priority="48" operator="equal">
+    <cfRule type="cellIs" dxfId="91" priority="75" operator="equal">
       <formula>"p5"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="65" priority="49" operator="equal">
+    <cfRule type="cellIs" dxfId="90" priority="76" operator="equal">
       <formula>"p4"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="64" priority="50" operator="equal">
+    <cfRule type="cellIs" dxfId="89" priority="77" operator="equal">
       <formula>"p3"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="63" priority="51" operator="equal">
+    <cfRule type="cellIs" dxfId="88" priority="78" operator="equal">
       <formula>"p2"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="62" priority="52" operator="equal">
+    <cfRule type="cellIs" dxfId="87" priority="79" operator="equal">
       <formula>"p1"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="61" priority="46" operator="equal">
-      <formula>"p7"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="60" priority="45" operator="equal">
-      <formula>"p8"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R4:S4">
-    <cfRule type="cellIs" dxfId="59" priority="90" operator="equal">
+    <cfRule type="cellIs" dxfId="86" priority="115" operator="equal">
+      <formula>"p7"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="80" priority="116" operator="equal">
+      <formula>"p6"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="81" priority="117" operator="equal">
       <formula>"p5"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="58" priority="89" operator="equal">
-      <formula>"p6"</formula>
+    <cfRule type="cellIs" dxfId="82" priority="118" operator="equal">
+      <formula>"p4"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="57" priority="93" operator="equal">
+    <cfRule type="cellIs" dxfId="83" priority="119" operator="equal">
+      <formula>"p3"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="84" priority="120" operator="equal">
       <formula>"p2"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="56" priority="92" operator="equal">
-      <formula>"p3"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="55" priority="88" operator="equal">
-      <formula>"p7"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="54" priority="91" operator="equal">
-      <formula>"p4"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="53" priority="94" operator="equal">
+    <cfRule type="cellIs" dxfId="85" priority="121" operator="equal">
       <formula>"p1"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R5:S27">
-    <cfRule type="cellIs" dxfId="52" priority="29" operator="equal">
+    <cfRule type="cellIs" dxfId="75" priority="54" operator="equal">
+      <formula>"p13"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="78" priority="55" operator="equal">
+      <formula>"p12"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="76" priority="56" operator="equal">
       <formula>"p11"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="51" priority="27" operator="equal">
-      <formula>"p13"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="50" priority="28" operator="equal">
-      <formula>"p12"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="49" priority="30" operator="equal">
+    <cfRule type="cellIs" dxfId="77" priority="57" operator="equal">
       <formula>"p10"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="48" priority="31" operator="equal">
+    <cfRule type="cellIs" dxfId="79" priority="58" operator="equal">
       <formula>"p9"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S5:S27">
-    <cfRule type="cellIs" dxfId="47" priority="33" operator="equal">
+    <cfRule type="cellIs" dxfId="70" priority="59" operator="equal">
+      <formula>"p8"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="71" priority="60" operator="equal">
       <formula>"p7"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="46" priority="39" operator="equal">
-      <formula>"p1"</formula>
+    <cfRule type="cellIs" dxfId="72" priority="61" operator="equal">
+      <formula>"p6"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="45" priority="38" operator="equal">
+    <cfRule type="cellIs" dxfId="73" priority="62" operator="equal">
+      <formula>"p5"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="74" priority="63" operator="equal">
+      <formula>"p4"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="67" priority="64" operator="equal">
+      <formula>"p3"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="68" priority="65" operator="equal">
       <formula>"p2"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="44" priority="32" operator="equal">
-      <formula>"p8"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="43" priority="37" operator="equal">
-      <formula>"p3"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="42" priority="36" operator="equal">
-      <formula>"p4"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="41" priority="35" operator="equal">
-      <formula>"p5"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="40" priority="34" operator="equal">
-      <formula>"p6"</formula>
+    <cfRule type="cellIs" dxfId="69" priority="66" operator="equal">
+      <formula>"p1"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V4:W4">
-    <cfRule type="cellIs" dxfId="39" priority="87" operator="equal">
-      <formula>"p1"</formula>
+    <cfRule type="cellIs" dxfId="60" priority="108" operator="equal">
+      <formula>"p7"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="38" priority="83" operator="equal">
+    <cfRule type="cellIs" dxfId="66" priority="109" operator="equal">
+      <formula>"p6"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="61" priority="110" operator="equal">
       <formula>"p5"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="37" priority="82" operator="equal">
-      <formula>"p6"</formula>
+    <cfRule type="cellIs" dxfId="62" priority="111" operator="equal">
+      <formula>"p4"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="36" priority="81" operator="equal">
-      <formula>"p7"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="35" priority="85" operator="equal">
+    <cfRule type="cellIs" dxfId="63" priority="112" operator="equal">
       <formula>"p3"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="34" priority="86" operator="equal">
+    <cfRule type="cellIs" dxfId="64" priority="113" operator="equal">
       <formula>"p2"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="33" priority="84" operator="equal">
-      <formula>"p4"</formula>
+    <cfRule type="cellIs" dxfId="65" priority="114" operator="equal">
+      <formula>"p1"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V5:W27">
-    <cfRule type="cellIs" dxfId="32" priority="15" operator="equal">
+    <cfRule type="cellIs" dxfId="59" priority="41" operator="equal">
+      <formula>"p13"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="55" priority="42" operator="equal">
       <formula>"p12"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="31" priority="17" operator="equal">
+    <cfRule type="cellIs" dxfId="56" priority="43" operator="equal">
+      <formula>"p11"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="58" priority="44" operator="equal">
       <formula>"p10"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="30" priority="18" operator="equal">
+    <cfRule type="cellIs" dxfId="57" priority="45" operator="equal">
       <formula>"p9"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="29" priority="14" operator="equal">
-      <formula>"p13"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="28" priority="16" operator="equal">
-      <formula>"p11"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W5:W27">
-    <cfRule type="cellIs" dxfId="27" priority="21" operator="equal">
+    <cfRule type="cellIs" dxfId="54" priority="46" operator="equal">
+      <formula>"p8"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="53" priority="47" operator="equal">
+      <formula>"p7"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="52" priority="48" operator="equal">
       <formula>"p6"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="26" priority="19" operator="equal">
-      <formula>"p8"</formula>
+    <cfRule type="cellIs" dxfId="51" priority="49" operator="equal">
+      <formula>"p5"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="25" priority="20" operator="equal">
-      <formula>"p7"</formula>
+    <cfRule type="cellIs" dxfId="50" priority="50" operator="equal">
+      <formula>"p4"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="24" priority="26" operator="equal">
-      <formula>"p1"</formula>
+    <cfRule type="cellIs" dxfId="49" priority="51" operator="equal">
+      <formula>"p3"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="23" priority="25" operator="equal">
+    <cfRule type="cellIs" dxfId="47" priority="52" operator="equal">
       <formula>"p2"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="22" priority="24" operator="equal">
-      <formula>"p3"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="21" priority="23" operator="equal">
-      <formula>"p4"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="20" priority="22" operator="equal">
-      <formula>"p5"</formula>
+    <cfRule type="cellIs" dxfId="48" priority="53" operator="equal">
+      <formula>"p1"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z4:AA4">
-    <cfRule type="cellIs" dxfId="19" priority="77" operator="equal">
+    <cfRule type="cellIs" dxfId="44" priority="101" operator="equal">
+      <formula>"p7"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="45" priority="102" operator="equal">
+      <formula>"p6"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="46" priority="103" operator="equal">
+      <formula>"p5"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="43" priority="104" operator="equal">
       <formula>"p4"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="18" priority="78" operator="equal">
+    <cfRule type="cellIs" dxfId="42" priority="105" operator="equal">
       <formula>"p3"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="17" priority="79" operator="equal">
+    <cfRule type="cellIs" dxfId="41" priority="106" operator="equal">
       <formula>"p2"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="16" priority="80" operator="equal">
+    <cfRule type="cellIs" dxfId="40" priority="107" operator="equal">
       <formula>"p1"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="15" priority="74" operator="equal">
-      <formula>"p7"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="14" priority="75" operator="equal">
-      <formula>"p6"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="13" priority="76" operator="equal">
-      <formula>"p5"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z5:AA27">
-    <cfRule type="cellIs" dxfId="12" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="39" priority="28" operator="equal">
+      <formula>"p13"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="38" priority="29" operator="equal">
+      <formula>"p12"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="37" priority="30" operator="equal">
       <formula>"p11"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="11" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="35" priority="31" operator="equal">
       <formula>"p10"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="10" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="36" priority="32" operator="equal">
       <formula>"p9"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="9" priority="1" operator="equal">
-      <formula>"p13"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="8" priority="2" operator="equal">
-      <formula>"p12"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA5:AA27">
+    <cfRule type="cellIs" dxfId="28" priority="33" operator="equal">
+      <formula>"p8"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="29" priority="34" operator="equal">
+      <formula>"p7"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="34" priority="35" operator="equal">
+      <formula>"p6"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="30" priority="36" operator="equal">
+      <formula>"p5"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="27" priority="37" operator="equal">
+      <formula>"p4"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="31" priority="38" operator="equal">
+      <formula>"p3"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="32" priority="39" operator="equal">
+      <formula>"p2"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="33" priority="40" operator="equal">
+      <formula>"p1"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AD4:AE4">
+    <cfRule type="cellIs" dxfId="22" priority="21" operator="equal">
+      <formula>"p7"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="23" priority="22" operator="equal">
+      <formula>"p6"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="24" priority="23" operator="equal">
+      <formula>"p5"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="25" priority="24" operator="equal">
+      <formula>"p4"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="26" priority="25" operator="equal">
+      <formula>"p3"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="20" priority="26" operator="equal">
+      <formula>"p2"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="21" priority="27" operator="equal">
+      <formula>"p1"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AH4:AI4">
+    <cfRule type="cellIs" dxfId="13" priority="14" operator="equal">
+      <formula>"p7"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="15" priority="15" operator="equal">
+      <formula>"p6"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="17" priority="16" operator="equal">
+      <formula>"p5"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="18" priority="17" operator="equal">
+      <formula>"p4"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="16" priority="18" operator="equal">
+      <formula>"p3"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="19" priority="19" operator="equal">
+      <formula>"p2"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="14" priority="20" operator="equal">
+      <formula>"p1"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AH5:AI27">
+    <cfRule type="cellIs" dxfId="8" priority="1" operator="equal">
+      <formula>"p13"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="12" priority="2" operator="equal">
+      <formula>"p12"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="11" priority="3" operator="equal">
+      <formula>"p11"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="10" priority="4" operator="equal">
+      <formula>"p10"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="9" priority="5" operator="equal">
+      <formula>"p9"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AI5:AI27">
     <cfRule type="cellIs" dxfId="7" priority="6" operator="equal">
       <formula>"p8"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="7" operator="equal">
       <formula>"p7"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="5" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="8" operator="equal">
       <formula>"p6"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="9" operator="equal">
+      <formula>"p5"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="10" operator="equal">
       <formula>"p4"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="11" operator="equal">
       <formula>"p3"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="9" operator="equal">
-      <formula>"p5"</formula>
+    <cfRule type="cellIs" dxfId="2" priority="12" operator="equal">
+      <formula>"p2"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="13" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="13" operator="equal">
       <formula>"p1"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="12" operator="equal">
-      <formula>"p2"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -16857,31 +17561,31 @@
         <v>28</v>
       </c>
       <c r="C4" s="6">
-        <f>VLOOKUP($A$1,[9]resultados_proyectados_proporci!$A$1:$AA$29,MATCH(C$2,[9]resultados_proyectados_proporci!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[1]resultados_proyectados_proporci!$A$1:$AA$29,MATCH(C$2,[1]resultados_proyectados_proporci!$A$1:$AA$1,0),FALSE)</f>
         <v>2.3508747473339298E-2</v>
       </c>
       <c r="D4" s="6">
-        <f>VLOOKUP($A$1,[9]resultados_proyectados_proporci!$A$1:$AA$29,MATCH(D$2,[9]resultados_proyectados_proporci!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[1]resultados_proyectados_proporci!$A$1:$AA$29,MATCH(D$2,[1]resultados_proyectados_proporci!$A$1:$AA$1,0),FALSE)</f>
         <v>4.2696034014079502E-2</v>
       </c>
       <c r="E4" s="6">
-        <f>VLOOKUP($A$1,[9]resultados_proyectados_proporci!$A$1:$AA$29,MATCH(E$2,[9]resultados_proyectados_proporci!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[1]resultados_proyectados_proporci!$A$1:$AA$29,MATCH(E$2,[1]resultados_proyectados_proporci!$A$1:$AA$1,0),FALSE)</f>
         <v>5.2674426709416598E-2</v>
       </c>
       <c r="F4" s="6">
-        <f>VLOOKUP($A$1,[9]resultados_proyectados_proporci!$A$1:$AA$29,MATCH(F$2,[9]resultados_proyectados_proporci!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[1]resultados_proyectados_proporci!$A$1:$AA$29,MATCH(F$2,[1]resultados_proyectados_proporci!$A$1:$AA$1,0),FALSE)</f>
         <v>5.2794312399804803E-2</v>
       </c>
       <c r="G4" s="6">
-        <f>VLOOKUP($A$1,[9]resultados_proyectados_proporci!$A$1:$AA$29,MATCH(G$2,[9]resultados_proyectados_proporci!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[1]resultados_proyectados_proporci!$A$1:$AA$29,MATCH(G$2,[1]resultados_proyectados_proporci!$A$1:$AA$1,0),FALSE)</f>
         <v>7.8909876629260398E-2</v>
       </c>
       <c r="H4" s="6">
-        <f>VLOOKUP($A$1,[9]resultados_proyectados_proporci!$A$1:$AA$29,MATCH(H$2,[9]resultados_proyectados_proporci!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[1]resultados_proyectados_proporci!$A$1:$AA$29,MATCH(H$2,[1]resultados_proyectados_proporci!$A$1:$AA$1,0),FALSE)</f>
         <v>0.14930229316233301</v>
       </c>
       <c r="I4" s="6">
-        <f>VLOOKUP($A$1,[9]resultados_proyectados_proporci!$A$1:$AA$29,MATCH(I$2,[9]resultados_proyectados_proporci!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[1]resultados_proyectados_proporci!$A$1:$AA$29,MATCH(I$2,[1]resultados_proyectados_proporci!$A$1:$AA$1,0),FALSE)</f>
         <v>4.73004809367812E-2</v>
       </c>
     </row>
@@ -16890,31 +17594,31 @@
         <v>2</v>
       </c>
       <c r="C5" s="4">
-        <f>VLOOKUP($A$1,[1]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[1]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[2]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[2]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="D5" s="4">
-        <f>VLOOKUP($A$1,[1]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[1]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[2]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[2]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="E5" s="4">
-        <f>VLOOKUP($A$1,[1]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[1]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[2]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[2]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="F5" s="4">
-        <f>VLOOKUP($A$1,[1]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[1]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[2]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[2]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="G5" s="4">
-        <f>VLOOKUP($A$1,[1]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[1]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[2]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[2]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="H5" s="4">
-        <f>VLOOKUP($A$1,[1]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[1]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[2]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[2]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="I5" s="4">
-        <f>VLOOKUP($A$1,[1]resultados_integracion_partido_!$A$1:$AA$29,MATCH(I$2,[1]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[2]resultados_integracion_partido_!$A$1:$AA$29,MATCH(I$2,[2]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
     </row>
@@ -16923,31 +17627,31 @@
         <v>3</v>
       </c>
       <c r="C6" s="4">
-        <f>VLOOKUP($A$1,[2]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[2]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[3]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[3]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="D6" s="4">
-        <f>VLOOKUP($A$1,[2]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[2]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[3]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[3]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="E6" s="4">
-        <f>VLOOKUP($A$1,[2]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[2]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[3]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[3]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="F6" s="4">
-        <f>VLOOKUP($A$1,[2]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[2]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[3]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[3]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="G6" s="4">
-        <f>VLOOKUP($A$1,[2]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[2]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[3]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[3]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="H6" s="4">
-        <f>VLOOKUP($A$1,[2]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[2]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[3]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[3]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="I6" s="4">
-        <f>VLOOKUP($A$1,[2]resultados_integracion_partido_!$A$1:$AA$29,MATCH(I$2,[2]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[3]resultados_integracion_partido_!$A$1:$AA$29,MATCH(I$2,[3]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
     </row>
@@ -16956,31 +17660,31 @@
         <v>4</v>
       </c>
       <c r="C7" s="4">
-        <f>VLOOKUP($A$1,[3]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[3]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[4]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[4]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="D7" s="4">
-        <f>VLOOKUP($A$1,[3]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[3]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[4]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[4]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="E7" s="4">
-        <f>VLOOKUP($A$1,[3]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[3]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[4]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[4]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="F7" s="4">
-        <f>VLOOKUP($A$1,[3]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[3]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[4]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[4]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="G7" s="4">
-        <f>VLOOKUP($A$1,[3]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[3]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[4]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[4]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="H7" s="4">
-        <f>VLOOKUP($A$1,[3]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[3]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[4]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[4]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="I7" s="4">
-        <f>VLOOKUP($A$1,[3]resultados_integracion_partido_!$A$1:$AA$29,MATCH(I$2,[3]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[4]resultados_integracion_partido_!$A$1:$AA$29,MATCH(I$2,[4]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
     </row>
@@ -16989,31 +17693,31 @@
         <v>5</v>
       </c>
       <c r="C8" s="4">
-        <f>VLOOKUP($A$1,[4]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[4]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[5]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[5]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="D8" s="4">
-        <f>VLOOKUP($A$1,[4]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[4]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[5]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[5]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="E8" s="4">
-        <f>VLOOKUP($A$1,[4]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[4]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[5]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[5]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="F8" s="4">
-        <f>VLOOKUP($A$1,[4]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[4]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[5]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[5]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="G8" s="4">
-        <f>VLOOKUP($A$1,[4]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[4]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[5]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[5]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="H8" s="4">
-        <f>VLOOKUP($A$1,[4]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[4]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[5]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[5]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="I8" s="4">
-        <f>VLOOKUP($A$1,[4]resultados_integracion_partido_!$A$1:$AA$29,MATCH(I$2,[4]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[5]resultados_integracion_partido_!$A$1:$AA$29,MATCH(I$2,[5]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
     </row>
@@ -17022,31 +17726,31 @@
         <v>31</v>
       </c>
       <c r="C9" s="4">
-        <f>VLOOKUP($A$1,[5]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[5]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[6]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[6]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="D9" s="4">
-        <f>VLOOKUP($A$1,[5]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[5]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[6]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[6]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="E9" s="4">
-        <f>VLOOKUP($A$1,[5]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[5]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[6]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[6]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="F9" s="4">
-        <f>VLOOKUP($A$1,[5]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[5]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[6]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[6]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="G9" s="4">
-        <f>VLOOKUP($A$1,[5]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[5]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[6]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[6]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="H9" s="4">
-        <f>VLOOKUP($A$1,[5]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[5]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[6]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[6]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="I9" s="4">
-        <f>VLOOKUP($A$1,[5]resultados_integracion_partido_!$A$1:$AA$29,MATCH(I$2,[5]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[6]resultados_integracion_partido_!$A$1:$AA$29,MATCH(I$2,[6]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
     </row>
@@ -17055,31 +17759,31 @@
         <v>32</v>
       </c>
       <c r="C10" s="4">
-        <f>VLOOKUP($A$1,[6]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[6]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[7]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[7]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="D10" s="4">
-        <f>VLOOKUP($A$1,[6]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[6]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[7]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[7]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="E10" s="4">
-        <f>VLOOKUP($A$1,[6]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[6]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[7]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[7]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="F10" s="4">
-        <f>VLOOKUP($A$1,[6]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[6]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[7]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[7]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="G10" s="4">
-        <f>VLOOKUP($A$1,[6]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[6]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[7]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[7]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="H10" s="4">
-        <f>VLOOKUP($A$1,[6]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[6]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[7]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[7]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="I10" s="4">
-        <f>VLOOKUP($A$1,[6]resultados_integracion_partido_!$A$1:$AA$29,MATCH(I$2,[6]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[7]resultados_integracion_partido_!$A$1:$AA$29,MATCH(I$2,[7]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
     </row>
@@ -17088,31 +17792,31 @@
         <v>33</v>
       </c>
       <c r="C11" s="4">
-        <f>VLOOKUP($A$1,[7]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[7]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[8]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[8]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="D11" s="4">
-        <f>VLOOKUP($A$1,[7]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[7]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[8]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[8]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="E11" s="4">
-        <f>VLOOKUP($A$1,[7]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[7]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[8]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[8]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="F11" s="4">
-        <f>VLOOKUP($A$1,[7]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[7]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[8]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[8]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="G11" s="4">
-        <f>VLOOKUP($A$1,[7]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[7]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[8]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[8]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="H11" s="4">
-        <f>VLOOKUP($A$1,[7]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[7]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[8]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[8]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="I11" s="4">
-        <f>VLOOKUP($A$1,[7]resultados_integracion_partido_!$A$1:$AA$29,MATCH(I$2,[7]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[8]resultados_integracion_partido_!$A$1:$AA$29,MATCH(I$2,[8]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
     </row>
@@ -17121,31 +17825,31 @@
         <v>34</v>
       </c>
       <c r="C12" s="4">
-        <f>VLOOKUP($A$1,[8]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[8]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[9]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[9]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="D12" s="4">
-        <f>VLOOKUP($A$1,[8]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[8]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[9]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[9]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="E12" s="4">
-        <f>VLOOKUP($A$1,[8]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[8]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[9]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[9]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="F12" s="4">
-        <f>VLOOKUP($A$1,[8]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[8]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[9]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[9]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="G12" s="4">
-        <f>VLOOKUP($A$1,[8]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[8]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[9]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[9]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="H12" s="4">
-        <f>VLOOKUP($A$1,[8]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[8]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[9]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[9]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="I12" s="4">
-        <f>VLOOKUP($A$1,[8]resultados_integracion_partido_!$A$1:$AA$29,MATCH(I$2,[8]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[9]resultados_integracion_partido_!$A$1:$AA$29,MATCH(I$2,[9]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
     </row>
@@ -17331,27 +18035,27 @@
         <v>28</v>
       </c>
       <c r="C4" s="6">
-        <f>VLOOKUP($A$1,[9]resultados_proyectados_proporci!$A$1:$AA$29,MATCH(C$2,[9]resultados_proyectados_proporci!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[1]resultados_proyectados_proporci!$A$1:$AA$29,MATCH(C$2,[1]resultados_proyectados_proporci!$A$1:$AA$1,0),FALSE)</f>
         <v>3.69628738310364E-2</v>
       </c>
       <c r="D4" s="6">
-        <f>VLOOKUP($A$1,[9]resultados_proyectados_proporci!$A$1:$AA$29,MATCH(D$2,[9]resultados_proyectados_proporci!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[1]resultados_proyectados_proporci!$A$1:$AA$29,MATCH(D$2,[1]resultados_proyectados_proporci!$A$1:$AA$1,0),FALSE)</f>
         <v>3.4214412632511397E-2</v>
       </c>
       <c r="E4" s="6">
-        <f>VLOOKUP($A$1,[9]resultados_proyectados_proporci!$A$1:$AA$29,MATCH(E$2,[9]resultados_proyectados_proporci!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[1]resultados_proyectados_proporci!$A$1:$AA$29,MATCH(E$2,[1]resultados_proyectados_proporci!$A$1:$AA$1,0),FALSE)</f>
         <v>5.8876060015043502E-2</v>
       </c>
       <c r="F4" s="6">
-        <f>VLOOKUP($A$1,[9]resultados_proyectados_proporci!$A$1:$AA$29,MATCH(F$2,[9]resultados_proyectados_proporci!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[1]resultados_proyectados_proporci!$A$1:$AA$29,MATCH(F$2,[1]resultados_proyectados_proporci!$A$1:$AA$1,0),FALSE)</f>
         <v>9.1851470829876006E-2</v>
       </c>
       <c r="G4" s="6">
-        <f>VLOOKUP($A$1,[9]resultados_proyectados_proporci!$A$1:$AA$29,MATCH(G$2,[9]resultados_proyectados_proporci!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[1]resultados_proyectados_proporci!$A$1:$AA$29,MATCH(G$2,[1]resultados_proyectados_proporci!$A$1:$AA$1,0),FALSE)</f>
         <v>0.121981463961274</v>
       </c>
       <c r="H4" s="6">
-        <f>VLOOKUP($A$1,[9]resultados_proyectados_proporci!$A$1:$AA$29,MATCH(H$2,[9]resultados_proyectados_proporci!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[1]resultados_proyectados_proporci!$A$1:$AA$29,MATCH(H$2,[1]resultados_proyectados_proporci!$A$1:$AA$1,0),FALSE)</f>
         <v>5.6262317300813103E-2</v>
       </c>
     </row>
@@ -17360,27 +18064,27 @@
         <v>2</v>
       </c>
       <c r="C5" s="4">
-        <f>VLOOKUP($A$1,[1]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[1]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[2]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[2]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="D5" s="4">
-        <f>VLOOKUP($A$1,[1]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[1]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[2]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[2]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="E5" s="4">
-        <f>VLOOKUP($A$1,[1]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[1]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[2]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[2]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="F5" s="4">
-        <f>VLOOKUP($A$1,[1]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[1]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[2]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[2]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="G5" s="4">
-        <f>VLOOKUP($A$1,[1]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[1]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[2]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[2]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="H5" s="4">
-        <f>VLOOKUP($A$1,[1]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[1]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[2]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[2]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
     </row>
@@ -17389,27 +18093,27 @@
         <v>3</v>
       </c>
       <c r="C6" s="4">
-        <f>VLOOKUP($A$1,[2]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[2]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[3]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[3]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="D6" s="4">
-        <f>VLOOKUP($A$1,[2]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[2]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[3]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[3]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="E6" s="4">
-        <f>VLOOKUP($A$1,[2]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[2]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[3]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[3]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="F6" s="4">
-        <f>VLOOKUP($A$1,[2]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[2]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[3]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[3]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="G6" s="4">
-        <f>VLOOKUP($A$1,[2]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[2]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[3]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[3]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="H6" s="4">
-        <f>VLOOKUP($A$1,[2]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[2]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[3]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[3]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
     </row>
@@ -17418,27 +18122,27 @@
         <v>4</v>
       </c>
       <c r="C7" s="4">
-        <f>VLOOKUP($A$1,[3]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[3]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[4]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[4]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="D7" s="4">
-        <f>VLOOKUP($A$1,[3]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[3]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[4]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[4]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="E7" s="4">
-        <f>VLOOKUP($A$1,[3]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[3]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[4]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[4]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="F7" s="4">
-        <f>VLOOKUP($A$1,[3]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[3]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[4]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[4]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="G7" s="4">
-        <f>VLOOKUP($A$1,[3]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[3]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[4]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[4]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="H7" s="4">
-        <f>VLOOKUP($A$1,[3]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[3]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[4]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[4]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
     </row>
@@ -17447,27 +18151,27 @@
         <v>5</v>
       </c>
       <c r="C8" s="4">
-        <f>VLOOKUP($A$1,[4]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[4]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[5]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[5]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="D8" s="4">
-        <f>VLOOKUP($A$1,[4]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[4]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[5]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[5]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="E8" s="4">
-        <f>VLOOKUP($A$1,[4]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[4]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[5]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[5]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="F8" s="4">
-        <f>VLOOKUP($A$1,[4]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[4]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[5]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[5]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="G8" s="4">
-        <f>VLOOKUP($A$1,[4]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[4]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[5]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[5]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="H8" s="4">
-        <f>VLOOKUP($A$1,[4]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[4]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[5]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[5]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
     </row>
@@ -17476,27 +18180,27 @@
         <v>31</v>
       </c>
       <c r="C9" s="4">
-        <f>VLOOKUP($A$1,[5]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[5]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[6]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[6]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="D9" s="4">
-        <f>VLOOKUP($A$1,[5]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[5]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[6]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[6]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="E9" s="4">
-        <f>VLOOKUP($A$1,[5]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[5]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[6]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[6]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="F9" s="4">
-        <f>VLOOKUP($A$1,[5]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[5]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[6]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[6]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="G9" s="4">
-        <f>VLOOKUP($A$1,[5]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[5]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[6]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[6]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="H9" s="4">
-        <f>VLOOKUP($A$1,[5]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[5]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[6]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[6]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
     </row>
@@ -17505,27 +18209,27 @@
         <v>32</v>
       </c>
       <c r="C10" s="4">
-        <f>VLOOKUP($A$1,[6]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[6]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[7]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[7]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="D10" s="4">
-        <f>VLOOKUP($A$1,[6]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[6]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[7]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[7]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="E10" s="4">
-        <f>VLOOKUP($A$1,[6]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[6]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[7]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[7]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="F10" s="4">
-        <f>VLOOKUP($A$1,[6]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[6]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[7]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[7]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="G10" s="4">
-        <f>VLOOKUP($A$1,[6]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[6]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[7]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[7]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="H10" s="4">
-        <f>VLOOKUP($A$1,[6]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[6]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[7]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[7]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
     </row>
@@ -17534,27 +18238,27 @@
         <v>33</v>
       </c>
       <c r="C11" s="4">
-        <f>VLOOKUP($A$1,[7]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[7]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[8]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[8]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="D11" s="4">
-        <f>VLOOKUP($A$1,[7]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[7]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[8]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[8]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="E11" s="4">
-        <f>VLOOKUP($A$1,[7]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[7]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[8]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[8]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="F11" s="4">
-        <f>VLOOKUP($A$1,[7]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[7]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[8]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[8]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="G11" s="4">
-        <f>VLOOKUP($A$1,[7]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[7]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[8]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[8]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="H11" s="4">
-        <f>VLOOKUP($A$1,[7]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[7]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[8]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[8]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
     </row>
@@ -17563,27 +18267,27 @@
         <v>34</v>
       </c>
       <c r="C12" s="4">
-        <f>VLOOKUP($A$1,[8]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[8]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[9]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[9]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="D12" s="4">
-        <f>VLOOKUP($A$1,[8]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[8]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[9]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[9]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="E12" s="4">
-        <f>VLOOKUP($A$1,[8]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[8]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[9]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[9]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="F12" s="4">
-        <f>VLOOKUP($A$1,[8]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[8]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[9]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[9]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="G12" s="4">
-        <f>VLOOKUP($A$1,[8]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[8]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[9]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[9]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="H12" s="4">
-        <f>VLOOKUP($A$1,[8]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[8]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[9]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[9]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
     </row>
@@ -17763,27 +18467,27 @@
         <v>28</v>
       </c>
       <c r="C4" s="6">
-        <f>VLOOKUP($A$1,[9]resultados_proyectados_proporci!$A$1:$AA$29,MATCH(C$2,[9]resultados_proyectados_proporci!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[1]resultados_proyectados_proporci!$A$1:$AA$29,MATCH(C$2,[1]resultados_proyectados_proporci!$A$1:$AA$1,0),FALSE)</f>
         <v>3.9417319956760503E-2</v>
       </c>
       <c r="D4" s="6">
-        <f>VLOOKUP($A$1,[9]resultados_proyectados_proporci!$A$1:$AA$29,MATCH(D$2,[9]resultados_proyectados_proporci!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[1]resultados_proyectados_proporci!$A$1:$AA$29,MATCH(D$2,[1]resultados_proyectados_proporci!$A$1:$AA$1,0),FALSE)</f>
         <v>8.7931659300052895E-2</v>
       </c>
       <c r="E4" s="6">
-        <f>VLOOKUP($A$1,[9]resultados_proyectados_proporci!$A$1:$AA$29,MATCH(E$2,[9]resultados_proyectados_proporci!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[1]resultados_proyectados_proporci!$A$1:$AA$29,MATCH(E$2,[1]resultados_proyectados_proporci!$A$1:$AA$1,0),FALSE)</f>
         <v>8.2266542358286801E-2</v>
       </c>
       <c r="F4" s="6">
-        <f>VLOOKUP($A$1,[9]resultados_proyectados_proporci!$A$1:$AA$29,MATCH(F$2,[9]resultados_proyectados_proporci!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[1]resultados_proyectados_proporci!$A$1:$AA$29,MATCH(F$2,[1]resultados_proyectados_proporci!$A$1:$AA$1,0),FALSE)</f>
         <v>0.107729110978267</v>
       </c>
       <c r="G4" s="6">
-        <f>VLOOKUP($A$1,[9]resultados_proyectados_proporci!$A$1:$AA$29,MATCH(G$2,[9]resultados_proyectados_proporci!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[1]resultados_proyectados_proporci!$A$1:$AA$29,MATCH(G$2,[1]resultados_proyectados_proporci!$A$1:$AA$1,0),FALSE)</f>
         <v>7.5657755490372805E-2</v>
       </c>
       <c r="H4" s="6">
-        <f>VLOOKUP($A$1,[9]resultados_proyectados_proporci!$A$1:$AA$29,MATCH(H$2,[9]resultados_proyectados_proporci!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[1]resultados_proyectados_proporci!$A$1:$AA$29,MATCH(H$2,[1]resultados_proyectados_proporci!$A$1:$AA$1,0),FALSE)</f>
         <v>1.94526094951365E-2</v>
       </c>
     </row>
@@ -17792,27 +18496,27 @@
         <v>2</v>
       </c>
       <c r="C5" s="4">
-        <f>VLOOKUP($A$1,[1]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[1]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[2]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[2]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="D5" s="4">
-        <f>VLOOKUP($A$1,[1]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[1]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[2]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[2]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="E5" s="4">
-        <f>VLOOKUP($A$1,[1]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[1]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[2]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[2]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="F5" s="4">
-        <f>VLOOKUP($A$1,[1]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[1]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[2]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[2]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="G5" s="4">
-        <f>VLOOKUP($A$1,[1]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[1]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[2]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[2]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="H5" s="4">
-        <f>VLOOKUP($A$1,[1]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[1]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[2]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[2]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
     </row>
@@ -17821,27 +18525,27 @@
         <v>3</v>
       </c>
       <c r="C6" s="4">
-        <f>VLOOKUP($A$1,[2]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[2]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[3]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[3]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="D6" s="4">
-        <f>VLOOKUP($A$1,[2]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[2]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[3]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[3]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="E6" s="4">
-        <f>VLOOKUP($A$1,[2]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[2]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[3]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[3]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="F6" s="4">
-        <f>VLOOKUP($A$1,[2]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[2]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[3]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[3]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="G6" s="4">
-        <f>VLOOKUP($A$1,[2]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[2]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[3]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[3]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="H6" s="4">
-        <f>VLOOKUP($A$1,[2]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[2]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[3]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[3]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
     </row>
@@ -17850,27 +18554,27 @@
         <v>4</v>
       </c>
       <c r="C7" s="4">
-        <f>VLOOKUP($A$1,[3]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[3]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[4]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[4]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="D7" s="4">
-        <f>VLOOKUP($A$1,[3]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[3]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[4]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[4]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="E7" s="4">
-        <f>VLOOKUP($A$1,[3]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[3]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[4]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[4]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="F7" s="4">
-        <f>VLOOKUP($A$1,[3]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[3]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[4]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[4]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="G7" s="4">
-        <f>VLOOKUP($A$1,[3]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[3]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[4]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[4]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="H7" s="4">
-        <f>VLOOKUP($A$1,[3]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[3]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[4]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[4]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
     </row>
@@ -17879,27 +18583,27 @@
         <v>5</v>
       </c>
       <c r="C8" s="4">
-        <f>VLOOKUP($A$1,[4]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[4]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[5]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[5]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="D8" s="4">
-        <f>VLOOKUP($A$1,[4]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[4]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[5]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[5]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="E8" s="4">
-        <f>VLOOKUP($A$1,[4]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[4]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[5]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[5]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="F8" s="4">
-        <f>VLOOKUP($A$1,[4]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[4]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[5]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[5]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="G8" s="4">
-        <f>VLOOKUP($A$1,[4]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[4]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[5]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[5]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="H8" s="4">
-        <f>VLOOKUP($A$1,[4]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[4]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[5]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[5]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
     </row>
@@ -17908,27 +18612,27 @@
         <v>31</v>
       </c>
       <c r="C9" s="4">
-        <f>VLOOKUP($A$1,[5]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[5]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[6]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[6]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="D9" s="4">
-        <f>VLOOKUP($A$1,[5]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[5]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[6]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[6]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="E9" s="4">
-        <f>VLOOKUP($A$1,[5]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[5]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[6]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[6]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="F9" s="4">
-        <f>VLOOKUP($A$1,[5]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[5]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[6]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[6]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="G9" s="4">
-        <f>VLOOKUP($A$1,[5]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[5]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[6]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[6]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="H9" s="4">
-        <f>VLOOKUP($A$1,[5]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[5]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[6]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[6]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
     </row>
@@ -17937,27 +18641,27 @@
         <v>32</v>
       </c>
       <c r="C10" s="4">
-        <f>VLOOKUP($A$1,[6]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[6]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[7]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[7]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="D10" s="4">
-        <f>VLOOKUP($A$1,[6]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[6]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[7]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[7]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="E10" s="4">
-        <f>VLOOKUP($A$1,[6]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[6]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[7]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[7]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="F10" s="4">
-        <f>VLOOKUP($A$1,[6]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[6]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[7]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[7]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="G10" s="4">
-        <f>VLOOKUP($A$1,[6]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[6]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[7]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[7]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="H10" s="4">
-        <f>VLOOKUP($A$1,[6]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[6]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[7]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[7]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
     </row>
@@ -17966,27 +18670,27 @@
         <v>33</v>
       </c>
       <c r="C11" s="4">
-        <f>VLOOKUP($A$1,[7]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[7]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[8]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[8]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="D11" s="4">
-        <f>VLOOKUP($A$1,[7]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[7]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[8]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[8]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="E11" s="4">
-        <f>VLOOKUP($A$1,[7]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[7]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[8]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[8]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="F11" s="4">
-        <f>VLOOKUP($A$1,[7]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[7]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[8]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[8]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="G11" s="4">
-        <f>VLOOKUP($A$1,[7]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[7]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[8]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[8]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="H11" s="4">
-        <f>VLOOKUP($A$1,[7]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[7]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[8]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[8]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
     </row>
@@ -17995,27 +18699,27 @@
         <v>34</v>
       </c>
       <c r="C12" s="4">
-        <f>VLOOKUP($A$1,[8]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[8]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[9]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[9]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="D12" s="4">
-        <f>VLOOKUP($A$1,[8]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[8]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[9]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[9]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="E12" s="4">
-        <f>VLOOKUP($A$1,[8]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[8]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[9]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[9]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="F12" s="4">
-        <f>VLOOKUP($A$1,[8]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[8]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[9]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[9]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="G12" s="4">
-        <f>VLOOKUP($A$1,[8]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[8]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[9]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[9]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="H12" s="4">
-        <f>VLOOKUP($A$1,[8]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[8]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[9]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[9]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
     </row>
@@ -18202,31 +18906,31 @@
         <v>29</v>
       </c>
       <c r="C4" s="6">
-        <f>VLOOKUP($A$1,[9]resultados_proyectados_proporci!$A$1:$AA$29,MATCH(C$2,[9]resultados_proyectados_proporci!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[1]resultados_proyectados_proporci!$A$1:$AA$29,MATCH(C$2,[1]resultados_proyectados_proporci!$A$1:$AA$1,0),FALSE)</f>
         <v>7.5344175533315502E-2</v>
       </c>
       <c r="D4" s="6">
-        <f>VLOOKUP($A$1,[9]resultados_proyectados_proporci!$A$1:$AA$29,MATCH(D$2,[9]resultados_proyectados_proporci!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[1]resultados_proyectados_proporci!$A$1:$AA$29,MATCH(D$2,[1]resultados_proyectados_proporci!$A$1:$AA$1,0),FALSE)</f>
         <v>3.3914876005763699E-2</v>
       </c>
       <c r="E4" s="6">
-        <f>VLOOKUP($A$1,[9]resultados_proyectados_proporci!$A$1:$AA$29,MATCH(E$2,[9]resultados_proyectados_proporci!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[1]resultados_proyectados_proporci!$A$1:$AA$29,MATCH(E$2,[1]resultados_proyectados_proporci!$A$1:$AA$1,0),FALSE)</f>
         <v>0.10626961654006201</v>
       </c>
       <c r="F4" s="6">
-        <f>VLOOKUP($A$1,[9]resultados_proyectados_proporci!$A$1:$AA$29,MATCH(F$2,[9]resultados_proyectados_proporci!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[1]resultados_proyectados_proporci!$A$1:$AA$29,MATCH(F$2,[1]resultados_proyectados_proporci!$A$1:$AA$1,0),FALSE)</f>
         <v>6.4773075180236298E-2</v>
       </c>
       <c r="G4" s="6">
-        <f>VLOOKUP($A$1,[9]resultados_proyectados_proporci!$A$1:$AA$29,MATCH(G$2,[9]resultados_proyectados_proporci!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[1]resultados_proyectados_proporci!$A$1:$AA$29,MATCH(G$2,[1]resultados_proyectados_proporci!$A$1:$AA$1,0),FALSE)</f>
         <v>6.1068228740051703E-2</v>
       </c>
       <c r="H4" s="6">
-        <f>VLOOKUP($A$1,[9]resultados_proyectados_proporci!$A$1:$AA$29,MATCH(H$2,[9]resultados_proyectados_proporci!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[1]resultados_proyectados_proporci!$A$1:$AA$29,MATCH(H$2,[1]resultados_proyectados_proporci!$A$1:$AA$1,0),FALSE)</f>
         <v>0.1371598002144</v>
       </c>
       <c r="I4" s="6">
-        <f>VLOOKUP($A$1,[9]resultados_proyectados_proporci!$A$1:$AA$29,MATCH(I$2,[9]resultados_proyectados_proporci!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[1]resultados_proyectados_proporci!$A$1:$AA$29,MATCH(I$2,[1]resultados_proyectados_proporci!$A$1:$AA$1,0),FALSE)</f>
         <v>4.6696923507655301E-2</v>
       </c>
     </row>
@@ -18235,31 +18939,31 @@
         <v>2</v>
       </c>
       <c r="C5" s="4">
-        <f>VLOOKUP($A$1,[1]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[1]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[2]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[2]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="D5" s="4">
-        <f>VLOOKUP($A$1,[1]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[1]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[2]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[2]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="E5" s="4">
-        <f>VLOOKUP($A$1,[1]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[1]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[2]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[2]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="F5" s="4">
-        <f>VLOOKUP($A$1,[1]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[1]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[2]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[2]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="G5" s="4">
-        <f>VLOOKUP($A$1,[1]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[1]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[2]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[2]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="H5" s="4">
-        <f>VLOOKUP($A$1,[1]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[1]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[2]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[2]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>2</v>
       </c>
       <c r="I5" s="4">
-        <f>VLOOKUP($A$1,[1]resultados_integracion_partido_!$A$1:$AA$29,MATCH(I$2,[1]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[2]resultados_integracion_partido_!$A$1:$AA$29,MATCH(I$2,[2]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
     </row>
@@ -18268,31 +18972,31 @@
         <v>3</v>
       </c>
       <c r="C6" s="4">
-        <f>VLOOKUP($A$1,[2]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[2]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[3]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[3]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="D6" s="4">
-        <f>VLOOKUP($A$1,[2]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[2]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[3]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[3]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="E6" s="4">
-        <f>VLOOKUP($A$1,[2]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[2]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[3]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[3]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="F6" s="4">
-        <f>VLOOKUP($A$1,[2]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[2]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[3]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[3]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="G6" s="4">
-        <f>VLOOKUP($A$1,[2]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[2]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[3]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[3]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="H6" s="4">
-        <f>VLOOKUP($A$1,[2]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[2]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[3]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[3]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>2</v>
       </c>
       <c r="I6" s="4">
-        <f>VLOOKUP($A$1,[2]resultados_integracion_partido_!$A$1:$AA$29,MATCH(I$2,[2]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[3]resultados_integracion_partido_!$A$1:$AA$29,MATCH(I$2,[3]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
     </row>
@@ -18301,31 +19005,31 @@
         <v>4</v>
       </c>
       <c r="C7" s="4">
-        <f>VLOOKUP($A$1,[3]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[3]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[4]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[4]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="D7" s="4">
-        <f>VLOOKUP($A$1,[3]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[3]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[4]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[4]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="E7" s="4">
-        <f>VLOOKUP($A$1,[3]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[3]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[4]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[4]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="F7" s="4">
-        <f>VLOOKUP($A$1,[3]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[3]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[4]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[4]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="G7" s="4">
-        <f>VLOOKUP($A$1,[3]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[3]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[4]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[4]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="H7" s="4">
-        <f>VLOOKUP($A$1,[3]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[3]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[4]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[4]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>2</v>
       </c>
       <c r="I7" s="4">
-        <f>VLOOKUP($A$1,[3]resultados_integracion_partido_!$A$1:$AA$29,MATCH(I$2,[3]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[4]resultados_integracion_partido_!$A$1:$AA$29,MATCH(I$2,[4]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
     </row>
@@ -18334,31 +19038,31 @@
         <v>5</v>
       </c>
       <c r="C8" s="4">
-        <f>VLOOKUP($A$1,[4]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[4]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[5]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[5]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="D8" s="4">
-        <f>VLOOKUP($A$1,[4]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[4]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[5]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[5]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="E8" s="4">
-        <f>VLOOKUP($A$1,[4]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[4]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[5]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[5]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="F8" s="4">
-        <f>VLOOKUP($A$1,[4]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[4]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[5]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[5]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="G8" s="4">
-        <f>VLOOKUP($A$1,[4]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[4]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[5]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[5]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="H8" s="4">
-        <f>VLOOKUP($A$1,[4]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[4]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[5]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[5]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="I8" s="4">
-        <f>VLOOKUP($A$1,[4]resultados_integracion_partido_!$A$1:$AA$29,MATCH(I$2,[4]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[5]resultados_integracion_partido_!$A$1:$AA$29,MATCH(I$2,[5]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
     </row>
@@ -18367,31 +19071,31 @@
         <v>31</v>
       </c>
       <c r="C9" s="4">
-        <f>VLOOKUP($A$1,[5]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[5]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[6]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[6]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="D9" s="4">
-        <f>VLOOKUP($A$1,[5]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[5]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[6]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[6]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="E9" s="4">
-        <f>VLOOKUP($A$1,[5]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[5]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[6]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[6]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="F9" s="4">
-        <f>VLOOKUP($A$1,[5]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[5]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[6]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[6]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="G9" s="4">
-        <f>VLOOKUP($A$1,[5]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[5]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[6]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[6]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="H9" s="4">
-        <f>VLOOKUP($A$1,[5]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[5]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[6]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[6]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="I9" s="4">
-        <f>VLOOKUP($A$1,[5]resultados_integracion_partido_!$A$1:$AA$29,MATCH(I$2,[5]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[6]resultados_integracion_partido_!$A$1:$AA$29,MATCH(I$2,[6]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
     </row>
@@ -18400,31 +19104,31 @@
         <v>32</v>
       </c>
       <c r="C10" s="4">
-        <f>VLOOKUP($A$1,[6]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[6]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[7]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[7]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="D10" s="4">
-        <f>VLOOKUP($A$1,[6]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[6]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[7]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[7]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="E10" s="4">
-        <f>VLOOKUP($A$1,[6]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[6]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[7]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[7]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="F10" s="4">
-        <f>VLOOKUP($A$1,[6]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[6]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[7]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[7]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="G10" s="4">
-        <f>VLOOKUP($A$1,[6]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[6]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[7]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[7]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="H10" s="4">
-        <f>VLOOKUP($A$1,[6]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[6]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[7]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[7]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="I10" s="4">
-        <f>VLOOKUP($A$1,[6]resultados_integracion_partido_!$A$1:$AA$29,MATCH(I$2,[6]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[7]resultados_integracion_partido_!$A$1:$AA$29,MATCH(I$2,[7]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
     </row>
@@ -18433,31 +19137,31 @@
         <v>33</v>
       </c>
       <c r="C11" s="4">
-        <f>VLOOKUP($A$1,[7]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[7]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[8]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[8]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="D11" s="4">
-        <f>VLOOKUP($A$1,[7]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[7]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[8]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[8]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="E11" s="4">
-        <f>VLOOKUP($A$1,[7]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[7]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[8]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[8]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="F11" s="4">
-        <f>VLOOKUP($A$1,[7]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[7]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[8]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[8]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="G11" s="4">
-        <f>VLOOKUP($A$1,[7]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[7]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[8]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[8]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="H11" s="4">
-        <f>VLOOKUP($A$1,[7]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[7]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[8]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[8]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="I11" s="4">
-        <f>VLOOKUP($A$1,[7]resultados_integracion_partido_!$A$1:$AA$29,MATCH(I$2,[7]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[8]resultados_integracion_partido_!$A$1:$AA$29,MATCH(I$2,[8]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
     </row>
@@ -18466,31 +19170,31 @@
         <v>34</v>
       </c>
       <c r="C12" s="4">
-        <f>VLOOKUP($A$1,[8]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[8]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[9]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[9]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="D12" s="4">
-        <f>VLOOKUP($A$1,[8]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[8]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[9]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[9]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="E12" s="4">
-        <f>VLOOKUP($A$1,[8]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[8]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[9]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[9]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="F12" s="4">
-        <f>VLOOKUP($A$1,[8]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[8]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[9]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[9]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="G12" s="4">
-        <f>VLOOKUP($A$1,[8]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[8]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[9]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[9]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="H12" s="4">
-        <f>VLOOKUP($A$1,[8]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[8]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[9]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[9]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="I12" s="4">
-        <f>VLOOKUP($A$1,[8]resultados_integracion_partido_!$A$1:$AA$29,MATCH(I$2,[8]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[9]resultados_integracion_partido_!$A$1:$AA$29,MATCH(I$2,[9]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
     </row>
@@ -18697,39 +19401,39 @@
         <v>29</v>
       </c>
       <c r="C4" s="6">
-        <f>VLOOKUP($A$1,[9]resultados_proyectados_proporci!$A$1:$AA$29,MATCH(C$2,[9]resultados_proyectados_proporci!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[1]resultados_proyectados_proporci!$A$1:$AA$29,MATCH(C$2,[1]resultados_proyectados_proporci!$A$1:$AA$1,0),FALSE)</f>
         <v>4.3984466997937802E-2</v>
       </c>
       <c r="D4" s="6">
-        <f>VLOOKUP($A$1,[9]resultados_proyectados_proporci!$A$1:$AA$29,MATCH(D$2,[9]resultados_proyectados_proporci!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[1]resultados_proyectados_proporci!$A$1:$AA$29,MATCH(D$2,[1]resultados_proyectados_proporci!$A$1:$AA$1,0),FALSE)</f>
         <v>2.46896626522768E-2</v>
       </c>
       <c r="E4" s="6">
-        <f>VLOOKUP($A$1,[9]resultados_proyectados_proporci!$A$1:$AA$29,MATCH(E$2,[9]resultados_proyectados_proporci!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[1]resultados_proyectados_proporci!$A$1:$AA$29,MATCH(E$2,[1]resultados_proyectados_proporci!$A$1:$AA$1,0),FALSE)</f>
         <v>2.8624667847333099E-2</v>
       </c>
       <c r="F4" s="6">
-        <f>VLOOKUP($A$1,[9]resultados_proyectados_proporci!$A$1:$AA$29,MATCH(F$2,[9]resultados_proyectados_proporci!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[1]resultados_proyectados_proporci!$A$1:$AA$29,MATCH(F$2,[1]resultados_proyectados_proporci!$A$1:$AA$1,0),FALSE)</f>
         <v>4.5000590745644699E-2</v>
       </c>
       <c r="G4" s="6">
-        <f>VLOOKUP($A$1,[9]resultados_proyectados_proporci!$A$1:$AA$29,MATCH(G$2,[9]resultados_proyectados_proporci!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[1]resultados_proyectados_proporci!$A$1:$AA$29,MATCH(G$2,[1]resultados_proyectados_proporci!$A$1:$AA$1,0),FALSE)</f>
         <v>0.140323225500087</v>
       </c>
       <c r="H4" s="6">
-        <f>VLOOKUP($A$1,[9]resultados_proyectados_proporci!$A$1:$AA$29,MATCH(H$2,[9]resultados_proyectados_proporci!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[1]resultados_proyectados_proporci!$A$1:$AA$29,MATCH(H$2,[1]resultados_proyectados_proporci!$A$1:$AA$1,0),FALSE)</f>
         <v>0.121224717787506</v>
       </c>
       <c r="I4" s="6">
-        <f>VLOOKUP($A$1,[9]resultados_proyectados_proporci!$A$1:$AA$29,MATCH(I$2,[9]resultados_proyectados_proporci!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[1]resultados_proyectados_proporci!$A$1:$AA$29,MATCH(I$2,[1]resultados_proyectados_proporci!$A$1:$AA$1,0),FALSE)</f>
         <v>7.4653960171165698E-2</v>
       </c>
       <c r="J4" s="6">
-        <f>VLOOKUP($A$1,[9]resultados_proyectados_proporci!$A$1:$AA$29,MATCH(J$2,[9]resultados_proyectados_proporci!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[1]resultados_proyectados_proporci!$A$1:$AA$29,MATCH(J$2,[1]resultados_proyectados_proporci!$A$1:$AA$1,0),FALSE)</f>
         <v>6.1016292826739503E-2</v>
       </c>
       <c r="K4" s="6">
-        <f>VLOOKUP($A$1,[9]resultados_proyectados_proporci!$A$1:$AA$29,MATCH(K$2,[9]resultados_proyectados_proporci!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[1]resultados_proyectados_proporci!$A$1:$AA$29,MATCH(K$2,[1]resultados_proyectados_proporci!$A$1:$AA$1,0),FALSE)</f>
         <v>9.6292983446956498E-2</v>
       </c>
     </row>
@@ -18738,39 +19442,39 @@
         <v>2</v>
       </c>
       <c r="C5" s="4">
-        <f>VLOOKUP($A$1,[1]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[1]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[2]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[2]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="D5" s="4">
-        <f>VLOOKUP($A$1,[1]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[1]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[2]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[2]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="E5" s="4">
-        <f>VLOOKUP($A$1,[1]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[1]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[2]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[2]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="F5" s="4">
-        <f>VLOOKUP($A$1,[1]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[1]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[2]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[2]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="G5" s="4">
-        <f>VLOOKUP($A$1,[1]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[1]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[2]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[2]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>2</v>
       </c>
       <c r="H5" s="4">
-        <f>VLOOKUP($A$1,[1]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[1]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[2]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[2]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="I5" s="4">
-        <f>VLOOKUP($A$1,[1]resultados_integracion_partido_!$A$1:$AA$29,MATCH(I$2,[1]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[2]resultados_integracion_partido_!$A$1:$AA$29,MATCH(I$2,[2]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="J5" s="4">
-        <f>VLOOKUP($A$1,[1]resultados_integracion_partido_!$A$1:$AA$29,MATCH(J$2,[1]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[2]resultados_integracion_partido_!$A$1:$AA$29,MATCH(J$2,[2]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="K5" s="4">
-        <f>VLOOKUP($A$1,[1]resultados_integracion_partido_!$A$1:$AA$29,MATCH(K$2,[1]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[2]resultados_integracion_partido_!$A$1:$AA$29,MATCH(K$2,[2]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
     </row>
@@ -18779,39 +19483,39 @@
         <v>3</v>
       </c>
       <c r="C6" s="4">
-        <f>VLOOKUP($A$1,[2]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[2]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[3]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[3]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="D6" s="4">
-        <f>VLOOKUP($A$1,[2]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[2]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[3]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[3]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="E6" s="4">
-        <f>VLOOKUP($A$1,[2]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[2]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[3]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[3]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="F6" s="4">
-        <f>VLOOKUP($A$1,[2]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[2]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[3]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[3]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="G6" s="4">
-        <f>VLOOKUP($A$1,[2]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[2]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[3]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[3]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="H6" s="4">
-        <f>VLOOKUP($A$1,[2]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[2]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[3]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[3]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="I6" s="4">
-        <f>VLOOKUP($A$1,[2]resultados_integracion_partido_!$A$1:$AA$29,MATCH(I$2,[2]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[3]resultados_integracion_partido_!$A$1:$AA$29,MATCH(I$2,[3]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="J6" s="4">
-        <f>VLOOKUP($A$1,[2]resultados_integracion_partido_!$A$1:$AA$29,MATCH(J$2,[2]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[3]resultados_integracion_partido_!$A$1:$AA$29,MATCH(J$2,[3]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="K6" s="4">
-        <f>VLOOKUP($A$1,[2]resultados_integracion_partido_!$A$1:$AA$29,MATCH(K$2,[2]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[3]resultados_integracion_partido_!$A$1:$AA$29,MATCH(K$2,[3]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
     </row>
@@ -18820,39 +19524,39 @@
         <v>4</v>
       </c>
       <c r="C7" s="4">
-        <f>VLOOKUP($A$1,[3]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[3]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[4]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[4]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="D7" s="4">
-        <f>VLOOKUP($A$1,[3]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[3]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[4]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[4]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="E7" s="4">
-        <f>VLOOKUP($A$1,[3]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[3]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[4]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[4]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="F7" s="4">
-        <f>VLOOKUP($A$1,[3]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[3]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[4]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[4]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="G7" s="4">
-        <f>VLOOKUP($A$1,[3]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[3]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[4]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[4]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="H7" s="4">
-        <f>VLOOKUP($A$1,[3]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[3]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[4]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[4]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="I7" s="4">
-        <f>VLOOKUP($A$1,[3]resultados_integracion_partido_!$A$1:$AA$29,MATCH(I$2,[3]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[4]resultados_integracion_partido_!$A$1:$AA$29,MATCH(I$2,[4]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="J7" s="4">
-        <f>VLOOKUP($A$1,[3]resultados_integracion_partido_!$A$1:$AA$29,MATCH(J$2,[3]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[4]resultados_integracion_partido_!$A$1:$AA$29,MATCH(J$2,[4]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="K7" s="4">
-        <f>VLOOKUP($A$1,[3]resultados_integracion_partido_!$A$1:$AA$29,MATCH(K$2,[3]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[4]resultados_integracion_partido_!$A$1:$AA$29,MATCH(K$2,[4]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
     </row>
@@ -18861,39 +19565,39 @@
         <v>5</v>
       </c>
       <c r="C8" s="4">
-        <f>VLOOKUP($A$1,[4]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[4]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[5]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[5]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="D8" s="4">
-        <f>VLOOKUP($A$1,[4]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[4]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[5]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[5]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="E8" s="4">
-        <f>VLOOKUP($A$1,[4]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[4]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[5]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[5]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="F8" s="4">
-        <f>VLOOKUP($A$1,[4]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[4]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[5]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[5]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="G8" s="4">
-        <f>VLOOKUP($A$1,[4]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[4]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[5]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[5]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="H8" s="4">
-        <f>VLOOKUP($A$1,[4]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[4]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[5]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[5]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="I8" s="4">
-        <f>VLOOKUP($A$1,[4]resultados_integracion_partido_!$A$1:$AA$29,MATCH(I$2,[4]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[5]resultados_integracion_partido_!$A$1:$AA$29,MATCH(I$2,[5]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="J8" s="4">
-        <f>VLOOKUP($A$1,[4]resultados_integracion_partido_!$A$1:$AA$29,MATCH(J$2,[4]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[5]resultados_integracion_partido_!$A$1:$AA$29,MATCH(J$2,[5]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="K8" s="4">
-        <f>VLOOKUP($A$1,[4]resultados_integracion_partido_!$A$1:$AA$29,MATCH(K$2,[4]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[5]resultados_integracion_partido_!$A$1:$AA$29,MATCH(K$2,[5]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
     </row>
@@ -18902,39 +19606,39 @@
         <v>31</v>
       </c>
       <c r="C9" s="4">
-        <f>VLOOKUP($A$1,[5]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[5]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[6]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[6]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="D9" s="4">
-        <f>VLOOKUP($A$1,[5]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[5]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[6]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[6]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="E9" s="4">
-        <f>VLOOKUP($A$1,[5]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[5]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[6]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[6]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="F9" s="4">
-        <f>VLOOKUP($A$1,[5]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[5]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[6]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[6]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="G9" s="4">
-        <f>VLOOKUP($A$1,[5]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[5]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[6]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[6]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="H9" s="4">
-        <f>VLOOKUP($A$1,[5]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[5]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[6]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[6]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="I9" s="4">
-        <f>VLOOKUP($A$1,[5]resultados_integracion_partido_!$A$1:$AA$29,MATCH(I$2,[5]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[6]resultados_integracion_partido_!$A$1:$AA$29,MATCH(I$2,[6]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="J9" s="4">
-        <f>VLOOKUP($A$1,[5]resultados_integracion_partido_!$A$1:$AA$29,MATCH(J$2,[5]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[6]resultados_integracion_partido_!$A$1:$AA$29,MATCH(J$2,[6]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="K9" s="4">
-        <f>VLOOKUP($A$1,[5]resultados_integracion_partido_!$A$1:$AA$29,MATCH(K$2,[5]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[6]resultados_integracion_partido_!$A$1:$AA$29,MATCH(K$2,[6]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
     </row>
@@ -18943,39 +19647,39 @@
         <v>32</v>
       </c>
       <c r="C10" s="4">
-        <f>VLOOKUP($A$1,[6]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[6]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[7]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[7]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="D10" s="4">
-        <f>VLOOKUP($A$1,[6]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[6]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[7]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[7]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="E10" s="4">
-        <f>VLOOKUP($A$1,[6]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[6]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[7]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[7]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="F10" s="4">
-        <f>VLOOKUP($A$1,[6]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[6]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[7]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[7]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="G10" s="4">
-        <f>VLOOKUP($A$1,[6]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[6]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[7]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[7]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="H10" s="4">
-        <f>VLOOKUP($A$1,[6]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[6]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[7]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[7]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="I10" s="4">
-        <f>VLOOKUP($A$1,[6]resultados_integracion_partido_!$A$1:$AA$29,MATCH(I$2,[6]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[7]resultados_integracion_partido_!$A$1:$AA$29,MATCH(I$2,[7]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="J10" s="4">
-        <f>VLOOKUP($A$1,[6]resultados_integracion_partido_!$A$1:$AA$29,MATCH(J$2,[6]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[7]resultados_integracion_partido_!$A$1:$AA$29,MATCH(J$2,[7]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="K10" s="4">
-        <f>VLOOKUP($A$1,[6]resultados_integracion_partido_!$A$1:$AA$29,MATCH(K$2,[6]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[7]resultados_integracion_partido_!$A$1:$AA$29,MATCH(K$2,[7]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
     </row>
@@ -18984,39 +19688,39 @@
         <v>33</v>
       </c>
       <c r="C11" s="4">
-        <f>VLOOKUP($A$1,[7]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[7]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[8]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[8]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="D11" s="4">
-        <f>VLOOKUP($A$1,[7]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[7]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[8]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[8]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="E11" s="4">
-        <f>VLOOKUP($A$1,[7]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[7]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[8]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[8]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="F11" s="4">
-        <f>VLOOKUP($A$1,[7]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[7]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[8]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[8]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="G11" s="4">
-        <f>VLOOKUP($A$1,[7]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[7]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[8]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[8]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="H11" s="4">
-        <f>VLOOKUP($A$1,[7]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[7]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[8]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[8]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="I11" s="4">
-        <f>VLOOKUP($A$1,[7]resultados_integracion_partido_!$A$1:$AA$29,MATCH(I$2,[7]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[8]resultados_integracion_partido_!$A$1:$AA$29,MATCH(I$2,[8]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="J11" s="4">
-        <f>VLOOKUP($A$1,[7]resultados_integracion_partido_!$A$1:$AA$29,MATCH(J$2,[7]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[8]resultados_integracion_partido_!$A$1:$AA$29,MATCH(J$2,[8]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="K11" s="4">
-        <f>VLOOKUP($A$1,[7]resultados_integracion_partido_!$A$1:$AA$29,MATCH(K$2,[7]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[8]resultados_integracion_partido_!$A$1:$AA$29,MATCH(K$2,[8]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
     </row>
@@ -19025,39 +19729,39 @@
         <v>34</v>
       </c>
       <c r="C12" s="4">
-        <f>VLOOKUP($A$1,[8]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[8]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[9]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[9]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="D12" s="4">
-        <f>VLOOKUP($A$1,[8]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[8]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[9]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[9]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="E12" s="4">
-        <f>VLOOKUP($A$1,[8]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[8]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[9]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[9]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="F12" s="4">
-        <f>VLOOKUP($A$1,[8]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[8]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[9]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[9]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="G12" s="4">
-        <f>VLOOKUP($A$1,[8]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[8]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[9]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[9]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="H12" s="4">
-        <f>VLOOKUP($A$1,[8]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[8]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[9]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[9]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="I12" s="4">
-        <f>VLOOKUP($A$1,[8]resultados_integracion_partido_!$A$1:$AA$29,MATCH(I$2,[8]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[9]resultados_integracion_partido_!$A$1:$AA$29,MATCH(I$2,[9]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="J12" s="4">
-        <f>VLOOKUP($A$1,[8]resultados_integracion_partido_!$A$1:$AA$29,MATCH(J$2,[8]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[9]resultados_integracion_partido_!$A$1:$AA$29,MATCH(J$2,[9]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="K12" s="4">
-        <f>VLOOKUP($A$1,[8]resultados_integracion_partido_!$A$1:$AA$29,MATCH(K$2,[8]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[9]resultados_integracion_partido_!$A$1:$AA$29,MATCH(K$2,[9]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
     </row>
@@ -19271,31 +19975,31 @@
         <v>28</v>
       </c>
       <c r="C4" s="6">
-        <f>VLOOKUP($A$1,[9]resultados_proyectados_proporci!$A$1:$AA$29,MATCH(C$2,[9]resultados_proyectados_proporci!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[1]resultados_proyectados_proporci!$A$1:$AA$29,MATCH(C$2,[1]resultados_proyectados_proporci!$A$1:$AA$1,0),FALSE)</f>
         <v>5.3475611494803302E-2</v>
       </c>
       <c r="D4" s="6">
-        <f>VLOOKUP($A$1,[9]resultados_proyectados_proporci!$A$1:$AA$29,MATCH(D$2,[9]resultados_proyectados_proporci!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[1]resultados_proyectados_proporci!$A$1:$AA$29,MATCH(D$2,[1]resultados_proyectados_proporci!$A$1:$AA$1,0),FALSE)</f>
         <v>5.8182133366766503E-2</v>
       </c>
       <c r="E4" s="6">
-        <f>VLOOKUP($A$1,[9]resultados_proyectados_proporci!$A$1:$AA$29,MATCH(E$2,[9]resultados_proyectados_proporci!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[1]resultados_proyectados_proporci!$A$1:$AA$29,MATCH(E$2,[1]resultados_proyectados_proporci!$A$1:$AA$1,0),FALSE)</f>
         <v>3.2077536649405401E-2</v>
       </c>
       <c r="F4" s="6">
-        <f>VLOOKUP($A$1,[9]resultados_proyectados_proporci!$A$1:$AA$29,MATCH(F$2,[9]resultados_proyectados_proporci!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[1]resultados_proyectados_proporci!$A$1:$AA$29,MATCH(F$2,[1]resultados_proyectados_proporci!$A$1:$AA$1,0),FALSE)</f>
         <v>0.13134470695638201</v>
       </c>
       <c r="G4" s="6">
-        <f>VLOOKUP($A$1,[9]resultados_proyectados_proporci!$A$1:$AA$29,MATCH(G$2,[9]resultados_proyectados_proporci!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[1]resultados_proyectados_proporci!$A$1:$AA$29,MATCH(G$2,[1]resultados_proyectados_proporci!$A$1:$AA$1,0),FALSE)</f>
         <v>8.6972550230132298E-2</v>
       </c>
       <c r="H4" s="6">
-        <f>VLOOKUP($A$1,[9]resultados_proyectados_proporci!$A$1:$AA$29,MATCH(H$2,[9]resultados_proyectados_proporci!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[1]resultados_proyectados_proporci!$A$1:$AA$29,MATCH(H$2,[1]resultados_proyectados_proporci!$A$1:$AA$1,0),FALSE)</f>
         <v>0.10683580604703299</v>
       </c>
       <c r="I4" s="6">
-        <f>VLOOKUP($A$1,[9]resultados_proyectados_proporci!$A$1:$AA$29,MATCH(I$2,[9]resultados_proyectados_proporci!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[1]resultados_proyectados_proporci!$A$1:$AA$29,MATCH(I$2,[1]resultados_proyectados_proporci!$A$1:$AA$1,0),FALSE)</f>
         <v>4.8912795031730599E-2</v>
       </c>
     </row>
@@ -19304,31 +20008,31 @@
         <v>2</v>
       </c>
       <c r="C5" s="4">
-        <f>VLOOKUP($A$1,[1]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[1]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[2]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[2]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="D5" s="4">
-        <f>VLOOKUP($A$1,[1]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[1]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[2]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[2]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="E5" s="4">
-        <f>VLOOKUP($A$1,[1]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[1]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[2]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[2]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="F5" s="4">
-        <f>VLOOKUP($A$1,[1]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[1]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[2]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[2]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>2</v>
       </c>
       <c r="G5" s="4">
-        <f>VLOOKUP($A$1,[1]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[1]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[2]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[2]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="H5" s="4">
-        <f>VLOOKUP($A$1,[1]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[1]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[2]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[2]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="I5" s="4">
-        <f>VLOOKUP($A$1,[1]resultados_integracion_partido_!$A$1:$AA$29,MATCH(I$2,[1]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[2]resultados_integracion_partido_!$A$1:$AA$29,MATCH(I$2,[2]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
     </row>
@@ -19337,31 +20041,31 @@
         <v>3</v>
       </c>
       <c r="C6" s="4">
-        <f>VLOOKUP($A$1,[2]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[2]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[3]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[3]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="D6" s="4">
-        <f>VLOOKUP($A$1,[2]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[2]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[3]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[3]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="E6" s="4">
-        <f>VLOOKUP($A$1,[2]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[2]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[3]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[3]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="F6" s="4">
-        <f>VLOOKUP($A$1,[2]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[2]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[3]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[3]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="G6" s="4">
-        <f>VLOOKUP($A$1,[2]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[2]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[3]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[3]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="H6" s="4">
-        <f>VLOOKUP($A$1,[2]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[2]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[3]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[3]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="I6" s="4">
-        <f>VLOOKUP($A$1,[2]resultados_integracion_partido_!$A$1:$AA$29,MATCH(I$2,[2]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[3]resultados_integracion_partido_!$A$1:$AA$29,MATCH(I$2,[3]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
     </row>
@@ -19370,31 +20074,31 @@
         <v>4</v>
       </c>
       <c r="C7" s="4">
-        <f>VLOOKUP($A$1,[3]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[3]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[4]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[4]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="D7" s="4">
-        <f>VLOOKUP($A$1,[3]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[3]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[4]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[4]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="E7" s="4">
-        <f>VLOOKUP($A$1,[3]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[3]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[4]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[4]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="F7" s="4">
-        <f>VLOOKUP($A$1,[3]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[3]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[4]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[4]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="G7" s="4">
-        <f>VLOOKUP($A$1,[3]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[3]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[4]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[4]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="H7" s="4">
-        <f>VLOOKUP($A$1,[3]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[3]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[4]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[4]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="I7" s="4">
-        <f>VLOOKUP($A$1,[3]resultados_integracion_partido_!$A$1:$AA$29,MATCH(I$2,[3]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[4]resultados_integracion_partido_!$A$1:$AA$29,MATCH(I$2,[4]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
     </row>
@@ -19403,31 +20107,31 @@
         <v>5</v>
       </c>
       <c r="C8" s="4">
-        <f>VLOOKUP($A$1,[4]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[4]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[5]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[5]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="D8" s="4">
-        <f>VLOOKUP($A$1,[4]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[4]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[5]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[5]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="E8" s="4">
-        <f>VLOOKUP($A$1,[4]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[4]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[5]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[5]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="F8" s="4">
-        <f>VLOOKUP($A$1,[4]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[4]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[5]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[5]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="G8" s="4">
-        <f>VLOOKUP($A$1,[4]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[4]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[5]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[5]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="H8" s="4">
-        <f>VLOOKUP($A$1,[4]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[4]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[5]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[5]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="I8" s="4">
-        <f>VLOOKUP($A$1,[4]resultados_integracion_partido_!$A$1:$AA$29,MATCH(I$2,[4]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[5]resultados_integracion_partido_!$A$1:$AA$29,MATCH(I$2,[5]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
     </row>
@@ -19436,31 +20140,31 @@
         <v>31</v>
       </c>
       <c r="C9" s="4">
-        <f>VLOOKUP($A$1,[5]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[5]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[6]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[6]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="D9" s="4">
-        <f>VLOOKUP($A$1,[5]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[5]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[6]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[6]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="E9" s="4">
-        <f>VLOOKUP($A$1,[5]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[5]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[6]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[6]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="F9" s="4">
-        <f>VLOOKUP($A$1,[5]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[5]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[6]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[6]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="G9" s="4">
-        <f>VLOOKUP($A$1,[5]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[5]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[6]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[6]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="H9" s="4">
-        <f>VLOOKUP($A$1,[5]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[5]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[6]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[6]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="I9" s="4">
-        <f>VLOOKUP($A$1,[5]resultados_integracion_partido_!$A$1:$AA$29,MATCH(I$2,[5]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[6]resultados_integracion_partido_!$A$1:$AA$29,MATCH(I$2,[6]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
     </row>
@@ -19469,31 +20173,31 @@
         <v>32</v>
       </c>
       <c r="C10" s="4">
-        <f>VLOOKUP($A$1,[6]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[6]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[7]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[7]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="D10" s="4">
-        <f>VLOOKUP($A$1,[6]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[6]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[7]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[7]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="E10" s="4">
-        <f>VLOOKUP($A$1,[6]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[6]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[7]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[7]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="F10" s="4">
-        <f>VLOOKUP($A$1,[6]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[6]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[7]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[7]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="G10" s="4">
-        <f>VLOOKUP($A$1,[6]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[6]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[7]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[7]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="H10" s="4">
-        <f>VLOOKUP($A$1,[6]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[6]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[7]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[7]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="I10" s="4">
-        <f>VLOOKUP($A$1,[6]resultados_integracion_partido_!$A$1:$AA$29,MATCH(I$2,[6]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[7]resultados_integracion_partido_!$A$1:$AA$29,MATCH(I$2,[7]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
     </row>
@@ -19502,31 +20206,31 @@
         <v>33</v>
       </c>
       <c r="C11" s="4">
-        <f>VLOOKUP($A$1,[7]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[7]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[8]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[8]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="D11" s="4">
-        <f>VLOOKUP($A$1,[7]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[7]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[8]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[8]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="E11" s="4">
-        <f>VLOOKUP($A$1,[7]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[7]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[8]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[8]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="F11" s="4">
-        <f>VLOOKUP($A$1,[7]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[7]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[8]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[8]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="G11" s="4">
-        <f>VLOOKUP($A$1,[7]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[7]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[8]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[8]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="H11" s="4">
-        <f>VLOOKUP($A$1,[7]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[7]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[8]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[8]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="I11" s="4">
-        <f>VLOOKUP($A$1,[7]resultados_integracion_partido_!$A$1:$AA$29,MATCH(I$2,[7]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[8]resultados_integracion_partido_!$A$1:$AA$29,MATCH(I$2,[8]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
     </row>
@@ -19535,31 +20239,31 @@
         <v>34</v>
       </c>
       <c r="C12" s="4">
-        <f>VLOOKUP($A$1,[8]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[8]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[9]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[9]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="D12" s="4">
-        <f>VLOOKUP($A$1,[8]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[8]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[9]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[9]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="E12" s="4">
-        <f>VLOOKUP($A$1,[8]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[8]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[9]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[9]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="F12" s="4">
-        <f>VLOOKUP($A$1,[8]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[8]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[9]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[9]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="G12" s="4">
-        <f>VLOOKUP($A$1,[8]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[8]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[9]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[9]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="H12" s="4">
-        <f>VLOOKUP($A$1,[8]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[8]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[9]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[9]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="I12" s="4">
-        <f>VLOOKUP($A$1,[8]resultados_integracion_partido_!$A$1:$AA$29,MATCH(I$2,[8]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[9]resultados_integracion_partido_!$A$1:$AA$29,MATCH(I$2,[9]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
     </row>
@@ -19747,27 +20451,27 @@
         <v>29</v>
       </c>
       <c r="C4" s="6">
-        <f>VLOOKUP($A$1,[9]resultados_proyectados_proporci!$A$1:$AA$29,MATCH(C$2,[9]resultados_proyectados_proporci!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[1]resultados_proyectados_proporci!$A$1:$AA$29,MATCH(C$2,[1]resultados_proyectados_proporci!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="D4" s="6">
-        <f>VLOOKUP($A$1,[9]resultados_proyectados_proporci!$A$1:$AA$29,MATCH(D$2,[9]resultados_proyectados_proporci!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[1]resultados_proyectados_proporci!$A$1:$AA$29,MATCH(D$2,[1]resultados_proyectados_proporci!$A$1:$AA$1,0),FALSE)</f>
         <v>5.6615076912916902E-2</v>
       </c>
       <c r="E4" s="6">
-        <f>VLOOKUP($A$1,[9]resultados_proyectados_proporci!$A$1:$AA$29,MATCH(E$2,[9]resultados_proyectados_proporci!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[1]resultados_proyectados_proporci!$A$1:$AA$29,MATCH(E$2,[1]resultados_proyectados_proporci!$A$1:$AA$1,0),FALSE)</f>
         <v>8.2483855599005604E-2</v>
       </c>
       <c r="F4" s="6">
-        <f>VLOOKUP($A$1,[9]resultados_proyectados_proporci!$A$1:$AA$29,MATCH(F$2,[9]resultados_proyectados_proporci!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[1]resultados_proyectados_proporci!$A$1:$AA$29,MATCH(F$2,[1]resultados_proyectados_proporci!$A$1:$AA$1,0),FALSE)</f>
         <v>0.15242956135343999</v>
       </c>
       <c r="G4" s="6">
-        <f>VLOOKUP($A$1,[9]resultados_proyectados_proporci!$A$1:$AA$29,MATCH(G$2,[9]resultados_proyectados_proporci!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[1]resultados_proyectados_proporci!$A$1:$AA$29,MATCH(G$2,[1]resultados_proyectados_proporci!$A$1:$AA$1,0),FALSE)</f>
         <v>0.153957913704697</v>
       </c>
       <c r="H4" s="6">
-        <f>VLOOKUP($A$1,[9]resultados_proyectados_proporci!$A$1:$AA$29,MATCH(H$2,[9]resultados_proyectados_proporci!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[1]resultados_proyectados_proporci!$A$1:$AA$29,MATCH(H$2,[1]resultados_proyectados_proporci!$A$1:$AA$1,0),FALSE)</f>
         <v>9.1977093583278602E-2</v>
       </c>
     </row>
@@ -19776,27 +20480,27 @@
         <v>2</v>
       </c>
       <c r="C5" s="4">
-        <f>VLOOKUP($A$1,[1]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[1]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[2]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[2]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="D5" s="4">
-        <f>VLOOKUP($A$1,[1]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[1]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[2]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[2]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="E5" s="4">
-        <f>VLOOKUP($A$1,[1]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[1]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[2]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[2]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="F5" s="4">
-        <f>VLOOKUP($A$1,[1]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[1]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[2]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[2]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="G5" s="4">
-        <f>VLOOKUP($A$1,[1]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[1]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[2]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[2]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="H5" s="4">
-        <f>VLOOKUP($A$1,[1]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[1]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[2]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[2]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
     </row>
@@ -19805,27 +20509,27 @@
         <v>3</v>
       </c>
       <c r="C6" s="4">
-        <f>VLOOKUP($A$1,[2]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[2]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[3]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[3]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="D6" s="4">
-        <f>VLOOKUP($A$1,[2]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[2]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[3]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[3]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="E6" s="4">
-        <f>VLOOKUP($A$1,[2]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[2]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[3]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[3]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="F6" s="4">
-        <f>VLOOKUP($A$1,[2]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[2]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[3]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[3]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="G6" s="4">
-        <f>VLOOKUP($A$1,[2]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[2]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[3]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[3]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="H6" s="4">
-        <f>VLOOKUP($A$1,[2]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[2]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[3]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[3]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
     </row>
@@ -19834,27 +20538,27 @@
         <v>4</v>
       </c>
       <c r="C7" s="4">
-        <f>VLOOKUP($A$1,[3]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[3]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[4]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[4]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="D7" s="4">
-        <f>VLOOKUP($A$1,[3]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[3]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[4]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[4]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="E7" s="4">
-        <f>VLOOKUP($A$1,[3]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[3]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[4]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[4]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="F7" s="4">
-        <f>VLOOKUP($A$1,[3]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[3]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[4]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[4]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="G7" s="4">
-        <f>VLOOKUP($A$1,[3]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[3]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[4]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[4]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="H7" s="4">
-        <f>VLOOKUP($A$1,[3]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[3]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[4]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[4]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
     </row>
@@ -19863,27 +20567,27 @@
         <v>5</v>
       </c>
       <c r="C8" s="4">
-        <f>VLOOKUP($A$1,[4]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[4]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[5]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[5]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="D8" s="4">
-        <f>VLOOKUP($A$1,[4]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[4]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[5]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[5]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="E8" s="4">
-        <f>VLOOKUP($A$1,[4]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[4]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[5]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[5]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="F8" s="4">
-        <f>VLOOKUP($A$1,[4]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[4]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[5]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[5]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="G8" s="4">
-        <f>VLOOKUP($A$1,[4]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[4]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[5]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[5]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="H8" s="4">
-        <f>VLOOKUP($A$1,[4]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[4]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[5]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[5]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
     </row>
@@ -19892,27 +20596,27 @@
         <v>31</v>
       </c>
       <c r="C9" s="4">
-        <f>VLOOKUP($A$1,[5]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[5]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[6]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[6]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="D9" s="4">
-        <f>VLOOKUP($A$1,[5]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[5]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[6]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[6]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="E9" s="4">
-        <f>VLOOKUP($A$1,[5]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[5]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[6]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[6]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="F9" s="4">
-        <f>VLOOKUP($A$1,[5]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[5]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[6]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[6]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="G9" s="4">
-        <f>VLOOKUP($A$1,[5]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[5]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[6]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[6]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="H9" s="4">
-        <f>VLOOKUP($A$1,[5]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[5]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[6]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[6]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
     </row>
@@ -19921,27 +20625,27 @@
         <v>32</v>
       </c>
       <c r="C10" s="4">
-        <f>VLOOKUP($A$1,[6]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[6]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[7]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[7]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="D10" s="4">
-        <f>VLOOKUP($A$1,[6]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[6]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[7]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[7]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="E10" s="4">
-        <f>VLOOKUP($A$1,[6]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[6]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[7]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[7]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="F10" s="4">
-        <f>VLOOKUP($A$1,[6]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[6]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[7]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[7]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="G10" s="4">
-        <f>VLOOKUP($A$1,[6]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[6]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[7]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[7]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="H10" s="4">
-        <f>VLOOKUP($A$1,[6]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[6]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[7]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[7]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
     </row>
@@ -19950,27 +20654,27 @@
         <v>33</v>
       </c>
       <c r="C11" s="4">
-        <f>VLOOKUP($A$1,[7]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[7]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[8]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[8]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="D11" s="4">
-        <f>VLOOKUP($A$1,[7]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[7]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[8]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[8]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="E11" s="4">
-        <f>VLOOKUP($A$1,[7]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[7]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[8]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[8]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="F11" s="4">
-        <f>VLOOKUP($A$1,[7]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[7]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[8]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[8]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="G11" s="4">
-        <f>VLOOKUP($A$1,[7]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[7]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[8]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[8]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="H11" s="4">
-        <f>VLOOKUP($A$1,[7]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[7]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[8]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[8]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
     </row>
@@ -19979,27 +20683,27 @@
         <v>34</v>
       </c>
       <c r="C12" s="4">
-        <f>VLOOKUP($A$1,[8]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[8]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[9]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[9]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="D12" s="4">
-        <f>VLOOKUP($A$1,[8]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[8]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[9]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[9]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="E12" s="4">
-        <f>VLOOKUP($A$1,[8]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[8]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[9]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[9]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="F12" s="4">
-        <f>VLOOKUP($A$1,[8]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[8]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[9]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[9]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
       <c r="G12" s="4">
-        <f>VLOOKUP($A$1,[8]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[8]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[9]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[9]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
       <c r="H12" s="4">
-        <f>VLOOKUP($A$1,[8]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[8]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <f>VLOOKUP($A$1,[9]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[9]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
     </row>

--- a/Resultados/Entregable/Reporte_Sen_SinInc_vf_2.xlsx
+++ b/Resultados/Entregable/Reporte_Sen_SinInc_vf_2.xlsx
@@ -8,22 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ivan\Desktop\Ivan\Laboral\EstrategiaSur\GitProjects\Proyeccion-electoral-congreso\Resultados\Entregable\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4ADB33C8-D4CB-4DC2-9528-DBB4C5BA16A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FCF944E1-A127-4E13-A213-3E2FC7569490}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{85AAF8D7-1A96-46DE-A921-B4694576F524}"/>
+    <workbookView xWindow="-28920" yWindow="1665" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{85AAF8D7-1A96-46DE-A921-B4694576F524}"/>
   </bookViews>
   <sheets>
     <sheet name="Resumen de Pactos" sheetId="34" r:id="rId1"/>
-    <sheet name="C15" sheetId="1" r:id="rId2"/>
-    <sheet name="C1" sheetId="16" r:id="rId3"/>
-    <sheet name="C3" sheetId="17" r:id="rId4"/>
-    <sheet name="C5" sheetId="18" r:id="rId5"/>
-    <sheet name="C7" sheetId="20" r:id="rId6"/>
-    <sheet name="C9" sheetId="19" r:id="rId7"/>
-    <sheet name="C11" sheetId="21" r:id="rId8"/>
+    <sheet name="Nacional" sheetId="35" r:id="rId2"/>
+    <sheet name="C15" sheetId="1" r:id="rId3"/>
+    <sheet name="C1" sheetId="16" r:id="rId4"/>
+    <sheet name="C3" sheetId="17" r:id="rId5"/>
+    <sheet name="C5" sheetId="18" r:id="rId6"/>
+    <sheet name="C7" sheetId="20" r:id="rId7"/>
+    <sheet name="C9" sheetId="19" r:id="rId8"/>
+    <sheet name="C11" sheetId="21" r:id="rId9"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId9"/>
     <externalReference r:id="rId10"/>
     <externalReference r:id="rId11"/>
     <externalReference r:id="rId12"/>
@@ -32,8 +32,12 @@
     <externalReference r:id="rId15"/>
     <externalReference r:id="rId16"/>
     <externalReference r:id="rId17"/>
+    <externalReference r:id="rId18"/>
+    <externalReference r:id="rId19"/>
+    <externalReference r:id="rId20"/>
   </externalReferences>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -54,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="600" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="641" uniqueCount="67">
   <si>
     <t>Esc</t>
   </si>
@@ -451,7 +455,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="17">
+  <borders count="18">
     <border>
       <left/>
       <right/>
@@ -635,12 +639,25 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3A3A3A"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3A3A3A"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3A3A3A"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -684,6 +701,7 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="top" wrapText="1"/>
     </xf>
@@ -711,634 +729,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Porcentaje" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="142">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF0070C0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF7030A0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFABAB"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF7030A0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF0070C0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF0070C0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF7030A0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF7030A0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF0070C0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFABAB"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF0070C0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF7030A0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF0070C0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF7030A0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFABAB"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF7030A0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF0070C0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF7030A0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF0070C0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFABAB"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF7030A0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF0070C0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="22">
     <dxf>
       <fill>
         <patternFill>
@@ -1398,286 +795,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFABAB"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF7030A0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF0070C0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
           <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF7030A0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF0070C0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFABAB"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF7030A0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF0070C0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF0070C0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF7030A0"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1705,14 +823,14 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
+          <bgColor theme="5" tint="-0.499984740745262"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="5" tint="-0.499984740745262"/>
+          <bgColor theme="2" tint="-0.24994659260841701"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1727,6 +845,48 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF7030A0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2209,14 +1369,69 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
+      <xdr:colOff>152400</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>101600</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>314324</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>114386</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Imagen 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9FB0EE21-CC0C-436F-846D-4F023AA30691}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1504950" y="2635250"/>
+          <a:ext cx="4448174" cy="555711"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
       <xdr:colOff>168275</xdr:colOff>
-      <xdr:row>23</xdr:row>
+      <xdr:row>25</xdr:row>
       <xdr:rowOff>104775</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
       <xdr:colOff>219075</xdr:colOff>
-      <xdr:row>26</xdr:row>
+      <xdr:row>28</xdr:row>
       <xdr:rowOff>67262</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2259,19 +1474,19 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>263526</xdr:colOff>
-      <xdr:row>23</xdr:row>
+      <xdr:row>25</xdr:row>
       <xdr:rowOff>152401</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>466726</xdr:colOff>
-      <xdr:row>26</xdr:row>
+      <xdr:row>28</xdr:row>
       <xdr:rowOff>19537</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2314,19 +1529,19 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>295276</xdr:colOff>
-      <xdr:row>23</xdr:row>
+      <xdr:row>25</xdr:row>
       <xdr:rowOff>133350</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>35355</xdr:colOff>
-      <xdr:row>26</xdr:row>
+      <xdr:row>28</xdr:row>
       <xdr:rowOff>6350</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2369,19 +1584,19 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>247650</xdr:colOff>
-      <xdr:row>24</xdr:row>
+      <xdr:row>26</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>368300</xdr:colOff>
-      <xdr:row>26</xdr:row>
+      <xdr:row>28</xdr:row>
       <xdr:rowOff>111448</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2424,19 +1639,19 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>161926</xdr:colOff>
-      <xdr:row>23</xdr:row>
+      <xdr:row>25</xdr:row>
       <xdr:rowOff>120651</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>1</xdr:colOff>
-      <xdr:row>26</xdr:row>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>88901</xdr:colOff>
+      <xdr:row>28</xdr:row>
       <xdr:rowOff>164325</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2479,19 +1694,19 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>257175</xdr:colOff>
-      <xdr:row>23</xdr:row>
+      <xdr:row>25</xdr:row>
       <xdr:rowOff>95250</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>439944</xdr:colOff>
-      <xdr:row>26</xdr:row>
+      <xdr:colOff>370094</xdr:colOff>
+      <xdr:row>28</xdr:row>
       <xdr:rowOff>19050</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2534,19 +1749,19 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing9.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>209550</xdr:colOff>
-      <xdr:row>23</xdr:row>
+      <xdr:row>25</xdr:row>
       <xdr:rowOff>152400</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>158750</xdr:colOff>
-      <xdr:row>26</xdr:row>
+      <xdr:row>28</xdr:row>
       <xdr:rowOff>59279</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2599,6 +1814,1383 @@
       <sheetName val="resultados_proyectados_proporci"/>
     </sheetNames>
     <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1">
+        <row r="1">
+          <cell r="A1" t="str">
+            <v>Circunscripcion</v>
+          </cell>
+          <cell r="B1" t="str">
+            <v>AH</v>
+          </cell>
+          <cell r="C1" t="str">
+            <v>AMA</v>
+          </cell>
+          <cell r="D1" t="str">
+            <v>DEM</v>
+          </cell>
+          <cell r="E1" t="str">
+            <v>EVO</v>
+          </cell>
+          <cell r="F1" t="str">
+            <v>FA</v>
+          </cell>
+          <cell r="G1" t="str">
+            <v>FREVS</v>
+          </cell>
+          <cell r="H1" t="str">
+            <v>IGU</v>
+          </cell>
+          <cell r="I1" t="str">
+            <v>IND</v>
+          </cell>
+          <cell r="J1" t="str">
+            <v>PAVP</v>
+          </cell>
+          <cell r="K1" t="str">
+            <v>PCCH</v>
+          </cell>
+          <cell r="L1" t="str">
+            <v>PDC</v>
+          </cell>
+          <cell r="M1" t="str">
+            <v>PDG</v>
+          </cell>
+          <cell r="N1" t="str">
+            <v>PH</v>
+          </cell>
+          <cell r="O1" t="str">
+            <v>PL</v>
+          </cell>
+          <cell r="P1" t="str">
+            <v>POP</v>
+          </cell>
+          <cell r="Q1" t="str">
+            <v>PPD</v>
+          </cell>
+          <cell r="R1" t="str">
+            <v>PR</v>
+          </cell>
+          <cell r="S1" t="str">
+            <v>PS</v>
+          </cell>
+          <cell r="T1" t="str">
+            <v>PSC</v>
+          </cell>
+          <cell r="U1" t="str">
+            <v>PTR</v>
+          </cell>
+          <cell r="V1" t="str">
+            <v>REP</v>
+          </cell>
+          <cell r="W1" t="str">
+            <v>RN</v>
+          </cell>
+          <cell r="X1" t="str">
+            <v>UDI</v>
+          </cell>
+          <cell r="Y1" t="str">
+            <v>Votos Blancos</v>
+          </cell>
+          <cell r="Z1" t="str">
+            <v>Votos Nulos</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="A2">
+            <v>1</v>
+          </cell>
+          <cell r="B2">
+            <v>2.94921215201552E-2</v>
+          </cell>
+          <cell r="C2">
+            <v>0</v>
+          </cell>
+          <cell r="D2">
+            <v>3.8370273754083598E-2</v>
+          </cell>
+          <cell r="E2">
+            <v>7.7003860909288504E-3</v>
+          </cell>
+          <cell r="F2">
+            <v>3.69628738310364E-2</v>
+          </cell>
+          <cell r="G2">
+            <v>3.5904517253661603E-2</v>
+          </cell>
+          <cell r="H2">
+            <v>3.7122426783395401E-3</v>
+          </cell>
+          <cell r="I2">
+            <v>5.6132701789408403E-4</v>
+          </cell>
+          <cell r="J2">
+            <v>0</v>
+          </cell>
+          <cell r="K2">
+            <v>2.64487084885912E-2</v>
+          </cell>
+          <cell r="L2">
+            <v>5.6262317300813103E-2</v>
+          </cell>
+          <cell r="M2">
+            <v>5.7424774525142802E-2</v>
+          </cell>
+          <cell r="N2">
+            <v>5.8452853463370601E-3</v>
+          </cell>
+          <cell r="O2">
+            <v>1.8447246997155602E-2</v>
+          </cell>
+          <cell r="P2">
+            <v>9.9735904143035594E-3</v>
+          </cell>
+          <cell r="Q2">
+            <v>3.4214412632511397E-2</v>
+          </cell>
+          <cell r="R2">
+            <v>4.3096647244751797E-2</v>
+          </cell>
+          <cell r="S2">
+            <v>2.6841637401117099E-2</v>
+          </cell>
+          <cell r="T2">
+            <v>3.7715052035014497E-2</v>
+          </cell>
+          <cell r="U2">
+            <v>0</v>
+          </cell>
+          <cell r="V2">
+            <v>0.121981463961274</v>
+          </cell>
+          <cell r="W2">
+            <v>9.1851470829876006E-2</v>
+          </cell>
+          <cell r="X2">
+            <v>5.8876060015043502E-2</v>
+          </cell>
+          <cell r="Y2">
+            <v>0.108846411742552</v>
+          </cell>
+          <cell r="Z2">
+            <v>0.149471178919414</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="A3">
+            <v>2</v>
+          </cell>
+          <cell r="B3">
+            <v>1.19339124020918E-2</v>
+          </cell>
+          <cell r="C3">
+            <v>0</v>
+          </cell>
+          <cell r="D3">
+            <v>3.4290097581162103E-2</v>
+          </cell>
+          <cell r="E3">
+            <v>3.6409073268422097E-2</v>
+          </cell>
+          <cell r="F3">
+            <v>4.0998132428207802E-2</v>
+          </cell>
+          <cell r="G3">
+            <v>5.1359296369277399E-2</v>
+          </cell>
+          <cell r="H3">
+            <v>2.37788417624217E-3</v>
+          </cell>
+          <cell r="I3">
+            <v>0</v>
+          </cell>
+          <cell r="J3">
+            <v>0</v>
+          </cell>
+          <cell r="K3">
+            <v>5.2003619358421502E-2</v>
+          </cell>
+          <cell r="L3">
+            <v>4.3976920157553598E-2</v>
+          </cell>
+          <cell r="M3">
+            <v>5.6756707498804598E-2</v>
+          </cell>
+          <cell r="N3">
+            <v>2.2009901775586899E-3</v>
+          </cell>
+          <cell r="O3">
+            <v>1.25712668397726E-2</v>
+          </cell>
+          <cell r="P3">
+            <v>1.3406420930526699E-3</v>
+          </cell>
+          <cell r="Q3">
+            <v>2.0125712668397699E-2</v>
+          </cell>
+          <cell r="R3">
+            <v>4.6313529067436202E-2</v>
+          </cell>
+          <cell r="S3">
+            <v>3.87097673361479E-2</v>
+          </cell>
+          <cell r="T3">
+            <v>3.8379029162851797E-2</v>
+          </cell>
+          <cell r="U3">
+            <v>0</v>
+          </cell>
+          <cell r="V3">
+            <v>0.101381702942444</v>
+          </cell>
+          <cell r="W3">
+            <v>6.1567688220574998E-2</v>
+          </cell>
+          <cell r="X3">
+            <v>4.0977226773817897E-2</v>
+          </cell>
+          <cell r="Y3">
+            <v>0.12466202525403</v>
+          </cell>
+          <cell r="Z3">
+            <v>0.18166477622373101</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="A4">
+            <v>3</v>
+          </cell>
+          <cell r="B4">
+            <v>0</v>
+          </cell>
+          <cell r="C4">
+            <v>2.2323885276993902E-2</v>
+          </cell>
+          <cell r="D4">
+            <v>1.09616450830563E-2</v>
+          </cell>
+          <cell r="E4">
+            <v>0</v>
+          </cell>
+          <cell r="F4">
+            <v>3.9417319956760503E-2</v>
+          </cell>
+          <cell r="G4">
+            <v>8.7931659300052895E-2</v>
+          </cell>
+          <cell r="H4">
+            <v>1.52353479068733E-2</v>
+          </cell>
+          <cell r="I4">
+            <v>6.86586981278373E-4</v>
+          </cell>
+          <cell r="J4">
+            <v>0</v>
+          </cell>
+          <cell r="K4">
+            <v>7.5657755490372805E-2</v>
+          </cell>
+          <cell r="L4">
+            <v>1.94526094951365E-2</v>
+          </cell>
+          <cell r="M4">
+            <v>2.72518246178085E-2</v>
+          </cell>
+          <cell r="N4">
+            <v>6.0722509762785003E-3</v>
+          </cell>
+          <cell r="O4">
+            <v>1.4518475384566101E-2</v>
+          </cell>
+          <cell r="P4">
+            <v>1.3000068486621099E-2</v>
+          </cell>
+          <cell r="Q4">
+            <v>3.6495453555229901E-2</v>
+          </cell>
+          <cell r="R4">
+            <v>4.8074510690623899E-2</v>
+          </cell>
+          <cell r="S4">
+            <v>8.2266542358286801E-2</v>
+          </cell>
+          <cell r="T4">
+            <v>2.6145025754755202E-2</v>
+          </cell>
+          <cell r="U4">
+            <v>0</v>
+          </cell>
+          <cell r="V4">
+            <v>7.9563557821464598E-2</v>
+          </cell>
+          <cell r="W4">
+            <v>0.107729110978267</v>
+          </cell>
+          <cell r="X4">
+            <v>5.4669875557400202E-2</v>
+          </cell>
+          <cell r="Y4">
+            <v>0.100040369249575</v>
+          </cell>
+          <cell r="Z4">
+            <v>0.13250612507859599</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="A5">
+            <v>4</v>
+          </cell>
+          <cell r="B5">
+            <v>8.8372020524635497E-3</v>
+          </cell>
+          <cell r="C5">
+            <v>1.30034388339584E-2</v>
+          </cell>
+          <cell r="D5">
+            <v>2.93165605128635E-2</v>
+          </cell>
+          <cell r="E5">
+            <v>1.2391455540471399E-2</v>
+          </cell>
+          <cell r="F5">
+            <v>4.8881840833870802E-2</v>
+          </cell>
+          <cell r="G5">
+            <v>2.2119726051189802E-2</v>
+          </cell>
+          <cell r="H5">
+            <v>1.85265045548034E-3</v>
+          </cell>
+          <cell r="I5">
+            <v>6.85094699682837E-3</v>
+          </cell>
+          <cell r="J5">
+            <v>0</v>
+          </cell>
+          <cell r="K5">
+            <v>7.4657879442631303E-2</v>
+          </cell>
+          <cell r="L5">
+            <v>6.0643128010278602E-2</v>
+          </cell>
+          <cell r="M5">
+            <v>4.1295697412301498E-2</v>
+          </cell>
+          <cell r="N5">
+            <v>1.85265045548034E-3</v>
+          </cell>
+          <cell r="O5">
+            <v>1.21290709507229E-2</v>
+          </cell>
+          <cell r="P5">
+            <v>1.85265045548034E-3</v>
+          </cell>
+          <cell r="Q5">
+            <v>2.9622366597662299E-2</v>
+          </cell>
+          <cell r="R5">
+            <v>3.3264947571328099E-2</v>
+          </cell>
+          <cell r="S5">
+            <v>5.9224692505301497E-2</v>
+          </cell>
+          <cell r="T5">
+            <v>2.94965555991832E-2</v>
+          </cell>
+          <cell r="U5">
+            <v>0</v>
+          </cell>
+          <cell r="V5">
+            <v>8.8958767393648802E-2</v>
+          </cell>
+          <cell r="W5">
+            <v>9.1046710394957403E-2</v>
+          </cell>
+          <cell r="X5">
+            <v>6.1780622731041297E-2</v>
+          </cell>
+          <cell r="Y5">
+            <v>0.123378281384648</v>
+          </cell>
+          <cell r="Z5">
+            <v>0.14754215781820701</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="A6">
+            <v>5</v>
+          </cell>
+          <cell r="B6">
+            <v>0</v>
+          </cell>
+          <cell r="C6">
+            <v>6.4869028679831499E-3</v>
+          </cell>
+          <cell r="D6">
+            <v>1.04419722326936E-2</v>
+          </cell>
+          <cell r="E6">
+            <v>1.0727601254744401E-2</v>
+          </cell>
+          <cell r="F6">
+            <v>7.5344175533315502E-2</v>
+          </cell>
+          <cell r="G6">
+            <v>1.99833204552331E-2</v>
+          </cell>
+          <cell r="H6">
+            <v>6.0856833510710903E-3</v>
+          </cell>
+          <cell r="I6">
+            <v>7.8443845483029892E-3</v>
+          </cell>
+          <cell r="J6">
+            <v>0</v>
+          </cell>
+          <cell r="K6">
+            <v>6.1068228740051703E-2</v>
+          </cell>
+          <cell r="L6">
+            <v>4.6696923507655301E-2</v>
+          </cell>
+          <cell r="M6">
+            <v>2.4516491059365299E-2</v>
+          </cell>
+          <cell r="N6">
+            <v>6.0856833510710903E-3</v>
+          </cell>
+          <cell r="O6">
+            <v>1.47460445587225E-2</v>
+          </cell>
+          <cell r="P6">
+            <v>1.6016498646386199E-2</v>
+          </cell>
+          <cell r="Q6">
+            <v>3.3914876005763699E-2</v>
+          </cell>
+          <cell r="R6">
+            <v>3.6716123133481202E-2</v>
+          </cell>
+          <cell r="S6">
+            <v>4.1651405845219397E-2</v>
+          </cell>
+          <cell r="T6">
+            <v>2.4874271162507101E-2</v>
+          </cell>
+          <cell r="U6">
+            <v>0</v>
+          </cell>
+          <cell r="V6">
+            <v>0.1371598002144</v>
+          </cell>
+          <cell r="W6">
+            <v>0.10626961654006201</v>
+          </cell>
+          <cell r="X6">
+            <v>6.4773075180236298E-2</v>
+          </cell>
+          <cell r="Y6">
+            <v>9.6271856942704306E-2</v>
+          </cell>
+          <cell r="Z6">
+            <v>0.152325064869028</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="A7">
+            <v>6</v>
+          </cell>
+          <cell r="B7">
+            <v>0</v>
+          </cell>
+          <cell r="C7">
+            <v>4.7263351114183901E-3</v>
+          </cell>
+          <cell r="D7">
+            <v>2.6360823979780498E-2</v>
+          </cell>
+          <cell r="E7">
+            <v>9.9077987891215205E-3</v>
+          </cell>
+          <cell r="F7">
+            <v>5.5805300497302701E-2</v>
+          </cell>
+          <cell r="G7">
+            <v>3.3050031450937302E-2</v>
+          </cell>
+          <cell r="H7">
+            <v>0</v>
+          </cell>
+          <cell r="I7">
+            <v>9.7471242621549794E-3</v>
+          </cell>
+          <cell r="J7">
+            <v>1.88666208987711E-2</v>
+          </cell>
+          <cell r="K7">
+            <v>4.45717629705265E-2</v>
+          </cell>
+          <cell r="L7">
+            <v>5.4940718518863702E-2</v>
+          </cell>
+          <cell r="M7">
+            <v>2.3737400786957401E-2</v>
+          </cell>
+          <cell r="N7">
+            <v>0</v>
+          </cell>
+          <cell r="O7">
+            <v>5.3864222373545302E-3</v>
+          </cell>
+          <cell r="P7">
+            <v>0</v>
+          </cell>
+          <cell r="Q7">
+            <v>4.0499023084964801E-2</v>
+          </cell>
+          <cell r="R7">
+            <v>6.3749067658814398E-2</v>
+          </cell>
+          <cell r="S7">
+            <v>7.4840710798139698E-2</v>
+          </cell>
+          <cell r="T7">
+            <v>1.3509644065348299E-2</v>
+          </cell>
+          <cell r="U7">
+            <v>0</v>
+          </cell>
+          <cell r="V7">
+            <v>0.119366798614535</v>
+          </cell>
+          <cell r="W7">
+            <v>0.10256552935532801</v>
+          </cell>
+          <cell r="X7">
+            <v>0.102845608473042</v>
+          </cell>
+          <cell r="Y7">
+            <v>8.2573491207069097E-2</v>
+          </cell>
+          <cell r="Z7">
+            <v>0.112949787239567</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="A8">
+            <v>7</v>
+          </cell>
+          <cell r="B8">
+            <v>4.1725406165982401E-3</v>
+          </cell>
+          <cell r="C8">
+            <v>9.3335749926337207E-3</v>
+          </cell>
+          <cell r="D8">
+            <v>2.8624667847333099E-2</v>
+          </cell>
+          <cell r="E8">
+            <v>3.2152027618441402E-2</v>
+          </cell>
+          <cell r="F8">
+            <v>4.3984466997937802E-2</v>
+          </cell>
+          <cell r="G8">
+            <v>2.1941509789160499E-2</v>
+          </cell>
+          <cell r="H8">
+            <v>0</v>
+          </cell>
+          <cell r="I8">
+            <v>5.0032960101678301E-3</v>
+          </cell>
+          <cell r="J8">
+            <v>5.0686594898803096E-3</v>
+          </cell>
+          <cell r="K8">
+            <v>3.9371702314506297E-2</v>
+          </cell>
+          <cell r="L8">
+            <v>6.1016292826739503E-2</v>
+          </cell>
+          <cell r="M8">
+            <v>1.77747426029469E-2</v>
+          </cell>
+          <cell r="N8">
+            <v>0</v>
+          </cell>
+          <cell r="O8">
+            <v>8.1075458116546103E-4</v>
+          </cell>
+          <cell r="P8">
+            <v>0</v>
+          </cell>
+          <cell r="Q8">
+            <v>4.0684951533082901E-2</v>
+          </cell>
+          <cell r="R8">
+            <v>7.4653960171165698E-2</v>
+          </cell>
+          <cell r="S8">
+            <v>4.5000590745644699E-2</v>
+          </cell>
+          <cell r="T8">
+            <v>2.46896626522768E-2</v>
+          </cell>
+          <cell r="U8">
+            <v>0</v>
+          </cell>
+          <cell r="V8">
+            <v>9.6292983446956498E-2</v>
+          </cell>
+          <cell r="W8">
+            <v>0.140323225500087</v>
+          </cell>
+          <cell r="X8">
+            <v>0.121224717787506</v>
+          </cell>
+          <cell r="Y8">
+            <v>8.2100242009830099E-2</v>
+          </cell>
+          <cell r="Z8">
+            <v>0.105775430465938</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="A9">
+            <v>8</v>
+          </cell>
+          <cell r="B9">
+            <v>0</v>
+          </cell>
+          <cell r="C9">
+            <v>9.0700278594555601E-3</v>
+          </cell>
+          <cell r="D9">
+            <v>4.2950330175467302E-2</v>
+          </cell>
+          <cell r="E9">
+            <v>1.84792218255839E-2</v>
+          </cell>
+          <cell r="F9">
+            <v>4.3808763337555803E-2</v>
+          </cell>
+          <cell r="G9">
+            <v>3.2906604546727697E-2</v>
+          </cell>
+          <cell r="H9">
+            <v>2.0465086926803499E-2</v>
+          </cell>
+          <cell r="I9">
+            <v>8.0951774440995404E-3</v>
+          </cell>
+          <cell r="J9">
+            <v>0</v>
+          </cell>
+          <cell r="K9">
+            <v>4.8370216086559101E-2</v>
+          </cell>
+          <cell r="L9">
+            <v>6.4069831909623301E-2</v>
+          </cell>
+          <cell r="M9">
+            <v>3.3127480350265998E-2</v>
+          </cell>
+          <cell r="N9">
+            <v>5.2503028577553996E-4</v>
+          </cell>
+          <cell r="O9">
+            <v>9.4156776002830896E-3</v>
+          </cell>
+          <cell r="P9">
+            <v>5.2503028577553996E-4</v>
+          </cell>
+          <cell r="Q9">
+            <v>2.6173998840438001E-2</v>
+          </cell>
+          <cell r="R9">
+            <v>5.3375293492505999E-2</v>
+          </cell>
+          <cell r="S9">
+            <v>4.9824711348607401E-2</v>
+          </cell>
+          <cell r="T9">
+            <v>6.72030120947152E-2</v>
+          </cell>
+          <cell r="U9">
+            <v>0</v>
+          </cell>
+          <cell r="V9">
+            <v>0.114026088991192</v>
+          </cell>
+          <cell r="W9">
+            <v>7.3919336675238506E-2</v>
+          </cell>
+          <cell r="X9">
+            <v>8.4178463038674697E-2</v>
+          </cell>
+          <cell r="Y9">
+            <v>8.1992757924729903E-2</v>
+          </cell>
+          <cell r="Z9">
+            <v>0.117497858959921</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="A10">
+            <v>9</v>
+          </cell>
+          <cell r="B10">
+            <v>0</v>
+          </cell>
+          <cell r="C10">
+            <v>2.6399249382519301E-2</v>
+          </cell>
+          <cell r="D10">
+            <v>2.9325182030622999E-2</v>
+          </cell>
+          <cell r="E10">
+            <v>3.2077536649405401E-2</v>
+          </cell>
+          <cell r="F10">
+            <v>5.3475611494803302E-2</v>
+          </cell>
+          <cell r="G10">
+            <v>2.26552142885269E-2</v>
+          </cell>
+          <cell r="H10">
+            <v>0</v>
+          </cell>
+          <cell r="I10">
+            <v>1.6837295151900002E-2</v>
+          </cell>
+          <cell r="J10">
+            <v>0</v>
+          </cell>
+          <cell r="K10">
+            <v>2.1980138328337201E-2</v>
+          </cell>
+          <cell r="L10">
+            <v>4.8912795031730599E-2</v>
+          </cell>
+          <cell r="M10">
+            <v>2.29840394209961E-2</v>
+          </cell>
+          <cell r="N10">
+            <v>0</v>
+          </cell>
+          <cell r="O10">
+            <v>1.7996669655437399E-2</v>
+          </cell>
+          <cell r="P10">
+            <v>0</v>
+          </cell>
+          <cell r="Q10">
+            <v>5.8182133366766503E-2</v>
+          </cell>
+          <cell r="R10">
+            <v>4.8732654078223699E-2</v>
+          </cell>
+          <cell r="S10">
+            <v>4.0948120763236298E-2</v>
+          </cell>
+          <cell r="T10">
+            <v>4.0444359755062602E-2</v>
+          </cell>
+          <cell r="U10">
+            <v>0</v>
+          </cell>
+          <cell r="V10">
+            <v>0.10683580604703299</v>
+          </cell>
+          <cell r="W10">
+            <v>0.13134470695638201</v>
+          </cell>
+          <cell r="X10">
+            <v>8.6972550230132298E-2</v>
+          </cell>
+          <cell r="Y10">
+            <v>9.1207673099388403E-2</v>
+          </cell>
+          <cell r="Z10">
+            <v>0.102688264269494</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="A11">
+            <v>10</v>
+          </cell>
+          <cell r="B11">
+            <v>0</v>
+          </cell>
+          <cell r="C11">
+            <v>2.0746305758587501E-2</v>
+          </cell>
+          <cell r="D11">
+            <v>0</v>
+          </cell>
+          <cell r="E11">
+            <v>1.07363366169312E-2</v>
+          </cell>
+          <cell r="F11">
+            <v>5.8270382346815502E-2</v>
+          </cell>
+          <cell r="G11">
+            <v>2.23269496028622E-2</v>
+          </cell>
+          <cell r="H11">
+            <v>0</v>
+          </cell>
+          <cell r="I11">
+            <v>1.65015392995553E-2</v>
+          </cell>
+          <cell r="J11">
+            <v>0</v>
+          </cell>
+          <cell r="K11">
+            <v>2.7072757162768801E-2</v>
+          </cell>
+          <cell r="L11">
+            <v>7.4696209917357898E-2</v>
+          </cell>
+          <cell r="M11">
+            <v>2.97417894118309E-2</v>
+          </cell>
+          <cell r="N11">
+            <v>0</v>
+          </cell>
+          <cell r="O11">
+            <v>2.4352819758022198E-2</v>
+          </cell>
+          <cell r="P11">
+            <v>0</v>
+          </cell>
+          <cell r="Q11">
+            <v>3.5278306496583103E-2</v>
+          </cell>
+          <cell r="R11">
+            <v>2.7824706416788601E-2</v>
+          </cell>
+          <cell r="S11">
+            <v>8.1851097509988494E-2</v>
+          </cell>
+          <cell r="T11">
+            <v>2.6434763104976701E-2</v>
+          </cell>
+          <cell r="U11">
+            <v>0</v>
+          </cell>
+          <cell r="V11">
+            <v>0.116297350192845</v>
+          </cell>
+          <cell r="W11">
+            <v>0.11305983397167101</v>
+          </cell>
+          <cell r="X11">
+            <v>0.10099815449430501</v>
+          </cell>
+          <cell r="Y11">
+            <v>0.10282195443756</v>
+          </cell>
+          <cell r="Z11">
+            <v>0.11098874350054801</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="A12">
+            <v>11</v>
+          </cell>
+          <cell r="B12">
+            <v>0</v>
+          </cell>
+          <cell r="C12">
+            <v>0</v>
+          </cell>
+          <cell r="D12">
+            <v>2.5873495822975202E-2</v>
+          </cell>
+          <cell r="E12">
+            <v>2.23946073691112E-2</v>
+          </cell>
+          <cell r="F12">
+            <v>0</v>
+          </cell>
+          <cell r="G12">
+            <v>2.1793172416070299E-2</v>
+          </cell>
+          <cell r="H12">
+            <v>0</v>
+          </cell>
+          <cell r="I12">
+            <v>0</v>
+          </cell>
+          <cell r="J12">
+            <v>0</v>
+          </cell>
+          <cell r="K12">
+            <v>6.1735529003316102E-2</v>
+          </cell>
+          <cell r="L12">
+            <v>9.1977093583278602E-2</v>
+          </cell>
+          <cell r="M12">
+            <v>0</v>
+          </cell>
+          <cell r="N12">
+            <v>0</v>
+          </cell>
+          <cell r="O12">
+            <v>0</v>
+          </cell>
+          <cell r="P12">
+            <v>0</v>
+          </cell>
+          <cell r="Q12">
+            <v>5.6615076912916902E-2</v>
+          </cell>
+          <cell r="R12">
+            <v>6.3910129108036506E-2</v>
+          </cell>
+          <cell r="S12">
+            <v>8.2483855599005604E-2</v>
+          </cell>
+          <cell r="T12">
+            <v>2.0326142844339201E-2</v>
+          </cell>
+          <cell r="U12">
+            <v>0</v>
+          </cell>
+          <cell r="V12">
+            <v>7.8137013958007998E-2</v>
+          </cell>
+          <cell r="W12">
+            <v>0.15242956135343999</v>
+          </cell>
+          <cell r="X12">
+            <v>0.153957913704697</v>
+          </cell>
+          <cell r="Y12">
+            <v>8.0297462652068705E-2</v>
+          </cell>
+          <cell r="Z12">
+            <v>8.8068945672734406E-2</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="A13">
+            <v>12</v>
+          </cell>
+          <cell r="B13">
+            <v>0</v>
+          </cell>
+          <cell r="C13">
+            <v>0</v>
+          </cell>
+          <cell r="D13">
+            <v>0</v>
+          </cell>
+          <cell r="E13">
+            <v>3.3436155846010097E-2</v>
+          </cell>
+          <cell r="F13">
+            <v>7.7490198644765501E-2</v>
+          </cell>
+          <cell r="G13">
+            <v>0</v>
+          </cell>
+          <cell r="H13">
+            <v>0</v>
+          </cell>
+          <cell r="I13">
+            <v>7.0647097668496998E-3</v>
+          </cell>
+          <cell r="J13">
+            <v>0</v>
+          </cell>
+          <cell r="K13">
+            <v>5.9413465485546303E-2</v>
+          </cell>
+          <cell r="L13">
+            <v>6.5028050616042596E-2</v>
+          </cell>
+          <cell r="M13">
+            <v>1.7749525548965101E-2</v>
+          </cell>
+          <cell r="N13">
+            <v>0</v>
+          </cell>
+          <cell r="O13">
+            <v>0</v>
+          </cell>
+          <cell r="P13">
+            <v>0</v>
+          </cell>
+          <cell r="Q13">
+            <v>4.46564022630868E-2</v>
+          </cell>
+          <cell r="R13">
+            <v>8.2639256584309498E-2</v>
+          </cell>
+          <cell r="S13">
+            <v>0.100997090826883</v>
+          </cell>
+          <cell r="T13">
+            <v>2.8303458286978899E-2</v>
+          </cell>
+          <cell r="U13">
+            <v>0</v>
+          </cell>
+          <cell r="V13">
+            <v>0.100134452581668</v>
+          </cell>
+          <cell r="W13">
+            <v>8.5927693067363101E-2</v>
+          </cell>
+          <cell r="X13">
+            <v>5.2802384451094302E-2</v>
+          </cell>
+          <cell r="Y13">
+            <v>0.106982015479894</v>
+          </cell>
+          <cell r="Z13">
+            <v>0.13737514055054101</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="A14">
+            <v>13</v>
+          </cell>
+          <cell r="B14">
+            <v>1.00094875593052E-2</v>
+          </cell>
+          <cell r="C14">
+            <v>0</v>
+          </cell>
+          <cell r="D14">
+            <v>1.9071504813614099E-2</v>
+          </cell>
+          <cell r="E14">
+            <v>2.78413993776786E-2</v>
+          </cell>
+          <cell r="F14">
+            <v>8.9453610220408597E-2</v>
+          </cell>
+          <cell r="G14">
+            <v>1.9074218911958599E-2</v>
+          </cell>
+          <cell r="H14">
+            <v>2.29636527830656E-3</v>
+          </cell>
+          <cell r="I14">
+            <v>5.9786943994187798E-3</v>
+          </cell>
+          <cell r="J14">
+            <v>3.3853162922716701E-2</v>
+          </cell>
+          <cell r="K14">
+            <v>7.6410903490126802E-2</v>
+          </cell>
+          <cell r="L14">
+            <v>3.3713815399815397E-2</v>
+          </cell>
+          <cell r="M14">
+            <v>2.18004949872567E-2</v>
+          </cell>
+          <cell r="N14">
+            <v>1.53299297825856E-2</v>
+          </cell>
+          <cell r="O14">
+            <v>1.50100352000699E-2</v>
+          </cell>
+          <cell r="P14">
+            <v>2.29636527830656E-3</v>
+          </cell>
+          <cell r="Q14">
+            <v>2.6261187040194599E-2</v>
+          </cell>
+          <cell r="R14">
+            <v>2.3235574486946999E-2</v>
+          </cell>
+          <cell r="S14">
+            <v>5.2216252356578299E-2</v>
+          </cell>
+          <cell r="T14">
+            <v>2.0518440637651601E-2</v>
+          </cell>
+          <cell r="U14">
+            <v>0</v>
+          </cell>
+          <cell r="V14">
+            <v>0.124168177961142</v>
+          </cell>
+          <cell r="W14">
+            <v>9.3413586840594101E-2</v>
+          </cell>
+          <cell r="X14">
+            <v>7.3968536386398706E-2</v>
+          </cell>
+          <cell r="Y14">
+            <v>8.5111802817326901E-2</v>
+          </cell>
+          <cell r="Z14">
+            <v>0.128966453851596</v>
+          </cell>
+        </row>
+        <row r="15">
+          <cell r="A15">
+            <v>14</v>
+          </cell>
+          <cell r="B15">
+            <v>0</v>
+          </cell>
+          <cell r="C15">
+            <v>1.6540157096204398E-2</v>
+          </cell>
+          <cell r="D15">
+            <v>0</v>
+          </cell>
+          <cell r="E15">
+            <v>2.3485385716802198E-2</v>
+          </cell>
+          <cell r="F15">
+            <v>7.6254669298487301E-2</v>
+          </cell>
+          <cell r="G15">
+            <v>1.72628538391006E-2</v>
+          </cell>
+          <cell r="H15">
+            <v>0</v>
+          </cell>
+          <cell r="I15">
+            <v>3.3537645725022899E-3</v>
+          </cell>
+          <cell r="J15">
+            <v>0</v>
+          </cell>
+          <cell r="K15">
+            <v>4.1970613343691898E-2</v>
+          </cell>
+          <cell r="L15">
+            <v>6.3377116711007098E-2</v>
+          </cell>
+          <cell r="M15">
+            <v>1.05299173867285E-2</v>
+          </cell>
+          <cell r="N15">
+            <v>0</v>
+          </cell>
+          <cell r="O15">
+            <v>0</v>
+          </cell>
+          <cell r="P15">
+            <v>0</v>
+          </cell>
+          <cell r="Q15">
+            <v>8.3298704114402794E-2</v>
+          </cell>
+          <cell r="R15">
+            <v>3.58756826096579E-2</v>
+          </cell>
+          <cell r="S15">
+            <v>9.4074225472350004E-2</v>
+          </cell>
+          <cell r="T15">
+            <v>1.34523223408147E-2</v>
+          </cell>
+          <cell r="U15">
+            <v>0</v>
+          </cell>
+          <cell r="V15">
+            <v>0.12300298564091899</v>
+          </cell>
+          <cell r="W15">
+            <v>0.13955048262591799</v>
+          </cell>
+          <cell r="X15">
+            <v>7.1679095545026203E-2</v>
+          </cell>
+          <cell r="Y15">
+            <v>8.3471473804501498E-2</v>
+          </cell>
+          <cell r="Z15">
+            <v>0.10282054988188399</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="A16">
+            <v>15</v>
+          </cell>
+          <cell r="B16">
+            <v>2.07625287516554E-2</v>
+          </cell>
+          <cell r="C16">
+            <v>0</v>
+          </cell>
+          <cell r="D16">
+            <v>5.2794312399804803E-2</v>
+          </cell>
+          <cell r="E16">
+            <v>2.5928765595594899E-3</v>
+          </cell>
+          <cell r="F16">
+            <v>2.3508747473339298E-2</v>
+          </cell>
+          <cell r="G16">
+            <v>2.98933574963407E-2</v>
+          </cell>
+          <cell r="H16">
+            <v>4.9980251388211201E-3</v>
+          </cell>
+          <cell r="I16">
+            <v>0</v>
+          </cell>
+          <cell r="J16">
+            <v>0</v>
+          </cell>
+          <cell r="K16">
+            <v>4.73004809367812E-2</v>
+          </cell>
+          <cell r="L16">
+            <v>3.8865268000278799E-2</v>
+          </cell>
+          <cell r="M16">
+            <v>5.07144350735345E-2</v>
+          </cell>
+          <cell r="N16">
+            <v>3.9520921911665598E-2</v>
+          </cell>
+          <cell r="O16">
+            <v>3.4033595873701798E-2</v>
+          </cell>
+          <cell r="P16">
+            <v>9.9258846216398293E-3</v>
+          </cell>
+          <cell r="Q16">
+            <v>1.5695267303268898E-2</v>
+          </cell>
+          <cell r="R16">
+            <v>3.0262772705095101E-2</v>
+          </cell>
+          <cell r="S16">
+            <v>4.2696034014079502E-2</v>
+          </cell>
+          <cell r="T16">
+            <v>2.28758625496619E-2</v>
+          </cell>
+          <cell r="U16">
+            <v>0</v>
+          </cell>
+          <cell r="V16">
+            <v>0.14930229316233301</v>
+          </cell>
+          <cell r="W16">
+            <v>7.8909876629260398E-2</v>
+          </cell>
+          <cell r="X16">
+            <v>5.2674426709416598E-2</v>
+          </cell>
+          <cell r="Y16">
+            <v>9.8612950442601197E-2</v>
+          </cell>
+          <cell r="Z16">
+            <v>0.154060082247159</v>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="A17">
+            <v>16</v>
+          </cell>
+          <cell r="B17">
+            <v>0</v>
+          </cell>
+          <cell r="C17">
+            <v>1.4190465273089099E-2</v>
+          </cell>
+          <cell r="D17">
+            <v>1.9918170656068698E-2</v>
+          </cell>
+          <cell r="E17">
+            <v>2.5116735613286301E-2</v>
+          </cell>
+          <cell r="F17">
+            <v>2.9529871371803001E-2</v>
+          </cell>
+          <cell r="G17">
+            <v>1.20399060797537E-2</v>
+          </cell>
+          <cell r="H17">
+            <v>0</v>
+          </cell>
+          <cell r="I17">
+            <v>1.29778881194898E-2</v>
+          </cell>
+          <cell r="J17">
+            <v>1.7507399902453299E-2</v>
+          </cell>
+          <cell r="K17">
+            <v>3.8783290843734802E-2</v>
+          </cell>
+          <cell r="L17">
+            <v>4.94676559645763E-2</v>
+          </cell>
+          <cell r="M17">
+            <v>2.2804906273713701E-2</v>
+          </cell>
+          <cell r="N17">
+            <v>0</v>
+          </cell>
+          <cell r="O17">
+            <v>1.3598124384612701E-2</v>
+          </cell>
+          <cell r="P17">
+            <v>0</v>
+          </cell>
+          <cell r="Q17">
+            <v>4.3662366565298899E-2</v>
+          </cell>
+          <cell r="R17">
+            <v>8.3377973200388603E-2</v>
+          </cell>
+          <cell r="S17">
+            <v>7.1588253779932498E-2</v>
+          </cell>
+          <cell r="T17">
+            <v>2.9990145086469099E-2</v>
+          </cell>
+          <cell r="U17">
+            <v>0</v>
+          </cell>
+          <cell r="V17">
+            <v>9.3306112094955804E-2</v>
+          </cell>
+          <cell r="W17">
+            <v>9.3854866457422206E-2</v>
+          </cell>
+          <cell r="X17">
+            <v>0.145324887426899</v>
+          </cell>
+          <cell r="Y17">
+            <v>8.7316887555916003E-2</v>
+          </cell>
+          <cell r="Z17">
+            <v>9.5644093350134393E-2</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink10.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="resultados_integracion_partido_"/>
+    </sheetNames>
+    <sheetDataSet>
       <sheetData sheetId="0">
         <row r="1">
           <cell r="A1" t="str">
@@ -2685,79 +3277,79 @@
             <v>1</v>
           </cell>
           <cell r="B2">
-            <v>2.94921215201552E-2</v>
+            <v>0</v>
           </cell>
           <cell r="C2">
             <v>0</v>
           </cell>
           <cell r="D2">
-            <v>3.8370273754083598E-2</v>
+            <v>0</v>
           </cell>
           <cell r="E2">
-            <v>7.7003860909288504E-3</v>
+            <v>0</v>
           </cell>
           <cell r="F2">
-            <v>3.69628738310364E-2</v>
+            <v>0</v>
           </cell>
           <cell r="G2">
-            <v>3.5904517253661603E-2</v>
+            <v>0</v>
           </cell>
           <cell r="H2">
-            <v>3.7122426783395401E-3</v>
+            <v>0</v>
           </cell>
           <cell r="I2">
-            <v>5.6132701789408403E-4</v>
+            <v>0</v>
           </cell>
           <cell r="J2">
             <v>0</v>
           </cell>
           <cell r="K2">
-            <v>2.64487084885912E-2</v>
+            <v>0</v>
           </cell>
           <cell r="L2">
-            <v>5.6262317300813103E-2</v>
+            <v>1</v>
           </cell>
           <cell r="M2">
-            <v>5.7424774525142802E-2</v>
+            <v>0</v>
           </cell>
           <cell r="N2">
-            <v>5.8452853463370601E-3</v>
+            <v>0</v>
           </cell>
           <cell r="O2">
-            <v>1.8447246997155602E-2</v>
+            <v>0</v>
           </cell>
           <cell r="P2">
-            <v>9.9735904143035594E-3</v>
+            <v>0</v>
           </cell>
           <cell r="Q2">
-            <v>3.4214412632511397E-2</v>
+            <v>0</v>
           </cell>
           <cell r="R2">
-            <v>4.3096647244751797E-2</v>
+            <v>0</v>
           </cell>
           <cell r="S2">
-            <v>2.6841637401117099E-2</v>
+            <v>0</v>
           </cell>
           <cell r="T2">
-            <v>3.7715052035014497E-2</v>
+            <v>0</v>
           </cell>
           <cell r="U2">
             <v>0</v>
           </cell>
           <cell r="V2">
-            <v>0.121981463961274</v>
+            <v>0</v>
           </cell>
           <cell r="W2">
-            <v>9.1851470829876006E-2</v>
+            <v>1</v>
           </cell>
           <cell r="X2">
-            <v>5.8876060015043502E-2</v>
+            <v>0</v>
           </cell>
           <cell r="Y2">
-            <v>0.108846411742552</v>
+            <v>0</v>
           </cell>
           <cell r="Z2">
-            <v>0.149471178919414</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="3">
@@ -2765,25 +3357,25 @@
             <v>2</v>
           </cell>
           <cell r="B3">
-            <v>1.19339124020918E-2</v>
+            <v>0</v>
           </cell>
           <cell r="C3">
             <v>0</v>
           </cell>
           <cell r="D3">
-            <v>3.4290097581162103E-2</v>
+            <v>0</v>
           </cell>
           <cell r="E3">
-            <v>3.6409073268422097E-2</v>
+            <v>0</v>
           </cell>
           <cell r="F3">
-            <v>4.0998132428207802E-2</v>
+            <v>0</v>
           </cell>
           <cell r="G3">
-            <v>5.1359296369277399E-2</v>
+            <v>1</v>
           </cell>
           <cell r="H3">
-            <v>2.37788417624217E-3</v>
+            <v>0</v>
           </cell>
           <cell r="I3">
             <v>0</v>
@@ -2792,52 +3384,52 @@
             <v>0</v>
           </cell>
           <cell r="K3">
-            <v>5.2003619358421502E-2</v>
+            <v>1</v>
           </cell>
           <cell r="L3">
-            <v>4.3976920157553598E-2</v>
+            <v>0</v>
           </cell>
           <cell r="M3">
-            <v>5.6756707498804598E-2</v>
+            <v>0</v>
           </cell>
           <cell r="N3">
-            <v>2.2009901775586899E-3</v>
+            <v>0</v>
           </cell>
           <cell r="O3">
-            <v>1.25712668397726E-2</v>
+            <v>0</v>
           </cell>
           <cell r="P3">
-            <v>1.3406420930526699E-3</v>
+            <v>0</v>
           </cell>
           <cell r="Q3">
-            <v>2.0125712668397699E-2</v>
+            <v>0</v>
           </cell>
           <cell r="R3">
-            <v>4.6313529067436202E-2</v>
+            <v>0</v>
           </cell>
           <cell r="S3">
-            <v>3.87097673361479E-2</v>
+            <v>0</v>
           </cell>
           <cell r="T3">
-            <v>3.8379029162851797E-2</v>
+            <v>0</v>
           </cell>
           <cell r="U3">
             <v>0</v>
           </cell>
           <cell r="V3">
-            <v>0.101381702942444</v>
+            <v>0</v>
           </cell>
           <cell r="W3">
-            <v>6.1567688220574998E-2</v>
+            <v>1</v>
           </cell>
           <cell r="X3">
-            <v>4.0977226773817897E-2</v>
+            <v>0</v>
           </cell>
           <cell r="Y3">
-            <v>0.12466202525403</v>
+            <v>0</v>
           </cell>
           <cell r="Z3">
-            <v>0.18166477622373101</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="4">
@@ -2848,76 +3440,76 @@
             <v>0</v>
           </cell>
           <cell r="C4">
-            <v>2.2323885276993902E-2</v>
+            <v>0</v>
           </cell>
           <cell r="D4">
-            <v>1.09616450830563E-2</v>
+            <v>0</v>
           </cell>
           <cell r="E4">
             <v>0</v>
           </cell>
           <cell r="F4">
-            <v>3.9417319956760503E-2</v>
+            <v>0</v>
           </cell>
           <cell r="G4">
-            <v>8.7931659300052895E-2</v>
+            <v>1</v>
           </cell>
           <cell r="H4">
-            <v>1.52353479068733E-2</v>
+            <v>0</v>
           </cell>
           <cell r="I4">
-            <v>6.86586981278373E-4</v>
+            <v>0</v>
           </cell>
           <cell r="J4">
             <v>0</v>
           </cell>
           <cell r="K4">
-            <v>7.5657755490372805E-2</v>
+            <v>0</v>
           </cell>
           <cell r="L4">
-            <v>1.94526094951365E-2</v>
+            <v>0</v>
           </cell>
           <cell r="M4">
-            <v>2.72518246178085E-2</v>
+            <v>0</v>
           </cell>
           <cell r="N4">
-            <v>6.0722509762785003E-3</v>
+            <v>0</v>
           </cell>
           <cell r="O4">
-            <v>1.4518475384566101E-2</v>
+            <v>0</v>
           </cell>
           <cell r="P4">
-            <v>1.3000068486621099E-2</v>
+            <v>0</v>
           </cell>
           <cell r="Q4">
-            <v>3.6495453555229901E-2</v>
+            <v>0</v>
           </cell>
           <cell r="R4">
-            <v>4.8074510690623899E-2</v>
+            <v>0</v>
           </cell>
           <cell r="S4">
-            <v>8.2266542358286801E-2</v>
+            <v>1</v>
           </cell>
           <cell r="T4">
-            <v>2.6145025754755202E-2</v>
+            <v>0</v>
           </cell>
           <cell r="U4">
             <v>0</v>
           </cell>
           <cell r="V4">
-            <v>7.9563557821464598E-2</v>
+            <v>0</v>
           </cell>
           <cell r="W4">
-            <v>0.107729110978267</v>
+            <v>0</v>
           </cell>
           <cell r="X4">
-            <v>5.4669875557400202E-2</v>
+            <v>0</v>
           </cell>
           <cell r="Y4">
-            <v>0.100040369249575</v>
+            <v>0</v>
           </cell>
           <cell r="Z4">
-            <v>0.13250612507859599</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="5">
@@ -2925,79 +3517,79 @@
             <v>4</v>
           </cell>
           <cell r="B5">
-            <v>8.8372020524635497E-3</v>
+            <v>0</v>
           </cell>
           <cell r="C5">
-            <v>1.30034388339584E-2</v>
+            <v>0</v>
           </cell>
           <cell r="D5">
-            <v>2.93165605128635E-2</v>
+            <v>0</v>
           </cell>
           <cell r="E5">
-            <v>1.2391455540471399E-2</v>
+            <v>0</v>
           </cell>
           <cell r="F5">
-            <v>4.8881840833870802E-2</v>
+            <v>0</v>
           </cell>
           <cell r="G5">
-            <v>2.2119726051189802E-2</v>
+            <v>0</v>
           </cell>
           <cell r="H5">
-            <v>1.85265045548034E-3</v>
+            <v>0</v>
           </cell>
           <cell r="I5">
-            <v>6.85094699682837E-3</v>
+            <v>0</v>
           </cell>
           <cell r="J5">
             <v>0</v>
           </cell>
           <cell r="K5">
-            <v>7.4657879442631303E-2</v>
+            <v>1</v>
           </cell>
           <cell r="L5">
-            <v>6.0643128010278602E-2</v>
+            <v>1</v>
           </cell>
           <cell r="M5">
-            <v>4.1295697412301498E-2</v>
+            <v>0</v>
           </cell>
           <cell r="N5">
-            <v>1.85265045548034E-3</v>
+            <v>0</v>
           </cell>
           <cell r="O5">
-            <v>1.21290709507229E-2</v>
+            <v>0</v>
           </cell>
           <cell r="P5">
-            <v>1.85265045548034E-3</v>
+            <v>0</v>
           </cell>
           <cell r="Q5">
-            <v>2.9622366597662299E-2</v>
+            <v>0</v>
           </cell>
           <cell r="R5">
-            <v>3.3264947571328099E-2</v>
+            <v>0</v>
           </cell>
           <cell r="S5">
-            <v>5.9224692505301497E-2</v>
+            <v>0</v>
           </cell>
           <cell r="T5">
-            <v>2.94965555991832E-2</v>
+            <v>0</v>
           </cell>
           <cell r="U5">
             <v>0</v>
           </cell>
           <cell r="V5">
-            <v>8.8958767393648802E-2</v>
+            <v>0</v>
           </cell>
           <cell r="W5">
-            <v>9.1046710394957403E-2</v>
+            <v>1</v>
           </cell>
           <cell r="X5">
-            <v>6.1780622731041297E-2</v>
+            <v>0</v>
           </cell>
           <cell r="Y5">
-            <v>0.123378281384648</v>
+            <v>0</v>
           </cell>
           <cell r="Z5">
-            <v>0.14754215781820701</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="6">
@@ -3008,76 +3600,76 @@
             <v>0</v>
           </cell>
           <cell r="C6">
-            <v>6.4869028679831499E-3</v>
+            <v>0</v>
           </cell>
           <cell r="D6">
-            <v>1.04419722326936E-2</v>
+            <v>0</v>
           </cell>
           <cell r="E6">
-            <v>1.0727601254744401E-2</v>
+            <v>0</v>
           </cell>
           <cell r="F6">
-            <v>7.5344175533315502E-2</v>
+            <v>1</v>
           </cell>
           <cell r="G6">
-            <v>1.99833204552331E-2</v>
+            <v>0</v>
           </cell>
           <cell r="H6">
-            <v>6.0856833510710903E-3</v>
+            <v>0</v>
           </cell>
           <cell r="I6">
-            <v>7.8443845483029892E-3</v>
+            <v>0</v>
           </cell>
           <cell r="J6">
             <v>0</v>
           </cell>
           <cell r="K6">
-            <v>6.1068228740051703E-2</v>
+            <v>1</v>
           </cell>
           <cell r="L6">
-            <v>4.6696923507655301E-2</v>
+            <v>1</v>
           </cell>
           <cell r="M6">
-            <v>2.4516491059365299E-2</v>
+            <v>0</v>
           </cell>
           <cell r="N6">
-            <v>6.0856833510710903E-3</v>
+            <v>0</v>
           </cell>
           <cell r="O6">
-            <v>1.47460445587225E-2</v>
+            <v>0</v>
           </cell>
           <cell r="P6">
-            <v>1.6016498646386199E-2</v>
+            <v>0</v>
           </cell>
           <cell r="Q6">
-            <v>3.3914876005763699E-2</v>
+            <v>0</v>
           </cell>
           <cell r="R6">
-            <v>3.6716123133481202E-2</v>
+            <v>0</v>
           </cell>
           <cell r="S6">
-            <v>4.1651405845219397E-2</v>
+            <v>0</v>
           </cell>
           <cell r="T6">
-            <v>2.4874271162507101E-2</v>
+            <v>0</v>
           </cell>
           <cell r="U6">
             <v>0</v>
           </cell>
           <cell r="V6">
-            <v>0.1371598002144</v>
+            <v>1</v>
           </cell>
           <cell r="W6">
-            <v>0.10626961654006201</v>
+            <v>1</v>
           </cell>
           <cell r="X6">
-            <v>6.4773075180236298E-2</v>
+            <v>0</v>
           </cell>
           <cell r="Y6">
-            <v>9.6271856942704306E-2</v>
+            <v>0</v>
           </cell>
           <cell r="Z6">
-            <v>0.152325064869028</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="7">
@@ -3088,76 +3680,76 @@
             <v>0</v>
           </cell>
           <cell r="C7">
-            <v>4.7263351114183901E-3</v>
+            <v>0</v>
           </cell>
           <cell r="D7">
-            <v>2.6360823979780498E-2</v>
+            <v>0</v>
           </cell>
           <cell r="E7">
-            <v>9.9077987891215205E-3</v>
+            <v>0</v>
           </cell>
           <cell r="F7">
-            <v>5.5805300497302701E-2</v>
+            <v>0</v>
           </cell>
           <cell r="G7">
-            <v>3.3050031450937302E-2</v>
+            <v>0</v>
           </cell>
           <cell r="H7">
             <v>0</v>
           </cell>
           <cell r="I7">
-            <v>9.7471242621549794E-3</v>
+            <v>0</v>
           </cell>
           <cell r="J7">
-            <v>1.88666208987711E-2</v>
+            <v>0</v>
           </cell>
           <cell r="K7">
-            <v>4.45717629705265E-2</v>
+            <v>0</v>
           </cell>
           <cell r="L7">
-            <v>5.4940718518863702E-2</v>
+            <v>0</v>
           </cell>
           <cell r="M7">
-            <v>2.3737400786957401E-2</v>
+            <v>0</v>
           </cell>
           <cell r="N7">
             <v>0</v>
           </cell>
           <cell r="O7">
-            <v>5.3864222373545302E-3</v>
+            <v>0</v>
           </cell>
           <cell r="P7">
             <v>0</v>
           </cell>
           <cell r="Q7">
-            <v>4.0499023084964801E-2</v>
+            <v>0</v>
           </cell>
           <cell r="R7">
-            <v>6.3749067658814398E-2</v>
+            <v>1</v>
           </cell>
           <cell r="S7">
-            <v>7.4840710798139698E-2</v>
+            <v>1</v>
           </cell>
           <cell r="T7">
-            <v>1.3509644065348299E-2</v>
+            <v>0</v>
           </cell>
           <cell r="U7">
             <v>0</v>
           </cell>
           <cell r="V7">
-            <v>0.119366798614535</v>
+            <v>0</v>
           </cell>
           <cell r="W7">
-            <v>0.10256552935532801</v>
+            <v>0</v>
           </cell>
           <cell r="X7">
-            <v>0.102845608473042</v>
+            <v>1</v>
           </cell>
           <cell r="Y7">
-            <v>8.2573491207069097E-2</v>
+            <v>0</v>
           </cell>
           <cell r="Z7">
-            <v>0.112949787239567</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="8">
@@ -3165,79 +3757,79 @@
             <v>7</v>
           </cell>
           <cell r="B8">
-            <v>4.1725406165982401E-3</v>
+            <v>0</v>
           </cell>
           <cell r="C8">
-            <v>9.3335749926337207E-3</v>
+            <v>0</v>
           </cell>
           <cell r="D8">
-            <v>2.8624667847333099E-2</v>
+            <v>0</v>
           </cell>
           <cell r="E8">
-            <v>3.2152027618441402E-2</v>
+            <v>0</v>
           </cell>
           <cell r="F8">
-            <v>4.3984466997937802E-2</v>
+            <v>0</v>
           </cell>
           <cell r="G8">
-            <v>2.1941509789160499E-2</v>
+            <v>0</v>
           </cell>
           <cell r="H8">
             <v>0</v>
           </cell>
           <cell r="I8">
-            <v>5.0032960101678301E-3</v>
+            <v>0</v>
           </cell>
           <cell r="J8">
-            <v>5.0686594898803096E-3</v>
+            <v>0</v>
           </cell>
           <cell r="K8">
-            <v>3.9371702314506297E-2</v>
+            <v>0</v>
           </cell>
           <cell r="L8">
-            <v>6.1016292826739503E-2</v>
+            <v>1</v>
           </cell>
           <cell r="M8">
-            <v>1.77747426029469E-2</v>
+            <v>0</v>
           </cell>
           <cell r="N8">
             <v>0</v>
           </cell>
           <cell r="O8">
-            <v>8.1075458116546103E-4</v>
+            <v>0</v>
           </cell>
           <cell r="P8">
             <v>0</v>
           </cell>
           <cell r="Q8">
-            <v>4.0684951533082901E-2</v>
+            <v>0</v>
           </cell>
           <cell r="R8">
-            <v>7.4653960171165698E-2</v>
+            <v>1</v>
           </cell>
           <cell r="S8">
-            <v>4.5000590745644699E-2</v>
+            <v>0</v>
           </cell>
           <cell r="T8">
-            <v>2.46896626522768E-2</v>
+            <v>0</v>
           </cell>
           <cell r="U8">
             <v>0</v>
           </cell>
           <cell r="V8">
-            <v>9.6292983446956498E-2</v>
+            <v>1</v>
           </cell>
           <cell r="W8">
-            <v>0.140323225500087</v>
+            <v>1</v>
           </cell>
           <cell r="X8">
-            <v>0.121224717787506</v>
+            <v>1</v>
           </cell>
           <cell r="Y8">
-            <v>8.2100242009830099E-2</v>
+            <v>0</v>
           </cell>
           <cell r="Z8">
-            <v>0.105775430465938</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="9">
@@ -3248,76 +3840,76 @@
             <v>0</v>
           </cell>
           <cell r="C9">
-            <v>9.0700278594555601E-3</v>
+            <v>0</v>
           </cell>
           <cell r="D9">
-            <v>4.2950330175467302E-2</v>
+            <v>0</v>
           </cell>
           <cell r="E9">
-            <v>1.84792218255839E-2</v>
+            <v>0</v>
           </cell>
           <cell r="F9">
-            <v>4.3808763337555803E-2</v>
+            <v>0</v>
           </cell>
           <cell r="G9">
-            <v>3.2906604546727697E-2</v>
+            <v>0</v>
           </cell>
           <cell r="H9">
-            <v>2.0465086926803499E-2</v>
+            <v>0</v>
           </cell>
           <cell r="I9">
-            <v>8.0951774440995404E-3</v>
+            <v>0</v>
           </cell>
           <cell r="J9">
             <v>0</v>
           </cell>
           <cell r="K9">
-            <v>4.8370216086559101E-2</v>
+            <v>0</v>
           </cell>
           <cell r="L9">
-            <v>6.4069831909623301E-2</v>
+            <v>1</v>
           </cell>
           <cell r="M9">
-            <v>3.3127480350265998E-2</v>
+            <v>0</v>
           </cell>
           <cell r="N9">
-            <v>5.2503028577553996E-4</v>
+            <v>0</v>
           </cell>
           <cell r="O9">
-            <v>9.4156776002830896E-3</v>
+            <v>0</v>
           </cell>
           <cell r="P9">
-            <v>5.2503028577553996E-4</v>
+            <v>0</v>
           </cell>
           <cell r="Q9">
-            <v>2.6173998840438001E-2</v>
+            <v>0</v>
           </cell>
           <cell r="R9">
-            <v>5.3375293492505999E-2</v>
+            <v>0</v>
           </cell>
           <cell r="S9">
-            <v>4.9824711348607401E-2</v>
+            <v>0</v>
           </cell>
           <cell r="T9">
-            <v>6.72030120947152E-2</v>
+            <v>0</v>
           </cell>
           <cell r="U9">
             <v>0</v>
           </cell>
           <cell r="V9">
-            <v>0.114026088991192</v>
+            <v>1</v>
           </cell>
           <cell r="W9">
-            <v>7.3919336675238506E-2</v>
+            <v>0</v>
           </cell>
           <cell r="X9">
-            <v>8.4178463038674697E-2</v>
+            <v>1</v>
           </cell>
           <cell r="Y9">
-            <v>8.1992757924729903E-2</v>
+            <v>0</v>
           </cell>
           <cell r="Z9">
-            <v>0.117497858959921</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="10">
@@ -3328,76 +3920,76 @@
             <v>0</v>
           </cell>
           <cell r="C10">
-            <v>2.6399249382519301E-2</v>
+            <v>0</v>
           </cell>
           <cell r="D10">
-            <v>2.9325182030622999E-2</v>
+            <v>0</v>
           </cell>
           <cell r="E10">
-            <v>3.2077536649405401E-2</v>
+            <v>0</v>
           </cell>
           <cell r="F10">
-            <v>5.3475611494803302E-2</v>
+            <v>1</v>
           </cell>
           <cell r="G10">
-            <v>2.26552142885269E-2</v>
+            <v>0</v>
           </cell>
           <cell r="H10">
             <v>0</v>
           </cell>
           <cell r="I10">
-            <v>1.6837295151900002E-2</v>
+            <v>0</v>
           </cell>
           <cell r="J10">
             <v>0</v>
           </cell>
           <cell r="K10">
-            <v>2.1980138328337201E-2</v>
+            <v>0</v>
           </cell>
           <cell r="L10">
-            <v>4.8912795031730599E-2</v>
+            <v>0</v>
           </cell>
           <cell r="M10">
-            <v>2.29840394209961E-2</v>
+            <v>0</v>
           </cell>
           <cell r="N10">
             <v>0</v>
           </cell>
           <cell r="O10">
-            <v>1.7996669655437399E-2</v>
+            <v>0</v>
           </cell>
           <cell r="P10">
             <v>0</v>
           </cell>
           <cell r="Q10">
-            <v>5.8182133366766503E-2</v>
+            <v>1</v>
           </cell>
           <cell r="R10">
-            <v>4.8732654078223699E-2</v>
+            <v>0</v>
           </cell>
           <cell r="S10">
-            <v>4.0948120763236298E-2</v>
+            <v>0</v>
           </cell>
           <cell r="T10">
-            <v>4.0444359755062602E-2</v>
+            <v>0</v>
           </cell>
           <cell r="U10">
             <v>0</v>
           </cell>
           <cell r="V10">
-            <v>0.10683580604703299</v>
+            <v>1</v>
           </cell>
           <cell r="W10">
-            <v>0.13134470695638201</v>
+            <v>1</v>
           </cell>
           <cell r="X10">
-            <v>8.6972550230132298E-2</v>
+            <v>1</v>
           </cell>
           <cell r="Y10">
-            <v>9.1207673099388403E-2</v>
+            <v>0</v>
           </cell>
           <cell r="Z10">
-            <v>0.102688264269494</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="11">
@@ -3408,76 +4000,76 @@
             <v>0</v>
           </cell>
           <cell r="C11">
-            <v>2.0746305758587501E-2</v>
+            <v>0</v>
           </cell>
           <cell r="D11">
             <v>0</v>
           </cell>
           <cell r="E11">
-            <v>1.07363366169312E-2</v>
+            <v>0</v>
           </cell>
           <cell r="F11">
-            <v>5.8270382346815502E-2</v>
+            <v>0</v>
           </cell>
           <cell r="G11">
-            <v>2.23269496028622E-2</v>
+            <v>0</v>
           </cell>
           <cell r="H11">
             <v>0</v>
           </cell>
           <cell r="I11">
-            <v>1.65015392995553E-2</v>
+            <v>0</v>
           </cell>
           <cell r="J11">
             <v>0</v>
           </cell>
           <cell r="K11">
-            <v>2.7072757162768801E-2</v>
+            <v>0</v>
           </cell>
           <cell r="L11">
-            <v>7.4696209917357898E-2</v>
+            <v>1</v>
           </cell>
           <cell r="M11">
-            <v>2.97417894118309E-2</v>
+            <v>0</v>
           </cell>
           <cell r="N11">
             <v>0</v>
           </cell>
           <cell r="O11">
-            <v>2.4352819758022198E-2</v>
+            <v>0</v>
           </cell>
           <cell r="P11">
             <v>0</v>
           </cell>
           <cell r="Q11">
-            <v>3.5278306496583103E-2</v>
+            <v>0</v>
           </cell>
           <cell r="R11">
-            <v>2.7824706416788601E-2</v>
+            <v>0</v>
           </cell>
           <cell r="S11">
-            <v>8.1851097509988494E-2</v>
+            <v>1</v>
           </cell>
           <cell r="T11">
-            <v>2.6434763104976701E-2</v>
+            <v>0</v>
           </cell>
           <cell r="U11">
             <v>0</v>
           </cell>
           <cell r="V11">
-            <v>0.116297350192845</v>
+            <v>0</v>
           </cell>
           <cell r="W11">
-            <v>0.11305983397167101</v>
+            <v>1</v>
           </cell>
           <cell r="X11">
-            <v>0.10099815449430501</v>
+            <v>0</v>
           </cell>
           <cell r="Y11">
-            <v>0.10282195443756</v>
+            <v>0</v>
           </cell>
           <cell r="Z11">
-            <v>0.11098874350054801</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="12">
@@ -3491,16 +4083,16 @@
             <v>0</v>
           </cell>
           <cell r="D12">
-            <v>2.5873495822975202E-2</v>
+            <v>0</v>
           </cell>
           <cell r="E12">
-            <v>2.23946073691112E-2</v>
+            <v>0</v>
           </cell>
           <cell r="F12">
             <v>0</v>
           </cell>
           <cell r="G12">
-            <v>2.1793172416070299E-2</v>
+            <v>0</v>
           </cell>
           <cell r="H12">
             <v>0</v>
@@ -3512,10 +4104,10 @@
             <v>0</v>
           </cell>
           <cell r="K12">
-            <v>6.1735529003316102E-2</v>
+            <v>0</v>
           </cell>
           <cell r="L12">
-            <v>9.1977093583278602E-2</v>
+            <v>1</v>
           </cell>
           <cell r="M12">
             <v>0</v>
@@ -3530,34 +4122,34 @@
             <v>0</v>
           </cell>
           <cell r="Q12">
-            <v>5.6615076912916902E-2</v>
+            <v>0</v>
           </cell>
           <cell r="R12">
-            <v>6.3910129108036506E-2</v>
+            <v>0</v>
           </cell>
           <cell r="S12">
-            <v>8.2483855599005604E-2</v>
+            <v>0</v>
           </cell>
           <cell r="T12">
-            <v>2.0326142844339201E-2</v>
+            <v>0</v>
           </cell>
           <cell r="U12">
             <v>0</v>
           </cell>
           <cell r="V12">
-            <v>7.8137013958007998E-2</v>
+            <v>0</v>
           </cell>
           <cell r="W12">
-            <v>0.15242956135343999</v>
+            <v>0</v>
           </cell>
           <cell r="X12">
-            <v>0.153957913704697</v>
+            <v>1</v>
           </cell>
           <cell r="Y12">
-            <v>8.0297462652068705E-2</v>
+            <v>0</v>
           </cell>
           <cell r="Z12">
-            <v>8.8068945672734406E-2</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="13">
@@ -3574,10 +4166,10 @@
             <v>0</v>
           </cell>
           <cell r="E13">
-            <v>3.3436155846010097E-2</v>
+            <v>0</v>
           </cell>
           <cell r="F13">
-            <v>7.7490198644765501E-2</v>
+            <v>0</v>
           </cell>
           <cell r="G13">
             <v>0</v>
@@ -3586,19 +4178,19 @@
             <v>0</v>
           </cell>
           <cell r="I13">
-            <v>7.0647097668496998E-3</v>
+            <v>0</v>
           </cell>
           <cell r="J13">
             <v>0</v>
           </cell>
           <cell r="K13">
-            <v>5.9413465485546303E-2</v>
+            <v>0</v>
           </cell>
           <cell r="L13">
-            <v>6.5028050616042596E-2</v>
+            <v>0</v>
           </cell>
           <cell r="M13">
-            <v>1.7749525548965101E-2</v>
+            <v>0</v>
           </cell>
           <cell r="N13">
             <v>0</v>
@@ -3610,34 +4202,34 @@
             <v>0</v>
           </cell>
           <cell r="Q13">
-            <v>4.46564022630868E-2</v>
+            <v>0</v>
           </cell>
           <cell r="R13">
-            <v>8.2639256584309498E-2</v>
+            <v>1</v>
           </cell>
           <cell r="S13">
-            <v>0.100997090826883</v>
+            <v>1</v>
           </cell>
           <cell r="T13">
-            <v>2.8303458286978899E-2</v>
+            <v>0</v>
           </cell>
           <cell r="U13">
             <v>0</v>
           </cell>
           <cell r="V13">
-            <v>0.100134452581668</v>
+            <v>0</v>
           </cell>
           <cell r="W13">
-            <v>8.5927693067363101E-2</v>
+            <v>0</v>
           </cell>
           <cell r="X13">
-            <v>5.2802384451094302E-2</v>
+            <v>0</v>
           </cell>
           <cell r="Y13">
-            <v>0.106982015479894</v>
+            <v>0</v>
           </cell>
           <cell r="Z13">
-            <v>0.13737514055054101</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="14">
@@ -3645,79 +4237,79 @@
             <v>13</v>
           </cell>
           <cell r="B14">
-            <v>1.00094875593052E-2</v>
+            <v>0</v>
           </cell>
           <cell r="C14">
             <v>0</v>
           </cell>
           <cell r="D14">
-            <v>1.9071504813614099E-2</v>
+            <v>0</v>
           </cell>
           <cell r="E14">
-            <v>2.78413993776786E-2</v>
+            <v>0</v>
           </cell>
           <cell r="F14">
-            <v>8.9453610220408597E-2</v>
+            <v>1</v>
           </cell>
           <cell r="G14">
-            <v>1.9074218911958599E-2</v>
+            <v>0</v>
           </cell>
           <cell r="H14">
-            <v>2.29636527830656E-3</v>
+            <v>0</v>
           </cell>
           <cell r="I14">
-            <v>5.9786943994187798E-3</v>
+            <v>0</v>
           </cell>
           <cell r="J14">
-            <v>3.3853162922716701E-2</v>
+            <v>0</v>
           </cell>
           <cell r="K14">
-            <v>7.6410903490126802E-2</v>
+            <v>1</v>
           </cell>
           <cell r="L14">
-            <v>3.3713815399815397E-2</v>
+            <v>0</v>
           </cell>
           <cell r="M14">
-            <v>2.18004949872567E-2</v>
+            <v>0</v>
           </cell>
           <cell r="N14">
-            <v>1.53299297825856E-2</v>
+            <v>0</v>
           </cell>
           <cell r="O14">
-            <v>1.50100352000699E-2</v>
+            <v>0</v>
           </cell>
           <cell r="P14">
-            <v>2.29636527830656E-3</v>
+            <v>0</v>
           </cell>
           <cell r="Q14">
-            <v>2.6261187040194599E-2</v>
+            <v>0</v>
           </cell>
           <cell r="R14">
-            <v>2.3235574486946999E-2</v>
+            <v>0</v>
           </cell>
           <cell r="S14">
-            <v>5.2216252356578299E-2</v>
+            <v>1</v>
           </cell>
           <cell r="T14">
-            <v>2.0518440637651601E-2</v>
+            <v>0</v>
           </cell>
           <cell r="U14">
             <v>0</v>
           </cell>
           <cell r="V14">
-            <v>0.124168177961142</v>
+            <v>1</v>
           </cell>
           <cell r="W14">
-            <v>9.3413586840594101E-2</v>
+            <v>1</v>
           </cell>
           <cell r="X14">
-            <v>7.3968536386398706E-2</v>
+            <v>0</v>
           </cell>
           <cell r="Y14">
-            <v>8.5111802817326901E-2</v>
+            <v>0</v>
           </cell>
           <cell r="Z14">
-            <v>0.128966453851596</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="15">
@@ -3728,37 +4320,37 @@
             <v>0</v>
           </cell>
           <cell r="C15">
-            <v>1.6540157096204398E-2</v>
+            <v>0</v>
           </cell>
           <cell r="D15">
             <v>0</v>
           </cell>
           <cell r="E15">
-            <v>2.3485385716802198E-2</v>
+            <v>0</v>
           </cell>
           <cell r="F15">
-            <v>7.6254669298487301E-2</v>
+            <v>0</v>
           </cell>
           <cell r="G15">
-            <v>1.72628538391006E-2</v>
+            <v>0</v>
           </cell>
           <cell r="H15">
             <v>0</v>
           </cell>
           <cell r="I15">
-            <v>3.3537645725022899E-3</v>
+            <v>0</v>
           </cell>
           <cell r="J15">
             <v>0</v>
           </cell>
           <cell r="K15">
-            <v>4.1970613343691898E-2</v>
+            <v>0</v>
           </cell>
           <cell r="L15">
-            <v>6.3377116711007098E-2</v>
+            <v>0</v>
           </cell>
           <cell r="M15">
-            <v>1.05299173867285E-2</v>
+            <v>0</v>
           </cell>
           <cell r="N15">
             <v>0</v>
@@ -3770,34 +4362,34 @@
             <v>0</v>
           </cell>
           <cell r="Q15">
-            <v>8.3298704114402794E-2</v>
+            <v>1</v>
           </cell>
           <cell r="R15">
-            <v>3.58756826096579E-2</v>
+            <v>0</v>
           </cell>
           <cell r="S15">
-            <v>9.4074225472350004E-2</v>
+            <v>1</v>
           </cell>
           <cell r="T15">
-            <v>1.34523223408147E-2</v>
+            <v>0</v>
           </cell>
           <cell r="U15">
             <v>0</v>
           </cell>
           <cell r="V15">
-            <v>0.12300298564091899</v>
+            <v>0</v>
           </cell>
           <cell r="W15">
-            <v>0.13955048262591799</v>
+            <v>1</v>
           </cell>
           <cell r="X15">
-            <v>7.1679095545026203E-2</v>
+            <v>0</v>
           </cell>
           <cell r="Y15">
-            <v>8.3471473804501498E-2</v>
+            <v>0</v>
           </cell>
           <cell r="Z15">
-            <v>0.10282054988188399</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="16">
@@ -3805,25 +4397,25 @@
             <v>15</v>
           </cell>
           <cell r="B16">
-            <v>2.07625287516554E-2</v>
+            <v>0</v>
           </cell>
           <cell r="C16">
             <v>0</v>
           </cell>
           <cell r="D16">
-            <v>5.2794312399804803E-2</v>
+            <v>0</v>
           </cell>
           <cell r="E16">
-            <v>2.5928765595594899E-3</v>
+            <v>0</v>
           </cell>
           <cell r="F16">
-            <v>2.3508747473339298E-2</v>
+            <v>0</v>
           </cell>
           <cell r="G16">
-            <v>2.98933574963407E-2</v>
+            <v>0</v>
           </cell>
           <cell r="H16">
-            <v>4.9980251388211201E-3</v>
+            <v>0</v>
           </cell>
           <cell r="I16">
             <v>0</v>
@@ -3832,52 +4424,52 @@
             <v>0</v>
           </cell>
           <cell r="K16">
-            <v>4.73004809367812E-2</v>
+            <v>1</v>
           </cell>
           <cell r="L16">
-            <v>3.8865268000278799E-2</v>
+            <v>0</v>
           </cell>
           <cell r="M16">
-            <v>5.07144350735345E-2</v>
+            <v>0</v>
           </cell>
           <cell r="N16">
-            <v>3.9520921911665598E-2</v>
+            <v>0</v>
           </cell>
           <cell r="O16">
-            <v>3.4033595873701798E-2</v>
+            <v>0</v>
           </cell>
           <cell r="P16">
-            <v>9.9258846216398293E-3</v>
+            <v>0</v>
           </cell>
           <cell r="Q16">
-            <v>1.5695267303268898E-2</v>
+            <v>0</v>
           </cell>
           <cell r="R16">
-            <v>3.0262772705095101E-2</v>
+            <v>0</v>
           </cell>
           <cell r="S16">
-            <v>4.2696034014079502E-2</v>
+            <v>0</v>
           </cell>
           <cell r="T16">
-            <v>2.28758625496619E-2</v>
+            <v>0</v>
           </cell>
           <cell r="U16">
             <v>0</v>
           </cell>
           <cell r="V16">
-            <v>0.14930229316233301</v>
+            <v>0</v>
           </cell>
           <cell r="W16">
-            <v>7.8909876629260398E-2</v>
+            <v>1</v>
           </cell>
           <cell r="X16">
-            <v>5.2674426709416598E-2</v>
+            <v>0</v>
           </cell>
           <cell r="Y16">
-            <v>9.8612950442601197E-2</v>
+            <v>0</v>
           </cell>
           <cell r="Z16">
-            <v>0.154060082247159</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="17">
@@ -3888,76 +4480,1453 @@
             <v>0</v>
           </cell>
           <cell r="C17">
-            <v>1.4190465273089099E-2</v>
+            <v>0</v>
           </cell>
           <cell r="D17">
-            <v>1.9918170656068698E-2</v>
+            <v>0</v>
           </cell>
           <cell r="E17">
-            <v>2.5116735613286301E-2</v>
+            <v>0</v>
           </cell>
           <cell r="F17">
-            <v>2.9529871371803001E-2</v>
+            <v>0</v>
           </cell>
           <cell r="G17">
-            <v>1.20399060797537E-2</v>
+            <v>0</v>
           </cell>
           <cell r="H17">
             <v>0</v>
           </cell>
           <cell r="I17">
-            <v>1.29778881194898E-2</v>
+            <v>0</v>
           </cell>
           <cell r="J17">
-            <v>1.7507399902453299E-2</v>
+            <v>0</v>
           </cell>
           <cell r="K17">
-            <v>3.8783290843734802E-2</v>
+            <v>0</v>
           </cell>
           <cell r="L17">
-            <v>4.94676559645763E-2</v>
+            <v>0</v>
           </cell>
           <cell r="M17">
-            <v>2.2804906273713701E-2</v>
+            <v>0</v>
           </cell>
           <cell r="N17">
             <v>0</v>
           </cell>
           <cell r="O17">
-            <v>1.3598124384612701E-2</v>
+            <v>0</v>
           </cell>
           <cell r="P17">
             <v>0</v>
           </cell>
           <cell r="Q17">
-            <v>4.3662366565298899E-2</v>
+            <v>0</v>
           </cell>
           <cell r="R17">
-            <v>8.3377973200388603E-2</v>
+            <v>1</v>
           </cell>
           <cell r="S17">
-            <v>7.1588253779932498E-2</v>
+            <v>0</v>
           </cell>
           <cell r="T17">
-            <v>2.9990145086469099E-2</v>
+            <v>0</v>
           </cell>
           <cell r="U17">
             <v>0</v>
           </cell>
           <cell r="V17">
-            <v>9.3306112094955804E-2</v>
+            <v>0</v>
           </cell>
           <cell r="W17">
-            <v>9.3854866457422206E-2</v>
+            <v>0</v>
           </cell>
           <cell r="X17">
-            <v>0.145324887426899</v>
+            <v>1</v>
           </cell>
           <cell r="Y17">
-            <v>8.7316887555916003E-2</v>
+            <v>0</v>
           </cell>
           <cell r="Z17">
-            <v>9.5644093350134393E-2</v>
+            <v>0</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink11.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="resultados_integracion_partido_"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="1">
+          <cell r="A1" t="str">
+            <v>Circunscripcion</v>
+          </cell>
+          <cell r="B1" t="str">
+            <v>AH</v>
+          </cell>
+          <cell r="C1" t="str">
+            <v>AMA</v>
+          </cell>
+          <cell r="D1" t="str">
+            <v>DEM</v>
+          </cell>
+          <cell r="E1" t="str">
+            <v>EVO</v>
+          </cell>
+          <cell r="F1" t="str">
+            <v>FA</v>
+          </cell>
+          <cell r="G1" t="str">
+            <v>FREVS</v>
+          </cell>
+          <cell r="H1" t="str">
+            <v>IGU</v>
+          </cell>
+          <cell r="I1" t="str">
+            <v>IND</v>
+          </cell>
+          <cell r="J1" t="str">
+            <v>PAVP</v>
+          </cell>
+          <cell r="K1" t="str">
+            <v>PCCH</v>
+          </cell>
+          <cell r="L1" t="str">
+            <v>PDC</v>
+          </cell>
+          <cell r="M1" t="str">
+            <v>PDG</v>
+          </cell>
+          <cell r="N1" t="str">
+            <v>PH</v>
+          </cell>
+          <cell r="O1" t="str">
+            <v>PL</v>
+          </cell>
+          <cell r="P1" t="str">
+            <v>POP</v>
+          </cell>
+          <cell r="Q1" t="str">
+            <v>PPD</v>
+          </cell>
+          <cell r="R1" t="str">
+            <v>PR</v>
+          </cell>
+          <cell r="S1" t="str">
+            <v>PS</v>
+          </cell>
+          <cell r="T1" t="str">
+            <v>PSC</v>
+          </cell>
+          <cell r="U1" t="str">
+            <v>PTR</v>
+          </cell>
+          <cell r="V1" t="str">
+            <v>REP</v>
+          </cell>
+          <cell r="W1" t="str">
+            <v>RN</v>
+          </cell>
+          <cell r="X1" t="str">
+            <v>UDI</v>
+          </cell>
+          <cell r="Y1" t="str">
+            <v>Votos Blancos</v>
+          </cell>
+          <cell r="Z1" t="str">
+            <v>Votos Nulos</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="A2">
+            <v>1</v>
+          </cell>
+          <cell r="B2">
+            <v>0</v>
+          </cell>
+          <cell r="C2">
+            <v>0</v>
+          </cell>
+          <cell r="D2">
+            <v>0</v>
+          </cell>
+          <cell r="E2">
+            <v>0</v>
+          </cell>
+          <cell r="F2">
+            <v>0</v>
+          </cell>
+          <cell r="G2">
+            <v>0</v>
+          </cell>
+          <cell r="H2">
+            <v>0</v>
+          </cell>
+          <cell r="I2">
+            <v>0</v>
+          </cell>
+          <cell r="J2">
+            <v>0</v>
+          </cell>
+          <cell r="K2">
+            <v>0</v>
+          </cell>
+          <cell r="L2">
+            <v>1</v>
+          </cell>
+          <cell r="M2">
+            <v>0</v>
+          </cell>
+          <cell r="N2">
+            <v>0</v>
+          </cell>
+          <cell r="O2">
+            <v>0</v>
+          </cell>
+          <cell r="P2">
+            <v>0</v>
+          </cell>
+          <cell r="Q2">
+            <v>0</v>
+          </cell>
+          <cell r="R2">
+            <v>0</v>
+          </cell>
+          <cell r="S2">
+            <v>0</v>
+          </cell>
+          <cell r="T2">
+            <v>0</v>
+          </cell>
+          <cell r="U2">
+            <v>0</v>
+          </cell>
+          <cell r="V2">
+            <v>1</v>
+          </cell>
+          <cell r="W2">
+            <v>0</v>
+          </cell>
+          <cell r="X2">
+            <v>0</v>
+          </cell>
+          <cell r="Y2">
+            <v>0</v>
+          </cell>
+          <cell r="Z2">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="A3">
+            <v>2</v>
+          </cell>
+          <cell r="B3">
+            <v>0</v>
+          </cell>
+          <cell r="C3">
+            <v>0</v>
+          </cell>
+          <cell r="D3">
+            <v>0</v>
+          </cell>
+          <cell r="E3">
+            <v>0</v>
+          </cell>
+          <cell r="F3">
+            <v>0</v>
+          </cell>
+          <cell r="G3">
+            <v>1</v>
+          </cell>
+          <cell r="H3">
+            <v>0</v>
+          </cell>
+          <cell r="I3">
+            <v>0</v>
+          </cell>
+          <cell r="J3">
+            <v>0</v>
+          </cell>
+          <cell r="K3">
+            <v>1</v>
+          </cell>
+          <cell r="L3">
+            <v>0</v>
+          </cell>
+          <cell r="M3">
+            <v>0</v>
+          </cell>
+          <cell r="N3">
+            <v>0</v>
+          </cell>
+          <cell r="O3">
+            <v>0</v>
+          </cell>
+          <cell r="P3">
+            <v>0</v>
+          </cell>
+          <cell r="Q3">
+            <v>0</v>
+          </cell>
+          <cell r="R3">
+            <v>0</v>
+          </cell>
+          <cell r="S3">
+            <v>0</v>
+          </cell>
+          <cell r="T3">
+            <v>0</v>
+          </cell>
+          <cell r="U3">
+            <v>0</v>
+          </cell>
+          <cell r="V3">
+            <v>1</v>
+          </cell>
+          <cell r="W3">
+            <v>0</v>
+          </cell>
+          <cell r="X3">
+            <v>0</v>
+          </cell>
+          <cell r="Y3">
+            <v>0</v>
+          </cell>
+          <cell r="Z3">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="A4">
+            <v>3</v>
+          </cell>
+          <cell r="B4">
+            <v>0</v>
+          </cell>
+          <cell r="C4">
+            <v>0</v>
+          </cell>
+          <cell r="D4">
+            <v>0</v>
+          </cell>
+          <cell r="E4">
+            <v>0</v>
+          </cell>
+          <cell r="F4">
+            <v>0</v>
+          </cell>
+          <cell r="G4">
+            <v>1</v>
+          </cell>
+          <cell r="H4">
+            <v>0</v>
+          </cell>
+          <cell r="I4">
+            <v>0</v>
+          </cell>
+          <cell r="J4">
+            <v>0</v>
+          </cell>
+          <cell r="K4">
+            <v>0</v>
+          </cell>
+          <cell r="L4">
+            <v>0</v>
+          </cell>
+          <cell r="M4">
+            <v>0</v>
+          </cell>
+          <cell r="N4">
+            <v>0</v>
+          </cell>
+          <cell r="O4">
+            <v>0</v>
+          </cell>
+          <cell r="P4">
+            <v>0</v>
+          </cell>
+          <cell r="Q4">
+            <v>0</v>
+          </cell>
+          <cell r="R4">
+            <v>0</v>
+          </cell>
+          <cell r="S4">
+            <v>1</v>
+          </cell>
+          <cell r="T4">
+            <v>0</v>
+          </cell>
+          <cell r="U4">
+            <v>0</v>
+          </cell>
+          <cell r="V4">
+            <v>0</v>
+          </cell>
+          <cell r="W4">
+            <v>0</v>
+          </cell>
+          <cell r="X4">
+            <v>0</v>
+          </cell>
+          <cell r="Y4">
+            <v>0</v>
+          </cell>
+          <cell r="Z4">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="A5">
+            <v>4</v>
+          </cell>
+          <cell r="B5">
+            <v>0</v>
+          </cell>
+          <cell r="C5">
+            <v>0</v>
+          </cell>
+          <cell r="D5">
+            <v>0</v>
+          </cell>
+          <cell r="E5">
+            <v>0</v>
+          </cell>
+          <cell r="F5">
+            <v>0</v>
+          </cell>
+          <cell r="G5">
+            <v>0</v>
+          </cell>
+          <cell r="H5">
+            <v>0</v>
+          </cell>
+          <cell r="I5">
+            <v>0</v>
+          </cell>
+          <cell r="J5">
+            <v>0</v>
+          </cell>
+          <cell r="K5">
+            <v>1</v>
+          </cell>
+          <cell r="L5">
+            <v>1</v>
+          </cell>
+          <cell r="M5">
+            <v>0</v>
+          </cell>
+          <cell r="N5">
+            <v>0</v>
+          </cell>
+          <cell r="O5">
+            <v>0</v>
+          </cell>
+          <cell r="P5">
+            <v>0</v>
+          </cell>
+          <cell r="Q5">
+            <v>0</v>
+          </cell>
+          <cell r="R5">
+            <v>0</v>
+          </cell>
+          <cell r="S5">
+            <v>0</v>
+          </cell>
+          <cell r="T5">
+            <v>0</v>
+          </cell>
+          <cell r="U5">
+            <v>0</v>
+          </cell>
+          <cell r="V5">
+            <v>0</v>
+          </cell>
+          <cell r="W5">
+            <v>1</v>
+          </cell>
+          <cell r="X5">
+            <v>0</v>
+          </cell>
+          <cell r="Y5">
+            <v>0</v>
+          </cell>
+          <cell r="Z5">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="A6">
+            <v>5</v>
+          </cell>
+          <cell r="B6">
+            <v>0</v>
+          </cell>
+          <cell r="C6">
+            <v>0</v>
+          </cell>
+          <cell r="D6">
+            <v>0</v>
+          </cell>
+          <cell r="E6">
+            <v>0</v>
+          </cell>
+          <cell r="F6">
+            <v>1</v>
+          </cell>
+          <cell r="G6">
+            <v>0</v>
+          </cell>
+          <cell r="H6">
+            <v>0</v>
+          </cell>
+          <cell r="I6">
+            <v>0</v>
+          </cell>
+          <cell r="J6">
+            <v>0</v>
+          </cell>
+          <cell r="K6">
+            <v>1</v>
+          </cell>
+          <cell r="L6">
+            <v>1</v>
+          </cell>
+          <cell r="M6">
+            <v>0</v>
+          </cell>
+          <cell r="N6">
+            <v>0</v>
+          </cell>
+          <cell r="O6">
+            <v>0</v>
+          </cell>
+          <cell r="P6">
+            <v>0</v>
+          </cell>
+          <cell r="Q6">
+            <v>0</v>
+          </cell>
+          <cell r="R6">
+            <v>0</v>
+          </cell>
+          <cell r="S6">
+            <v>0</v>
+          </cell>
+          <cell r="T6">
+            <v>0</v>
+          </cell>
+          <cell r="U6">
+            <v>0</v>
+          </cell>
+          <cell r="V6">
+            <v>1</v>
+          </cell>
+          <cell r="W6">
+            <v>1</v>
+          </cell>
+          <cell r="X6">
+            <v>0</v>
+          </cell>
+          <cell r="Y6">
+            <v>0</v>
+          </cell>
+          <cell r="Z6">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="A7">
+            <v>6</v>
+          </cell>
+          <cell r="B7">
+            <v>0</v>
+          </cell>
+          <cell r="C7">
+            <v>0</v>
+          </cell>
+          <cell r="D7">
+            <v>0</v>
+          </cell>
+          <cell r="E7">
+            <v>0</v>
+          </cell>
+          <cell r="F7">
+            <v>0</v>
+          </cell>
+          <cell r="G7">
+            <v>0</v>
+          </cell>
+          <cell r="H7">
+            <v>0</v>
+          </cell>
+          <cell r="I7">
+            <v>0</v>
+          </cell>
+          <cell r="J7">
+            <v>0</v>
+          </cell>
+          <cell r="K7">
+            <v>0</v>
+          </cell>
+          <cell r="L7">
+            <v>0</v>
+          </cell>
+          <cell r="M7">
+            <v>0</v>
+          </cell>
+          <cell r="N7">
+            <v>0</v>
+          </cell>
+          <cell r="O7">
+            <v>0</v>
+          </cell>
+          <cell r="P7">
+            <v>0</v>
+          </cell>
+          <cell r="Q7">
+            <v>0</v>
+          </cell>
+          <cell r="R7">
+            <v>1</v>
+          </cell>
+          <cell r="S7">
+            <v>1</v>
+          </cell>
+          <cell r="T7">
+            <v>0</v>
+          </cell>
+          <cell r="U7">
+            <v>0</v>
+          </cell>
+          <cell r="V7">
+            <v>0</v>
+          </cell>
+          <cell r="W7">
+            <v>0</v>
+          </cell>
+          <cell r="X7">
+            <v>1</v>
+          </cell>
+          <cell r="Y7">
+            <v>0</v>
+          </cell>
+          <cell r="Z7">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="A8">
+            <v>7</v>
+          </cell>
+          <cell r="B8">
+            <v>0</v>
+          </cell>
+          <cell r="C8">
+            <v>0</v>
+          </cell>
+          <cell r="D8">
+            <v>0</v>
+          </cell>
+          <cell r="E8">
+            <v>0</v>
+          </cell>
+          <cell r="F8">
+            <v>0</v>
+          </cell>
+          <cell r="G8">
+            <v>0</v>
+          </cell>
+          <cell r="H8">
+            <v>0</v>
+          </cell>
+          <cell r="I8">
+            <v>0</v>
+          </cell>
+          <cell r="J8">
+            <v>0</v>
+          </cell>
+          <cell r="K8">
+            <v>0</v>
+          </cell>
+          <cell r="L8">
+            <v>1</v>
+          </cell>
+          <cell r="M8">
+            <v>0</v>
+          </cell>
+          <cell r="N8">
+            <v>0</v>
+          </cell>
+          <cell r="O8">
+            <v>0</v>
+          </cell>
+          <cell r="P8">
+            <v>0</v>
+          </cell>
+          <cell r="Q8">
+            <v>0</v>
+          </cell>
+          <cell r="R8">
+            <v>1</v>
+          </cell>
+          <cell r="S8">
+            <v>0</v>
+          </cell>
+          <cell r="T8">
+            <v>0</v>
+          </cell>
+          <cell r="U8">
+            <v>0</v>
+          </cell>
+          <cell r="V8">
+            <v>1</v>
+          </cell>
+          <cell r="W8">
+            <v>1</v>
+          </cell>
+          <cell r="X8">
+            <v>1</v>
+          </cell>
+          <cell r="Y8">
+            <v>0</v>
+          </cell>
+          <cell r="Z8">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="A9">
+            <v>8</v>
+          </cell>
+          <cell r="B9">
+            <v>0</v>
+          </cell>
+          <cell r="C9">
+            <v>0</v>
+          </cell>
+          <cell r="D9">
+            <v>0</v>
+          </cell>
+          <cell r="E9">
+            <v>0</v>
+          </cell>
+          <cell r="F9">
+            <v>0</v>
+          </cell>
+          <cell r="G9">
+            <v>0</v>
+          </cell>
+          <cell r="H9">
+            <v>0</v>
+          </cell>
+          <cell r="I9">
+            <v>0</v>
+          </cell>
+          <cell r="J9">
+            <v>0</v>
+          </cell>
+          <cell r="K9">
+            <v>0</v>
+          </cell>
+          <cell r="L9">
+            <v>1</v>
+          </cell>
+          <cell r="M9">
+            <v>0</v>
+          </cell>
+          <cell r="N9">
+            <v>0</v>
+          </cell>
+          <cell r="O9">
+            <v>0</v>
+          </cell>
+          <cell r="P9">
+            <v>0</v>
+          </cell>
+          <cell r="Q9">
+            <v>0</v>
+          </cell>
+          <cell r="R9">
+            <v>0</v>
+          </cell>
+          <cell r="S9">
+            <v>0</v>
+          </cell>
+          <cell r="T9">
+            <v>0</v>
+          </cell>
+          <cell r="U9">
+            <v>0</v>
+          </cell>
+          <cell r="V9">
+            <v>1</v>
+          </cell>
+          <cell r="W9">
+            <v>0</v>
+          </cell>
+          <cell r="X9">
+            <v>1</v>
+          </cell>
+          <cell r="Y9">
+            <v>0</v>
+          </cell>
+          <cell r="Z9">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="A10">
+            <v>9</v>
+          </cell>
+          <cell r="B10">
+            <v>0</v>
+          </cell>
+          <cell r="C10">
+            <v>0</v>
+          </cell>
+          <cell r="D10">
+            <v>0</v>
+          </cell>
+          <cell r="E10">
+            <v>0</v>
+          </cell>
+          <cell r="F10">
+            <v>1</v>
+          </cell>
+          <cell r="G10">
+            <v>0</v>
+          </cell>
+          <cell r="H10">
+            <v>0</v>
+          </cell>
+          <cell r="I10">
+            <v>0</v>
+          </cell>
+          <cell r="J10">
+            <v>0</v>
+          </cell>
+          <cell r="K10">
+            <v>0</v>
+          </cell>
+          <cell r="L10">
+            <v>0</v>
+          </cell>
+          <cell r="M10">
+            <v>0</v>
+          </cell>
+          <cell r="N10">
+            <v>0</v>
+          </cell>
+          <cell r="O10">
+            <v>0</v>
+          </cell>
+          <cell r="P10">
+            <v>0</v>
+          </cell>
+          <cell r="Q10">
+            <v>1</v>
+          </cell>
+          <cell r="R10">
+            <v>0</v>
+          </cell>
+          <cell r="S10">
+            <v>0</v>
+          </cell>
+          <cell r="T10">
+            <v>0</v>
+          </cell>
+          <cell r="U10">
+            <v>0</v>
+          </cell>
+          <cell r="V10">
+            <v>1</v>
+          </cell>
+          <cell r="W10">
+            <v>1</v>
+          </cell>
+          <cell r="X10">
+            <v>1</v>
+          </cell>
+          <cell r="Y10">
+            <v>0</v>
+          </cell>
+          <cell r="Z10">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="A11">
+            <v>10</v>
+          </cell>
+          <cell r="B11">
+            <v>0</v>
+          </cell>
+          <cell r="C11">
+            <v>0</v>
+          </cell>
+          <cell r="D11">
+            <v>0</v>
+          </cell>
+          <cell r="E11">
+            <v>0</v>
+          </cell>
+          <cell r="F11">
+            <v>0</v>
+          </cell>
+          <cell r="G11">
+            <v>0</v>
+          </cell>
+          <cell r="H11">
+            <v>0</v>
+          </cell>
+          <cell r="I11">
+            <v>0</v>
+          </cell>
+          <cell r="J11">
+            <v>0</v>
+          </cell>
+          <cell r="K11">
+            <v>0</v>
+          </cell>
+          <cell r="L11">
+            <v>1</v>
+          </cell>
+          <cell r="M11">
+            <v>0</v>
+          </cell>
+          <cell r="N11">
+            <v>0</v>
+          </cell>
+          <cell r="O11">
+            <v>0</v>
+          </cell>
+          <cell r="P11">
+            <v>0</v>
+          </cell>
+          <cell r="Q11">
+            <v>0</v>
+          </cell>
+          <cell r="R11">
+            <v>0</v>
+          </cell>
+          <cell r="S11">
+            <v>1</v>
+          </cell>
+          <cell r="T11">
+            <v>0</v>
+          </cell>
+          <cell r="U11">
+            <v>0</v>
+          </cell>
+          <cell r="V11">
+            <v>0</v>
+          </cell>
+          <cell r="W11">
+            <v>1</v>
+          </cell>
+          <cell r="X11">
+            <v>0</v>
+          </cell>
+          <cell r="Y11">
+            <v>0</v>
+          </cell>
+          <cell r="Z11">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="A12">
+            <v>11</v>
+          </cell>
+          <cell r="B12">
+            <v>0</v>
+          </cell>
+          <cell r="C12">
+            <v>0</v>
+          </cell>
+          <cell r="D12">
+            <v>0</v>
+          </cell>
+          <cell r="E12">
+            <v>0</v>
+          </cell>
+          <cell r="F12">
+            <v>0</v>
+          </cell>
+          <cell r="G12">
+            <v>0</v>
+          </cell>
+          <cell r="H12">
+            <v>0</v>
+          </cell>
+          <cell r="I12">
+            <v>0</v>
+          </cell>
+          <cell r="J12">
+            <v>0</v>
+          </cell>
+          <cell r="K12">
+            <v>0</v>
+          </cell>
+          <cell r="L12">
+            <v>1</v>
+          </cell>
+          <cell r="M12">
+            <v>0</v>
+          </cell>
+          <cell r="N12">
+            <v>0</v>
+          </cell>
+          <cell r="O12">
+            <v>0</v>
+          </cell>
+          <cell r="P12">
+            <v>0</v>
+          </cell>
+          <cell r="Q12">
+            <v>0</v>
+          </cell>
+          <cell r="R12">
+            <v>0</v>
+          </cell>
+          <cell r="S12">
+            <v>0</v>
+          </cell>
+          <cell r="T12">
+            <v>0</v>
+          </cell>
+          <cell r="U12">
+            <v>0</v>
+          </cell>
+          <cell r="V12">
+            <v>0</v>
+          </cell>
+          <cell r="W12">
+            <v>0</v>
+          </cell>
+          <cell r="X12">
+            <v>1</v>
+          </cell>
+          <cell r="Y12">
+            <v>0</v>
+          </cell>
+          <cell r="Z12">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="A13">
+            <v>12</v>
+          </cell>
+          <cell r="B13">
+            <v>0</v>
+          </cell>
+          <cell r="C13">
+            <v>0</v>
+          </cell>
+          <cell r="D13">
+            <v>0</v>
+          </cell>
+          <cell r="E13">
+            <v>0</v>
+          </cell>
+          <cell r="F13">
+            <v>0</v>
+          </cell>
+          <cell r="G13">
+            <v>0</v>
+          </cell>
+          <cell r="H13">
+            <v>0</v>
+          </cell>
+          <cell r="I13">
+            <v>0</v>
+          </cell>
+          <cell r="J13">
+            <v>0</v>
+          </cell>
+          <cell r="K13">
+            <v>0</v>
+          </cell>
+          <cell r="L13">
+            <v>0</v>
+          </cell>
+          <cell r="M13">
+            <v>0</v>
+          </cell>
+          <cell r="N13">
+            <v>0</v>
+          </cell>
+          <cell r="O13">
+            <v>0</v>
+          </cell>
+          <cell r="P13">
+            <v>0</v>
+          </cell>
+          <cell r="Q13">
+            <v>0</v>
+          </cell>
+          <cell r="R13">
+            <v>1</v>
+          </cell>
+          <cell r="S13">
+            <v>1</v>
+          </cell>
+          <cell r="T13">
+            <v>0</v>
+          </cell>
+          <cell r="U13">
+            <v>0</v>
+          </cell>
+          <cell r="V13">
+            <v>0</v>
+          </cell>
+          <cell r="W13">
+            <v>0</v>
+          </cell>
+          <cell r="X13">
+            <v>0</v>
+          </cell>
+          <cell r="Y13">
+            <v>0</v>
+          </cell>
+          <cell r="Z13">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="A14">
+            <v>13</v>
+          </cell>
+          <cell r="B14">
+            <v>0</v>
+          </cell>
+          <cell r="C14">
+            <v>0</v>
+          </cell>
+          <cell r="D14">
+            <v>0</v>
+          </cell>
+          <cell r="E14">
+            <v>0</v>
+          </cell>
+          <cell r="F14">
+            <v>1</v>
+          </cell>
+          <cell r="G14">
+            <v>0</v>
+          </cell>
+          <cell r="H14">
+            <v>0</v>
+          </cell>
+          <cell r="I14">
+            <v>0</v>
+          </cell>
+          <cell r="J14">
+            <v>0</v>
+          </cell>
+          <cell r="K14">
+            <v>1</v>
+          </cell>
+          <cell r="L14">
+            <v>0</v>
+          </cell>
+          <cell r="M14">
+            <v>0</v>
+          </cell>
+          <cell r="N14">
+            <v>0</v>
+          </cell>
+          <cell r="O14">
+            <v>0</v>
+          </cell>
+          <cell r="P14">
+            <v>0</v>
+          </cell>
+          <cell r="Q14">
+            <v>0</v>
+          </cell>
+          <cell r="R14">
+            <v>0</v>
+          </cell>
+          <cell r="S14">
+            <v>1</v>
+          </cell>
+          <cell r="T14">
+            <v>0</v>
+          </cell>
+          <cell r="U14">
+            <v>0</v>
+          </cell>
+          <cell r="V14">
+            <v>1</v>
+          </cell>
+          <cell r="W14">
+            <v>1</v>
+          </cell>
+          <cell r="X14">
+            <v>0</v>
+          </cell>
+          <cell r="Y14">
+            <v>0</v>
+          </cell>
+          <cell r="Z14">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="15">
+          <cell r="A15">
+            <v>14</v>
+          </cell>
+          <cell r="B15">
+            <v>0</v>
+          </cell>
+          <cell r="C15">
+            <v>0</v>
+          </cell>
+          <cell r="D15">
+            <v>0</v>
+          </cell>
+          <cell r="E15">
+            <v>0</v>
+          </cell>
+          <cell r="F15">
+            <v>0</v>
+          </cell>
+          <cell r="G15">
+            <v>0</v>
+          </cell>
+          <cell r="H15">
+            <v>0</v>
+          </cell>
+          <cell r="I15">
+            <v>0</v>
+          </cell>
+          <cell r="J15">
+            <v>0</v>
+          </cell>
+          <cell r="K15">
+            <v>0</v>
+          </cell>
+          <cell r="L15">
+            <v>0</v>
+          </cell>
+          <cell r="M15">
+            <v>0</v>
+          </cell>
+          <cell r="N15">
+            <v>0</v>
+          </cell>
+          <cell r="O15">
+            <v>0</v>
+          </cell>
+          <cell r="P15">
+            <v>0</v>
+          </cell>
+          <cell r="Q15">
+            <v>1</v>
+          </cell>
+          <cell r="R15">
+            <v>0</v>
+          </cell>
+          <cell r="S15">
+            <v>1</v>
+          </cell>
+          <cell r="T15">
+            <v>0</v>
+          </cell>
+          <cell r="U15">
+            <v>0</v>
+          </cell>
+          <cell r="V15">
+            <v>0</v>
+          </cell>
+          <cell r="W15">
+            <v>1</v>
+          </cell>
+          <cell r="X15">
+            <v>0</v>
+          </cell>
+          <cell r="Y15">
+            <v>0</v>
+          </cell>
+          <cell r="Z15">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="A16">
+            <v>15</v>
+          </cell>
+          <cell r="B16">
+            <v>0</v>
+          </cell>
+          <cell r="C16">
+            <v>0</v>
+          </cell>
+          <cell r="D16">
+            <v>0</v>
+          </cell>
+          <cell r="E16">
+            <v>0</v>
+          </cell>
+          <cell r="F16">
+            <v>0</v>
+          </cell>
+          <cell r="G16">
+            <v>0</v>
+          </cell>
+          <cell r="H16">
+            <v>0</v>
+          </cell>
+          <cell r="I16">
+            <v>0</v>
+          </cell>
+          <cell r="J16">
+            <v>0</v>
+          </cell>
+          <cell r="K16">
+            <v>1</v>
+          </cell>
+          <cell r="L16">
+            <v>0</v>
+          </cell>
+          <cell r="M16">
+            <v>0</v>
+          </cell>
+          <cell r="N16">
+            <v>0</v>
+          </cell>
+          <cell r="O16">
+            <v>0</v>
+          </cell>
+          <cell r="P16">
+            <v>0</v>
+          </cell>
+          <cell r="Q16">
+            <v>0</v>
+          </cell>
+          <cell r="R16">
+            <v>0</v>
+          </cell>
+          <cell r="S16">
+            <v>0</v>
+          </cell>
+          <cell r="T16">
+            <v>0</v>
+          </cell>
+          <cell r="U16">
+            <v>0</v>
+          </cell>
+          <cell r="V16">
+            <v>1</v>
+          </cell>
+          <cell r="W16">
+            <v>0</v>
+          </cell>
+          <cell r="X16">
+            <v>0</v>
+          </cell>
+          <cell r="Y16">
+            <v>0</v>
+          </cell>
+          <cell r="Z16">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="A17">
+            <v>16</v>
+          </cell>
+          <cell r="B17">
+            <v>0</v>
+          </cell>
+          <cell r="C17">
+            <v>0</v>
+          </cell>
+          <cell r="D17">
+            <v>0</v>
+          </cell>
+          <cell r="E17">
+            <v>0</v>
+          </cell>
+          <cell r="F17">
+            <v>0</v>
+          </cell>
+          <cell r="G17">
+            <v>0</v>
+          </cell>
+          <cell r="H17">
+            <v>0</v>
+          </cell>
+          <cell r="I17">
+            <v>0</v>
+          </cell>
+          <cell r="J17">
+            <v>0</v>
+          </cell>
+          <cell r="K17">
+            <v>0</v>
+          </cell>
+          <cell r="L17">
+            <v>0</v>
+          </cell>
+          <cell r="M17">
+            <v>0</v>
+          </cell>
+          <cell r="N17">
+            <v>0</v>
+          </cell>
+          <cell r="O17">
+            <v>0</v>
+          </cell>
+          <cell r="P17">
+            <v>0</v>
+          </cell>
+          <cell r="Q17">
+            <v>0</v>
+          </cell>
+          <cell r="R17">
+            <v>1</v>
+          </cell>
+          <cell r="S17">
+            <v>0</v>
+          </cell>
+          <cell r="T17">
+            <v>0</v>
+          </cell>
+          <cell r="U17">
+            <v>0</v>
+          </cell>
+          <cell r="V17">
+            <v>0</v>
+          </cell>
+          <cell r="W17">
+            <v>0</v>
+          </cell>
+          <cell r="X17">
+            <v>1</v>
+          </cell>
+          <cell r="Y17">
+            <v>0</v>
+          </cell>
+          <cell r="Z17">
+            <v>0</v>
           </cell>
         </row>
       </sheetData>
@@ -3976,7 +5945,7 @@
       <sheetName val="resultados_integracion_partido_"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0">
+      <sheetData sheetId="0" refreshError="1">
         <row r="1">
           <cell r="A1" t="str">
             <v>Circunscripcion</v>
@@ -5404,7 +7373,7 @@
       <sheetName val="resultados_integracion_partido_"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0">
+      <sheetData sheetId="0" refreshError="1">
         <row r="1">
           <cell r="A1" t="str">
             <v>Circunscripcion</v>
@@ -6832,7 +8801,7 @@
       <sheetName val="resultados_integracion_partido_"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0">
+      <sheetData sheetId="0" refreshError="1">
         <row r="1">
           <cell r="A1" t="str">
             <v>Circunscripcion</v>
@@ -8260,7 +10229,7 @@
       <sheetName val="resultados_integracion_partido_"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0">
+      <sheetData sheetId="0" refreshError="1">
         <row r="1">
           <cell r="A1" t="str">
             <v>Circunscripcion</v>
@@ -9688,7 +11657,7 @@
       <sheetName val="resultados_integracion_partido_"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0">
+      <sheetData sheetId="0" refreshError="1">
         <row r="1">
           <cell r="A1" t="str">
             <v>Circunscripcion</v>
@@ -11065,7 +13034,7 @@
       <sheetName val="resultados_integracion_partido_"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0">
+      <sheetData sheetId="0" refreshError="1">
         <row r="1">
           <cell r="A1" t="str">
             <v>Circunscripcion</v>
@@ -12442,7 +14411,7 @@
       <sheetName val="resultados_integracion_partido_"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0">
+      <sheetData sheetId="0" refreshError="1">
         <row r="1">
           <cell r="A1" t="str">
             <v>Circunscripcion</v>
@@ -13819,7 +15788,7 @@
       <sheetName val="resultados_integracion_partido_"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0">
+      <sheetData sheetId="0" refreshError="1">
         <row r="1">
           <cell r="A1" t="str">
             <v>Circunscripcion</v>
@@ -16265,13 +18234,13 @@
       <c r="AA14" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="AD14" s="40" t="s">
+      <c r="AD14" s="31" t="s">
         <v>25</v>
       </c>
       <c r="AE14" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="AH14" s="40" t="s">
+      <c r="AH14" s="31" t="s">
         <v>25</v>
       </c>
       <c r="AI14" s="17" t="s">
@@ -17008,472 +18977,76 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4:C27">
-    <cfRule type="cellIs" dxfId="140" priority="136" operator="equal">
+    <cfRule type="cellIs" dxfId="21" priority="136" operator="equal">
       <formula>"p7"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="138" priority="137" operator="equal">
+    <cfRule type="cellIs" dxfId="20" priority="137" operator="equal">
       <formula>"p6"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="139" priority="138" operator="equal">
+    <cfRule type="cellIs" dxfId="19" priority="138" operator="equal">
       <formula>"p5"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="137" priority="139" operator="equal">
+    <cfRule type="cellIs" dxfId="18" priority="139" operator="equal">
       <formula>"p4"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="136" priority="140" operator="equal">
+    <cfRule type="cellIs" dxfId="17" priority="140" operator="equal">
       <formula>"p3"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="135" priority="141" operator="equal">
+    <cfRule type="cellIs" dxfId="16" priority="141" operator="equal">
       <formula>"p2"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="141" priority="142" operator="equal">
+    <cfRule type="cellIs" dxfId="15" priority="142" operator="equal">
       <formula>"p1"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F4:G27">
-    <cfRule type="cellIs" dxfId="130" priority="94" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="94" operator="equal">
       <formula>"p7"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="131" priority="95" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="95" operator="equal">
       <formula>"p6"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="132" priority="96" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="96" operator="equal">
       <formula>"p5"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="133" priority="97" operator="equal">
+    <cfRule type="cellIs" dxfId="11" priority="97" operator="equal">
       <formula>"p4"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="134" priority="98" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="98" operator="equal">
       <formula>"p3"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="129" priority="99" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="99" operator="equal">
       <formula>"p2"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="128" priority="100" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="100" operator="equal">
       <formula>"p1"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:G27">
-    <cfRule type="cellIs" dxfId="127" priority="93" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="93" operator="equal">
       <formula>"p8"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J4:K4">
-    <cfRule type="cellIs" dxfId="126" priority="129" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="129" operator="equal">
       <formula>"p7"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="125" priority="130" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="130" operator="equal">
       <formula>"p6"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="120" priority="131" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="131" operator="equal">
       <formula>"p5"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="121" priority="132" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="132" operator="equal">
       <formula>"p4"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="122" priority="133" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="133" operator="equal">
       <formula>"p3"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="123" priority="134" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="134" operator="equal">
       <formula>"p2"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="124" priority="135" operator="equal">
-      <formula>"p1"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J5:K27 AD5:AE27">
-    <cfRule type="cellIs" dxfId="118" priority="80" operator="equal">
-      <formula>"p13"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="117" priority="81" operator="equal">
-      <formula>"p12"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="119" priority="82" operator="equal">
-      <formula>"p11"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="116" priority="83" operator="equal">
-      <formula>"p10"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="115" priority="84" operator="equal">
-      <formula>"p9"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K5:K27 AE5:AE27">
-    <cfRule type="cellIs" dxfId="107" priority="85" operator="equal">
-      <formula>"p8"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="108" priority="86" operator="equal">
-      <formula>"p7"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="109" priority="87" operator="equal">
-      <formula>"p6"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="110" priority="88" operator="equal">
-      <formula>"p5"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="113" priority="89" operator="equal">
-      <formula>"p4"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="111" priority="90" operator="equal">
-      <formula>"p3"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="112" priority="91" operator="equal">
-      <formula>"p2"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="114" priority="92" operator="equal">
-      <formula>"p1"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N4:O4">
-    <cfRule type="cellIs" dxfId="101" priority="122" operator="equal">
-      <formula>"p7"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="102" priority="123" operator="equal">
-      <formula>"p6"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="100" priority="124" operator="equal">
-      <formula>"p5"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="106" priority="125" operator="equal">
-      <formula>"p4"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="103" priority="126" operator="equal">
-      <formula>"p3"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="104" priority="127" operator="equal">
-      <formula>"p2"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="105" priority="128" operator="equal">
-      <formula>"p1"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N5:O27">
-    <cfRule type="cellIs" dxfId="96" priority="67" operator="equal">
-      <formula>"p13"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="97" priority="68" operator="equal">
-      <formula>"p12"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="98" priority="69" operator="equal">
-      <formula>"p11"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="95" priority="70" operator="equal">
-      <formula>"p10"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="99" priority="71" operator="equal">
-      <formula>"p9"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="O5:O27">
-    <cfRule type="cellIs" dxfId="94" priority="72" operator="equal">
-      <formula>"p8"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="93" priority="73" operator="equal">
-      <formula>"p7"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="92" priority="74" operator="equal">
-      <formula>"p6"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="91" priority="75" operator="equal">
-      <formula>"p5"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="90" priority="76" operator="equal">
-      <formula>"p4"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="89" priority="77" operator="equal">
-      <formula>"p3"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="88" priority="78" operator="equal">
-      <formula>"p2"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="87" priority="79" operator="equal">
-      <formula>"p1"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="R4:S4">
-    <cfRule type="cellIs" dxfId="86" priority="115" operator="equal">
-      <formula>"p7"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="80" priority="116" operator="equal">
-      <formula>"p6"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="81" priority="117" operator="equal">
-      <formula>"p5"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="82" priority="118" operator="equal">
-      <formula>"p4"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="83" priority="119" operator="equal">
-      <formula>"p3"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="84" priority="120" operator="equal">
-      <formula>"p2"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="85" priority="121" operator="equal">
-      <formula>"p1"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="R5:S27">
-    <cfRule type="cellIs" dxfId="75" priority="54" operator="equal">
-      <formula>"p13"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="78" priority="55" operator="equal">
-      <formula>"p12"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="76" priority="56" operator="equal">
-      <formula>"p11"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="77" priority="57" operator="equal">
-      <formula>"p10"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="79" priority="58" operator="equal">
-      <formula>"p9"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="S5:S27">
-    <cfRule type="cellIs" dxfId="70" priority="59" operator="equal">
-      <formula>"p8"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="71" priority="60" operator="equal">
-      <formula>"p7"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="72" priority="61" operator="equal">
-      <formula>"p6"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="73" priority="62" operator="equal">
-      <formula>"p5"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="74" priority="63" operator="equal">
-      <formula>"p4"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="67" priority="64" operator="equal">
-      <formula>"p3"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="68" priority="65" operator="equal">
-      <formula>"p2"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="69" priority="66" operator="equal">
-      <formula>"p1"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="V4:W4">
-    <cfRule type="cellIs" dxfId="60" priority="108" operator="equal">
-      <formula>"p7"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="66" priority="109" operator="equal">
-      <formula>"p6"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="61" priority="110" operator="equal">
-      <formula>"p5"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="62" priority="111" operator="equal">
-      <formula>"p4"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="63" priority="112" operator="equal">
-      <formula>"p3"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="64" priority="113" operator="equal">
-      <formula>"p2"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="65" priority="114" operator="equal">
-      <formula>"p1"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="V5:W27">
-    <cfRule type="cellIs" dxfId="59" priority="41" operator="equal">
-      <formula>"p13"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="55" priority="42" operator="equal">
-      <formula>"p12"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="56" priority="43" operator="equal">
-      <formula>"p11"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="58" priority="44" operator="equal">
-      <formula>"p10"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="57" priority="45" operator="equal">
-      <formula>"p9"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="W5:W27">
-    <cfRule type="cellIs" dxfId="54" priority="46" operator="equal">
-      <formula>"p8"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="53" priority="47" operator="equal">
-      <formula>"p7"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="52" priority="48" operator="equal">
-      <formula>"p6"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="51" priority="49" operator="equal">
-      <formula>"p5"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="50" priority="50" operator="equal">
-      <formula>"p4"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="49" priority="51" operator="equal">
-      <formula>"p3"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="47" priority="52" operator="equal">
-      <formula>"p2"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="48" priority="53" operator="equal">
-      <formula>"p1"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Z4:AA4">
-    <cfRule type="cellIs" dxfId="44" priority="101" operator="equal">
-      <formula>"p7"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="45" priority="102" operator="equal">
-      <formula>"p6"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="46" priority="103" operator="equal">
-      <formula>"p5"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="43" priority="104" operator="equal">
-      <formula>"p4"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="42" priority="105" operator="equal">
-      <formula>"p3"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="41" priority="106" operator="equal">
-      <formula>"p2"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="40" priority="107" operator="equal">
-      <formula>"p1"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Z5:AA27">
-    <cfRule type="cellIs" dxfId="39" priority="28" operator="equal">
-      <formula>"p13"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="38" priority="29" operator="equal">
-      <formula>"p12"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="37" priority="30" operator="equal">
-      <formula>"p11"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="35" priority="31" operator="equal">
-      <formula>"p10"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="36" priority="32" operator="equal">
-      <formula>"p9"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AA5:AA27">
-    <cfRule type="cellIs" dxfId="28" priority="33" operator="equal">
-      <formula>"p8"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="29" priority="34" operator="equal">
-      <formula>"p7"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="34" priority="35" operator="equal">
-      <formula>"p6"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="30" priority="36" operator="equal">
-      <formula>"p5"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="27" priority="37" operator="equal">
-      <formula>"p4"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="31" priority="38" operator="equal">
-      <formula>"p3"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="32" priority="39" operator="equal">
-      <formula>"p2"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="33" priority="40" operator="equal">
-      <formula>"p1"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD4:AE4">
-    <cfRule type="cellIs" dxfId="22" priority="21" operator="equal">
-      <formula>"p7"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="23" priority="22" operator="equal">
-      <formula>"p6"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="24" priority="23" operator="equal">
-      <formula>"p5"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="25" priority="24" operator="equal">
-      <formula>"p4"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="26" priority="25" operator="equal">
-      <formula>"p3"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="20" priority="26" operator="equal">
-      <formula>"p2"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="21" priority="27" operator="equal">
-      <formula>"p1"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AH4:AI4">
-    <cfRule type="cellIs" dxfId="13" priority="14" operator="equal">
-      <formula>"p7"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="15" priority="15" operator="equal">
-      <formula>"p6"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="17" priority="16" operator="equal">
-      <formula>"p5"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="18" priority="17" operator="equal">
-      <formula>"p4"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="16" priority="18" operator="equal">
-      <formula>"p3"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="19" priority="19" operator="equal">
-      <formula>"p2"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="14" priority="20" operator="equal">
-      <formula>"p1"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AH5:AI27">
-    <cfRule type="cellIs" dxfId="8" priority="1" operator="equal">
-      <formula>"p13"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="12" priority="2" operator="equal">
-      <formula>"p12"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="11" priority="3" operator="equal">
-      <formula>"p11"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="10" priority="4" operator="equal">
-      <formula>"p10"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="9" priority="5" operator="equal">
-      <formula>"p9"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AI5:AI27">
-    <cfRule type="cellIs" dxfId="7" priority="6" operator="equal">
-      <formula>"p8"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="5" priority="7" operator="equal">
-      <formula>"p7"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="8" operator="equal">
-      <formula>"p6"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="9" operator="equal">
-      <formula>"p5"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="10" operator="equal">
-      <formula>"p4"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="11" operator="equal">
-      <formula>"p3"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="12" operator="equal">
-      <formula>"p2"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="13" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="135" operator="equal">
       <formula>"p1"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -17484,8 +19057,728 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4570876E-5C95-4658-A458-65BCE2086BBD}">
+  <dimension ref="A2:O13"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="19.36328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="15" width="6.1796875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A3" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="41">
+        <v>1</v>
+      </c>
+      <c r="C3" s="41">
+        <v>3</v>
+      </c>
+      <c r="D3" s="41">
+        <v>4</v>
+      </c>
+      <c r="E3" s="41">
+        <v>1</v>
+      </c>
+      <c r="F3" s="41">
+        <v>5</v>
+      </c>
+      <c r="G3" s="41">
+        <v>1</v>
+      </c>
+      <c r="H3" s="41">
+        <v>0</v>
+      </c>
+      <c r="I3" s="41">
+        <v>4</v>
+      </c>
+      <c r="J3" s="41">
+        <v>2</v>
+      </c>
+      <c r="K3" s="41">
+        <v>0</v>
+      </c>
+      <c r="L3" s="41">
+        <v>1</v>
+      </c>
+      <c r="M3" s="41">
+        <v>0</v>
+      </c>
+      <c r="N3" s="41">
+        <v>1</v>
+      </c>
+      <c r="O3" s="41">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A4" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="1">
+        <f>IFERROR(INDEX('C15'!$B$2:$Z$14,MATCH($A4,'C15'!$B$2:$B$14,0),MATCH(B$2,'C15'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C1'!$B$2:$Z$14,MATCH($A4,'C1'!$B$2:$B$14,0),MATCH(B$2,'C1'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C3'!$B$2:$Z$14,MATCH($A4,'C3'!$B$2:$B$14,0),MATCH(B$2,'C3'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C5'!$B$2:$Z$14,MATCH($A4,'C5'!$B$2:$B$14,0),MATCH(B$2,'C5'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C7'!$B$2:$Z$14,MATCH($A4,'C7'!$B$2:$B$14,0),MATCH(B$2,'C7'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C9'!$B$2:$Z$14,MATCH($A4,'C9'!$B$2:$B$14,0),MATCH(B$2,'C9'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C11'!$B$2:$Z$14,MATCH($A4,'C11'!$B$2:$B$14,0),MATCH(B$2,'C11'!$B$2:$Z$2,0)),0)</f>
+        <v>1</v>
+      </c>
+      <c r="C4" s="1">
+        <f>IFERROR(INDEX('C15'!$B$2:$Z$14,MATCH($A4,'C15'!$B$2:$B$14,0),MATCH(C$2,'C15'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C1'!$B$2:$Z$14,MATCH($A4,'C1'!$B$2:$B$14,0),MATCH(C$2,'C1'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C3'!$B$2:$Z$14,MATCH($A4,'C3'!$B$2:$B$14,0),MATCH(C$2,'C3'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C5'!$B$2:$Z$14,MATCH($A4,'C5'!$B$2:$B$14,0),MATCH(C$2,'C5'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C7'!$B$2:$Z$14,MATCH($A4,'C7'!$B$2:$B$14,0),MATCH(C$2,'C7'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C9'!$B$2:$Z$14,MATCH($A4,'C9'!$B$2:$B$14,0),MATCH(C$2,'C9'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C11'!$B$2:$Z$14,MATCH($A4,'C11'!$B$2:$B$14,0),MATCH(C$2,'C11'!$B$2:$Z$2,0)),0)</f>
+        <v>0</v>
+      </c>
+      <c r="D4" s="1">
+        <f>IFERROR(INDEX('C15'!$B$2:$Z$14,MATCH($A4,'C15'!$B$2:$B$14,0),MATCH(D$2,'C15'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C1'!$B$2:$Z$14,MATCH($A4,'C1'!$B$2:$B$14,0),MATCH(D$2,'C1'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C3'!$B$2:$Z$14,MATCH($A4,'C3'!$B$2:$B$14,0),MATCH(D$2,'C3'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C5'!$B$2:$Z$14,MATCH($A4,'C5'!$B$2:$B$14,0),MATCH(D$2,'C5'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C7'!$B$2:$Z$14,MATCH($A4,'C7'!$B$2:$B$14,0),MATCH(D$2,'C7'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C9'!$B$2:$Z$14,MATCH($A4,'C9'!$B$2:$B$14,0),MATCH(D$2,'C9'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C11'!$B$2:$Z$14,MATCH($A4,'C11'!$B$2:$B$14,0),MATCH(D$2,'C11'!$B$2:$Z$2,0)),0)</f>
+        <v>4</v>
+      </c>
+      <c r="E4" s="1">
+        <f>IFERROR(INDEX('C15'!$B$2:$Z$14,MATCH($A4,'C15'!$B$2:$B$14,0),MATCH(E$2,'C15'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C1'!$B$2:$Z$14,MATCH($A4,'C1'!$B$2:$B$14,0),MATCH(E$2,'C1'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C3'!$B$2:$Z$14,MATCH($A4,'C3'!$B$2:$B$14,0),MATCH(E$2,'C3'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C5'!$B$2:$Z$14,MATCH($A4,'C5'!$B$2:$B$14,0),MATCH(E$2,'C5'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C7'!$B$2:$Z$14,MATCH($A4,'C7'!$B$2:$B$14,0),MATCH(E$2,'C7'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C9'!$B$2:$Z$14,MATCH($A4,'C9'!$B$2:$B$14,0),MATCH(E$2,'C9'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C11'!$B$2:$Z$14,MATCH($A4,'C11'!$B$2:$B$14,0),MATCH(E$2,'C11'!$B$2:$Z$2,0)),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F4" s="1">
+        <f>IFERROR(INDEX('C15'!$B$2:$Z$14,MATCH($A4,'C15'!$B$2:$B$14,0),MATCH(F$2,'C15'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C1'!$B$2:$Z$14,MATCH($A4,'C1'!$B$2:$B$14,0),MATCH(F$2,'C1'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C3'!$B$2:$Z$14,MATCH($A4,'C3'!$B$2:$B$14,0),MATCH(F$2,'C3'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C5'!$B$2:$Z$14,MATCH($A4,'C5'!$B$2:$B$14,0),MATCH(F$2,'C5'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C7'!$B$2:$Z$14,MATCH($A4,'C7'!$B$2:$B$14,0),MATCH(F$2,'C7'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C9'!$B$2:$Z$14,MATCH($A4,'C9'!$B$2:$B$14,0),MATCH(F$2,'C9'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C11'!$B$2:$Z$14,MATCH($A4,'C11'!$B$2:$B$14,0),MATCH(F$2,'C11'!$B$2:$Z$2,0)),0)</f>
+        <v>9</v>
+      </c>
+      <c r="G4" s="1">
+        <f>IFERROR(INDEX('C15'!$B$2:$Z$14,MATCH($A4,'C15'!$B$2:$B$14,0),MATCH(G$2,'C15'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C1'!$B$2:$Z$14,MATCH($A4,'C1'!$B$2:$B$14,0),MATCH(G$2,'C1'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C3'!$B$2:$Z$14,MATCH($A4,'C3'!$B$2:$B$14,0),MATCH(G$2,'C3'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C5'!$B$2:$Z$14,MATCH($A4,'C5'!$B$2:$B$14,0),MATCH(G$2,'C5'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C7'!$B$2:$Z$14,MATCH($A4,'C7'!$B$2:$B$14,0),MATCH(G$2,'C7'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C9'!$B$2:$Z$14,MATCH($A4,'C9'!$B$2:$B$14,0),MATCH(G$2,'C9'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C11'!$B$2:$Z$14,MATCH($A4,'C11'!$B$2:$B$14,0),MATCH(G$2,'C11'!$B$2:$Z$2,0)),0)</f>
+        <v>6</v>
+      </c>
+      <c r="H4" s="1">
+        <f>IFERROR(INDEX('C15'!$B$2:$Z$14,MATCH($A4,'C15'!$B$2:$B$14,0),MATCH(H$2,'C15'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C1'!$B$2:$Z$14,MATCH($A4,'C1'!$B$2:$B$14,0),MATCH(H$2,'C1'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C3'!$B$2:$Z$14,MATCH($A4,'C3'!$B$2:$B$14,0),MATCH(H$2,'C3'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C5'!$B$2:$Z$14,MATCH($A4,'C5'!$B$2:$B$14,0),MATCH(H$2,'C5'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C7'!$B$2:$Z$14,MATCH($A4,'C7'!$B$2:$B$14,0),MATCH(H$2,'C7'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C9'!$B$2:$Z$14,MATCH($A4,'C9'!$B$2:$B$14,0),MATCH(H$2,'C9'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C11'!$B$2:$Z$14,MATCH($A4,'C11'!$B$2:$B$14,0),MATCH(H$2,'C11'!$B$2:$Z$2,0)),0)</f>
+        <v>0</v>
+      </c>
+      <c r="I4" s="1">
+        <f>IFERROR(INDEX('C15'!$B$2:$Z$14,MATCH($A4,'C15'!$B$2:$B$14,0),MATCH(I$2,'C15'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C1'!$B$2:$Z$14,MATCH($A4,'C1'!$B$2:$B$14,0),MATCH(I$2,'C1'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C3'!$B$2:$Z$14,MATCH($A4,'C3'!$B$2:$B$14,0),MATCH(I$2,'C3'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C5'!$B$2:$Z$14,MATCH($A4,'C5'!$B$2:$B$14,0),MATCH(I$2,'C5'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C7'!$B$2:$Z$14,MATCH($A4,'C7'!$B$2:$B$14,0),MATCH(I$2,'C7'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C9'!$B$2:$Z$14,MATCH($A4,'C9'!$B$2:$B$14,0),MATCH(I$2,'C9'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C11'!$B$2:$Z$14,MATCH($A4,'C11'!$B$2:$B$14,0),MATCH(I$2,'C11'!$B$2:$Z$2,0)),0)</f>
+        <v>1</v>
+      </c>
+      <c r="J4" s="1">
+        <f>IFERROR(INDEX('C15'!$B$2:$Z$14,MATCH($A4,'C15'!$B$2:$B$14,0),MATCH(J$2,'C15'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C1'!$B$2:$Z$14,MATCH($A4,'C1'!$B$2:$B$14,0),MATCH(J$2,'C1'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C3'!$B$2:$Z$14,MATCH($A4,'C3'!$B$2:$B$14,0),MATCH(J$2,'C3'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C5'!$B$2:$Z$14,MATCH($A4,'C5'!$B$2:$B$14,0),MATCH(J$2,'C5'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C7'!$B$2:$Z$14,MATCH($A4,'C7'!$B$2:$B$14,0),MATCH(J$2,'C7'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C9'!$B$2:$Z$14,MATCH($A4,'C9'!$B$2:$B$14,0),MATCH(J$2,'C9'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C11'!$B$2:$Z$14,MATCH($A4,'C11'!$B$2:$B$14,0),MATCH(J$2,'C11'!$B$2:$Z$2,0)),0)</f>
+        <v>0</v>
+      </c>
+      <c r="K4" s="1">
+        <f>IFERROR(INDEX('C15'!$B$2:$Z$14,MATCH($A4,'C15'!$B$2:$B$14,0),MATCH(K$2,'C15'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C1'!$B$2:$Z$14,MATCH($A4,'C1'!$B$2:$B$14,0),MATCH(K$2,'C1'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C3'!$B$2:$Z$14,MATCH($A4,'C3'!$B$2:$B$14,0),MATCH(K$2,'C3'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C5'!$B$2:$Z$14,MATCH($A4,'C5'!$B$2:$B$14,0),MATCH(K$2,'C5'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C7'!$B$2:$Z$14,MATCH($A4,'C7'!$B$2:$B$14,0),MATCH(K$2,'C7'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C9'!$B$2:$Z$14,MATCH($A4,'C9'!$B$2:$B$14,0),MATCH(K$2,'C9'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C11'!$B$2:$Z$14,MATCH($A4,'C11'!$B$2:$B$14,0),MATCH(K$2,'C11'!$B$2:$Z$2,0)),0)</f>
+        <v>1</v>
+      </c>
+      <c r="L4" s="1">
+        <f>IFERROR(INDEX('C15'!$B$2:$Z$14,MATCH($A4,'C15'!$B$2:$B$14,0),MATCH(L$2,'C15'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C1'!$B$2:$Z$14,MATCH($A4,'C1'!$B$2:$B$14,0),MATCH(L$2,'C1'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C3'!$B$2:$Z$14,MATCH($A4,'C3'!$B$2:$B$14,0),MATCH(L$2,'C3'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C5'!$B$2:$Z$14,MATCH($A4,'C5'!$B$2:$B$14,0),MATCH(L$2,'C5'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C7'!$B$2:$Z$14,MATCH($A4,'C7'!$B$2:$B$14,0),MATCH(L$2,'C7'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C9'!$B$2:$Z$14,MATCH($A4,'C9'!$B$2:$B$14,0),MATCH(L$2,'C9'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C11'!$B$2:$Z$14,MATCH($A4,'C11'!$B$2:$B$14,0),MATCH(L$2,'C11'!$B$2:$Z$2,0)),0)</f>
+        <v>0</v>
+      </c>
+      <c r="M4" s="1">
+        <f>IFERROR(INDEX('C15'!$B$2:$Z$14,MATCH($A4,'C15'!$B$2:$B$14,0),MATCH(M$2,'C15'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C1'!$B$2:$Z$14,MATCH($A4,'C1'!$B$2:$B$14,0),MATCH(M$2,'C1'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C3'!$B$2:$Z$14,MATCH($A4,'C3'!$B$2:$B$14,0),MATCH(M$2,'C3'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C5'!$B$2:$Z$14,MATCH($A4,'C5'!$B$2:$B$14,0),MATCH(M$2,'C5'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C7'!$B$2:$Z$14,MATCH($A4,'C7'!$B$2:$B$14,0),MATCH(M$2,'C7'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C9'!$B$2:$Z$14,MATCH($A4,'C9'!$B$2:$B$14,0),MATCH(M$2,'C9'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C11'!$B$2:$Z$14,MATCH($A4,'C11'!$B$2:$B$14,0),MATCH(M$2,'C11'!$B$2:$Z$2,0)),0)</f>
+        <v>1</v>
+      </c>
+      <c r="N4" s="1">
+        <f>IFERROR(INDEX('C15'!$B$2:$Z$14,MATCH($A4,'C15'!$B$2:$B$14,0),MATCH(N$2,'C15'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C1'!$B$2:$Z$14,MATCH($A4,'C1'!$B$2:$B$14,0),MATCH(N$2,'C1'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C3'!$B$2:$Z$14,MATCH($A4,'C3'!$B$2:$B$14,0),MATCH(N$2,'C3'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C5'!$B$2:$Z$14,MATCH($A4,'C5'!$B$2:$B$14,0),MATCH(N$2,'C5'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C7'!$B$2:$Z$14,MATCH($A4,'C7'!$B$2:$B$14,0),MATCH(N$2,'C7'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C9'!$B$2:$Z$14,MATCH($A4,'C9'!$B$2:$B$14,0),MATCH(N$2,'C9'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C11'!$B$2:$Z$14,MATCH($A4,'C11'!$B$2:$B$14,0),MATCH(N$2,'C11'!$B$2:$Z$2,0)),0)</f>
+        <v>0</v>
+      </c>
+      <c r="O4" s="1">
+        <f>IFERROR(INDEX('C15'!$B$2:$Z$14,MATCH($A4,'C15'!$B$2:$B$14,0),MATCH(O$2,'C15'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C1'!$B$2:$Z$14,MATCH($A4,'C1'!$B$2:$B$14,0),MATCH(O$2,'C1'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C3'!$B$2:$Z$14,MATCH($A4,'C3'!$B$2:$B$14,0),MATCH(O$2,'C3'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C5'!$B$2:$Z$14,MATCH($A4,'C5'!$B$2:$B$14,0),MATCH(O$2,'C5'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C7'!$B$2:$Z$14,MATCH($A4,'C7'!$B$2:$B$14,0),MATCH(O$2,'C7'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C9'!$B$2:$Z$14,MATCH($A4,'C9'!$B$2:$B$14,0),MATCH(O$2,'C9'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C11'!$B$2:$Z$14,MATCH($A4,'C11'!$B$2:$B$14,0),MATCH(O$2,'C11'!$B$2:$Z$2,0)),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="1">
+        <f>IFERROR(INDEX('C15'!$B$2:$Z$14,MATCH($A5,'C15'!$B$2:$B$14,0),MATCH(B$2,'C15'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C1'!$B$2:$Z$14,MATCH($A5,'C1'!$B$2:$B$14,0),MATCH(B$2,'C1'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C3'!$B$2:$Z$14,MATCH($A5,'C3'!$B$2:$B$14,0),MATCH(B$2,'C3'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C5'!$B$2:$Z$14,MATCH($A5,'C5'!$B$2:$B$14,0),MATCH(B$2,'C5'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C7'!$B$2:$Z$14,MATCH($A5,'C7'!$B$2:$B$14,0),MATCH(B$2,'C7'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C9'!$B$2:$Z$14,MATCH($A5,'C9'!$B$2:$B$14,0),MATCH(B$2,'C9'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C11'!$B$2:$Z$14,MATCH($A5,'C11'!$B$2:$B$14,0),MATCH(B$2,'C11'!$B$2:$Z$2,0)),0)</f>
+        <v>1</v>
+      </c>
+      <c r="C5" s="1">
+        <f>IFERROR(INDEX('C15'!$B$2:$Z$14,MATCH($A5,'C15'!$B$2:$B$14,0),MATCH(C$2,'C15'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C1'!$B$2:$Z$14,MATCH($A5,'C1'!$B$2:$B$14,0),MATCH(C$2,'C1'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C3'!$B$2:$Z$14,MATCH($A5,'C3'!$B$2:$B$14,0),MATCH(C$2,'C3'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C5'!$B$2:$Z$14,MATCH($A5,'C5'!$B$2:$B$14,0),MATCH(C$2,'C5'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C7'!$B$2:$Z$14,MATCH($A5,'C7'!$B$2:$B$14,0),MATCH(C$2,'C7'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C9'!$B$2:$Z$14,MATCH($A5,'C9'!$B$2:$B$14,0),MATCH(C$2,'C9'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C11'!$B$2:$Z$14,MATCH($A5,'C11'!$B$2:$B$14,0),MATCH(C$2,'C11'!$B$2:$Z$2,0)),0)</f>
+        <v>1</v>
+      </c>
+      <c r="D5" s="1">
+        <f>IFERROR(INDEX('C15'!$B$2:$Z$14,MATCH($A5,'C15'!$B$2:$B$14,0),MATCH(D$2,'C15'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C1'!$B$2:$Z$14,MATCH($A5,'C1'!$B$2:$B$14,0),MATCH(D$2,'C1'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C3'!$B$2:$Z$14,MATCH($A5,'C3'!$B$2:$B$14,0),MATCH(D$2,'C3'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C5'!$B$2:$Z$14,MATCH($A5,'C5'!$B$2:$B$14,0),MATCH(D$2,'C5'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C7'!$B$2:$Z$14,MATCH($A5,'C7'!$B$2:$B$14,0),MATCH(D$2,'C7'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C9'!$B$2:$Z$14,MATCH($A5,'C9'!$B$2:$B$14,0),MATCH(D$2,'C9'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C11'!$B$2:$Z$14,MATCH($A5,'C11'!$B$2:$B$14,0),MATCH(D$2,'C11'!$B$2:$Z$2,0)),0)</f>
+        <v>3</v>
+      </c>
+      <c r="E5" s="1">
+        <f>IFERROR(INDEX('C15'!$B$2:$Z$14,MATCH($A5,'C15'!$B$2:$B$14,0),MATCH(E$2,'C15'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C1'!$B$2:$Z$14,MATCH($A5,'C1'!$B$2:$B$14,0),MATCH(E$2,'C1'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C3'!$B$2:$Z$14,MATCH($A5,'C3'!$B$2:$B$14,0),MATCH(E$2,'C3'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C5'!$B$2:$Z$14,MATCH($A5,'C5'!$B$2:$B$14,0),MATCH(E$2,'C5'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C7'!$B$2:$Z$14,MATCH($A5,'C7'!$B$2:$B$14,0),MATCH(E$2,'C7'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C9'!$B$2:$Z$14,MATCH($A5,'C9'!$B$2:$B$14,0),MATCH(E$2,'C9'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C11'!$B$2:$Z$14,MATCH($A5,'C11'!$B$2:$B$14,0),MATCH(E$2,'C11'!$B$2:$Z$2,0)),0)</f>
+        <v>1</v>
+      </c>
+      <c r="F5" s="1">
+        <f>IFERROR(INDEX('C15'!$B$2:$Z$14,MATCH($A5,'C15'!$B$2:$B$14,0),MATCH(F$2,'C15'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C1'!$B$2:$Z$14,MATCH($A5,'C1'!$B$2:$B$14,0),MATCH(F$2,'C1'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C3'!$B$2:$Z$14,MATCH($A5,'C3'!$B$2:$B$14,0),MATCH(F$2,'C3'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C5'!$B$2:$Z$14,MATCH($A5,'C5'!$B$2:$B$14,0),MATCH(F$2,'C5'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C7'!$B$2:$Z$14,MATCH($A5,'C7'!$B$2:$B$14,0),MATCH(F$2,'C7'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C9'!$B$2:$Z$14,MATCH($A5,'C9'!$B$2:$B$14,0),MATCH(F$2,'C9'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C11'!$B$2:$Z$14,MATCH($A5,'C11'!$B$2:$B$14,0),MATCH(F$2,'C11'!$B$2:$Z$2,0)),0)</f>
+        <v>4</v>
+      </c>
+      <c r="G5" s="1">
+        <f>IFERROR(INDEX('C15'!$B$2:$Z$14,MATCH($A5,'C15'!$B$2:$B$14,0),MATCH(G$2,'C15'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C1'!$B$2:$Z$14,MATCH($A5,'C1'!$B$2:$B$14,0),MATCH(G$2,'C1'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C3'!$B$2:$Z$14,MATCH($A5,'C3'!$B$2:$B$14,0),MATCH(G$2,'C3'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C5'!$B$2:$Z$14,MATCH($A5,'C5'!$B$2:$B$14,0),MATCH(G$2,'C5'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C7'!$B$2:$Z$14,MATCH($A5,'C7'!$B$2:$B$14,0),MATCH(G$2,'C7'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C9'!$B$2:$Z$14,MATCH($A5,'C9'!$B$2:$B$14,0),MATCH(G$2,'C9'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C11'!$B$2:$Z$14,MATCH($A5,'C11'!$B$2:$B$14,0),MATCH(G$2,'C11'!$B$2:$Z$2,0)),0)</f>
+        <v>6</v>
+      </c>
+      <c r="H5" s="1">
+        <f>IFERROR(INDEX('C15'!$B$2:$Z$14,MATCH($A5,'C15'!$B$2:$B$14,0),MATCH(H$2,'C15'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C1'!$B$2:$Z$14,MATCH($A5,'C1'!$B$2:$B$14,0),MATCH(H$2,'C1'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C3'!$B$2:$Z$14,MATCH($A5,'C3'!$B$2:$B$14,0),MATCH(H$2,'C3'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C5'!$B$2:$Z$14,MATCH($A5,'C5'!$B$2:$B$14,0),MATCH(H$2,'C5'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C7'!$B$2:$Z$14,MATCH($A5,'C7'!$B$2:$B$14,0),MATCH(H$2,'C7'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C9'!$B$2:$Z$14,MATCH($A5,'C9'!$B$2:$B$14,0),MATCH(H$2,'C9'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C11'!$B$2:$Z$14,MATCH($A5,'C11'!$B$2:$B$14,0),MATCH(H$2,'C11'!$B$2:$Z$2,0)),0)</f>
+        <v>0</v>
+      </c>
+      <c r="I5" s="1">
+        <f>IFERROR(INDEX('C15'!$B$2:$Z$14,MATCH($A5,'C15'!$B$2:$B$14,0),MATCH(I$2,'C15'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C1'!$B$2:$Z$14,MATCH($A5,'C1'!$B$2:$B$14,0),MATCH(I$2,'C1'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C3'!$B$2:$Z$14,MATCH($A5,'C3'!$B$2:$B$14,0),MATCH(I$2,'C3'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C5'!$B$2:$Z$14,MATCH($A5,'C5'!$B$2:$B$14,0),MATCH(I$2,'C5'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C7'!$B$2:$Z$14,MATCH($A5,'C7'!$B$2:$B$14,0),MATCH(I$2,'C7'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C9'!$B$2:$Z$14,MATCH($A5,'C9'!$B$2:$B$14,0),MATCH(I$2,'C9'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C11'!$B$2:$Z$14,MATCH($A5,'C11'!$B$2:$B$14,0),MATCH(I$2,'C11'!$B$2:$Z$2,0)),0)</f>
+        <v>1</v>
+      </c>
+      <c r="J5" s="1">
+        <f>IFERROR(INDEX('C15'!$B$2:$Z$14,MATCH($A5,'C15'!$B$2:$B$14,0),MATCH(J$2,'C15'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C1'!$B$2:$Z$14,MATCH($A5,'C1'!$B$2:$B$14,0),MATCH(J$2,'C1'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C3'!$B$2:$Z$14,MATCH($A5,'C3'!$B$2:$B$14,0),MATCH(J$2,'C3'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C5'!$B$2:$Z$14,MATCH($A5,'C5'!$B$2:$B$14,0),MATCH(J$2,'C5'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C7'!$B$2:$Z$14,MATCH($A5,'C7'!$B$2:$B$14,0),MATCH(J$2,'C7'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C9'!$B$2:$Z$14,MATCH($A5,'C9'!$B$2:$B$14,0),MATCH(J$2,'C9'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C11'!$B$2:$Z$14,MATCH($A5,'C11'!$B$2:$B$14,0),MATCH(J$2,'C11'!$B$2:$Z$2,0)),0)</f>
+        <v>5</v>
+      </c>
+      <c r="K5" s="1">
+        <f>IFERROR(INDEX('C15'!$B$2:$Z$14,MATCH($A5,'C15'!$B$2:$B$14,0),MATCH(K$2,'C15'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C1'!$B$2:$Z$14,MATCH($A5,'C1'!$B$2:$B$14,0),MATCH(K$2,'C1'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C3'!$B$2:$Z$14,MATCH($A5,'C3'!$B$2:$B$14,0),MATCH(K$2,'C3'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C5'!$B$2:$Z$14,MATCH($A5,'C5'!$B$2:$B$14,0),MATCH(K$2,'C5'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C7'!$B$2:$Z$14,MATCH($A5,'C7'!$B$2:$B$14,0),MATCH(K$2,'C7'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C9'!$B$2:$Z$14,MATCH($A5,'C9'!$B$2:$B$14,0),MATCH(K$2,'C9'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C11'!$B$2:$Z$14,MATCH($A5,'C11'!$B$2:$B$14,0),MATCH(K$2,'C11'!$B$2:$Z$2,0)),0)</f>
+        <v>0</v>
+      </c>
+      <c r="L5" s="1">
+        <f>IFERROR(INDEX('C15'!$B$2:$Z$14,MATCH($A5,'C15'!$B$2:$B$14,0),MATCH(L$2,'C15'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C1'!$B$2:$Z$14,MATCH($A5,'C1'!$B$2:$B$14,0),MATCH(L$2,'C1'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C3'!$B$2:$Z$14,MATCH($A5,'C3'!$B$2:$B$14,0),MATCH(L$2,'C3'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C5'!$B$2:$Z$14,MATCH($A5,'C5'!$B$2:$B$14,0),MATCH(L$2,'C5'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C7'!$B$2:$Z$14,MATCH($A5,'C7'!$B$2:$B$14,0),MATCH(L$2,'C7'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C9'!$B$2:$Z$14,MATCH($A5,'C9'!$B$2:$B$14,0),MATCH(L$2,'C9'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C11'!$B$2:$Z$14,MATCH($A5,'C11'!$B$2:$B$14,0),MATCH(L$2,'C11'!$B$2:$Z$2,0)),0)</f>
+        <v>0</v>
+      </c>
+      <c r="M5" s="1">
+        <f>IFERROR(INDEX('C15'!$B$2:$Z$14,MATCH($A5,'C15'!$B$2:$B$14,0),MATCH(M$2,'C15'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C1'!$B$2:$Z$14,MATCH($A5,'C1'!$B$2:$B$14,0),MATCH(M$2,'C1'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C3'!$B$2:$Z$14,MATCH($A5,'C3'!$B$2:$B$14,0),MATCH(M$2,'C3'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C5'!$B$2:$Z$14,MATCH($A5,'C5'!$B$2:$B$14,0),MATCH(M$2,'C5'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C7'!$B$2:$Z$14,MATCH($A5,'C7'!$B$2:$B$14,0),MATCH(M$2,'C7'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C9'!$B$2:$Z$14,MATCH($A5,'C9'!$B$2:$B$14,0),MATCH(M$2,'C9'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C11'!$B$2:$Z$14,MATCH($A5,'C11'!$B$2:$B$14,0),MATCH(M$2,'C11'!$B$2:$Z$2,0)),0)</f>
+        <v>1</v>
+      </c>
+      <c r="N5" s="1">
+        <f>IFERROR(INDEX('C15'!$B$2:$Z$14,MATCH($A5,'C15'!$B$2:$B$14,0),MATCH(N$2,'C15'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C1'!$B$2:$Z$14,MATCH($A5,'C1'!$B$2:$B$14,0),MATCH(N$2,'C1'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C3'!$B$2:$Z$14,MATCH($A5,'C3'!$B$2:$B$14,0),MATCH(N$2,'C3'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C5'!$B$2:$Z$14,MATCH($A5,'C5'!$B$2:$B$14,0),MATCH(N$2,'C5'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C7'!$B$2:$Z$14,MATCH($A5,'C7'!$B$2:$B$14,0),MATCH(N$2,'C7'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C9'!$B$2:$Z$14,MATCH($A5,'C9'!$B$2:$B$14,0),MATCH(N$2,'C9'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C11'!$B$2:$Z$14,MATCH($A5,'C11'!$B$2:$B$14,0),MATCH(N$2,'C11'!$B$2:$Z$2,0)),0)</f>
+        <v>0</v>
+      </c>
+      <c r="O5" s="1">
+        <f>IFERROR(INDEX('C15'!$B$2:$Z$14,MATCH($A5,'C15'!$B$2:$B$14,0),MATCH(O$2,'C15'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C1'!$B$2:$Z$14,MATCH($A5,'C1'!$B$2:$B$14,0),MATCH(O$2,'C1'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C3'!$B$2:$Z$14,MATCH($A5,'C3'!$B$2:$B$14,0),MATCH(O$2,'C3'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C5'!$B$2:$Z$14,MATCH($A5,'C5'!$B$2:$B$14,0),MATCH(O$2,'C5'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C7'!$B$2:$Z$14,MATCH($A5,'C7'!$B$2:$B$14,0),MATCH(O$2,'C7'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C9'!$B$2:$Z$14,MATCH($A5,'C9'!$B$2:$B$14,0),MATCH(O$2,'C9'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C11'!$B$2:$Z$14,MATCH($A5,'C11'!$B$2:$B$14,0),MATCH(O$2,'C11'!$B$2:$Z$2,0)),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="1">
+        <f>IFERROR(INDEX('C15'!$B$2:$Z$14,MATCH($A6,'C15'!$B$2:$B$14,0),MATCH(B$2,'C15'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C1'!$B$2:$Z$14,MATCH($A6,'C1'!$B$2:$B$14,0),MATCH(B$2,'C1'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C3'!$B$2:$Z$14,MATCH($A6,'C3'!$B$2:$B$14,0),MATCH(B$2,'C3'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C5'!$B$2:$Z$14,MATCH($A6,'C5'!$B$2:$B$14,0),MATCH(B$2,'C5'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C7'!$B$2:$Z$14,MATCH($A6,'C7'!$B$2:$B$14,0),MATCH(B$2,'C7'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C9'!$B$2:$Z$14,MATCH($A6,'C9'!$B$2:$B$14,0),MATCH(B$2,'C9'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C11'!$B$2:$Z$14,MATCH($A6,'C11'!$B$2:$B$14,0),MATCH(B$2,'C11'!$B$2:$Z$2,0)),0)</f>
+        <v>1</v>
+      </c>
+      <c r="C6" s="1">
+        <f>IFERROR(INDEX('C15'!$B$2:$Z$14,MATCH($A6,'C15'!$B$2:$B$14,0),MATCH(C$2,'C15'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C1'!$B$2:$Z$14,MATCH($A6,'C1'!$B$2:$B$14,0),MATCH(C$2,'C1'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C3'!$B$2:$Z$14,MATCH($A6,'C3'!$B$2:$B$14,0),MATCH(C$2,'C3'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C5'!$B$2:$Z$14,MATCH($A6,'C5'!$B$2:$B$14,0),MATCH(C$2,'C5'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C7'!$B$2:$Z$14,MATCH($A6,'C7'!$B$2:$B$14,0),MATCH(C$2,'C7'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C9'!$B$2:$Z$14,MATCH($A6,'C9'!$B$2:$B$14,0),MATCH(C$2,'C9'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C11'!$B$2:$Z$14,MATCH($A6,'C11'!$B$2:$B$14,0),MATCH(C$2,'C11'!$B$2:$Z$2,0)),0)</f>
+        <v>1</v>
+      </c>
+      <c r="D6" s="1">
+        <f>IFERROR(INDEX('C15'!$B$2:$Z$14,MATCH($A6,'C15'!$B$2:$B$14,0),MATCH(D$2,'C15'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C1'!$B$2:$Z$14,MATCH($A6,'C1'!$B$2:$B$14,0),MATCH(D$2,'C1'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C3'!$B$2:$Z$14,MATCH($A6,'C3'!$B$2:$B$14,0),MATCH(D$2,'C3'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C5'!$B$2:$Z$14,MATCH($A6,'C5'!$B$2:$B$14,0),MATCH(D$2,'C5'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C7'!$B$2:$Z$14,MATCH($A6,'C7'!$B$2:$B$14,0),MATCH(D$2,'C7'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C9'!$B$2:$Z$14,MATCH($A6,'C9'!$B$2:$B$14,0),MATCH(D$2,'C9'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C11'!$B$2:$Z$14,MATCH($A6,'C11'!$B$2:$B$14,0),MATCH(D$2,'C11'!$B$2:$Z$2,0)),0)</f>
+        <v>3</v>
+      </c>
+      <c r="E6" s="1">
+        <f>IFERROR(INDEX('C15'!$B$2:$Z$14,MATCH($A6,'C15'!$B$2:$B$14,0),MATCH(E$2,'C15'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C1'!$B$2:$Z$14,MATCH($A6,'C1'!$B$2:$B$14,0),MATCH(E$2,'C1'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C3'!$B$2:$Z$14,MATCH($A6,'C3'!$B$2:$B$14,0),MATCH(E$2,'C3'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C5'!$B$2:$Z$14,MATCH($A6,'C5'!$B$2:$B$14,0),MATCH(E$2,'C5'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C7'!$B$2:$Z$14,MATCH($A6,'C7'!$B$2:$B$14,0),MATCH(E$2,'C7'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C9'!$B$2:$Z$14,MATCH($A6,'C9'!$B$2:$B$14,0),MATCH(E$2,'C9'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C11'!$B$2:$Z$14,MATCH($A6,'C11'!$B$2:$B$14,0),MATCH(E$2,'C11'!$B$2:$Z$2,0)),0)</f>
+        <v>1</v>
+      </c>
+      <c r="F6" s="1">
+        <f>IFERROR(INDEX('C15'!$B$2:$Z$14,MATCH($A6,'C15'!$B$2:$B$14,0),MATCH(F$2,'C15'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C1'!$B$2:$Z$14,MATCH($A6,'C1'!$B$2:$B$14,0),MATCH(F$2,'C1'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C3'!$B$2:$Z$14,MATCH($A6,'C3'!$B$2:$B$14,0),MATCH(F$2,'C3'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C5'!$B$2:$Z$14,MATCH($A6,'C5'!$B$2:$B$14,0),MATCH(F$2,'C5'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C7'!$B$2:$Z$14,MATCH($A6,'C7'!$B$2:$B$14,0),MATCH(F$2,'C7'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C9'!$B$2:$Z$14,MATCH($A6,'C9'!$B$2:$B$14,0),MATCH(F$2,'C9'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C11'!$B$2:$Z$14,MATCH($A6,'C11'!$B$2:$B$14,0),MATCH(F$2,'C11'!$B$2:$Z$2,0)),0)</f>
+        <v>4</v>
+      </c>
+      <c r="G6" s="1">
+        <f>IFERROR(INDEX('C15'!$B$2:$Z$14,MATCH($A6,'C15'!$B$2:$B$14,0),MATCH(G$2,'C15'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C1'!$B$2:$Z$14,MATCH($A6,'C1'!$B$2:$B$14,0),MATCH(G$2,'C1'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C3'!$B$2:$Z$14,MATCH($A6,'C3'!$B$2:$B$14,0),MATCH(G$2,'C3'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C5'!$B$2:$Z$14,MATCH($A6,'C5'!$B$2:$B$14,0),MATCH(G$2,'C5'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C7'!$B$2:$Z$14,MATCH($A6,'C7'!$B$2:$B$14,0),MATCH(G$2,'C7'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C9'!$B$2:$Z$14,MATCH($A6,'C9'!$B$2:$B$14,0),MATCH(G$2,'C9'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C11'!$B$2:$Z$14,MATCH($A6,'C11'!$B$2:$B$14,0),MATCH(G$2,'C11'!$B$2:$Z$2,0)),0)</f>
+        <v>6</v>
+      </c>
+      <c r="H6" s="1">
+        <f>IFERROR(INDEX('C15'!$B$2:$Z$14,MATCH($A6,'C15'!$B$2:$B$14,0),MATCH(H$2,'C15'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C1'!$B$2:$Z$14,MATCH($A6,'C1'!$B$2:$B$14,0),MATCH(H$2,'C1'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C3'!$B$2:$Z$14,MATCH($A6,'C3'!$B$2:$B$14,0),MATCH(H$2,'C3'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C5'!$B$2:$Z$14,MATCH($A6,'C5'!$B$2:$B$14,0),MATCH(H$2,'C5'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C7'!$B$2:$Z$14,MATCH($A6,'C7'!$B$2:$B$14,0),MATCH(H$2,'C7'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C9'!$B$2:$Z$14,MATCH($A6,'C9'!$B$2:$B$14,0),MATCH(H$2,'C9'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C11'!$B$2:$Z$14,MATCH($A6,'C11'!$B$2:$B$14,0),MATCH(H$2,'C11'!$B$2:$Z$2,0)),0)</f>
+        <v>0</v>
+      </c>
+      <c r="I6" s="1">
+        <f>IFERROR(INDEX('C15'!$B$2:$Z$14,MATCH($A6,'C15'!$B$2:$B$14,0),MATCH(I$2,'C15'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C1'!$B$2:$Z$14,MATCH($A6,'C1'!$B$2:$B$14,0),MATCH(I$2,'C1'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C3'!$B$2:$Z$14,MATCH($A6,'C3'!$B$2:$B$14,0),MATCH(I$2,'C3'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C5'!$B$2:$Z$14,MATCH($A6,'C5'!$B$2:$B$14,0),MATCH(I$2,'C5'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C7'!$B$2:$Z$14,MATCH($A6,'C7'!$B$2:$B$14,0),MATCH(I$2,'C7'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C9'!$B$2:$Z$14,MATCH($A6,'C9'!$B$2:$B$14,0),MATCH(I$2,'C9'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C11'!$B$2:$Z$14,MATCH($A6,'C11'!$B$2:$B$14,0),MATCH(I$2,'C11'!$B$2:$Z$2,0)),0)</f>
+        <v>1</v>
+      </c>
+      <c r="J6" s="1">
+        <f>IFERROR(INDEX('C15'!$B$2:$Z$14,MATCH($A6,'C15'!$B$2:$B$14,0),MATCH(J$2,'C15'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C1'!$B$2:$Z$14,MATCH($A6,'C1'!$B$2:$B$14,0),MATCH(J$2,'C1'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C3'!$B$2:$Z$14,MATCH($A6,'C3'!$B$2:$B$14,0),MATCH(J$2,'C3'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C5'!$B$2:$Z$14,MATCH($A6,'C5'!$B$2:$B$14,0),MATCH(J$2,'C5'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C7'!$B$2:$Z$14,MATCH($A6,'C7'!$B$2:$B$14,0),MATCH(J$2,'C7'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C9'!$B$2:$Z$14,MATCH($A6,'C9'!$B$2:$B$14,0),MATCH(J$2,'C9'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C11'!$B$2:$Z$14,MATCH($A6,'C11'!$B$2:$B$14,0),MATCH(J$2,'C11'!$B$2:$Z$2,0)),0)</f>
+        <v>5</v>
+      </c>
+      <c r="K6" s="1">
+        <f>IFERROR(INDEX('C15'!$B$2:$Z$14,MATCH($A6,'C15'!$B$2:$B$14,0),MATCH(K$2,'C15'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C1'!$B$2:$Z$14,MATCH($A6,'C1'!$B$2:$B$14,0),MATCH(K$2,'C1'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C3'!$B$2:$Z$14,MATCH($A6,'C3'!$B$2:$B$14,0),MATCH(K$2,'C3'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C5'!$B$2:$Z$14,MATCH($A6,'C5'!$B$2:$B$14,0),MATCH(K$2,'C5'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C7'!$B$2:$Z$14,MATCH($A6,'C7'!$B$2:$B$14,0),MATCH(K$2,'C7'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C9'!$B$2:$Z$14,MATCH($A6,'C9'!$B$2:$B$14,0),MATCH(K$2,'C9'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C11'!$B$2:$Z$14,MATCH($A6,'C11'!$B$2:$B$14,0),MATCH(K$2,'C11'!$B$2:$Z$2,0)),0)</f>
+        <v>0</v>
+      </c>
+      <c r="L6" s="1">
+        <f>IFERROR(INDEX('C15'!$B$2:$Z$14,MATCH($A6,'C15'!$B$2:$B$14,0),MATCH(L$2,'C15'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C1'!$B$2:$Z$14,MATCH($A6,'C1'!$B$2:$B$14,0),MATCH(L$2,'C1'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C3'!$B$2:$Z$14,MATCH($A6,'C3'!$B$2:$B$14,0),MATCH(L$2,'C3'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C5'!$B$2:$Z$14,MATCH($A6,'C5'!$B$2:$B$14,0),MATCH(L$2,'C5'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C7'!$B$2:$Z$14,MATCH($A6,'C7'!$B$2:$B$14,0),MATCH(L$2,'C7'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C9'!$B$2:$Z$14,MATCH($A6,'C9'!$B$2:$B$14,0),MATCH(L$2,'C9'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C11'!$B$2:$Z$14,MATCH($A6,'C11'!$B$2:$B$14,0),MATCH(L$2,'C11'!$B$2:$Z$2,0)),0)</f>
+        <v>0</v>
+      </c>
+      <c r="M6" s="1">
+        <f>IFERROR(INDEX('C15'!$B$2:$Z$14,MATCH($A6,'C15'!$B$2:$B$14,0),MATCH(M$2,'C15'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C1'!$B$2:$Z$14,MATCH($A6,'C1'!$B$2:$B$14,0),MATCH(M$2,'C1'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C3'!$B$2:$Z$14,MATCH($A6,'C3'!$B$2:$B$14,0),MATCH(M$2,'C3'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C5'!$B$2:$Z$14,MATCH($A6,'C5'!$B$2:$B$14,0),MATCH(M$2,'C5'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C7'!$B$2:$Z$14,MATCH($A6,'C7'!$B$2:$B$14,0),MATCH(M$2,'C7'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C9'!$B$2:$Z$14,MATCH($A6,'C9'!$B$2:$B$14,0),MATCH(M$2,'C9'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C11'!$B$2:$Z$14,MATCH($A6,'C11'!$B$2:$B$14,0),MATCH(M$2,'C11'!$B$2:$Z$2,0)),0)</f>
+        <v>1</v>
+      </c>
+      <c r="N6" s="1">
+        <f>IFERROR(INDEX('C15'!$B$2:$Z$14,MATCH($A6,'C15'!$B$2:$B$14,0),MATCH(N$2,'C15'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C1'!$B$2:$Z$14,MATCH($A6,'C1'!$B$2:$B$14,0),MATCH(N$2,'C1'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C3'!$B$2:$Z$14,MATCH($A6,'C3'!$B$2:$B$14,0),MATCH(N$2,'C3'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C5'!$B$2:$Z$14,MATCH($A6,'C5'!$B$2:$B$14,0),MATCH(N$2,'C5'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C7'!$B$2:$Z$14,MATCH($A6,'C7'!$B$2:$B$14,0),MATCH(N$2,'C7'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C9'!$B$2:$Z$14,MATCH($A6,'C9'!$B$2:$B$14,0),MATCH(N$2,'C9'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C11'!$B$2:$Z$14,MATCH($A6,'C11'!$B$2:$B$14,0),MATCH(N$2,'C11'!$B$2:$Z$2,0)),0)</f>
+        <v>0</v>
+      </c>
+      <c r="O6" s="1">
+        <f>IFERROR(INDEX('C15'!$B$2:$Z$14,MATCH($A6,'C15'!$B$2:$B$14,0),MATCH(O$2,'C15'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C1'!$B$2:$Z$14,MATCH($A6,'C1'!$B$2:$B$14,0),MATCH(O$2,'C1'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C3'!$B$2:$Z$14,MATCH($A6,'C3'!$B$2:$B$14,0),MATCH(O$2,'C3'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C5'!$B$2:$Z$14,MATCH($A6,'C5'!$B$2:$B$14,0),MATCH(O$2,'C5'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C7'!$B$2:$Z$14,MATCH($A6,'C7'!$B$2:$B$14,0),MATCH(O$2,'C7'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C9'!$B$2:$Z$14,MATCH($A6,'C9'!$B$2:$B$14,0),MATCH(O$2,'C9'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C11'!$B$2:$Z$14,MATCH($A6,'C11'!$B$2:$B$14,0),MATCH(O$2,'C11'!$B$2:$Z$2,0)),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A7" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="1">
+        <f>IFERROR(INDEX('C15'!$B$2:$Z$14,MATCH($A7,'C15'!$B$2:$B$14,0),MATCH(B$2,'C15'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C1'!$B$2:$Z$14,MATCH($A7,'C1'!$B$2:$B$14,0),MATCH(B$2,'C1'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C3'!$B$2:$Z$14,MATCH($A7,'C3'!$B$2:$B$14,0),MATCH(B$2,'C3'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C5'!$B$2:$Z$14,MATCH($A7,'C5'!$B$2:$B$14,0),MATCH(B$2,'C5'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C7'!$B$2:$Z$14,MATCH($A7,'C7'!$B$2:$B$14,0),MATCH(B$2,'C7'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C9'!$B$2:$Z$14,MATCH($A7,'C9'!$B$2:$B$14,0),MATCH(B$2,'C9'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C11'!$B$2:$Z$14,MATCH($A7,'C11'!$B$2:$B$14,0),MATCH(B$2,'C11'!$B$2:$Z$2,0)),0)</f>
+        <v>3</v>
+      </c>
+      <c r="C7" s="1">
+        <f>IFERROR(INDEX('C15'!$B$2:$Z$14,MATCH($A7,'C15'!$B$2:$B$14,0),MATCH(C$2,'C15'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C1'!$B$2:$Z$14,MATCH($A7,'C1'!$B$2:$B$14,0),MATCH(C$2,'C1'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C3'!$B$2:$Z$14,MATCH($A7,'C3'!$B$2:$B$14,0),MATCH(C$2,'C3'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C5'!$B$2:$Z$14,MATCH($A7,'C5'!$B$2:$B$14,0),MATCH(C$2,'C5'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C7'!$B$2:$Z$14,MATCH($A7,'C7'!$B$2:$B$14,0),MATCH(C$2,'C7'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C9'!$B$2:$Z$14,MATCH($A7,'C9'!$B$2:$B$14,0),MATCH(C$2,'C9'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C11'!$B$2:$Z$14,MATCH($A7,'C11'!$B$2:$B$14,0),MATCH(C$2,'C11'!$B$2:$Z$2,0)),0)</f>
+        <v>2</v>
+      </c>
+      <c r="D7" s="1">
+        <f>IFERROR(INDEX('C15'!$B$2:$Z$14,MATCH($A7,'C15'!$B$2:$B$14,0),MATCH(D$2,'C15'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C1'!$B$2:$Z$14,MATCH($A7,'C1'!$B$2:$B$14,0),MATCH(D$2,'C1'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C3'!$B$2:$Z$14,MATCH($A7,'C3'!$B$2:$B$14,0),MATCH(D$2,'C3'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C5'!$B$2:$Z$14,MATCH($A7,'C5'!$B$2:$B$14,0),MATCH(D$2,'C5'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C7'!$B$2:$Z$14,MATCH($A7,'C7'!$B$2:$B$14,0),MATCH(D$2,'C7'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C9'!$B$2:$Z$14,MATCH($A7,'C9'!$B$2:$B$14,0),MATCH(D$2,'C9'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C11'!$B$2:$Z$14,MATCH($A7,'C11'!$B$2:$B$14,0),MATCH(D$2,'C11'!$B$2:$Z$2,0)),0)</f>
+        <v>4</v>
+      </c>
+      <c r="E7" s="1">
+        <f>IFERROR(INDEX('C15'!$B$2:$Z$14,MATCH($A7,'C15'!$B$2:$B$14,0),MATCH(E$2,'C15'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C1'!$B$2:$Z$14,MATCH($A7,'C1'!$B$2:$B$14,0),MATCH(E$2,'C1'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C3'!$B$2:$Z$14,MATCH($A7,'C3'!$B$2:$B$14,0),MATCH(E$2,'C3'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C5'!$B$2:$Z$14,MATCH($A7,'C5'!$B$2:$B$14,0),MATCH(E$2,'C5'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C7'!$B$2:$Z$14,MATCH($A7,'C7'!$B$2:$B$14,0),MATCH(E$2,'C7'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C9'!$B$2:$Z$14,MATCH($A7,'C9'!$B$2:$B$14,0),MATCH(E$2,'C9'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C11'!$B$2:$Z$14,MATCH($A7,'C11'!$B$2:$B$14,0),MATCH(E$2,'C11'!$B$2:$Z$2,0)),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F7" s="1">
+        <f>IFERROR(INDEX('C15'!$B$2:$Z$14,MATCH($A7,'C15'!$B$2:$B$14,0),MATCH(F$2,'C15'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C1'!$B$2:$Z$14,MATCH($A7,'C1'!$B$2:$B$14,0),MATCH(F$2,'C1'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C3'!$B$2:$Z$14,MATCH($A7,'C3'!$B$2:$B$14,0),MATCH(F$2,'C3'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C5'!$B$2:$Z$14,MATCH($A7,'C5'!$B$2:$B$14,0),MATCH(F$2,'C5'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C7'!$B$2:$Z$14,MATCH($A7,'C7'!$B$2:$B$14,0),MATCH(F$2,'C7'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C9'!$B$2:$Z$14,MATCH($A7,'C9'!$B$2:$B$14,0),MATCH(F$2,'C9'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C11'!$B$2:$Z$14,MATCH($A7,'C11'!$B$2:$B$14,0),MATCH(F$2,'C11'!$B$2:$Z$2,0)),0)</f>
+        <v>3</v>
+      </c>
+      <c r="G7" s="1">
+        <f>IFERROR(INDEX('C15'!$B$2:$Z$14,MATCH($A7,'C15'!$B$2:$B$14,0),MATCH(G$2,'C15'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C1'!$B$2:$Z$14,MATCH($A7,'C1'!$B$2:$B$14,0),MATCH(G$2,'C1'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C3'!$B$2:$Z$14,MATCH($A7,'C3'!$B$2:$B$14,0),MATCH(G$2,'C3'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C5'!$B$2:$Z$14,MATCH($A7,'C5'!$B$2:$B$14,0),MATCH(G$2,'C5'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C7'!$B$2:$Z$14,MATCH($A7,'C7'!$B$2:$B$14,0),MATCH(G$2,'C7'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C9'!$B$2:$Z$14,MATCH($A7,'C9'!$B$2:$B$14,0),MATCH(G$2,'C9'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C11'!$B$2:$Z$14,MATCH($A7,'C11'!$B$2:$B$14,0),MATCH(G$2,'C11'!$B$2:$Z$2,0)),0)</f>
+        <v>5</v>
+      </c>
+      <c r="H7" s="1">
+        <f>IFERROR(INDEX('C15'!$B$2:$Z$14,MATCH($A7,'C15'!$B$2:$B$14,0),MATCH(H$2,'C15'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C1'!$B$2:$Z$14,MATCH($A7,'C1'!$B$2:$B$14,0),MATCH(H$2,'C1'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C3'!$B$2:$Z$14,MATCH($A7,'C3'!$B$2:$B$14,0),MATCH(H$2,'C3'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C5'!$B$2:$Z$14,MATCH($A7,'C5'!$B$2:$B$14,0),MATCH(H$2,'C5'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C7'!$B$2:$Z$14,MATCH($A7,'C7'!$B$2:$B$14,0),MATCH(H$2,'C7'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C9'!$B$2:$Z$14,MATCH($A7,'C9'!$B$2:$B$14,0),MATCH(H$2,'C9'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C11'!$B$2:$Z$14,MATCH($A7,'C11'!$B$2:$B$14,0),MATCH(H$2,'C11'!$B$2:$Z$2,0)),0)</f>
+        <v>1</v>
+      </c>
+      <c r="I7" s="1">
+        <f>IFERROR(INDEX('C15'!$B$2:$Z$14,MATCH($A7,'C15'!$B$2:$B$14,0),MATCH(I$2,'C15'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C1'!$B$2:$Z$14,MATCH($A7,'C1'!$B$2:$B$14,0),MATCH(I$2,'C1'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C3'!$B$2:$Z$14,MATCH($A7,'C3'!$B$2:$B$14,0),MATCH(I$2,'C3'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C5'!$B$2:$Z$14,MATCH($A7,'C5'!$B$2:$B$14,0),MATCH(I$2,'C5'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C7'!$B$2:$Z$14,MATCH($A7,'C7'!$B$2:$B$14,0),MATCH(I$2,'C7'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C9'!$B$2:$Z$14,MATCH($A7,'C9'!$B$2:$B$14,0),MATCH(I$2,'C9'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C11'!$B$2:$Z$14,MATCH($A7,'C11'!$B$2:$B$14,0),MATCH(I$2,'C11'!$B$2:$Z$2,0)),0)</f>
+        <v>1</v>
+      </c>
+      <c r="J7" s="1">
+        <f>IFERROR(INDEX('C15'!$B$2:$Z$14,MATCH($A7,'C15'!$B$2:$B$14,0),MATCH(J$2,'C15'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C1'!$B$2:$Z$14,MATCH($A7,'C1'!$B$2:$B$14,0),MATCH(J$2,'C1'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C3'!$B$2:$Z$14,MATCH($A7,'C3'!$B$2:$B$14,0),MATCH(J$2,'C3'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C5'!$B$2:$Z$14,MATCH($A7,'C5'!$B$2:$B$14,0),MATCH(J$2,'C5'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C7'!$B$2:$Z$14,MATCH($A7,'C7'!$B$2:$B$14,0),MATCH(J$2,'C7'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C9'!$B$2:$Z$14,MATCH($A7,'C9'!$B$2:$B$14,0),MATCH(J$2,'C9'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C11'!$B$2:$Z$14,MATCH($A7,'C11'!$B$2:$B$14,0),MATCH(J$2,'C11'!$B$2:$Z$2,0)),0)</f>
+        <v>4</v>
+      </c>
+      <c r="K7" s="1">
+        <f>IFERROR(INDEX('C15'!$B$2:$Z$14,MATCH($A7,'C15'!$B$2:$B$14,0),MATCH(K$2,'C15'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C1'!$B$2:$Z$14,MATCH($A7,'C1'!$B$2:$B$14,0),MATCH(K$2,'C1'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C3'!$B$2:$Z$14,MATCH($A7,'C3'!$B$2:$B$14,0),MATCH(K$2,'C3'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C5'!$B$2:$Z$14,MATCH($A7,'C5'!$B$2:$B$14,0),MATCH(K$2,'C5'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C7'!$B$2:$Z$14,MATCH($A7,'C7'!$B$2:$B$14,0),MATCH(K$2,'C7'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C9'!$B$2:$Z$14,MATCH($A7,'C9'!$B$2:$B$14,0),MATCH(K$2,'C9'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C11'!$B$2:$Z$14,MATCH($A7,'C11'!$B$2:$B$14,0),MATCH(K$2,'C11'!$B$2:$Z$2,0)),0)</f>
+        <v>0</v>
+      </c>
+      <c r="L7" s="1">
+        <f>IFERROR(INDEX('C15'!$B$2:$Z$14,MATCH($A7,'C15'!$B$2:$B$14,0),MATCH(L$2,'C15'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C1'!$B$2:$Z$14,MATCH($A7,'C1'!$B$2:$B$14,0),MATCH(L$2,'C1'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C3'!$B$2:$Z$14,MATCH($A7,'C3'!$B$2:$B$14,0),MATCH(L$2,'C3'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C5'!$B$2:$Z$14,MATCH($A7,'C5'!$B$2:$B$14,0),MATCH(L$2,'C5'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C7'!$B$2:$Z$14,MATCH($A7,'C7'!$B$2:$B$14,0),MATCH(L$2,'C7'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C9'!$B$2:$Z$14,MATCH($A7,'C9'!$B$2:$B$14,0),MATCH(L$2,'C9'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C11'!$B$2:$Z$14,MATCH($A7,'C11'!$B$2:$B$14,0),MATCH(L$2,'C11'!$B$2:$Z$2,0)),0)</f>
+        <v>0</v>
+      </c>
+      <c r="M7" s="1">
+        <f>IFERROR(INDEX('C15'!$B$2:$Z$14,MATCH($A7,'C15'!$B$2:$B$14,0),MATCH(M$2,'C15'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C1'!$B$2:$Z$14,MATCH($A7,'C1'!$B$2:$B$14,0),MATCH(M$2,'C1'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C3'!$B$2:$Z$14,MATCH($A7,'C3'!$B$2:$B$14,0),MATCH(M$2,'C3'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C5'!$B$2:$Z$14,MATCH($A7,'C5'!$B$2:$B$14,0),MATCH(M$2,'C5'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C7'!$B$2:$Z$14,MATCH($A7,'C7'!$B$2:$B$14,0),MATCH(M$2,'C7'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C9'!$B$2:$Z$14,MATCH($A7,'C9'!$B$2:$B$14,0),MATCH(M$2,'C9'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C11'!$B$2:$Z$14,MATCH($A7,'C11'!$B$2:$B$14,0),MATCH(M$2,'C11'!$B$2:$Z$2,0)),0)</f>
+        <v>0</v>
+      </c>
+      <c r="N7" s="1">
+        <f>IFERROR(INDEX('C15'!$B$2:$Z$14,MATCH($A7,'C15'!$B$2:$B$14,0),MATCH(N$2,'C15'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C1'!$B$2:$Z$14,MATCH($A7,'C1'!$B$2:$B$14,0),MATCH(N$2,'C1'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C3'!$B$2:$Z$14,MATCH($A7,'C3'!$B$2:$B$14,0),MATCH(N$2,'C3'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C5'!$B$2:$Z$14,MATCH($A7,'C5'!$B$2:$B$14,0),MATCH(N$2,'C5'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C7'!$B$2:$Z$14,MATCH($A7,'C7'!$B$2:$B$14,0),MATCH(N$2,'C7'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C9'!$B$2:$Z$14,MATCH($A7,'C9'!$B$2:$B$14,0),MATCH(N$2,'C9'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C11'!$B$2:$Z$14,MATCH($A7,'C11'!$B$2:$B$14,0),MATCH(N$2,'C11'!$B$2:$Z$2,0)),0)</f>
+        <v>0</v>
+      </c>
+      <c r="O7" s="1">
+        <f>IFERROR(INDEX('C15'!$B$2:$Z$14,MATCH($A7,'C15'!$B$2:$B$14,0),MATCH(O$2,'C15'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C1'!$B$2:$Z$14,MATCH($A7,'C1'!$B$2:$B$14,0),MATCH(O$2,'C1'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C3'!$B$2:$Z$14,MATCH($A7,'C3'!$B$2:$B$14,0),MATCH(O$2,'C3'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C5'!$B$2:$Z$14,MATCH($A7,'C5'!$B$2:$B$14,0),MATCH(O$2,'C5'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C7'!$B$2:$Z$14,MATCH($A7,'C7'!$B$2:$B$14,0),MATCH(O$2,'C7'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C9'!$B$2:$Z$14,MATCH($A7,'C9'!$B$2:$B$14,0),MATCH(O$2,'C9'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C11'!$B$2:$Z$14,MATCH($A7,'C11'!$B$2:$B$14,0),MATCH(O$2,'C11'!$B$2:$Z$2,0)),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A8" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B8" s="1">
+        <f>IFERROR(INDEX('C15'!$B$2:$Z$14,MATCH($A8,'C15'!$B$2:$B$14,0),MATCH(B$2,'C15'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C1'!$B$2:$Z$14,MATCH($A8,'C1'!$B$2:$B$14,0),MATCH(B$2,'C1'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C3'!$B$2:$Z$14,MATCH($A8,'C3'!$B$2:$B$14,0),MATCH(B$2,'C3'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C5'!$B$2:$Z$14,MATCH($A8,'C5'!$B$2:$B$14,0),MATCH(B$2,'C5'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C7'!$B$2:$Z$14,MATCH($A8,'C7'!$B$2:$B$14,0),MATCH(B$2,'C7'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C9'!$B$2:$Z$14,MATCH($A8,'C9'!$B$2:$B$14,0),MATCH(B$2,'C9'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C11'!$B$2:$Z$14,MATCH($A8,'C11'!$B$2:$B$14,0),MATCH(B$2,'C11'!$B$2:$Z$2,0)),0)</f>
+        <v>2</v>
+      </c>
+      <c r="C8" s="1">
+        <f>IFERROR(INDEX('C15'!$B$2:$Z$14,MATCH($A8,'C15'!$B$2:$B$14,0),MATCH(C$2,'C15'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C1'!$B$2:$Z$14,MATCH($A8,'C1'!$B$2:$B$14,0),MATCH(C$2,'C1'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C3'!$B$2:$Z$14,MATCH($A8,'C3'!$B$2:$B$14,0),MATCH(C$2,'C3'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C5'!$B$2:$Z$14,MATCH($A8,'C5'!$B$2:$B$14,0),MATCH(C$2,'C5'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C7'!$B$2:$Z$14,MATCH($A8,'C7'!$B$2:$B$14,0),MATCH(C$2,'C7'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C9'!$B$2:$Z$14,MATCH($A8,'C9'!$B$2:$B$14,0),MATCH(C$2,'C9'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C11'!$B$2:$Z$14,MATCH($A8,'C11'!$B$2:$B$14,0),MATCH(C$2,'C11'!$B$2:$Z$2,0)),0)</f>
+        <v>0</v>
+      </c>
+      <c r="D8" s="1">
+        <f>IFERROR(INDEX('C15'!$B$2:$Z$14,MATCH($A8,'C15'!$B$2:$B$14,0),MATCH(D$2,'C15'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C1'!$B$2:$Z$14,MATCH($A8,'C1'!$B$2:$B$14,0),MATCH(D$2,'C1'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C3'!$B$2:$Z$14,MATCH($A8,'C3'!$B$2:$B$14,0),MATCH(D$2,'C3'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C5'!$B$2:$Z$14,MATCH($A8,'C5'!$B$2:$B$14,0),MATCH(D$2,'C5'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C7'!$B$2:$Z$14,MATCH($A8,'C7'!$B$2:$B$14,0),MATCH(D$2,'C7'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C9'!$B$2:$Z$14,MATCH($A8,'C9'!$B$2:$B$14,0),MATCH(D$2,'C9'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C11'!$B$2:$Z$14,MATCH($A8,'C11'!$B$2:$B$14,0),MATCH(D$2,'C11'!$B$2:$Z$2,0)),0)</f>
+        <v>4</v>
+      </c>
+      <c r="E8" s="1">
+        <f>IFERROR(INDEX('C15'!$B$2:$Z$14,MATCH($A8,'C15'!$B$2:$B$14,0),MATCH(E$2,'C15'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C1'!$B$2:$Z$14,MATCH($A8,'C1'!$B$2:$B$14,0),MATCH(E$2,'C1'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C3'!$B$2:$Z$14,MATCH($A8,'C3'!$B$2:$B$14,0),MATCH(E$2,'C3'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C5'!$B$2:$Z$14,MATCH($A8,'C5'!$B$2:$B$14,0),MATCH(E$2,'C5'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C7'!$B$2:$Z$14,MATCH($A8,'C7'!$B$2:$B$14,0),MATCH(E$2,'C7'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C9'!$B$2:$Z$14,MATCH($A8,'C9'!$B$2:$B$14,0),MATCH(E$2,'C9'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C11'!$B$2:$Z$14,MATCH($A8,'C11'!$B$2:$B$14,0),MATCH(E$2,'C11'!$B$2:$Z$2,0)),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F8" s="1">
+        <f>IFERROR(INDEX('C15'!$B$2:$Z$14,MATCH($A8,'C15'!$B$2:$B$14,0),MATCH(F$2,'C15'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C1'!$B$2:$Z$14,MATCH($A8,'C1'!$B$2:$B$14,0),MATCH(F$2,'C1'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C3'!$B$2:$Z$14,MATCH($A8,'C3'!$B$2:$B$14,0),MATCH(F$2,'C3'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C5'!$B$2:$Z$14,MATCH($A8,'C5'!$B$2:$B$14,0),MATCH(F$2,'C5'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C7'!$B$2:$Z$14,MATCH($A8,'C7'!$B$2:$B$14,0),MATCH(F$2,'C7'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C9'!$B$2:$Z$14,MATCH($A8,'C9'!$B$2:$B$14,0),MATCH(F$2,'C9'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C11'!$B$2:$Z$14,MATCH($A8,'C11'!$B$2:$B$14,0),MATCH(F$2,'C11'!$B$2:$Z$2,0)),0)</f>
+        <v>6</v>
+      </c>
+      <c r="G8" s="1">
+        <f>IFERROR(INDEX('C15'!$B$2:$Z$14,MATCH($A8,'C15'!$B$2:$B$14,0),MATCH(G$2,'C15'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C1'!$B$2:$Z$14,MATCH($A8,'C1'!$B$2:$B$14,0),MATCH(G$2,'C1'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C3'!$B$2:$Z$14,MATCH($A8,'C3'!$B$2:$B$14,0),MATCH(G$2,'C3'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C5'!$B$2:$Z$14,MATCH($A8,'C5'!$B$2:$B$14,0),MATCH(G$2,'C5'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C7'!$B$2:$Z$14,MATCH($A8,'C7'!$B$2:$B$14,0),MATCH(G$2,'C7'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C9'!$B$2:$Z$14,MATCH($A8,'C9'!$B$2:$B$14,0),MATCH(G$2,'C9'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C11'!$B$2:$Z$14,MATCH($A8,'C11'!$B$2:$B$14,0),MATCH(G$2,'C11'!$B$2:$Z$2,0)),0)</f>
+        <v>4</v>
+      </c>
+      <c r="H8" s="1">
+        <f>IFERROR(INDEX('C15'!$B$2:$Z$14,MATCH($A8,'C15'!$B$2:$B$14,0),MATCH(H$2,'C15'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C1'!$B$2:$Z$14,MATCH($A8,'C1'!$B$2:$B$14,0),MATCH(H$2,'C1'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C3'!$B$2:$Z$14,MATCH($A8,'C3'!$B$2:$B$14,0),MATCH(H$2,'C3'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C5'!$B$2:$Z$14,MATCH($A8,'C5'!$B$2:$B$14,0),MATCH(H$2,'C5'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C7'!$B$2:$Z$14,MATCH($A8,'C7'!$B$2:$B$14,0),MATCH(H$2,'C7'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C9'!$B$2:$Z$14,MATCH($A8,'C9'!$B$2:$B$14,0),MATCH(H$2,'C9'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C11'!$B$2:$Z$14,MATCH($A8,'C11'!$B$2:$B$14,0),MATCH(H$2,'C11'!$B$2:$Z$2,0)),0)</f>
+        <v>0</v>
+      </c>
+      <c r="I8" s="1">
+        <f>IFERROR(INDEX('C15'!$B$2:$Z$14,MATCH($A8,'C15'!$B$2:$B$14,0),MATCH(I$2,'C15'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C1'!$B$2:$Z$14,MATCH($A8,'C1'!$B$2:$B$14,0),MATCH(I$2,'C1'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C3'!$B$2:$Z$14,MATCH($A8,'C3'!$B$2:$B$14,0),MATCH(I$2,'C3'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C5'!$B$2:$Z$14,MATCH($A8,'C5'!$B$2:$B$14,0),MATCH(I$2,'C5'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C7'!$B$2:$Z$14,MATCH($A8,'C7'!$B$2:$B$14,0),MATCH(I$2,'C7'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C9'!$B$2:$Z$14,MATCH($A8,'C9'!$B$2:$B$14,0),MATCH(I$2,'C9'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C11'!$B$2:$Z$14,MATCH($A8,'C11'!$B$2:$B$14,0),MATCH(I$2,'C11'!$B$2:$Z$2,0)),0)</f>
+        <v>1</v>
+      </c>
+      <c r="J8" s="1">
+        <f>IFERROR(INDEX('C15'!$B$2:$Z$14,MATCH($A8,'C15'!$B$2:$B$14,0),MATCH(J$2,'C15'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C1'!$B$2:$Z$14,MATCH($A8,'C1'!$B$2:$B$14,0),MATCH(J$2,'C1'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C3'!$B$2:$Z$14,MATCH($A8,'C3'!$B$2:$B$14,0),MATCH(J$2,'C3'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C5'!$B$2:$Z$14,MATCH($A8,'C5'!$B$2:$B$14,0),MATCH(J$2,'C5'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C7'!$B$2:$Z$14,MATCH($A8,'C7'!$B$2:$B$14,0),MATCH(J$2,'C7'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C9'!$B$2:$Z$14,MATCH($A8,'C9'!$B$2:$B$14,0),MATCH(J$2,'C9'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C11'!$B$2:$Z$14,MATCH($A8,'C11'!$B$2:$B$14,0),MATCH(J$2,'C11'!$B$2:$Z$2,0)),0)</f>
+        <v>4</v>
+      </c>
+      <c r="K8" s="1">
+        <f>IFERROR(INDEX('C15'!$B$2:$Z$14,MATCH($A8,'C15'!$B$2:$B$14,0),MATCH(K$2,'C15'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C1'!$B$2:$Z$14,MATCH($A8,'C1'!$B$2:$B$14,0),MATCH(K$2,'C1'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C3'!$B$2:$Z$14,MATCH($A8,'C3'!$B$2:$B$14,0),MATCH(K$2,'C3'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C5'!$B$2:$Z$14,MATCH($A8,'C5'!$B$2:$B$14,0),MATCH(K$2,'C5'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C7'!$B$2:$Z$14,MATCH($A8,'C7'!$B$2:$B$14,0),MATCH(K$2,'C7'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C9'!$B$2:$Z$14,MATCH($A8,'C9'!$B$2:$B$14,0),MATCH(K$2,'C9'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C11'!$B$2:$Z$14,MATCH($A8,'C11'!$B$2:$B$14,0),MATCH(K$2,'C11'!$B$2:$Z$2,0)),0)</f>
+        <v>1</v>
+      </c>
+      <c r="L8" s="1">
+        <f>IFERROR(INDEX('C15'!$B$2:$Z$14,MATCH($A8,'C15'!$B$2:$B$14,0),MATCH(L$2,'C15'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C1'!$B$2:$Z$14,MATCH($A8,'C1'!$B$2:$B$14,0),MATCH(L$2,'C1'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C3'!$B$2:$Z$14,MATCH($A8,'C3'!$B$2:$B$14,0),MATCH(L$2,'C3'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C5'!$B$2:$Z$14,MATCH($A8,'C5'!$B$2:$B$14,0),MATCH(L$2,'C5'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C7'!$B$2:$Z$14,MATCH($A8,'C7'!$B$2:$B$14,0),MATCH(L$2,'C7'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C9'!$B$2:$Z$14,MATCH($A8,'C9'!$B$2:$B$14,0),MATCH(L$2,'C9'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C11'!$B$2:$Z$14,MATCH($A8,'C11'!$B$2:$B$14,0),MATCH(L$2,'C11'!$B$2:$Z$2,0)),0)</f>
+        <v>0</v>
+      </c>
+      <c r="M8" s="1">
+        <f>IFERROR(INDEX('C15'!$B$2:$Z$14,MATCH($A8,'C15'!$B$2:$B$14,0),MATCH(M$2,'C15'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C1'!$B$2:$Z$14,MATCH($A8,'C1'!$B$2:$B$14,0),MATCH(M$2,'C1'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C3'!$B$2:$Z$14,MATCH($A8,'C3'!$B$2:$B$14,0),MATCH(M$2,'C3'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C5'!$B$2:$Z$14,MATCH($A8,'C5'!$B$2:$B$14,0),MATCH(M$2,'C5'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C7'!$B$2:$Z$14,MATCH($A8,'C7'!$B$2:$B$14,0),MATCH(M$2,'C7'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C9'!$B$2:$Z$14,MATCH($A8,'C9'!$B$2:$B$14,0),MATCH(M$2,'C9'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C11'!$B$2:$Z$14,MATCH($A8,'C11'!$B$2:$B$14,0),MATCH(M$2,'C11'!$B$2:$Z$2,0)),0)</f>
+        <v>1</v>
+      </c>
+      <c r="N8" s="1">
+        <f>IFERROR(INDEX('C15'!$B$2:$Z$14,MATCH($A8,'C15'!$B$2:$B$14,0),MATCH(N$2,'C15'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C1'!$B$2:$Z$14,MATCH($A8,'C1'!$B$2:$B$14,0),MATCH(N$2,'C1'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C3'!$B$2:$Z$14,MATCH($A8,'C3'!$B$2:$B$14,0),MATCH(N$2,'C3'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C5'!$B$2:$Z$14,MATCH($A8,'C5'!$B$2:$B$14,0),MATCH(N$2,'C5'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C7'!$B$2:$Z$14,MATCH($A8,'C7'!$B$2:$B$14,0),MATCH(N$2,'C7'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C9'!$B$2:$Z$14,MATCH($A8,'C9'!$B$2:$B$14,0),MATCH(N$2,'C9'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C11'!$B$2:$Z$14,MATCH($A8,'C11'!$B$2:$B$14,0),MATCH(N$2,'C11'!$B$2:$Z$2,0)),0)</f>
+        <v>0</v>
+      </c>
+      <c r="O8" s="1">
+        <f>IFERROR(INDEX('C15'!$B$2:$Z$14,MATCH($A8,'C15'!$B$2:$B$14,0),MATCH(O$2,'C15'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C1'!$B$2:$Z$14,MATCH($A8,'C1'!$B$2:$B$14,0),MATCH(O$2,'C1'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C3'!$B$2:$Z$14,MATCH($A8,'C3'!$B$2:$B$14,0),MATCH(O$2,'C3'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C5'!$B$2:$Z$14,MATCH($A8,'C5'!$B$2:$B$14,0),MATCH(O$2,'C5'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C7'!$B$2:$Z$14,MATCH($A8,'C7'!$B$2:$B$14,0),MATCH(O$2,'C7'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C9'!$B$2:$Z$14,MATCH($A8,'C9'!$B$2:$B$14,0),MATCH(O$2,'C9'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C11'!$B$2:$Z$14,MATCH($A8,'C11'!$B$2:$B$14,0),MATCH(O$2,'C11'!$B$2:$Z$2,0)),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A9" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" s="1">
+        <f>IFERROR(INDEX('C15'!$B$2:$Z$14,MATCH($A9,'C15'!$B$2:$B$14,0),MATCH(B$2,'C15'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C1'!$B$2:$Z$14,MATCH($A9,'C1'!$B$2:$B$14,0),MATCH(B$2,'C1'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C3'!$B$2:$Z$14,MATCH($A9,'C3'!$B$2:$B$14,0),MATCH(B$2,'C3'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C5'!$B$2:$Z$14,MATCH($A9,'C5'!$B$2:$B$14,0),MATCH(B$2,'C5'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C7'!$B$2:$Z$14,MATCH($A9,'C7'!$B$2:$B$14,0),MATCH(B$2,'C7'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C9'!$B$2:$Z$14,MATCH($A9,'C9'!$B$2:$B$14,0),MATCH(B$2,'C9'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C11'!$B$2:$Z$14,MATCH($A9,'C11'!$B$2:$B$14,0),MATCH(B$2,'C11'!$B$2:$Z$2,0)),0)</f>
+        <v>2</v>
+      </c>
+      <c r="C9" s="1">
+        <f>IFERROR(INDEX('C15'!$B$2:$Z$14,MATCH($A9,'C15'!$B$2:$B$14,0),MATCH(C$2,'C15'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C1'!$B$2:$Z$14,MATCH($A9,'C1'!$B$2:$B$14,0),MATCH(C$2,'C1'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C3'!$B$2:$Z$14,MATCH($A9,'C3'!$B$2:$B$14,0),MATCH(C$2,'C3'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C5'!$B$2:$Z$14,MATCH($A9,'C5'!$B$2:$B$14,0),MATCH(C$2,'C5'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C7'!$B$2:$Z$14,MATCH($A9,'C7'!$B$2:$B$14,0),MATCH(C$2,'C7'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C9'!$B$2:$Z$14,MATCH($A9,'C9'!$B$2:$B$14,0),MATCH(C$2,'C9'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C11'!$B$2:$Z$14,MATCH($A9,'C11'!$B$2:$B$14,0),MATCH(C$2,'C11'!$B$2:$Z$2,0)),0)</f>
+        <v>1</v>
+      </c>
+      <c r="D9" s="1">
+        <f>IFERROR(INDEX('C15'!$B$2:$Z$14,MATCH($A9,'C15'!$B$2:$B$14,0),MATCH(D$2,'C15'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C1'!$B$2:$Z$14,MATCH($A9,'C1'!$B$2:$B$14,0),MATCH(D$2,'C1'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C3'!$B$2:$Z$14,MATCH($A9,'C3'!$B$2:$B$14,0),MATCH(D$2,'C3'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C5'!$B$2:$Z$14,MATCH($A9,'C5'!$B$2:$B$14,0),MATCH(D$2,'C5'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C7'!$B$2:$Z$14,MATCH($A9,'C7'!$B$2:$B$14,0),MATCH(D$2,'C7'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C9'!$B$2:$Z$14,MATCH($A9,'C9'!$B$2:$B$14,0),MATCH(D$2,'C9'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C11'!$B$2:$Z$14,MATCH($A9,'C11'!$B$2:$B$14,0),MATCH(D$2,'C11'!$B$2:$Z$2,0)),0)</f>
+        <v>4</v>
+      </c>
+      <c r="E9" s="1">
+        <f>IFERROR(INDEX('C15'!$B$2:$Z$14,MATCH($A9,'C15'!$B$2:$B$14,0),MATCH(E$2,'C15'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C1'!$B$2:$Z$14,MATCH($A9,'C1'!$B$2:$B$14,0),MATCH(E$2,'C1'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C3'!$B$2:$Z$14,MATCH($A9,'C3'!$B$2:$B$14,0),MATCH(E$2,'C3'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C5'!$B$2:$Z$14,MATCH($A9,'C5'!$B$2:$B$14,0),MATCH(E$2,'C5'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C7'!$B$2:$Z$14,MATCH($A9,'C7'!$B$2:$B$14,0),MATCH(E$2,'C7'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C9'!$B$2:$Z$14,MATCH($A9,'C9'!$B$2:$B$14,0),MATCH(E$2,'C9'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C11'!$B$2:$Z$14,MATCH($A9,'C11'!$B$2:$B$14,0),MATCH(E$2,'C11'!$B$2:$Z$2,0)),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F9" s="1">
+        <f>IFERROR(INDEX('C15'!$B$2:$Z$14,MATCH($A9,'C15'!$B$2:$B$14,0),MATCH(F$2,'C15'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C1'!$B$2:$Z$14,MATCH($A9,'C1'!$B$2:$B$14,0),MATCH(F$2,'C1'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C3'!$B$2:$Z$14,MATCH($A9,'C3'!$B$2:$B$14,0),MATCH(F$2,'C3'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C5'!$B$2:$Z$14,MATCH($A9,'C5'!$B$2:$B$14,0),MATCH(F$2,'C5'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C7'!$B$2:$Z$14,MATCH($A9,'C7'!$B$2:$B$14,0),MATCH(F$2,'C7'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C9'!$B$2:$Z$14,MATCH($A9,'C9'!$B$2:$B$14,0),MATCH(F$2,'C9'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C11'!$B$2:$Z$14,MATCH($A9,'C11'!$B$2:$B$14,0),MATCH(F$2,'C11'!$B$2:$Z$2,0)),0)</f>
+        <v>3</v>
+      </c>
+      <c r="G9" s="1">
+        <f>IFERROR(INDEX('C15'!$B$2:$Z$14,MATCH($A9,'C15'!$B$2:$B$14,0),MATCH(G$2,'C15'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C1'!$B$2:$Z$14,MATCH($A9,'C1'!$B$2:$B$14,0),MATCH(G$2,'C1'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C3'!$B$2:$Z$14,MATCH($A9,'C3'!$B$2:$B$14,0),MATCH(G$2,'C3'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C5'!$B$2:$Z$14,MATCH($A9,'C5'!$B$2:$B$14,0),MATCH(G$2,'C5'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C7'!$B$2:$Z$14,MATCH($A9,'C7'!$B$2:$B$14,0),MATCH(G$2,'C7'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C9'!$B$2:$Z$14,MATCH($A9,'C9'!$B$2:$B$14,0),MATCH(G$2,'C9'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C11'!$B$2:$Z$14,MATCH($A9,'C11'!$B$2:$B$14,0),MATCH(G$2,'C11'!$B$2:$Z$2,0)),0)</f>
+        <v>5</v>
+      </c>
+      <c r="H9" s="1">
+        <f>IFERROR(INDEX('C15'!$B$2:$Z$14,MATCH($A9,'C15'!$B$2:$B$14,0),MATCH(H$2,'C15'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C1'!$B$2:$Z$14,MATCH($A9,'C1'!$B$2:$B$14,0),MATCH(H$2,'C1'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C3'!$B$2:$Z$14,MATCH($A9,'C3'!$B$2:$B$14,0),MATCH(H$2,'C3'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C5'!$B$2:$Z$14,MATCH($A9,'C5'!$B$2:$B$14,0),MATCH(H$2,'C5'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C7'!$B$2:$Z$14,MATCH($A9,'C7'!$B$2:$B$14,0),MATCH(H$2,'C7'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C9'!$B$2:$Z$14,MATCH($A9,'C9'!$B$2:$B$14,0),MATCH(H$2,'C9'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C11'!$B$2:$Z$14,MATCH($A9,'C11'!$B$2:$B$14,0),MATCH(H$2,'C11'!$B$2:$Z$2,0)),0)</f>
+        <v>1</v>
+      </c>
+      <c r="I9" s="1">
+        <f>IFERROR(INDEX('C15'!$B$2:$Z$14,MATCH($A9,'C15'!$B$2:$B$14,0),MATCH(I$2,'C15'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C1'!$B$2:$Z$14,MATCH($A9,'C1'!$B$2:$B$14,0),MATCH(I$2,'C1'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C3'!$B$2:$Z$14,MATCH($A9,'C3'!$B$2:$B$14,0),MATCH(I$2,'C3'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C5'!$B$2:$Z$14,MATCH($A9,'C5'!$B$2:$B$14,0),MATCH(I$2,'C5'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C7'!$B$2:$Z$14,MATCH($A9,'C7'!$B$2:$B$14,0),MATCH(I$2,'C7'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C9'!$B$2:$Z$14,MATCH($A9,'C9'!$B$2:$B$14,0),MATCH(I$2,'C9'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C11'!$B$2:$Z$14,MATCH($A9,'C11'!$B$2:$B$14,0),MATCH(I$2,'C11'!$B$2:$Z$2,0)),0)</f>
+        <v>1</v>
+      </c>
+      <c r="J9" s="1">
+        <f>IFERROR(INDEX('C15'!$B$2:$Z$14,MATCH($A9,'C15'!$B$2:$B$14,0),MATCH(J$2,'C15'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C1'!$B$2:$Z$14,MATCH($A9,'C1'!$B$2:$B$14,0),MATCH(J$2,'C1'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C3'!$B$2:$Z$14,MATCH($A9,'C3'!$B$2:$B$14,0),MATCH(J$2,'C3'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C5'!$B$2:$Z$14,MATCH($A9,'C5'!$B$2:$B$14,0),MATCH(J$2,'C5'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C7'!$B$2:$Z$14,MATCH($A9,'C7'!$B$2:$B$14,0),MATCH(J$2,'C7'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C9'!$B$2:$Z$14,MATCH($A9,'C9'!$B$2:$B$14,0),MATCH(J$2,'C9'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C11'!$B$2:$Z$14,MATCH($A9,'C11'!$B$2:$B$14,0),MATCH(J$2,'C11'!$B$2:$Z$2,0)),0)</f>
+        <v>4</v>
+      </c>
+      <c r="K9" s="1">
+        <f>IFERROR(INDEX('C15'!$B$2:$Z$14,MATCH($A9,'C15'!$B$2:$B$14,0),MATCH(K$2,'C15'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C1'!$B$2:$Z$14,MATCH($A9,'C1'!$B$2:$B$14,0),MATCH(K$2,'C1'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C3'!$B$2:$Z$14,MATCH($A9,'C3'!$B$2:$B$14,0),MATCH(K$2,'C3'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C5'!$B$2:$Z$14,MATCH($A9,'C5'!$B$2:$B$14,0),MATCH(K$2,'C5'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C7'!$B$2:$Z$14,MATCH($A9,'C7'!$B$2:$B$14,0),MATCH(K$2,'C7'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C9'!$B$2:$Z$14,MATCH($A9,'C9'!$B$2:$B$14,0),MATCH(K$2,'C9'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C11'!$B$2:$Z$14,MATCH($A9,'C11'!$B$2:$B$14,0),MATCH(K$2,'C11'!$B$2:$Z$2,0)),0)</f>
+        <v>1</v>
+      </c>
+      <c r="L9" s="1">
+        <f>IFERROR(INDEX('C15'!$B$2:$Z$14,MATCH($A9,'C15'!$B$2:$B$14,0),MATCH(L$2,'C15'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C1'!$B$2:$Z$14,MATCH($A9,'C1'!$B$2:$B$14,0),MATCH(L$2,'C1'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C3'!$B$2:$Z$14,MATCH($A9,'C3'!$B$2:$B$14,0),MATCH(L$2,'C3'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C5'!$B$2:$Z$14,MATCH($A9,'C5'!$B$2:$B$14,0),MATCH(L$2,'C5'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C7'!$B$2:$Z$14,MATCH($A9,'C7'!$B$2:$B$14,0),MATCH(L$2,'C7'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C9'!$B$2:$Z$14,MATCH($A9,'C9'!$B$2:$B$14,0),MATCH(L$2,'C9'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C11'!$B$2:$Z$14,MATCH($A9,'C11'!$B$2:$B$14,0),MATCH(L$2,'C11'!$B$2:$Z$2,0)),0)</f>
+        <v>0</v>
+      </c>
+      <c r="M9" s="1">
+        <f>IFERROR(INDEX('C15'!$B$2:$Z$14,MATCH($A9,'C15'!$B$2:$B$14,0),MATCH(M$2,'C15'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C1'!$B$2:$Z$14,MATCH($A9,'C1'!$B$2:$B$14,0),MATCH(M$2,'C1'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C3'!$B$2:$Z$14,MATCH($A9,'C3'!$B$2:$B$14,0),MATCH(M$2,'C3'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C5'!$B$2:$Z$14,MATCH($A9,'C5'!$B$2:$B$14,0),MATCH(M$2,'C5'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C7'!$B$2:$Z$14,MATCH($A9,'C7'!$B$2:$B$14,0),MATCH(M$2,'C7'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C9'!$B$2:$Z$14,MATCH($A9,'C9'!$B$2:$B$14,0),MATCH(M$2,'C9'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C11'!$B$2:$Z$14,MATCH($A9,'C11'!$B$2:$B$14,0),MATCH(M$2,'C11'!$B$2:$Z$2,0)),0)</f>
+        <v>1</v>
+      </c>
+      <c r="N9" s="1">
+        <f>IFERROR(INDEX('C15'!$B$2:$Z$14,MATCH($A9,'C15'!$B$2:$B$14,0),MATCH(N$2,'C15'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C1'!$B$2:$Z$14,MATCH($A9,'C1'!$B$2:$B$14,0),MATCH(N$2,'C1'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C3'!$B$2:$Z$14,MATCH($A9,'C3'!$B$2:$B$14,0),MATCH(N$2,'C3'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C5'!$B$2:$Z$14,MATCH($A9,'C5'!$B$2:$B$14,0),MATCH(N$2,'C5'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C7'!$B$2:$Z$14,MATCH($A9,'C7'!$B$2:$B$14,0),MATCH(N$2,'C7'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C9'!$B$2:$Z$14,MATCH($A9,'C9'!$B$2:$B$14,0),MATCH(N$2,'C9'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C11'!$B$2:$Z$14,MATCH($A9,'C11'!$B$2:$B$14,0),MATCH(N$2,'C11'!$B$2:$Z$2,0)),0)</f>
+        <v>0</v>
+      </c>
+      <c r="O9" s="1">
+        <f>IFERROR(INDEX('C15'!$B$2:$Z$14,MATCH($A9,'C15'!$B$2:$B$14,0),MATCH(O$2,'C15'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C1'!$B$2:$Z$14,MATCH($A9,'C1'!$B$2:$B$14,0),MATCH(O$2,'C1'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C3'!$B$2:$Z$14,MATCH($A9,'C3'!$B$2:$B$14,0),MATCH(O$2,'C3'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C5'!$B$2:$Z$14,MATCH($A9,'C5'!$B$2:$B$14,0),MATCH(O$2,'C5'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C7'!$B$2:$Z$14,MATCH($A9,'C7'!$B$2:$B$14,0),MATCH(O$2,'C7'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C9'!$B$2:$Z$14,MATCH($A9,'C9'!$B$2:$B$14,0),MATCH(O$2,'C9'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C11'!$B$2:$Z$14,MATCH($A9,'C11'!$B$2:$B$14,0),MATCH(O$2,'C11'!$B$2:$Z$2,0)),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A10" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B10" s="1">
+        <f>IFERROR(INDEX('C15'!$B$2:$Z$14,MATCH($A10,'C15'!$B$2:$B$14,0),MATCH(B$2,'C15'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C1'!$B$2:$Z$14,MATCH($A10,'C1'!$B$2:$B$14,0),MATCH(B$2,'C1'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C3'!$B$2:$Z$14,MATCH($A10,'C3'!$B$2:$B$14,0),MATCH(B$2,'C3'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C5'!$B$2:$Z$14,MATCH($A10,'C5'!$B$2:$B$14,0),MATCH(B$2,'C5'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C7'!$B$2:$Z$14,MATCH($A10,'C7'!$B$2:$B$14,0),MATCH(B$2,'C7'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C9'!$B$2:$Z$14,MATCH($A10,'C9'!$B$2:$B$14,0),MATCH(B$2,'C9'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C11'!$B$2:$Z$14,MATCH($A10,'C11'!$B$2:$B$14,0),MATCH(B$2,'C11'!$B$2:$Z$2,0)),0)</f>
+        <v>1</v>
+      </c>
+      <c r="C10" s="1">
+        <f>IFERROR(INDEX('C15'!$B$2:$Z$14,MATCH($A10,'C15'!$B$2:$B$14,0),MATCH(C$2,'C15'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C1'!$B$2:$Z$14,MATCH($A10,'C1'!$B$2:$B$14,0),MATCH(C$2,'C1'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C3'!$B$2:$Z$14,MATCH($A10,'C3'!$B$2:$B$14,0),MATCH(C$2,'C3'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C5'!$B$2:$Z$14,MATCH($A10,'C5'!$B$2:$B$14,0),MATCH(C$2,'C5'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C7'!$B$2:$Z$14,MATCH($A10,'C7'!$B$2:$B$14,0),MATCH(C$2,'C7'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C9'!$B$2:$Z$14,MATCH($A10,'C9'!$B$2:$B$14,0),MATCH(C$2,'C9'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C11'!$B$2:$Z$14,MATCH($A10,'C11'!$B$2:$B$14,0),MATCH(C$2,'C11'!$B$2:$Z$2,0)),0)</f>
+        <v>3</v>
+      </c>
+      <c r="D10" s="1">
+        <f>IFERROR(INDEX('C15'!$B$2:$Z$14,MATCH($A10,'C15'!$B$2:$B$14,0),MATCH(D$2,'C15'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C1'!$B$2:$Z$14,MATCH($A10,'C1'!$B$2:$B$14,0),MATCH(D$2,'C1'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C3'!$B$2:$Z$14,MATCH($A10,'C3'!$B$2:$B$14,0),MATCH(D$2,'C3'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C5'!$B$2:$Z$14,MATCH($A10,'C5'!$B$2:$B$14,0),MATCH(D$2,'C5'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C7'!$B$2:$Z$14,MATCH($A10,'C7'!$B$2:$B$14,0),MATCH(D$2,'C7'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C9'!$B$2:$Z$14,MATCH($A10,'C9'!$B$2:$B$14,0),MATCH(D$2,'C9'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C11'!$B$2:$Z$14,MATCH($A10,'C11'!$B$2:$B$14,0),MATCH(D$2,'C11'!$B$2:$Z$2,0)),0)</f>
+        <v>3</v>
+      </c>
+      <c r="E10" s="1">
+        <f>IFERROR(INDEX('C15'!$B$2:$Z$14,MATCH($A10,'C15'!$B$2:$B$14,0),MATCH(E$2,'C15'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C1'!$B$2:$Z$14,MATCH($A10,'C1'!$B$2:$B$14,0),MATCH(E$2,'C1'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C3'!$B$2:$Z$14,MATCH($A10,'C3'!$B$2:$B$14,0),MATCH(E$2,'C3'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C5'!$B$2:$Z$14,MATCH($A10,'C5'!$B$2:$B$14,0),MATCH(E$2,'C5'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C7'!$B$2:$Z$14,MATCH($A10,'C7'!$B$2:$B$14,0),MATCH(E$2,'C7'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C9'!$B$2:$Z$14,MATCH($A10,'C9'!$B$2:$B$14,0),MATCH(E$2,'C9'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C11'!$B$2:$Z$14,MATCH($A10,'C11'!$B$2:$B$14,0),MATCH(E$2,'C11'!$B$2:$Z$2,0)),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F10" s="1">
+        <f>IFERROR(INDEX('C15'!$B$2:$Z$14,MATCH($A10,'C15'!$B$2:$B$14,0),MATCH(F$2,'C15'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C1'!$B$2:$Z$14,MATCH($A10,'C1'!$B$2:$B$14,0),MATCH(F$2,'C1'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C3'!$B$2:$Z$14,MATCH($A10,'C3'!$B$2:$B$14,0),MATCH(F$2,'C3'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C5'!$B$2:$Z$14,MATCH($A10,'C5'!$B$2:$B$14,0),MATCH(F$2,'C5'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C7'!$B$2:$Z$14,MATCH($A10,'C7'!$B$2:$B$14,0),MATCH(F$2,'C7'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C9'!$B$2:$Z$14,MATCH($A10,'C9'!$B$2:$B$14,0),MATCH(F$2,'C9'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C11'!$B$2:$Z$14,MATCH($A10,'C11'!$B$2:$B$14,0),MATCH(F$2,'C11'!$B$2:$Z$2,0)),0)</f>
+        <v>6</v>
+      </c>
+      <c r="G10" s="1">
+        <f>IFERROR(INDEX('C15'!$B$2:$Z$14,MATCH($A10,'C15'!$B$2:$B$14,0),MATCH(G$2,'C15'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C1'!$B$2:$Z$14,MATCH($A10,'C1'!$B$2:$B$14,0),MATCH(G$2,'C1'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C3'!$B$2:$Z$14,MATCH($A10,'C3'!$B$2:$B$14,0),MATCH(G$2,'C3'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C5'!$B$2:$Z$14,MATCH($A10,'C5'!$B$2:$B$14,0),MATCH(G$2,'C5'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C7'!$B$2:$Z$14,MATCH($A10,'C7'!$B$2:$B$14,0),MATCH(G$2,'C7'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C9'!$B$2:$Z$14,MATCH($A10,'C9'!$B$2:$B$14,0),MATCH(G$2,'C9'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C11'!$B$2:$Z$14,MATCH($A10,'C11'!$B$2:$B$14,0),MATCH(G$2,'C11'!$B$2:$Z$2,0)),0)</f>
+        <v>5</v>
+      </c>
+      <c r="H10" s="1">
+        <f>IFERROR(INDEX('C15'!$B$2:$Z$14,MATCH($A10,'C15'!$B$2:$B$14,0),MATCH(H$2,'C15'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C1'!$B$2:$Z$14,MATCH($A10,'C1'!$B$2:$B$14,0),MATCH(H$2,'C1'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C3'!$B$2:$Z$14,MATCH($A10,'C3'!$B$2:$B$14,0),MATCH(H$2,'C3'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C5'!$B$2:$Z$14,MATCH($A10,'C5'!$B$2:$B$14,0),MATCH(H$2,'C5'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C7'!$B$2:$Z$14,MATCH($A10,'C7'!$B$2:$B$14,0),MATCH(H$2,'C7'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C9'!$B$2:$Z$14,MATCH($A10,'C9'!$B$2:$B$14,0),MATCH(H$2,'C9'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C11'!$B$2:$Z$14,MATCH($A10,'C11'!$B$2:$B$14,0),MATCH(H$2,'C11'!$B$2:$Z$2,0)),0)</f>
+        <v>1</v>
+      </c>
+      <c r="I10" s="1">
+        <f>IFERROR(INDEX('C15'!$B$2:$Z$14,MATCH($A10,'C15'!$B$2:$B$14,0),MATCH(I$2,'C15'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C1'!$B$2:$Z$14,MATCH($A10,'C1'!$B$2:$B$14,0),MATCH(I$2,'C1'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C3'!$B$2:$Z$14,MATCH($A10,'C3'!$B$2:$B$14,0),MATCH(I$2,'C3'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C5'!$B$2:$Z$14,MATCH($A10,'C5'!$B$2:$B$14,0),MATCH(I$2,'C5'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C7'!$B$2:$Z$14,MATCH($A10,'C7'!$B$2:$B$14,0),MATCH(I$2,'C7'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C9'!$B$2:$Z$14,MATCH($A10,'C9'!$B$2:$B$14,0),MATCH(I$2,'C9'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C11'!$B$2:$Z$14,MATCH($A10,'C11'!$B$2:$B$14,0),MATCH(I$2,'C11'!$B$2:$Z$2,0)),0)</f>
+        <v>1</v>
+      </c>
+      <c r="J10" s="1">
+        <f>IFERROR(INDEX('C15'!$B$2:$Z$14,MATCH($A10,'C15'!$B$2:$B$14,0),MATCH(J$2,'C15'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C1'!$B$2:$Z$14,MATCH($A10,'C1'!$B$2:$B$14,0),MATCH(J$2,'C1'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C3'!$B$2:$Z$14,MATCH($A10,'C3'!$B$2:$B$14,0),MATCH(J$2,'C3'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C5'!$B$2:$Z$14,MATCH($A10,'C5'!$B$2:$B$14,0),MATCH(J$2,'C5'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C7'!$B$2:$Z$14,MATCH($A10,'C7'!$B$2:$B$14,0),MATCH(J$2,'C7'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C9'!$B$2:$Z$14,MATCH($A10,'C9'!$B$2:$B$14,0),MATCH(J$2,'C9'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C11'!$B$2:$Z$14,MATCH($A10,'C11'!$B$2:$B$14,0),MATCH(J$2,'C11'!$B$2:$Z$2,0)),0)</f>
+        <v>2</v>
+      </c>
+      <c r="K10" s="1">
+        <f>IFERROR(INDEX('C15'!$B$2:$Z$14,MATCH($A10,'C15'!$B$2:$B$14,0),MATCH(K$2,'C15'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C1'!$B$2:$Z$14,MATCH($A10,'C1'!$B$2:$B$14,0),MATCH(K$2,'C1'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C3'!$B$2:$Z$14,MATCH($A10,'C3'!$B$2:$B$14,0),MATCH(K$2,'C3'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C5'!$B$2:$Z$14,MATCH($A10,'C5'!$B$2:$B$14,0),MATCH(K$2,'C5'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C7'!$B$2:$Z$14,MATCH($A10,'C7'!$B$2:$B$14,0),MATCH(K$2,'C7'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C9'!$B$2:$Z$14,MATCH($A10,'C9'!$B$2:$B$14,0),MATCH(K$2,'C9'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C11'!$B$2:$Z$14,MATCH($A10,'C11'!$B$2:$B$14,0),MATCH(K$2,'C11'!$B$2:$Z$2,0)),0)</f>
+        <v>0</v>
+      </c>
+      <c r="L10" s="1">
+        <f>IFERROR(INDEX('C15'!$B$2:$Z$14,MATCH($A10,'C15'!$B$2:$B$14,0),MATCH(L$2,'C15'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C1'!$B$2:$Z$14,MATCH($A10,'C1'!$B$2:$B$14,0),MATCH(L$2,'C1'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C3'!$B$2:$Z$14,MATCH($A10,'C3'!$B$2:$B$14,0),MATCH(L$2,'C3'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C5'!$B$2:$Z$14,MATCH($A10,'C5'!$B$2:$B$14,0),MATCH(L$2,'C5'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C7'!$B$2:$Z$14,MATCH($A10,'C7'!$B$2:$B$14,0),MATCH(L$2,'C7'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C9'!$B$2:$Z$14,MATCH($A10,'C9'!$B$2:$B$14,0),MATCH(L$2,'C9'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C11'!$B$2:$Z$14,MATCH($A10,'C11'!$B$2:$B$14,0),MATCH(L$2,'C11'!$B$2:$Z$2,0)),0)</f>
+        <v>0</v>
+      </c>
+      <c r="M10" s="1">
+        <f>IFERROR(INDEX('C15'!$B$2:$Z$14,MATCH($A10,'C15'!$B$2:$B$14,0),MATCH(M$2,'C15'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C1'!$B$2:$Z$14,MATCH($A10,'C1'!$B$2:$B$14,0),MATCH(M$2,'C1'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C3'!$B$2:$Z$14,MATCH($A10,'C3'!$B$2:$B$14,0),MATCH(M$2,'C3'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C5'!$B$2:$Z$14,MATCH($A10,'C5'!$B$2:$B$14,0),MATCH(M$2,'C5'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C7'!$B$2:$Z$14,MATCH($A10,'C7'!$B$2:$B$14,0),MATCH(M$2,'C7'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C9'!$B$2:$Z$14,MATCH($A10,'C9'!$B$2:$B$14,0),MATCH(M$2,'C9'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C11'!$B$2:$Z$14,MATCH($A10,'C11'!$B$2:$B$14,0),MATCH(M$2,'C11'!$B$2:$Z$2,0)),0)</f>
+        <v>1</v>
+      </c>
+      <c r="N10" s="1">
+        <f>IFERROR(INDEX('C15'!$B$2:$Z$14,MATCH($A10,'C15'!$B$2:$B$14,0),MATCH(N$2,'C15'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C1'!$B$2:$Z$14,MATCH($A10,'C1'!$B$2:$B$14,0),MATCH(N$2,'C1'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C3'!$B$2:$Z$14,MATCH($A10,'C3'!$B$2:$B$14,0),MATCH(N$2,'C3'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C5'!$B$2:$Z$14,MATCH($A10,'C5'!$B$2:$B$14,0),MATCH(N$2,'C5'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C7'!$B$2:$Z$14,MATCH($A10,'C7'!$B$2:$B$14,0),MATCH(N$2,'C7'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C9'!$B$2:$Z$14,MATCH($A10,'C9'!$B$2:$B$14,0),MATCH(N$2,'C9'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C11'!$B$2:$Z$14,MATCH($A10,'C11'!$B$2:$B$14,0),MATCH(N$2,'C11'!$B$2:$Z$2,0)),0)</f>
+        <v>0</v>
+      </c>
+      <c r="O10" s="1">
+        <f>IFERROR(INDEX('C15'!$B$2:$Z$14,MATCH($A10,'C15'!$B$2:$B$14,0),MATCH(O$2,'C15'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C1'!$B$2:$Z$14,MATCH($A10,'C1'!$B$2:$B$14,0),MATCH(O$2,'C1'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C3'!$B$2:$Z$14,MATCH($A10,'C3'!$B$2:$B$14,0),MATCH(O$2,'C3'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C5'!$B$2:$Z$14,MATCH($A10,'C5'!$B$2:$B$14,0),MATCH(O$2,'C5'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C7'!$B$2:$Z$14,MATCH($A10,'C7'!$B$2:$B$14,0),MATCH(O$2,'C7'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C9'!$B$2:$Z$14,MATCH($A10,'C9'!$B$2:$B$14,0),MATCH(O$2,'C9'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C11'!$B$2:$Z$14,MATCH($A10,'C11'!$B$2:$B$14,0),MATCH(O$2,'C11'!$B$2:$Z$2,0)),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A11" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B11" s="1">
+        <f>IFERROR(INDEX('C15'!$B$2:$Z$14,MATCH($A11,'C15'!$B$2:$B$14,0),MATCH(B$2,'C15'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C1'!$B$2:$Z$14,MATCH($A11,'C1'!$B$2:$B$14,0),MATCH(B$2,'C1'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C3'!$B$2:$Z$14,MATCH($A11,'C3'!$B$2:$B$14,0),MATCH(B$2,'C3'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C5'!$B$2:$Z$14,MATCH($A11,'C5'!$B$2:$B$14,0),MATCH(B$2,'C5'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C7'!$B$2:$Z$14,MATCH($A11,'C7'!$B$2:$B$14,0),MATCH(B$2,'C7'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C9'!$B$2:$Z$14,MATCH($A11,'C9'!$B$2:$B$14,0),MATCH(B$2,'C9'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C11'!$B$2:$Z$14,MATCH($A11,'C11'!$B$2:$B$14,0),MATCH(B$2,'C11'!$B$2:$Z$2,0)),0)</f>
+        <v>1</v>
+      </c>
+      <c r="C11" s="1">
+        <f>IFERROR(INDEX('C15'!$B$2:$Z$14,MATCH($A11,'C15'!$B$2:$B$14,0),MATCH(C$2,'C15'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C1'!$B$2:$Z$14,MATCH($A11,'C1'!$B$2:$B$14,0),MATCH(C$2,'C1'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C3'!$B$2:$Z$14,MATCH($A11,'C3'!$B$2:$B$14,0),MATCH(C$2,'C3'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C5'!$B$2:$Z$14,MATCH($A11,'C5'!$B$2:$B$14,0),MATCH(C$2,'C5'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C7'!$B$2:$Z$14,MATCH($A11,'C7'!$B$2:$B$14,0),MATCH(C$2,'C7'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C9'!$B$2:$Z$14,MATCH($A11,'C9'!$B$2:$B$14,0),MATCH(C$2,'C9'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C11'!$B$2:$Z$14,MATCH($A11,'C11'!$B$2:$B$14,0),MATCH(C$2,'C11'!$B$2:$Z$2,0)),0)</f>
+        <v>3</v>
+      </c>
+      <c r="D11" s="1">
+        <f>IFERROR(INDEX('C15'!$B$2:$Z$14,MATCH($A11,'C15'!$B$2:$B$14,0),MATCH(D$2,'C15'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C1'!$B$2:$Z$14,MATCH($A11,'C1'!$B$2:$B$14,0),MATCH(D$2,'C1'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C3'!$B$2:$Z$14,MATCH($A11,'C3'!$B$2:$B$14,0),MATCH(D$2,'C3'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C5'!$B$2:$Z$14,MATCH($A11,'C5'!$B$2:$B$14,0),MATCH(D$2,'C5'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C7'!$B$2:$Z$14,MATCH($A11,'C7'!$B$2:$B$14,0),MATCH(D$2,'C7'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C9'!$B$2:$Z$14,MATCH($A11,'C9'!$B$2:$B$14,0),MATCH(D$2,'C9'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C11'!$B$2:$Z$14,MATCH($A11,'C11'!$B$2:$B$14,0),MATCH(D$2,'C11'!$B$2:$Z$2,0)),0)</f>
+        <v>3</v>
+      </c>
+      <c r="E11" s="1">
+        <f>IFERROR(INDEX('C15'!$B$2:$Z$14,MATCH($A11,'C15'!$B$2:$B$14,0),MATCH(E$2,'C15'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C1'!$B$2:$Z$14,MATCH($A11,'C1'!$B$2:$B$14,0),MATCH(E$2,'C1'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C3'!$B$2:$Z$14,MATCH($A11,'C3'!$B$2:$B$14,0),MATCH(E$2,'C3'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C5'!$B$2:$Z$14,MATCH($A11,'C5'!$B$2:$B$14,0),MATCH(E$2,'C5'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C7'!$B$2:$Z$14,MATCH($A11,'C7'!$B$2:$B$14,0),MATCH(E$2,'C7'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C9'!$B$2:$Z$14,MATCH($A11,'C9'!$B$2:$B$14,0),MATCH(E$2,'C9'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C11'!$B$2:$Z$14,MATCH($A11,'C11'!$B$2:$B$14,0),MATCH(E$2,'C11'!$B$2:$Z$2,0)),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F11" s="1">
+        <f>IFERROR(INDEX('C15'!$B$2:$Z$14,MATCH($A11,'C15'!$B$2:$B$14,0),MATCH(F$2,'C15'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C1'!$B$2:$Z$14,MATCH($A11,'C1'!$B$2:$B$14,0),MATCH(F$2,'C1'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C3'!$B$2:$Z$14,MATCH($A11,'C3'!$B$2:$B$14,0),MATCH(F$2,'C3'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C5'!$B$2:$Z$14,MATCH($A11,'C5'!$B$2:$B$14,0),MATCH(F$2,'C5'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C7'!$B$2:$Z$14,MATCH($A11,'C7'!$B$2:$B$14,0),MATCH(F$2,'C7'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C9'!$B$2:$Z$14,MATCH($A11,'C9'!$B$2:$B$14,0),MATCH(F$2,'C9'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C11'!$B$2:$Z$14,MATCH($A11,'C11'!$B$2:$B$14,0),MATCH(F$2,'C11'!$B$2:$Z$2,0)),0)</f>
+        <v>4</v>
+      </c>
+      <c r="G11" s="1">
+        <f>IFERROR(INDEX('C15'!$B$2:$Z$14,MATCH($A11,'C15'!$B$2:$B$14,0),MATCH(G$2,'C15'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C1'!$B$2:$Z$14,MATCH($A11,'C1'!$B$2:$B$14,0),MATCH(G$2,'C1'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C3'!$B$2:$Z$14,MATCH($A11,'C3'!$B$2:$B$14,0),MATCH(G$2,'C3'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C5'!$B$2:$Z$14,MATCH($A11,'C5'!$B$2:$B$14,0),MATCH(G$2,'C5'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C7'!$B$2:$Z$14,MATCH($A11,'C7'!$B$2:$B$14,0),MATCH(G$2,'C7'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C9'!$B$2:$Z$14,MATCH($A11,'C9'!$B$2:$B$14,0),MATCH(G$2,'C9'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C11'!$B$2:$Z$14,MATCH($A11,'C11'!$B$2:$B$14,0),MATCH(G$2,'C11'!$B$2:$Z$2,0)),0)</f>
+        <v>5</v>
+      </c>
+      <c r="H11" s="1">
+        <f>IFERROR(INDEX('C15'!$B$2:$Z$14,MATCH($A11,'C15'!$B$2:$B$14,0),MATCH(H$2,'C15'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C1'!$B$2:$Z$14,MATCH($A11,'C1'!$B$2:$B$14,0),MATCH(H$2,'C1'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C3'!$B$2:$Z$14,MATCH($A11,'C3'!$B$2:$B$14,0),MATCH(H$2,'C3'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C5'!$B$2:$Z$14,MATCH($A11,'C5'!$B$2:$B$14,0),MATCH(H$2,'C5'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C7'!$B$2:$Z$14,MATCH($A11,'C7'!$B$2:$B$14,0),MATCH(H$2,'C7'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C9'!$B$2:$Z$14,MATCH($A11,'C9'!$B$2:$B$14,0),MATCH(H$2,'C9'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C11'!$B$2:$Z$14,MATCH($A11,'C11'!$B$2:$B$14,0),MATCH(H$2,'C11'!$B$2:$Z$2,0)),0)</f>
+        <v>2</v>
+      </c>
+      <c r="I11" s="1">
+        <f>IFERROR(INDEX('C15'!$B$2:$Z$14,MATCH($A11,'C15'!$B$2:$B$14,0),MATCH(I$2,'C15'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C1'!$B$2:$Z$14,MATCH($A11,'C1'!$B$2:$B$14,0),MATCH(I$2,'C1'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C3'!$B$2:$Z$14,MATCH($A11,'C3'!$B$2:$B$14,0),MATCH(I$2,'C3'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C5'!$B$2:$Z$14,MATCH($A11,'C5'!$B$2:$B$14,0),MATCH(I$2,'C5'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C7'!$B$2:$Z$14,MATCH($A11,'C7'!$B$2:$B$14,0),MATCH(I$2,'C7'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C9'!$B$2:$Z$14,MATCH($A11,'C9'!$B$2:$B$14,0),MATCH(I$2,'C9'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C11'!$B$2:$Z$14,MATCH($A11,'C11'!$B$2:$B$14,0),MATCH(I$2,'C11'!$B$2:$Z$2,0)),0)</f>
+        <v>1</v>
+      </c>
+      <c r="J11" s="1">
+        <f>IFERROR(INDEX('C15'!$B$2:$Z$14,MATCH($A11,'C15'!$B$2:$B$14,0),MATCH(J$2,'C15'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C1'!$B$2:$Z$14,MATCH($A11,'C1'!$B$2:$B$14,0),MATCH(J$2,'C1'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C3'!$B$2:$Z$14,MATCH($A11,'C3'!$B$2:$B$14,0),MATCH(J$2,'C3'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C5'!$B$2:$Z$14,MATCH($A11,'C5'!$B$2:$B$14,0),MATCH(J$2,'C5'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C7'!$B$2:$Z$14,MATCH($A11,'C7'!$B$2:$B$14,0),MATCH(J$2,'C7'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C9'!$B$2:$Z$14,MATCH($A11,'C9'!$B$2:$B$14,0),MATCH(J$2,'C9'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C11'!$B$2:$Z$14,MATCH($A11,'C11'!$B$2:$B$14,0),MATCH(J$2,'C11'!$B$2:$Z$2,0)),0)</f>
+        <v>2</v>
+      </c>
+      <c r="K11" s="1">
+        <f>IFERROR(INDEX('C15'!$B$2:$Z$14,MATCH($A11,'C15'!$B$2:$B$14,0),MATCH(K$2,'C15'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C1'!$B$2:$Z$14,MATCH($A11,'C1'!$B$2:$B$14,0),MATCH(K$2,'C1'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C3'!$B$2:$Z$14,MATCH($A11,'C3'!$B$2:$B$14,0),MATCH(K$2,'C3'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C5'!$B$2:$Z$14,MATCH($A11,'C5'!$B$2:$B$14,0),MATCH(K$2,'C5'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C7'!$B$2:$Z$14,MATCH($A11,'C7'!$B$2:$B$14,0),MATCH(K$2,'C7'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C9'!$B$2:$Z$14,MATCH($A11,'C9'!$B$2:$B$14,0),MATCH(K$2,'C9'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C11'!$B$2:$Z$14,MATCH($A11,'C11'!$B$2:$B$14,0),MATCH(K$2,'C11'!$B$2:$Z$2,0)),0)</f>
+        <v>1</v>
+      </c>
+      <c r="L11" s="1">
+        <f>IFERROR(INDEX('C15'!$B$2:$Z$14,MATCH($A11,'C15'!$B$2:$B$14,0),MATCH(L$2,'C15'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C1'!$B$2:$Z$14,MATCH($A11,'C1'!$B$2:$B$14,0),MATCH(L$2,'C1'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C3'!$B$2:$Z$14,MATCH($A11,'C3'!$B$2:$B$14,0),MATCH(L$2,'C3'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C5'!$B$2:$Z$14,MATCH($A11,'C5'!$B$2:$B$14,0),MATCH(L$2,'C5'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C7'!$B$2:$Z$14,MATCH($A11,'C7'!$B$2:$B$14,0),MATCH(L$2,'C7'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C9'!$B$2:$Z$14,MATCH($A11,'C9'!$B$2:$B$14,0),MATCH(L$2,'C9'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C11'!$B$2:$Z$14,MATCH($A11,'C11'!$B$2:$B$14,0),MATCH(L$2,'C11'!$B$2:$Z$2,0)),0)</f>
+        <v>0</v>
+      </c>
+      <c r="M11" s="1">
+        <f>IFERROR(INDEX('C15'!$B$2:$Z$14,MATCH($A11,'C15'!$B$2:$B$14,0),MATCH(M$2,'C15'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C1'!$B$2:$Z$14,MATCH($A11,'C1'!$B$2:$B$14,0),MATCH(M$2,'C1'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C3'!$B$2:$Z$14,MATCH($A11,'C3'!$B$2:$B$14,0),MATCH(M$2,'C3'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C5'!$B$2:$Z$14,MATCH($A11,'C5'!$B$2:$B$14,0),MATCH(M$2,'C5'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C7'!$B$2:$Z$14,MATCH($A11,'C7'!$B$2:$B$14,0),MATCH(M$2,'C7'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C9'!$B$2:$Z$14,MATCH($A11,'C9'!$B$2:$B$14,0),MATCH(M$2,'C9'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C11'!$B$2:$Z$14,MATCH($A11,'C11'!$B$2:$B$14,0),MATCH(M$2,'C11'!$B$2:$Z$2,0)),0)</f>
+        <v>1</v>
+      </c>
+      <c r="N11" s="1">
+        <f>IFERROR(INDEX('C15'!$B$2:$Z$14,MATCH($A11,'C15'!$B$2:$B$14,0),MATCH(N$2,'C15'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C1'!$B$2:$Z$14,MATCH($A11,'C1'!$B$2:$B$14,0),MATCH(N$2,'C1'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C3'!$B$2:$Z$14,MATCH($A11,'C3'!$B$2:$B$14,0),MATCH(N$2,'C3'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C5'!$B$2:$Z$14,MATCH($A11,'C5'!$B$2:$B$14,0),MATCH(N$2,'C5'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C7'!$B$2:$Z$14,MATCH($A11,'C7'!$B$2:$B$14,0),MATCH(N$2,'C7'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C9'!$B$2:$Z$14,MATCH($A11,'C9'!$B$2:$B$14,0),MATCH(N$2,'C9'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C11'!$B$2:$Z$14,MATCH($A11,'C11'!$B$2:$B$14,0),MATCH(N$2,'C11'!$B$2:$Z$2,0)),0)</f>
+        <v>0</v>
+      </c>
+      <c r="O11" s="1">
+        <f>IFERROR(INDEX('C15'!$B$2:$Z$14,MATCH($A11,'C15'!$B$2:$B$14,0),MATCH(O$2,'C15'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C1'!$B$2:$Z$14,MATCH($A11,'C1'!$B$2:$B$14,0),MATCH(O$2,'C1'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C3'!$B$2:$Z$14,MATCH($A11,'C3'!$B$2:$B$14,0),MATCH(O$2,'C3'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C5'!$B$2:$Z$14,MATCH($A11,'C5'!$B$2:$B$14,0),MATCH(O$2,'C5'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C7'!$B$2:$Z$14,MATCH($A11,'C7'!$B$2:$B$14,0),MATCH(O$2,'C7'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C9'!$B$2:$Z$14,MATCH($A11,'C9'!$B$2:$B$14,0),MATCH(O$2,'C9'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C11'!$B$2:$Z$14,MATCH($A11,'C11'!$B$2:$B$14,0),MATCH(O$2,'C11'!$B$2:$Z$2,0)),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A12" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B12" s="1">
+        <f>IFERROR(INDEX('C15'!$B$2:$Z$14,MATCH($A12,'C15'!$B$2:$B$14,0),MATCH(B$2,'C15'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C1'!$B$2:$Z$14,MATCH($A12,'C1'!$B$2:$B$14,0),MATCH(B$2,'C1'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C3'!$B$2:$Z$14,MATCH($A12,'C3'!$B$2:$B$14,0),MATCH(B$2,'C3'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C5'!$B$2:$Z$14,MATCH($A12,'C5'!$B$2:$B$14,0),MATCH(B$2,'C5'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C7'!$B$2:$Z$14,MATCH($A12,'C7'!$B$2:$B$14,0),MATCH(B$2,'C7'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C9'!$B$2:$Z$14,MATCH($A12,'C9'!$B$2:$B$14,0),MATCH(B$2,'C9'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C11'!$B$2:$Z$14,MATCH($A12,'C11'!$B$2:$B$14,0),MATCH(B$2,'C11'!$B$2:$Z$2,0)),0)</f>
+        <v>2</v>
+      </c>
+      <c r="C12" s="1">
+        <f>IFERROR(INDEX('C15'!$B$2:$Z$14,MATCH($A12,'C15'!$B$2:$B$14,0),MATCH(C$2,'C15'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C1'!$B$2:$Z$14,MATCH($A12,'C1'!$B$2:$B$14,0),MATCH(C$2,'C1'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C3'!$B$2:$Z$14,MATCH($A12,'C3'!$B$2:$B$14,0),MATCH(C$2,'C3'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C5'!$B$2:$Z$14,MATCH($A12,'C5'!$B$2:$B$14,0),MATCH(C$2,'C5'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C7'!$B$2:$Z$14,MATCH($A12,'C7'!$B$2:$B$14,0),MATCH(C$2,'C7'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C9'!$B$2:$Z$14,MATCH($A12,'C9'!$B$2:$B$14,0),MATCH(C$2,'C9'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C11'!$B$2:$Z$14,MATCH($A12,'C11'!$B$2:$B$14,0),MATCH(C$2,'C11'!$B$2:$Z$2,0)),0)</f>
+        <v>1</v>
+      </c>
+      <c r="D12" s="1">
+        <f>IFERROR(INDEX('C15'!$B$2:$Z$14,MATCH($A12,'C15'!$B$2:$B$14,0),MATCH(D$2,'C15'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C1'!$B$2:$Z$14,MATCH($A12,'C1'!$B$2:$B$14,0),MATCH(D$2,'C1'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C3'!$B$2:$Z$14,MATCH($A12,'C3'!$B$2:$B$14,0),MATCH(D$2,'C3'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C5'!$B$2:$Z$14,MATCH($A12,'C5'!$B$2:$B$14,0),MATCH(D$2,'C5'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C7'!$B$2:$Z$14,MATCH($A12,'C7'!$B$2:$B$14,0),MATCH(D$2,'C7'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C9'!$B$2:$Z$14,MATCH($A12,'C9'!$B$2:$B$14,0),MATCH(D$2,'C9'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C11'!$B$2:$Z$14,MATCH($A12,'C11'!$B$2:$B$14,0),MATCH(D$2,'C11'!$B$2:$Z$2,0)),0)</f>
+        <v>3</v>
+      </c>
+      <c r="E12" s="1">
+        <f>IFERROR(INDEX('C15'!$B$2:$Z$14,MATCH($A12,'C15'!$B$2:$B$14,0),MATCH(E$2,'C15'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C1'!$B$2:$Z$14,MATCH($A12,'C1'!$B$2:$B$14,0),MATCH(E$2,'C1'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C3'!$B$2:$Z$14,MATCH($A12,'C3'!$B$2:$B$14,0),MATCH(E$2,'C3'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C5'!$B$2:$Z$14,MATCH($A12,'C5'!$B$2:$B$14,0),MATCH(E$2,'C5'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C7'!$B$2:$Z$14,MATCH($A12,'C7'!$B$2:$B$14,0),MATCH(E$2,'C7'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C9'!$B$2:$Z$14,MATCH($A12,'C9'!$B$2:$B$14,0),MATCH(E$2,'C9'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C11'!$B$2:$Z$14,MATCH($A12,'C11'!$B$2:$B$14,0),MATCH(E$2,'C11'!$B$2:$Z$2,0)),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F12" s="1">
+        <f>IFERROR(INDEX('C15'!$B$2:$Z$14,MATCH($A12,'C15'!$B$2:$B$14,0),MATCH(F$2,'C15'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C1'!$B$2:$Z$14,MATCH($A12,'C1'!$B$2:$B$14,0),MATCH(F$2,'C1'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C3'!$B$2:$Z$14,MATCH($A12,'C3'!$B$2:$B$14,0),MATCH(F$2,'C3'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C5'!$B$2:$Z$14,MATCH($A12,'C5'!$B$2:$B$14,0),MATCH(F$2,'C5'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C7'!$B$2:$Z$14,MATCH($A12,'C7'!$B$2:$B$14,0),MATCH(F$2,'C7'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C9'!$B$2:$Z$14,MATCH($A12,'C9'!$B$2:$B$14,0),MATCH(F$2,'C9'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C11'!$B$2:$Z$14,MATCH($A12,'C11'!$B$2:$B$14,0),MATCH(F$2,'C11'!$B$2:$Z$2,0)),0)</f>
+        <v>5</v>
+      </c>
+      <c r="G12" s="1">
+        <f>IFERROR(INDEX('C15'!$B$2:$Z$14,MATCH($A12,'C15'!$B$2:$B$14,0),MATCH(G$2,'C15'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C1'!$B$2:$Z$14,MATCH($A12,'C1'!$B$2:$B$14,0),MATCH(G$2,'C1'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C3'!$B$2:$Z$14,MATCH($A12,'C3'!$B$2:$B$14,0),MATCH(G$2,'C3'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C5'!$B$2:$Z$14,MATCH($A12,'C5'!$B$2:$B$14,0),MATCH(G$2,'C5'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C7'!$B$2:$Z$14,MATCH($A12,'C7'!$B$2:$B$14,0),MATCH(G$2,'C7'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C9'!$B$2:$Z$14,MATCH($A12,'C9'!$B$2:$B$14,0),MATCH(G$2,'C9'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C11'!$B$2:$Z$14,MATCH($A12,'C11'!$B$2:$B$14,0),MATCH(G$2,'C11'!$B$2:$Z$2,0)),0)</f>
+        <v>3</v>
+      </c>
+      <c r="H12" s="1">
+        <f>IFERROR(INDEX('C15'!$B$2:$Z$14,MATCH($A12,'C15'!$B$2:$B$14,0),MATCH(H$2,'C15'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C1'!$B$2:$Z$14,MATCH($A12,'C1'!$B$2:$B$14,0),MATCH(H$2,'C1'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C3'!$B$2:$Z$14,MATCH($A12,'C3'!$B$2:$B$14,0),MATCH(H$2,'C3'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C5'!$B$2:$Z$14,MATCH($A12,'C5'!$B$2:$B$14,0),MATCH(H$2,'C5'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C7'!$B$2:$Z$14,MATCH($A12,'C7'!$B$2:$B$14,0),MATCH(H$2,'C7'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C9'!$B$2:$Z$14,MATCH($A12,'C9'!$B$2:$B$14,0),MATCH(H$2,'C9'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C11'!$B$2:$Z$14,MATCH($A12,'C11'!$B$2:$B$14,0),MATCH(H$2,'C11'!$B$2:$Z$2,0)),0)</f>
+        <v>2</v>
+      </c>
+      <c r="I12" s="1">
+        <f>IFERROR(INDEX('C15'!$B$2:$Z$14,MATCH($A12,'C15'!$B$2:$B$14,0),MATCH(I$2,'C15'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C1'!$B$2:$Z$14,MATCH($A12,'C1'!$B$2:$B$14,0),MATCH(I$2,'C1'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C3'!$B$2:$Z$14,MATCH($A12,'C3'!$B$2:$B$14,0),MATCH(I$2,'C3'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C5'!$B$2:$Z$14,MATCH($A12,'C5'!$B$2:$B$14,0),MATCH(I$2,'C5'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C7'!$B$2:$Z$14,MATCH($A12,'C7'!$B$2:$B$14,0),MATCH(I$2,'C7'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C9'!$B$2:$Z$14,MATCH($A12,'C9'!$B$2:$B$14,0),MATCH(I$2,'C9'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C11'!$B$2:$Z$14,MATCH($A12,'C11'!$B$2:$B$14,0),MATCH(I$2,'C11'!$B$2:$Z$2,0)),0)</f>
+        <v>1</v>
+      </c>
+      <c r="J12" s="1">
+        <f>IFERROR(INDEX('C15'!$B$2:$Z$14,MATCH($A12,'C15'!$B$2:$B$14,0),MATCH(J$2,'C15'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C1'!$B$2:$Z$14,MATCH($A12,'C1'!$B$2:$B$14,0),MATCH(J$2,'C1'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C3'!$B$2:$Z$14,MATCH($A12,'C3'!$B$2:$B$14,0),MATCH(J$2,'C3'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C5'!$B$2:$Z$14,MATCH($A12,'C5'!$B$2:$B$14,0),MATCH(J$2,'C5'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C7'!$B$2:$Z$14,MATCH($A12,'C7'!$B$2:$B$14,0),MATCH(J$2,'C7'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C9'!$B$2:$Z$14,MATCH($A12,'C9'!$B$2:$B$14,0),MATCH(J$2,'C9'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C11'!$B$2:$Z$14,MATCH($A12,'C11'!$B$2:$B$14,0),MATCH(J$2,'C11'!$B$2:$Z$2,0)),0)</f>
+        <v>4</v>
+      </c>
+      <c r="K12" s="1">
+        <f>IFERROR(INDEX('C15'!$B$2:$Z$14,MATCH($A12,'C15'!$B$2:$B$14,0),MATCH(K$2,'C15'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C1'!$B$2:$Z$14,MATCH($A12,'C1'!$B$2:$B$14,0),MATCH(K$2,'C1'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C3'!$B$2:$Z$14,MATCH($A12,'C3'!$B$2:$B$14,0),MATCH(K$2,'C3'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C5'!$B$2:$Z$14,MATCH($A12,'C5'!$B$2:$B$14,0),MATCH(K$2,'C5'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C7'!$B$2:$Z$14,MATCH($A12,'C7'!$B$2:$B$14,0),MATCH(K$2,'C7'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C9'!$B$2:$Z$14,MATCH($A12,'C9'!$B$2:$B$14,0),MATCH(K$2,'C9'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C11'!$B$2:$Z$14,MATCH($A12,'C11'!$B$2:$B$14,0),MATCH(K$2,'C11'!$B$2:$Z$2,0)),0)</f>
+        <v>1</v>
+      </c>
+      <c r="L12" s="1">
+        <f>IFERROR(INDEX('C15'!$B$2:$Z$14,MATCH($A12,'C15'!$B$2:$B$14,0),MATCH(L$2,'C15'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C1'!$B$2:$Z$14,MATCH($A12,'C1'!$B$2:$B$14,0),MATCH(L$2,'C1'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C3'!$B$2:$Z$14,MATCH($A12,'C3'!$B$2:$B$14,0),MATCH(L$2,'C3'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C5'!$B$2:$Z$14,MATCH($A12,'C5'!$B$2:$B$14,0),MATCH(L$2,'C5'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C7'!$B$2:$Z$14,MATCH($A12,'C7'!$B$2:$B$14,0),MATCH(L$2,'C7'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C9'!$B$2:$Z$14,MATCH($A12,'C9'!$B$2:$B$14,0),MATCH(L$2,'C9'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C11'!$B$2:$Z$14,MATCH($A12,'C11'!$B$2:$B$14,0),MATCH(L$2,'C11'!$B$2:$Z$2,0)),0)</f>
+        <v>0</v>
+      </c>
+      <c r="M12" s="1">
+        <f>IFERROR(INDEX('C15'!$B$2:$Z$14,MATCH($A12,'C15'!$B$2:$B$14,0),MATCH(M$2,'C15'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C1'!$B$2:$Z$14,MATCH($A12,'C1'!$B$2:$B$14,0),MATCH(M$2,'C1'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C3'!$B$2:$Z$14,MATCH($A12,'C3'!$B$2:$B$14,0),MATCH(M$2,'C3'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C5'!$B$2:$Z$14,MATCH($A12,'C5'!$B$2:$B$14,0),MATCH(M$2,'C5'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C7'!$B$2:$Z$14,MATCH($A12,'C7'!$B$2:$B$14,0),MATCH(M$2,'C7'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C9'!$B$2:$Z$14,MATCH($A12,'C9'!$B$2:$B$14,0),MATCH(M$2,'C9'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C11'!$B$2:$Z$14,MATCH($A12,'C11'!$B$2:$B$14,0),MATCH(M$2,'C11'!$B$2:$Z$2,0)),0)</f>
+        <v>1</v>
+      </c>
+      <c r="N12" s="1">
+        <f>IFERROR(INDEX('C15'!$B$2:$Z$14,MATCH($A12,'C15'!$B$2:$B$14,0),MATCH(N$2,'C15'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C1'!$B$2:$Z$14,MATCH($A12,'C1'!$B$2:$B$14,0),MATCH(N$2,'C1'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C3'!$B$2:$Z$14,MATCH($A12,'C3'!$B$2:$B$14,0),MATCH(N$2,'C3'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C5'!$B$2:$Z$14,MATCH($A12,'C5'!$B$2:$B$14,0),MATCH(N$2,'C5'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C7'!$B$2:$Z$14,MATCH($A12,'C7'!$B$2:$B$14,0),MATCH(N$2,'C7'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C9'!$B$2:$Z$14,MATCH($A12,'C9'!$B$2:$B$14,0),MATCH(N$2,'C9'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C11'!$B$2:$Z$14,MATCH($A12,'C11'!$B$2:$B$14,0),MATCH(N$2,'C11'!$B$2:$Z$2,0)),0)</f>
+        <v>0</v>
+      </c>
+      <c r="O12" s="1">
+        <f>IFERROR(INDEX('C15'!$B$2:$Z$14,MATCH($A12,'C15'!$B$2:$B$14,0),MATCH(O$2,'C15'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C1'!$B$2:$Z$14,MATCH($A12,'C1'!$B$2:$B$14,0),MATCH(O$2,'C1'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C3'!$B$2:$Z$14,MATCH($A12,'C3'!$B$2:$B$14,0),MATCH(O$2,'C3'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C5'!$B$2:$Z$14,MATCH($A12,'C5'!$B$2:$B$14,0),MATCH(O$2,'C5'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C7'!$B$2:$Z$14,MATCH($A12,'C7'!$B$2:$B$14,0),MATCH(O$2,'C7'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C9'!$B$2:$Z$14,MATCH($A12,'C9'!$B$2:$B$14,0),MATCH(O$2,'C9'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C11'!$B$2:$Z$14,MATCH($A12,'C11'!$B$2:$B$14,0),MATCH(O$2,'C11'!$B$2:$Z$2,0)),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A13" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B13" s="1">
+        <f>IFERROR(INDEX('C15'!$B$2:$Z$14,MATCH($A13,'C15'!$B$2:$B$14,0),MATCH(B$2,'C15'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C1'!$B$2:$Z$14,MATCH($A13,'C1'!$B$2:$B$14,0),MATCH(B$2,'C1'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C3'!$B$2:$Z$14,MATCH($A13,'C3'!$B$2:$B$14,0),MATCH(B$2,'C3'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C5'!$B$2:$Z$14,MATCH($A13,'C5'!$B$2:$B$14,0),MATCH(B$2,'C5'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C7'!$B$2:$Z$14,MATCH($A13,'C7'!$B$2:$B$14,0),MATCH(B$2,'C7'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C9'!$B$2:$Z$14,MATCH($A13,'C9'!$B$2:$B$14,0),MATCH(B$2,'C9'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C11'!$B$2:$Z$14,MATCH($A13,'C11'!$B$2:$B$14,0),MATCH(B$2,'C11'!$B$2:$Z$2,0)),0)</f>
+        <v>2</v>
+      </c>
+      <c r="C13" s="1">
+        <f>IFERROR(INDEX('C15'!$B$2:$Z$14,MATCH($A13,'C15'!$B$2:$B$14,0),MATCH(C$2,'C15'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C1'!$B$2:$Z$14,MATCH($A13,'C1'!$B$2:$B$14,0),MATCH(C$2,'C1'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C3'!$B$2:$Z$14,MATCH($A13,'C3'!$B$2:$B$14,0),MATCH(C$2,'C3'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C5'!$B$2:$Z$14,MATCH($A13,'C5'!$B$2:$B$14,0),MATCH(C$2,'C5'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C7'!$B$2:$Z$14,MATCH($A13,'C7'!$B$2:$B$14,0),MATCH(C$2,'C7'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C9'!$B$2:$Z$14,MATCH($A13,'C9'!$B$2:$B$14,0),MATCH(C$2,'C9'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C11'!$B$2:$Z$14,MATCH($A13,'C11'!$B$2:$B$14,0),MATCH(C$2,'C11'!$B$2:$Z$2,0)),0)</f>
+        <v>1</v>
+      </c>
+      <c r="D13" s="1">
+        <f>IFERROR(INDEX('C15'!$B$2:$Z$14,MATCH($A13,'C15'!$B$2:$B$14,0),MATCH(D$2,'C15'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C1'!$B$2:$Z$14,MATCH($A13,'C1'!$B$2:$B$14,0),MATCH(D$2,'C1'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C3'!$B$2:$Z$14,MATCH($A13,'C3'!$B$2:$B$14,0),MATCH(D$2,'C3'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C5'!$B$2:$Z$14,MATCH($A13,'C5'!$B$2:$B$14,0),MATCH(D$2,'C5'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C7'!$B$2:$Z$14,MATCH($A13,'C7'!$B$2:$B$14,0),MATCH(D$2,'C7'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C9'!$B$2:$Z$14,MATCH($A13,'C9'!$B$2:$B$14,0),MATCH(D$2,'C9'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C11'!$B$2:$Z$14,MATCH($A13,'C11'!$B$2:$B$14,0),MATCH(D$2,'C11'!$B$2:$Z$2,0)),0)</f>
+        <v>3</v>
+      </c>
+      <c r="E13" s="1">
+        <f>IFERROR(INDEX('C15'!$B$2:$Z$14,MATCH($A13,'C15'!$B$2:$B$14,0),MATCH(E$2,'C15'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C1'!$B$2:$Z$14,MATCH($A13,'C1'!$B$2:$B$14,0),MATCH(E$2,'C1'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C3'!$B$2:$Z$14,MATCH($A13,'C3'!$B$2:$B$14,0),MATCH(E$2,'C3'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C5'!$B$2:$Z$14,MATCH($A13,'C5'!$B$2:$B$14,0),MATCH(E$2,'C5'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C7'!$B$2:$Z$14,MATCH($A13,'C7'!$B$2:$B$14,0),MATCH(E$2,'C7'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C9'!$B$2:$Z$14,MATCH($A13,'C9'!$B$2:$B$14,0),MATCH(E$2,'C9'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C11'!$B$2:$Z$14,MATCH($A13,'C11'!$B$2:$B$14,0),MATCH(E$2,'C11'!$B$2:$Z$2,0)),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F13" s="1">
+        <f>IFERROR(INDEX('C15'!$B$2:$Z$14,MATCH($A13,'C15'!$B$2:$B$14,0),MATCH(F$2,'C15'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C1'!$B$2:$Z$14,MATCH($A13,'C1'!$B$2:$B$14,0),MATCH(F$2,'C1'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C3'!$B$2:$Z$14,MATCH($A13,'C3'!$B$2:$B$14,0),MATCH(F$2,'C3'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C5'!$B$2:$Z$14,MATCH($A13,'C5'!$B$2:$B$14,0),MATCH(F$2,'C5'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C7'!$B$2:$Z$14,MATCH($A13,'C7'!$B$2:$B$14,0),MATCH(F$2,'C7'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C9'!$B$2:$Z$14,MATCH($A13,'C9'!$B$2:$B$14,0),MATCH(F$2,'C9'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C11'!$B$2:$Z$14,MATCH($A13,'C11'!$B$2:$B$14,0),MATCH(F$2,'C11'!$B$2:$Z$2,0)),0)</f>
+        <v>3</v>
+      </c>
+      <c r="G13" s="1">
+        <f>IFERROR(INDEX('C15'!$B$2:$Z$14,MATCH($A13,'C15'!$B$2:$B$14,0),MATCH(G$2,'C15'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C1'!$B$2:$Z$14,MATCH($A13,'C1'!$B$2:$B$14,0),MATCH(G$2,'C1'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C3'!$B$2:$Z$14,MATCH($A13,'C3'!$B$2:$B$14,0),MATCH(G$2,'C3'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C5'!$B$2:$Z$14,MATCH($A13,'C5'!$B$2:$B$14,0),MATCH(G$2,'C5'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C7'!$B$2:$Z$14,MATCH($A13,'C7'!$B$2:$B$14,0),MATCH(G$2,'C7'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C9'!$B$2:$Z$14,MATCH($A13,'C9'!$B$2:$B$14,0),MATCH(G$2,'C9'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C11'!$B$2:$Z$14,MATCH($A13,'C11'!$B$2:$B$14,0),MATCH(G$2,'C11'!$B$2:$Z$2,0)),0)</f>
+        <v>5</v>
+      </c>
+      <c r="H13" s="1">
+        <f>IFERROR(INDEX('C15'!$B$2:$Z$14,MATCH($A13,'C15'!$B$2:$B$14,0),MATCH(H$2,'C15'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C1'!$B$2:$Z$14,MATCH($A13,'C1'!$B$2:$B$14,0),MATCH(H$2,'C1'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C3'!$B$2:$Z$14,MATCH($A13,'C3'!$B$2:$B$14,0),MATCH(H$2,'C3'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C5'!$B$2:$Z$14,MATCH($A13,'C5'!$B$2:$B$14,0),MATCH(H$2,'C5'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C7'!$B$2:$Z$14,MATCH($A13,'C7'!$B$2:$B$14,0),MATCH(H$2,'C7'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C9'!$B$2:$Z$14,MATCH($A13,'C9'!$B$2:$B$14,0),MATCH(H$2,'C9'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C11'!$B$2:$Z$14,MATCH($A13,'C11'!$B$2:$B$14,0),MATCH(H$2,'C11'!$B$2:$Z$2,0)),0)</f>
+        <v>2</v>
+      </c>
+      <c r="I13" s="1">
+        <f>IFERROR(INDEX('C15'!$B$2:$Z$14,MATCH($A13,'C15'!$B$2:$B$14,0),MATCH(I$2,'C15'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C1'!$B$2:$Z$14,MATCH($A13,'C1'!$B$2:$B$14,0),MATCH(I$2,'C1'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C3'!$B$2:$Z$14,MATCH($A13,'C3'!$B$2:$B$14,0),MATCH(I$2,'C3'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C5'!$B$2:$Z$14,MATCH($A13,'C5'!$B$2:$B$14,0),MATCH(I$2,'C5'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C7'!$B$2:$Z$14,MATCH($A13,'C7'!$B$2:$B$14,0),MATCH(I$2,'C7'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C9'!$B$2:$Z$14,MATCH($A13,'C9'!$B$2:$B$14,0),MATCH(I$2,'C9'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C11'!$B$2:$Z$14,MATCH($A13,'C11'!$B$2:$B$14,0),MATCH(I$2,'C11'!$B$2:$Z$2,0)),0)</f>
+        <v>1</v>
+      </c>
+      <c r="J13" s="1">
+        <f>IFERROR(INDEX('C15'!$B$2:$Z$14,MATCH($A13,'C15'!$B$2:$B$14,0),MATCH(J$2,'C15'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C1'!$B$2:$Z$14,MATCH($A13,'C1'!$B$2:$B$14,0),MATCH(J$2,'C1'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C3'!$B$2:$Z$14,MATCH($A13,'C3'!$B$2:$B$14,0),MATCH(J$2,'C3'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C5'!$B$2:$Z$14,MATCH($A13,'C5'!$B$2:$B$14,0),MATCH(J$2,'C5'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C7'!$B$2:$Z$14,MATCH($A13,'C7'!$B$2:$B$14,0),MATCH(J$2,'C7'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C9'!$B$2:$Z$14,MATCH($A13,'C9'!$B$2:$B$14,0),MATCH(J$2,'C9'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C11'!$B$2:$Z$14,MATCH($A13,'C11'!$B$2:$B$14,0),MATCH(J$2,'C11'!$B$2:$Z$2,0)),0)</f>
+        <v>4</v>
+      </c>
+      <c r="K13" s="1">
+        <f>IFERROR(INDEX('C15'!$B$2:$Z$14,MATCH($A13,'C15'!$B$2:$B$14,0),MATCH(K$2,'C15'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C1'!$B$2:$Z$14,MATCH($A13,'C1'!$B$2:$B$14,0),MATCH(K$2,'C1'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C3'!$B$2:$Z$14,MATCH($A13,'C3'!$B$2:$B$14,0),MATCH(K$2,'C3'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C5'!$B$2:$Z$14,MATCH($A13,'C5'!$B$2:$B$14,0),MATCH(K$2,'C5'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C7'!$B$2:$Z$14,MATCH($A13,'C7'!$B$2:$B$14,0),MATCH(K$2,'C7'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C9'!$B$2:$Z$14,MATCH($A13,'C9'!$B$2:$B$14,0),MATCH(K$2,'C9'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C11'!$B$2:$Z$14,MATCH($A13,'C11'!$B$2:$B$14,0),MATCH(K$2,'C11'!$B$2:$Z$2,0)),0)</f>
+        <v>1</v>
+      </c>
+      <c r="L13" s="1">
+        <f>IFERROR(INDEX('C15'!$B$2:$Z$14,MATCH($A13,'C15'!$B$2:$B$14,0),MATCH(L$2,'C15'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C1'!$B$2:$Z$14,MATCH($A13,'C1'!$B$2:$B$14,0),MATCH(L$2,'C1'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C3'!$B$2:$Z$14,MATCH($A13,'C3'!$B$2:$B$14,0),MATCH(L$2,'C3'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C5'!$B$2:$Z$14,MATCH($A13,'C5'!$B$2:$B$14,0),MATCH(L$2,'C5'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C7'!$B$2:$Z$14,MATCH($A13,'C7'!$B$2:$B$14,0),MATCH(L$2,'C7'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C9'!$B$2:$Z$14,MATCH($A13,'C9'!$B$2:$B$14,0),MATCH(L$2,'C9'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C11'!$B$2:$Z$14,MATCH($A13,'C11'!$B$2:$B$14,0),MATCH(L$2,'C11'!$B$2:$Z$2,0)),0)</f>
+        <v>0</v>
+      </c>
+      <c r="M13" s="1">
+        <f>IFERROR(INDEX('C15'!$B$2:$Z$14,MATCH($A13,'C15'!$B$2:$B$14,0),MATCH(M$2,'C15'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C1'!$B$2:$Z$14,MATCH($A13,'C1'!$B$2:$B$14,0),MATCH(M$2,'C1'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C3'!$B$2:$Z$14,MATCH($A13,'C3'!$B$2:$B$14,0),MATCH(M$2,'C3'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C5'!$B$2:$Z$14,MATCH($A13,'C5'!$B$2:$B$14,0),MATCH(M$2,'C5'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C7'!$B$2:$Z$14,MATCH($A13,'C7'!$B$2:$B$14,0),MATCH(M$2,'C7'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C9'!$B$2:$Z$14,MATCH($A13,'C9'!$B$2:$B$14,0),MATCH(M$2,'C9'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C11'!$B$2:$Z$14,MATCH($A13,'C11'!$B$2:$B$14,0),MATCH(M$2,'C11'!$B$2:$Z$2,0)),0)</f>
+        <v>1</v>
+      </c>
+      <c r="N13" s="1">
+        <f>IFERROR(INDEX('C15'!$B$2:$Z$14,MATCH($A13,'C15'!$B$2:$B$14,0),MATCH(N$2,'C15'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C1'!$B$2:$Z$14,MATCH($A13,'C1'!$B$2:$B$14,0),MATCH(N$2,'C1'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C3'!$B$2:$Z$14,MATCH($A13,'C3'!$B$2:$B$14,0),MATCH(N$2,'C3'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C5'!$B$2:$Z$14,MATCH($A13,'C5'!$B$2:$B$14,0),MATCH(N$2,'C5'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C7'!$B$2:$Z$14,MATCH($A13,'C7'!$B$2:$B$14,0),MATCH(N$2,'C7'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C9'!$B$2:$Z$14,MATCH($A13,'C9'!$B$2:$B$14,0),MATCH(N$2,'C9'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C11'!$B$2:$Z$14,MATCH($A13,'C11'!$B$2:$B$14,0),MATCH(N$2,'C11'!$B$2:$Z$2,0)),0)</f>
+        <v>0</v>
+      </c>
+      <c r="O13" s="1">
+        <f>IFERROR(INDEX('C15'!$B$2:$Z$14,MATCH($A13,'C15'!$B$2:$B$14,0),MATCH(O$2,'C15'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C1'!$B$2:$Z$14,MATCH($A13,'C1'!$B$2:$B$14,0),MATCH(O$2,'C1'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C3'!$B$2:$Z$14,MATCH($A13,'C3'!$B$2:$B$14,0),MATCH(O$2,'C3'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C5'!$B$2:$Z$14,MATCH($A13,'C5'!$B$2:$B$14,0),MATCH(O$2,'C5'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C7'!$B$2:$Z$14,MATCH($A13,'C7'!$B$2:$B$14,0),MATCH(O$2,'C7'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C9'!$B$2:$Z$14,MATCH($A13,'C9'!$B$2:$B$14,0),MATCH(O$2,'C9'!$B$2:$Z$2,0)),0)+IFERROR(INDEX('C11'!$B$2:$Z$14,MATCH($A13,'C11'!$B$2:$B$14,0),MATCH(O$2,'C11'!$B$2:$Z$2,0)),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89480051-BCA3-405F-B673-471E1D4EE818}">
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="2.81640625" bestFit="1" customWidth="1"/>
@@ -17853,112 +20146,178 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="6.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="14" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="31" t="s">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="B13" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C13" s="4">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="D13" s="4">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="E13" s="4">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F13" s="4">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="G13" s="4">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="H13" s="4">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="I13" s="4">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(I$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="B14" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C14" s="4">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="D14" s="4">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="E14" s="4">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F14" s="4">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="G14" s="4">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="H14" s="4">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="I14" s="4">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(I$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="6.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="16" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B16" s="32" t="s">
         <v>63</v>
       </c>
-      <c r="C14" s="32"/>
-      <c r="D14" s="32"/>
-      <c r="E14" s="32"/>
-      <c r="F14" s="32"/>
-      <c r="G14" s="32"/>
-      <c r="H14" s="32"/>
-      <c r="I14" s="33"/>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="B15" s="34"/>
-      <c r="C15" s="35"/>
-      <c r="D15" s="35"/>
-      <c r="E15" s="35"/>
-      <c r="F15" s="35"/>
-      <c r="G15" s="35"/>
-      <c r="H15" s="35"/>
-      <c r="I15" s="36"/>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="B16" s="34"/>
-      <c r="C16" s="35"/>
-      <c r="D16" s="35"/>
-      <c r="E16" s="35"/>
-      <c r="F16" s="35"/>
-      <c r="G16" s="35"/>
-      <c r="H16" s="35"/>
-      <c r="I16" s="36"/>
+      <c r="C16" s="33"/>
+      <c r="D16" s="33"/>
+      <c r="E16" s="33"/>
+      <c r="F16" s="33"/>
+      <c r="G16" s="33"/>
+      <c r="H16" s="33"/>
+      <c r="I16" s="34"/>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B17" s="34"/>
-      <c r="C17" s="35"/>
-      <c r="D17" s="35"/>
-      <c r="E17" s="35"/>
-      <c r="F17" s="35"/>
-      <c r="G17" s="35"/>
-      <c r="H17" s="35"/>
-      <c r="I17" s="36"/>
+      <c r="B17" s="35"/>
+      <c r="C17" s="36"/>
+      <c r="D17" s="36"/>
+      <c r="E17" s="36"/>
+      <c r="F17" s="36"/>
+      <c r="G17" s="36"/>
+      <c r="H17" s="36"/>
+      <c r="I17" s="37"/>
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B18" s="34"/>
-      <c r="C18" s="35"/>
-      <c r="D18" s="35"/>
-      <c r="E18" s="35"/>
-      <c r="F18" s="35"/>
-      <c r="G18" s="35"/>
-      <c r="H18" s="35"/>
-      <c r="I18" s="36"/>
+      <c r="B18" s="35"/>
+      <c r="C18" s="36"/>
+      <c r="D18" s="36"/>
+      <c r="E18" s="36"/>
+      <c r="F18" s="36"/>
+      <c r="G18" s="36"/>
+      <c r="H18" s="36"/>
+      <c r="I18" s="37"/>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B19" s="34"/>
-      <c r="C19" s="35"/>
-      <c r="D19" s="35"/>
-      <c r="E19" s="35"/>
-      <c r="F19" s="35"/>
-      <c r="G19" s="35"/>
-      <c r="H19" s="35"/>
-      <c r="I19" s="36"/>
+      <c r="B19" s="35"/>
+      <c r="C19" s="36"/>
+      <c r="D19" s="36"/>
+      <c r="E19" s="36"/>
+      <c r="F19" s="36"/>
+      <c r="G19" s="36"/>
+      <c r="H19" s="36"/>
+      <c r="I19" s="37"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B20" s="34"/>
-      <c r="C20" s="35"/>
-      <c r="D20" s="35"/>
-      <c r="E20" s="35"/>
-      <c r="F20" s="35"/>
-      <c r="G20" s="35"/>
-      <c r="H20" s="35"/>
-      <c r="I20" s="36"/>
+      <c r="B20" s="35"/>
+      <c r="C20" s="36"/>
+      <c r="D20" s="36"/>
+      <c r="E20" s="36"/>
+      <c r="F20" s="36"/>
+      <c r="G20" s="36"/>
+      <c r="H20" s="36"/>
+      <c r="I20" s="37"/>
     </row>
     <row r="21" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B21" s="34"/>
-      <c r="C21" s="35"/>
-      <c r="D21" s="35"/>
-      <c r="E21" s="35"/>
-      <c r="F21" s="35"/>
-      <c r="G21" s="35"/>
-      <c r="H21" s="35"/>
-      <c r="I21" s="36"/>
+      <c r="B21" s="35"/>
+      <c r="C21" s="36"/>
+      <c r="D21" s="36"/>
+      <c r="E21" s="36"/>
+      <c r="F21" s="36"/>
+      <c r="G21" s="36"/>
+      <c r="H21" s="36"/>
+      <c r="I21" s="37"/>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B22" s="34"/>
-      <c r="C22" s="35"/>
-      <c r="D22" s="35"/>
-      <c r="E22" s="35"/>
-      <c r="F22" s="35"/>
-      <c r="G22" s="35"/>
-      <c r="H22" s="35"/>
-      <c r="I22" s="36"/>
+      <c r="B22" s="35"/>
+      <c r="C22" s="36"/>
+      <c r="D22" s="36"/>
+      <c r="E22" s="36"/>
+      <c r="F22" s="36"/>
+      <c r="G22" s="36"/>
+      <c r="H22" s="36"/>
+      <c r="I22" s="37"/>
     </row>
-    <row r="23" spans="2:9" ht="79" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B23" s="37"/>
-      <c r="C23" s="38"/>
-      <c r="D23" s="38"/>
-      <c r="E23" s="38"/>
-      <c r="F23" s="38"/>
-      <c r="G23" s="38"/>
-      <c r="H23" s="38"/>
-      <c r="I23" s="39"/>
+    <row r="23" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B23" s="35"/>
+      <c r="C23" s="36"/>
+      <c r="D23" s="36"/>
+      <c r="E23" s="36"/>
+      <c r="F23" s="36"/>
+      <c r="G23" s="36"/>
+      <c r="H23" s="36"/>
+      <c r="I23" s="37"/>
+    </row>
+    <row r="24" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B24" s="35"/>
+      <c r="C24" s="36"/>
+      <c r="D24" s="36"/>
+      <c r="E24" s="36"/>
+      <c r="F24" s="36"/>
+      <c r="G24" s="36"/>
+      <c r="H24" s="36"/>
+      <c r="I24" s="37"/>
+    </row>
+    <row r="25" spans="2:9" ht="79" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B25" s="38"/>
+      <c r="C25" s="39"/>
+      <c r="D25" s="39"/>
+      <c r="E25" s="39"/>
+      <c r="F25" s="39"/>
+      <c r="G25" s="39"/>
+      <c r="H25" s="39"/>
+      <c r="I25" s="40"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="B14:I23"/>
+    <mergeCell ref="B16:I25"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" r:id="rId1"/>
@@ -17966,9 +20325,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4DB6AE84-88BE-4054-A4FA-FD43BA13B48C}">
-  <dimension ref="A1:H23"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="1.90625" bestFit="1" customWidth="1"/>
@@ -18291,102 +20650,160 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="14" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="31" t="s">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B13" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C13" s="4">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="D13" s="4">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="E13" s="4">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F13" s="4">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="G13" s="4">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="H13" s="4">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B14" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C14" s="4">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="D14" s="4">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="E14" s="4">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F14" s="4">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="G14" s="4">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="H14" s="4">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="16" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B16" s="32" t="s">
         <v>64</v>
       </c>
-      <c r="C14" s="32"/>
-      <c r="D14" s="32"/>
-      <c r="E14" s="32"/>
-      <c r="F14" s="32"/>
-      <c r="G14" s="32"/>
-      <c r="H14" s="33"/>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="B15" s="34"/>
-      <c r="C15" s="35"/>
-      <c r="D15" s="35"/>
-      <c r="E15" s="35"/>
-      <c r="F15" s="35"/>
-      <c r="G15" s="35"/>
-      <c r="H15" s="36"/>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="B16" s="34"/>
-      <c r="C16" s="35"/>
-      <c r="D16" s="35"/>
-      <c r="E16" s="35"/>
-      <c r="F16" s="35"/>
-      <c r="G16" s="35"/>
-      <c r="H16" s="36"/>
+      <c r="C16" s="33"/>
+      <c r="D16" s="33"/>
+      <c r="E16" s="33"/>
+      <c r="F16" s="33"/>
+      <c r="G16" s="33"/>
+      <c r="H16" s="34"/>
     </row>
     <row r="17" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B17" s="34"/>
-      <c r="C17" s="35"/>
-      <c r="D17" s="35"/>
-      <c r="E17" s="35"/>
-      <c r="F17" s="35"/>
-      <c r="G17" s="35"/>
-      <c r="H17" s="36"/>
+      <c r="B17" s="35"/>
+      <c r="C17" s="36"/>
+      <c r="D17" s="36"/>
+      <c r="E17" s="36"/>
+      <c r="F17" s="36"/>
+      <c r="G17" s="36"/>
+      <c r="H17" s="37"/>
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B18" s="34"/>
-      <c r="C18" s="35"/>
-      <c r="D18" s="35"/>
-      <c r="E18" s="35"/>
-      <c r="F18" s="35"/>
-      <c r="G18" s="35"/>
-      <c r="H18" s="36"/>
+      <c r="B18" s="35"/>
+      <c r="C18" s="36"/>
+      <c r="D18" s="36"/>
+      <c r="E18" s="36"/>
+      <c r="F18" s="36"/>
+      <c r="G18" s="36"/>
+      <c r="H18" s="37"/>
     </row>
     <row r="19" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B19" s="34"/>
-      <c r="C19" s="35"/>
-      <c r="D19" s="35"/>
-      <c r="E19" s="35"/>
-      <c r="F19" s="35"/>
-      <c r="G19" s="35"/>
-      <c r="H19" s="36"/>
+      <c r="B19" s="35"/>
+      <c r="C19" s="36"/>
+      <c r="D19" s="36"/>
+      <c r="E19" s="36"/>
+      <c r="F19" s="36"/>
+      <c r="G19" s="36"/>
+      <c r="H19" s="37"/>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B20" s="34"/>
-      <c r="C20" s="35"/>
-      <c r="D20" s="35"/>
-      <c r="E20" s="35"/>
-      <c r="F20" s="35"/>
-      <c r="G20" s="35"/>
-      <c r="H20" s="36"/>
+      <c r="B20" s="35"/>
+      <c r="C20" s="36"/>
+      <c r="D20" s="36"/>
+      <c r="E20" s="36"/>
+      <c r="F20" s="36"/>
+      <c r="G20" s="36"/>
+      <c r="H20" s="37"/>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B21" s="34"/>
-      <c r="C21" s="35"/>
-      <c r="D21" s="35"/>
-      <c r="E21" s="35"/>
-      <c r="F21" s="35"/>
-      <c r="G21" s="35"/>
-      <c r="H21" s="36"/>
+      <c r="B21" s="35"/>
+      <c r="C21" s="36"/>
+      <c r="D21" s="36"/>
+      <c r="E21" s="36"/>
+      <c r="F21" s="36"/>
+      <c r="G21" s="36"/>
+      <c r="H21" s="37"/>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B22" s="34"/>
-      <c r="C22" s="35"/>
-      <c r="D22" s="35"/>
-      <c r="E22" s="35"/>
-      <c r="F22" s="35"/>
-      <c r="G22" s="35"/>
-      <c r="H22" s="36"/>
+      <c r="B22" s="35"/>
+      <c r="C22" s="36"/>
+      <c r="D22" s="36"/>
+      <c r="E22" s="36"/>
+      <c r="F22" s="36"/>
+      <c r="G22" s="36"/>
+      <c r="H22" s="37"/>
     </row>
-    <row r="23" spans="2:8" ht="87" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B23" s="37"/>
-      <c r="C23" s="38"/>
-      <c r="D23" s="38"/>
-      <c r="E23" s="38"/>
-      <c r="F23" s="38"/>
-      <c r="G23" s="38"/>
-      <c r="H23" s="39"/>
+    <row r="23" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B23" s="35"/>
+      <c r="C23" s="36"/>
+      <c r="D23" s="36"/>
+      <c r="E23" s="36"/>
+      <c r="F23" s="36"/>
+      <c r="G23" s="36"/>
+      <c r="H23" s="37"/>
+    </row>
+    <row r="24" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B24" s="35"/>
+      <c r="C24" s="36"/>
+      <c r="D24" s="36"/>
+      <c r="E24" s="36"/>
+      <c r="F24" s="36"/>
+      <c r="G24" s="36"/>
+      <c r="H24" s="37"/>
+    </row>
+    <row r="25" spans="2:8" ht="87" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B25" s="38"/>
+      <c r="C25" s="39"/>
+      <c r="D25" s="39"/>
+      <c r="E25" s="39"/>
+      <c r="F25" s="39"/>
+      <c r="G25" s="39"/>
+      <c r="H25" s="40"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="B14:H23"/>
+    <mergeCell ref="B16:H25"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -18394,9 +20811,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A45733F-34D0-4D88-A6B5-E28376F26D12}">
-  <dimension ref="A1:H23"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="1.90625" bestFit="1" customWidth="1"/>
@@ -18723,102 +21140,160 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="14" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="31" t="s">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B13" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C13" s="4">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="D13" s="4">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="E13" s="4">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="F13" s="4">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="G13" s="4">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="H13" s="4">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B14" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C14" s="4">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="D14" s="4">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="E14" s="4">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="F14" s="4">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="G14" s="4">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="H14" s="4">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="16" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B16" s="32" t="s">
         <v>64</v>
       </c>
-      <c r="C14" s="32"/>
-      <c r="D14" s="32"/>
-      <c r="E14" s="32"/>
-      <c r="F14" s="32"/>
-      <c r="G14" s="32"/>
-      <c r="H14" s="33"/>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="B15" s="34"/>
-      <c r="C15" s="35"/>
-      <c r="D15" s="35"/>
-      <c r="E15" s="35"/>
-      <c r="F15" s="35"/>
-      <c r="G15" s="35"/>
-      <c r="H15" s="36"/>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="B16" s="34"/>
-      <c r="C16" s="35"/>
-      <c r="D16" s="35"/>
-      <c r="E16" s="35"/>
-      <c r="F16" s="35"/>
-      <c r="G16" s="35"/>
-      <c r="H16" s="36"/>
+      <c r="C16" s="33"/>
+      <c r="D16" s="33"/>
+      <c r="E16" s="33"/>
+      <c r="F16" s="33"/>
+      <c r="G16" s="33"/>
+      <c r="H16" s="34"/>
     </row>
     <row r="17" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B17" s="34"/>
-      <c r="C17" s="35"/>
-      <c r="D17" s="35"/>
-      <c r="E17" s="35"/>
-      <c r="F17" s="35"/>
-      <c r="G17" s="35"/>
-      <c r="H17" s="36"/>
+      <c r="B17" s="35"/>
+      <c r="C17" s="36"/>
+      <c r="D17" s="36"/>
+      <c r="E17" s="36"/>
+      <c r="F17" s="36"/>
+      <c r="G17" s="36"/>
+      <c r="H17" s="37"/>
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B18" s="34"/>
-      <c r="C18" s="35"/>
-      <c r="D18" s="35"/>
-      <c r="E18" s="35"/>
-      <c r="F18" s="35"/>
-      <c r="G18" s="35"/>
-      <c r="H18" s="36"/>
+      <c r="B18" s="35"/>
+      <c r="C18" s="36"/>
+      <c r="D18" s="36"/>
+      <c r="E18" s="36"/>
+      <c r="F18" s="36"/>
+      <c r="G18" s="36"/>
+      <c r="H18" s="37"/>
     </row>
     <row r="19" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B19" s="34"/>
-      <c r="C19" s="35"/>
-      <c r="D19" s="35"/>
-      <c r="E19" s="35"/>
-      <c r="F19" s="35"/>
-      <c r="G19" s="35"/>
-      <c r="H19" s="36"/>
+      <c r="B19" s="35"/>
+      <c r="C19" s="36"/>
+      <c r="D19" s="36"/>
+      <c r="E19" s="36"/>
+      <c r="F19" s="36"/>
+      <c r="G19" s="36"/>
+      <c r="H19" s="37"/>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B20" s="34"/>
-      <c r="C20" s="35"/>
-      <c r="D20" s="35"/>
-      <c r="E20" s="35"/>
-      <c r="F20" s="35"/>
-      <c r="G20" s="35"/>
-      <c r="H20" s="36"/>
+      <c r="B20" s="35"/>
+      <c r="C20" s="36"/>
+      <c r="D20" s="36"/>
+      <c r="E20" s="36"/>
+      <c r="F20" s="36"/>
+      <c r="G20" s="36"/>
+      <c r="H20" s="37"/>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B21" s="34"/>
-      <c r="C21" s="35"/>
-      <c r="D21" s="35"/>
-      <c r="E21" s="35"/>
-      <c r="F21" s="35"/>
-      <c r="G21" s="35"/>
-      <c r="H21" s="36"/>
+      <c r="B21" s="35"/>
+      <c r="C21" s="36"/>
+      <c r="D21" s="36"/>
+      <c r="E21" s="36"/>
+      <c r="F21" s="36"/>
+      <c r="G21" s="36"/>
+      <c r="H21" s="37"/>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B22" s="34"/>
-      <c r="C22" s="35"/>
-      <c r="D22" s="35"/>
-      <c r="E22" s="35"/>
-      <c r="F22" s="35"/>
-      <c r="G22" s="35"/>
-      <c r="H22" s="36"/>
+      <c r="B22" s="35"/>
+      <c r="C22" s="36"/>
+      <c r="D22" s="36"/>
+      <c r="E22" s="36"/>
+      <c r="F22" s="36"/>
+      <c r="G22" s="36"/>
+      <c r="H22" s="37"/>
     </row>
-    <row r="23" spans="2:8" ht="97.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B23" s="37"/>
-      <c r="C23" s="38"/>
-      <c r="D23" s="38"/>
-      <c r="E23" s="38"/>
-      <c r="F23" s="38"/>
-      <c r="G23" s="38"/>
-      <c r="H23" s="39"/>
+    <row r="23" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B23" s="35"/>
+      <c r="C23" s="36"/>
+      <c r="D23" s="36"/>
+      <c r="E23" s="36"/>
+      <c r="F23" s="36"/>
+      <c r="G23" s="36"/>
+      <c r="H23" s="37"/>
+    </row>
+    <row r="24" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B24" s="35"/>
+      <c r="C24" s="36"/>
+      <c r="D24" s="36"/>
+      <c r="E24" s="36"/>
+      <c r="F24" s="36"/>
+      <c r="G24" s="36"/>
+      <c r="H24" s="37"/>
+    </row>
+    <row r="25" spans="2:8" ht="97.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B25" s="38"/>
+      <c r="C25" s="39"/>
+      <c r="D25" s="39"/>
+      <c r="E25" s="39"/>
+      <c r="F25" s="39"/>
+      <c r="G25" s="39"/>
+      <c r="H25" s="40"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="B14:H23"/>
+    <mergeCell ref="B16:H25"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -18826,9 +21301,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81B720F0-81EA-4B55-8BF5-5CBED46DDED6}">
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:J25"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="1.90625" bestFit="1" customWidth="1"/>
@@ -18839,17 +21314,18 @@
     <col min="6" max="6" width="5.90625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.08984375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="6.90625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="5.90625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="16.26953125" customWidth="1"/>
-    <col min="12" max="12" width="46.6328125" customWidth="1"/>
+    <col min="9" max="9" width="6.90625" customWidth="1"/>
+    <col min="10" max="10" width="5.90625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.26953125" customWidth="1"/>
+    <col min="13" max="13" width="46.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" s="27">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
@@ -18872,10 +21348,13 @@
         <v>60</v>
       </c>
       <c r="I2" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J2" s="2" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
@@ -18898,10 +21377,13 @@
         <v>0</v>
       </c>
       <c r="I3" s="3">
+        <v>1</v>
+      </c>
+      <c r="J3" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B4" s="5" t="s">
         <v>29</v>
       </c>
@@ -18931,10 +21413,14 @@
       </c>
       <c r="I4" s="6">
         <f>VLOOKUP($A$1,[1]resultados_proyectados_proporci!$A$1:$AA$29,MATCH(I$2,[1]resultados_proyectados_proporci!$A$1:$AA$1,0),FALSE)</f>
+        <v>4.1651405845219397E-2</v>
+      </c>
+      <c r="J4" s="6">
+        <f>VLOOKUP($A$1,[1]resultados_proyectados_proporci!$A$1:$AA$29,MATCH(J$2,[1]resultados_proyectados_proporci!$A$1:$AA$1,0),FALSE)</f>
         <v>4.6696923507655301E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B5" s="1" t="s">
         <v>2</v>
       </c>
@@ -18966,8 +21452,12 @@
         <f>VLOOKUP($A$1,[2]resultados_integracion_partido_!$A$1:$AA$29,MATCH(I$2,[2]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>0</v>
       </c>
+      <c r="J5" s="4">
+        <f>VLOOKUP($A$1,[2]resultados_integracion_partido_!$A$1:$AA$29,MATCH(J$2,[2]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>0</v>
+      </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B6" s="1" t="s">
         <v>3</v>
       </c>
@@ -18997,10 +21487,14 @@
       </c>
       <c r="I6" s="4">
         <f>VLOOKUP($A$1,[3]resultados_integracion_partido_!$A$1:$AA$29,MATCH(I$2,[3]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="J6" s="4">
+        <f>VLOOKUP($A$1,[3]resultados_integracion_partido_!$A$1:$AA$29,MATCH(J$2,[3]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B7" s="1" t="s">
         <v>4</v>
       </c>
@@ -19030,10 +21524,14 @@
       </c>
       <c r="I7" s="4">
         <f>VLOOKUP($A$1,[4]resultados_integracion_partido_!$A$1:$AA$29,MATCH(I$2,[4]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="J7" s="4">
+        <f>VLOOKUP($A$1,[4]resultados_integracion_partido_!$A$1:$AA$29,MATCH(J$2,[4]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B8" s="1" t="s">
         <v>5</v>
       </c>
@@ -19063,10 +21561,14 @@
       </c>
       <c r="I8" s="4">
         <f>VLOOKUP($A$1,[5]resultados_integracion_partido_!$A$1:$AA$29,MATCH(I$2,[5]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="J8" s="4">
+        <f>VLOOKUP($A$1,[5]resultados_integracion_partido_!$A$1:$AA$29,MATCH(J$2,[5]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B9" s="1" t="s">
         <v>31</v>
       </c>
@@ -19096,10 +21598,14 @@
       </c>
       <c r="I9" s="4">
         <f>VLOOKUP($A$1,[6]resultados_integracion_partido_!$A$1:$AA$29,MATCH(I$2,[6]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="J9" s="4">
+        <f>VLOOKUP($A$1,[6]resultados_integracion_partido_!$A$1:$AA$29,MATCH(J$2,[6]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B10" s="1" t="s">
         <v>32</v>
       </c>
@@ -19129,10 +21635,14 @@
       </c>
       <c r="I10" s="4">
         <f>VLOOKUP($A$1,[7]resultados_integracion_partido_!$A$1:$AA$29,MATCH(I$2,[7]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="J10" s="4">
+        <f>VLOOKUP($A$1,[7]resultados_integracion_partido_!$A$1:$AA$29,MATCH(J$2,[7]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B11" s="1" t="s">
         <v>33</v>
       </c>
@@ -19162,10 +21672,14 @@
       </c>
       <c r="I11" s="4">
         <f>VLOOKUP($A$1,[8]resultados_integracion_partido_!$A$1:$AA$29,MATCH(I$2,[8]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="J11" s="4">
+        <f>VLOOKUP($A$1,[8]resultados_integracion_partido_!$A$1:$AA$29,MATCH(J$2,[8]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B12" s="1" t="s">
         <v>34</v>
       </c>
@@ -19195,115 +21709,203 @@
       </c>
       <c r="I12" s="4">
         <f>VLOOKUP($A$1,[9]resultados_integracion_partido_!$A$1:$AA$29,MATCH(I$2,[9]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="J12" s="4">
+        <f>VLOOKUP($A$1,[9]resultados_integracion_partido_!$A$1:$AA$29,MATCH(J$2,[9]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="14" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="31" t="s">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="B13" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C13" s="4">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="D13" s="4">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="E13" s="4">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="F13" s="4">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="G13" s="4">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="H13" s="4">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="I13" s="4">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(I$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="J13" s="4">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(J$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="B14" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C14" s="4">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="D14" s="4">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="E14" s="4">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="F14" s="4">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="G14" s="4">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="H14" s="4">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="I14" s="4">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(I$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="J14" s="4">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(J$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="16" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B16" s="32" t="s">
         <v>64</v>
       </c>
-      <c r="C14" s="32"/>
-      <c r="D14" s="32"/>
-      <c r="E14" s="32"/>
-      <c r="F14" s="32"/>
-      <c r="G14" s="32"/>
-      <c r="H14" s="32"/>
-      <c r="I14" s="33"/>
+      <c r="C16" s="33"/>
+      <c r="D16" s="33"/>
+      <c r="E16" s="33"/>
+      <c r="F16" s="33"/>
+      <c r="G16" s="33"/>
+      <c r="H16" s="33"/>
+      <c r="I16" s="33"/>
+      <c r="J16" s="34"/>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="B15" s="34"/>
-      <c r="C15" s="35"/>
-      <c r="D15" s="35"/>
-      <c r="E15" s="35"/>
-      <c r="F15" s="35"/>
-      <c r="G15" s="35"/>
-      <c r="H15" s="35"/>
-      <c r="I15" s="36"/>
+    <row r="17" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B17" s="35"/>
+      <c r="C17" s="36"/>
+      <c r="D17" s="36"/>
+      <c r="E17" s="36"/>
+      <c r="F17" s="36"/>
+      <c r="G17" s="36"/>
+      <c r="H17" s="36"/>
+      <c r="I17" s="36"/>
+      <c r="J17" s="37"/>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="B16" s="34"/>
-      <c r="C16" s="35"/>
-      <c r="D16" s="35"/>
-      <c r="E16" s="35"/>
-      <c r="F16" s="35"/>
-      <c r="G16" s="35"/>
-      <c r="H16" s="35"/>
-      <c r="I16" s="36"/>
+    <row r="18" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B18" s="35"/>
+      <c r="C18" s="36"/>
+      <c r="D18" s="36"/>
+      <c r="E18" s="36"/>
+      <c r="F18" s="36"/>
+      <c r="G18" s="36"/>
+      <c r="H18" s="36"/>
+      <c r="I18" s="36"/>
+      <c r="J18" s="37"/>
     </row>
-    <row r="17" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B17" s="34"/>
-      <c r="C17" s="35"/>
-      <c r="D17" s="35"/>
-      <c r="E17" s="35"/>
-      <c r="F17" s="35"/>
-      <c r="G17" s="35"/>
-      <c r="H17" s="35"/>
-      <c r="I17" s="36"/>
+    <row r="19" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B19" s="35"/>
+      <c r="C19" s="36"/>
+      <c r="D19" s="36"/>
+      <c r="E19" s="36"/>
+      <c r="F19" s="36"/>
+      <c r="G19" s="36"/>
+      <c r="H19" s="36"/>
+      <c r="I19" s="36"/>
+      <c r="J19" s="37"/>
     </row>
-    <row r="18" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B18" s="34"/>
-      <c r="C18" s="35"/>
-      <c r="D18" s="35"/>
-      <c r="E18" s="35"/>
-      <c r="F18" s="35"/>
-      <c r="G18" s="35"/>
-      <c r="H18" s="35"/>
-      <c r="I18" s="36"/>
+    <row r="20" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B20" s="35"/>
+      <c r="C20" s="36"/>
+      <c r="D20" s="36"/>
+      <c r="E20" s="36"/>
+      <c r="F20" s="36"/>
+      <c r="G20" s="36"/>
+      <c r="H20" s="36"/>
+      <c r="I20" s="36"/>
+      <c r="J20" s="37"/>
     </row>
-    <row r="19" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B19" s="34"/>
-      <c r="C19" s="35"/>
-      <c r="D19" s="35"/>
-      <c r="E19" s="35"/>
-      <c r="F19" s="35"/>
-      <c r="G19" s="35"/>
-      <c r="H19" s="35"/>
-      <c r="I19" s="36"/>
+    <row r="21" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B21" s="35"/>
+      <c r="C21" s="36"/>
+      <c r="D21" s="36"/>
+      <c r="E21" s="36"/>
+      <c r="F21" s="36"/>
+      <c r="G21" s="36"/>
+      <c r="H21" s="36"/>
+      <c r="I21" s="36"/>
+      <c r="J21" s="37"/>
     </row>
-    <row r="20" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B20" s="34"/>
-      <c r="C20" s="35"/>
-      <c r="D20" s="35"/>
-      <c r="E20" s="35"/>
-      <c r="F20" s="35"/>
-      <c r="G20" s="35"/>
-      <c r="H20" s="35"/>
-      <c r="I20" s="36"/>
+    <row r="22" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B22" s="35"/>
+      <c r="C22" s="36"/>
+      <c r="D22" s="36"/>
+      <c r="E22" s="36"/>
+      <c r="F22" s="36"/>
+      <c r="G22" s="36"/>
+      <c r="H22" s="36"/>
+      <c r="I22" s="36"/>
+      <c r="J22" s="37"/>
     </row>
-    <row r="21" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B21" s="34"/>
-      <c r="C21" s="35"/>
-      <c r="D21" s="35"/>
-      <c r="E21" s="35"/>
-      <c r="F21" s="35"/>
-      <c r="G21" s="35"/>
-      <c r="H21" s="35"/>
-      <c r="I21" s="36"/>
+    <row r="23" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B23" s="35"/>
+      <c r="C23" s="36"/>
+      <c r="D23" s="36"/>
+      <c r="E23" s="36"/>
+      <c r="F23" s="36"/>
+      <c r="G23" s="36"/>
+      <c r="H23" s="36"/>
+      <c r="I23" s="36"/>
+      <c r="J23" s="37"/>
     </row>
-    <row r="22" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B22" s="34"/>
-      <c r="C22" s="35"/>
-      <c r="D22" s="35"/>
-      <c r="E22" s="35"/>
-      <c r="F22" s="35"/>
-      <c r="G22" s="35"/>
-      <c r="H22" s="35"/>
-      <c r="I22" s="36"/>
+    <row r="24" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B24" s="35"/>
+      <c r="C24" s="36"/>
+      <c r="D24" s="36"/>
+      <c r="E24" s="36"/>
+      <c r="F24" s="36"/>
+      <c r="G24" s="36"/>
+      <c r="H24" s="36"/>
+      <c r="I24" s="36"/>
+      <c r="J24" s="37"/>
     </row>
-    <row r="23" spans="2:9" ht="68.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B23" s="37"/>
-      <c r="C23" s="38"/>
-      <c r="D23" s="38"/>
-      <c r="E23" s="38"/>
-      <c r="F23" s="38"/>
-      <c r="G23" s="38"/>
-      <c r="H23" s="38"/>
-      <c r="I23" s="39"/>
+    <row r="25" spans="2:10" ht="68.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B25" s="38"/>
+      <c r="C25" s="39"/>
+      <c r="D25" s="39"/>
+      <c r="E25" s="39"/>
+      <c r="F25" s="39"/>
+      <c r="G25" s="39"/>
+      <c r="H25" s="39"/>
+      <c r="I25" s="39"/>
+      <c r="J25" s="40"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="B14:I23"/>
+    <mergeCell ref="B16:J25"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -19311,15 +21913,17 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A80A2506-0B9F-4B14-ADA0-702CD03037C2}">
-  <dimension ref="A1:K23"/>
+  <dimension ref="A1:K25"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="1.90625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="19.36328125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.90625" bestFit="1" customWidth="1"/>
-    <col min="4" max="8" width="5.90625" bestFit="1" customWidth="1"/>
+    <col min="4" max="6" width="5.90625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.7265625" customWidth="1"/>
+    <col min="8" max="8" width="7.90625" customWidth="1"/>
     <col min="9" max="9" width="6.08984375" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.08984375" customWidth="1"/>
     <col min="11" max="11" width="6.90625" bestFit="1" customWidth="1"/>
@@ -19765,132 +22369,214 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="14" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="31" t="s">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B13" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C13" s="4">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="D13" s="4">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="E13" s="4">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F13" s="4">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="G13" s="4">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="H13" s="4">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="I13" s="4">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(I$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="J13" s="4">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(J$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="K13" s="4">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(K$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B14" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C14" s="4">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="D14" s="4">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="E14" s="4">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F14" s="4">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="G14" s="4">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="H14" s="4">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="I14" s="4">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(I$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="J14" s="4">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(J$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="K14" s="4">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(K$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="16" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B16" s="32" t="s">
         <v>64</v>
       </c>
-      <c r="C14" s="32"/>
-      <c r="D14" s="32"/>
-      <c r="E14" s="32"/>
-      <c r="F14" s="32"/>
-      <c r="G14" s="32"/>
-      <c r="H14" s="32"/>
-      <c r="I14" s="32"/>
-      <c r="J14" s="32"/>
-      <c r="K14" s="33"/>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="B15" s="34"/>
-      <c r="C15" s="35"/>
-      <c r="D15" s="35"/>
-      <c r="E15" s="35"/>
-      <c r="F15" s="35"/>
-      <c r="G15" s="35"/>
-      <c r="H15" s="35"/>
-      <c r="I15" s="35"/>
-      <c r="J15" s="35"/>
-      <c r="K15" s="36"/>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="B16" s="34"/>
-      <c r="C16" s="35"/>
-      <c r="D16" s="35"/>
-      <c r="E16" s="35"/>
-      <c r="F16" s="35"/>
-      <c r="G16" s="35"/>
-      <c r="H16" s="35"/>
-      <c r="I16" s="35"/>
-      <c r="J16" s="35"/>
-      <c r="K16" s="36"/>
+      <c r="C16" s="33"/>
+      <c r="D16" s="33"/>
+      <c r="E16" s="33"/>
+      <c r="F16" s="33"/>
+      <c r="G16" s="33"/>
+      <c r="H16" s="33"/>
+      <c r="I16" s="33"/>
+      <c r="J16" s="33"/>
+      <c r="K16" s="34"/>
     </row>
     <row r="17" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B17" s="34"/>
-      <c r="C17" s="35"/>
-      <c r="D17" s="35"/>
-      <c r="E17" s="35"/>
-      <c r="F17" s="35"/>
-      <c r="G17" s="35"/>
-      <c r="H17" s="35"/>
-      <c r="I17" s="35"/>
-      <c r="J17" s="35"/>
-      <c r="K17" s="36"/>
+      <c r="B17" s="35"/>
+      <c r="C17" s="36"/>
+      <c r="D17" s="36"/>
+      <c r="E17" s="36"/>
+      <c r="F17" s="36"/>
+      <c r="G17" s="36"/>
+      <c r="H17" s="36"/>
+      <c r="I17" s="36"/>
+      <c r="J17" s="36"/>
+      <c r="K17" s="37"/>
     </row>
     <row r="18" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B18" s="34"/>
-      <c r="C18" s="35"/>
-      <c r="D18" s="35"/>
-      <c r="E18" s="35"/>
-      <c r="F18" s="35"/>
-      <c r="G18" s="35"/>
-      <c r="H18" s="35"/>
-      <c r="I18" s="35"/>
-      <c r="J18" s="35"/>
-      <c r="K18" s="36"/>
+      <c r="B18" s="35"/>
+      <c r="C18" s="36"/>
+      <c r="D18" s="36"/>
+      <c r="E18" s="36"/>
+      <c r="F18" s="36"/>
+      <c r="G18" s="36"/>
+      <c r="H18" s="36"/>
+      <c r="I18" s="36"/>
+      <c r="J18" s="36"/>
+      <c r="K18" s="37"/>
     </row>
     <row r="19" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B19" s="34"/>
-      <c r="C19" s="35"/>
-      <c r="D19" s="35"/>
-      <c r="E19" s="35"/>
-      <c r="F19" s="35"/>
-      <c r="G19" s="35"/>
-      <c r="H19" s="35"/>
-      <c r="I19" s="35"/>
-      <c r="J19" s="35"/>
-      <c r="K19" s="36"/>
+      <c r="B19" s="35"/>
+      <c r="C19" s="36"/>
+      <c r="D19" s="36"/>
+      <c r="E19" s="36"/>
+      <c r="F19" s="36"/>
+      <c r="G19" s="36"/>
+      <c r="H19" s="36"/>
+      <c r="I19" s="36"/>
+      <c r="J19" s="36"/>
+      <c r="K19" s="37"/>
     </row>
     <row r="20" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B20" s="34"/>
-      <c r="C20" s="35"/>
-      <c r="D20" s="35"/>
-      <c r="E20" s="35"/>
-      <c r="F20" s="35"/>
-      <c r="G20" s="35"/>
-      <c r="H20" s="35"/>
-      <c r="I20" s="35"/>
-      <c r="J20" s="35"/>
-      <c r="K20" s="36"/>
+      <c r="B20" s="35"/>
+      <c r="C20" s="36"/>
+      <c r="D20" s="36"/>
+      <c r="E20" s="36"/>
+      <c r="F20" s="36"/>
+      <c r="G20" s="36"/>
+      <c r="H20" s="36"/>
+      <c r="I20" s="36"/>
+      <c r="J20" s="36"/>
+      <c r="K20" s="37"/>
     </row>
     <row r="21" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B21" s="34"/>
-      <c r="C21" s="35"/>
-      <c r="D21" s="35"/>
-      <c r="E21" s="35"/>
-      <c r="F21" s="35"/>
-      <c r="G21" s="35"/>
-      <c r="H21" s="35"/>
-      <c r="I21" s="35"/>
-      <c r="J21" s="35"/>
-      <c r="K21" s="36"/>
+      <c r="B21" s="35"/>
+      <c r="C21" s="36"/>
+      <c r="D21" s="36"/>
+      <c r="E21" s="36"/>
+      <c r="F21" s="36"/>
+      <c r="G21" s="36"/>
+      <c r="H21" s="36"/>
+      <c r="I21" s="36"/>
+      <c r="J21" s="36"/>
+      <c r="K21" s="37"/>
     </row>
     <row r="22" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B22" s="34"/>
-      <c r="C22" s="35"/>
-      <c r="D22" s="35"/>
-      <c r="E22" s="35"/>
-      <c r="F22" s="35"/>
-      <c r="G22" s="35"/>
-      <c r="H22" s="35"/>
-      <c r="I22" s="35"/>
-      <c r="J22" s="35"/>
-      <c r="K22" s="36"/>
+      <c r="B22" s="35"/>
+      <c r="C22" s="36"/>
+      <c r="D22" s="36"/>
+      <c r="E22" s="36"/>
+      <c r="F22" s="36"/>
+      <c r="G22" s="36"/>
+      <c r="H22" s="36"/>
+      <c r="I22" s="36"/>
+      <c r="J22" s="36"/>
+      <c r="K22" s="37"/>
     </row>
-    <row r="23" spans="2:11" ht="17.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B23" s="37"/>
-      <c r="C23" s="38"/>
-      <c r="D23" s="38"/>
-      <c r="E23" s="38"/>
-      <c r="F23" s="38"/>
-      <c r="G23" s="38"/>
-      <c r="H23" s="38"/>
-      <c r="I23" s="38"/>
-      <c r="J23" s="38"/>
-      <c r="K23" s="39"/>
+    <row r="23" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="B23" s="35"/>
+      <c r="C23" s="36"/>
+      <c r="D23" s="36"/>
+      <c r="E23" s="36"/>
+      <c r="F23" s="36"/>
+      <c r="G23" s="36"/>
+      <c r="H23" s="36"/>
+      <c r="I23" s="36"/>
+      <c r="J23" s="36"/>
+      <c r="K23" s="37"/>
+    </row>
+    <row r="24" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="B24" s="35"/>
+      <c r="C24" s="36"/>
+      <c r="D24" s="36"/>
+      <c r="E24" s="36"/>
+      <c r="F24" s="36"/>
+      <c r="G24" s="36"/>
+      <c r="H24" s="36"/>
+      <c r="I24" s="36"/>
+      <c r="J24" s="36"/>
+      <c r="K24" s="37"/>
+    </row>
+    <row r="25" spans="2:11" ht="17.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B25" s="38"/>
+      <c r="C25" s="39"/>
+      <c r="D25" s="39"/>
+      <c r="E25" s="39"/>
+      <c r="F25" s="39"/>
+      <c r="G25" s="39"/>
+      <c r="H25" s="39"/>
+      <c r="I25" s="39"/>
+      <c r="J25" s="39"/>
+      <c r="K25" s="40"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="B14:K23"/>
+    <mergeCell ref="B16:K25"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -19898,15 +22584,17 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5FCF9B40-470A-4DE1-8AB1-26EEC2BE06FE}">
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="1.90625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="19.36328125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.90625" bestFit="1" customWidth="1"/>
-    <col min="4" max="7" width="5.90625" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="5.90625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.90625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.90625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="6.90625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="5.90625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="16.26953125" customWidth="1"/>
@@ -20267,112 +22955,178 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="14" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="31" t="s">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="B13" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C13" s="4">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="D13" s="4">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="E13" s="4">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F13" s="4">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="G13" s="4">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="H13" s="4">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="I13" s="4">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(I$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="B14" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C14" s="4">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="D14" s="4">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="E14" s="4">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F14" s="4">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="G14" s="4">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="H14" s="4">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="I14" s="4">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(I$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="16" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B16" s="32" t="s">
         <v>64</v>
       </c>
-      <c r="C14" s="32"/>
-      <c r="D14" s="32"/>
-      <c r="E14" s="32"/>
-      <c r="F14" s="32"/>
-      <c r="G14" s="32"/>
-      <c r="H14" s="32"/>
-      <c r="I14" s="33"/>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="B15" s="34"/>
-      <c r="C15" s="35"/>
-      <c r="D15" s="35"/>
-      <c r="E15" s="35"/>
-      <c r="F15" s="35"/>
-      <c r="G15" s="35"/>
-      <c r="H15" s="35"/>
-      <c r="I15" s="36"/>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="B16" s="34"/>
-      <c r="C16" s="35"/>
-      <c r="D16" s="35"/>
-      <c r="E16" s="35"/>
-      <c r="F16" s="35"/>
-      <c r="G16" s="35"/>
-      <c r="H16" s="35"/>
-      <c r="I16" s="36"/>
+      <c r="C16" s="33"/>
+      <c r="D16" s="33"/>
+      <c r="E16" s="33"/>
+      <c r="F16" s="33"/>
+      <c r="G16" s="33"/>
+      <c r="H16" s="33"/>
+      <c r="I16" s="34"/>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B17" s="34"/>
-      <c r="C17" s="35"/>
-      <c r="D17" s="35"/>
-      <c r="E17" s="35"/>
-      <c r="F17" s="35"/>
-      <c r="G17" s="35"/>
-      <c r="H17" s="35"/>
-      <c r="I17" s="36"/>
+      <c r="B17" s="35"/>
+      <c r="C17" s="36"/>
+      <c r="D17" s="36"/>
+      <c r="E17" s="36"/>
+      <c r="F17" s="36"/>
+      <c r="G17" s="36"/>
+      <c r="H17" s="36"/>
+      <c r="I17" s="37"/>
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B18" s="34"/>
-      <c r="C18" s="35"/>
-      <c r="D18" s="35"/>
-      <c r="E18" s="35"/>
-      <c r="F18" s="35"/>
-      <c r="G18" s="35"/>
-      <c r="H18" s="35"/>
-      <c r="I18" s="36"/>
+      <c r="B18" s="35"/>
+      <c r="C18" s="36"/>
+      <c r="D18" s="36"/>
+      <c r="E18" s="36"/>
+      <c r="F18" s="36"/>
+      <c r="G18" s="36"/>
+      <c r="H18" s="36"/>
+      <c r="I18" s="37"/>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B19" s="34"/>
-      <c r="C19" s="35"/>
-      <c r="D19" s="35"/>
-      <c r="E19" s="35"/>
-      <c r="F19" s="35"/>
-      <c r="G19" s="35"/>
-      <c r="H19" s="35"/>
-      <c r="I19" s="36"/>
+      <c r="B19" s="35"/>
+      <c r="C19" s="36"/>
+      <c r="D19" s="36"/>
+      <c r="E19" s="36"/>
+      <c r="F19" s="36"/>
+      <c r="G19" s="36"/>
+      <c r="H19" s="36"/>
+      <c r="I19" s="37"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B20" s="34"/>
-      <c r="C20" s="35"/>
-      <c r="D20" s="35"/>
-      <c r="E20" s="35"/>
-      <c r="F20" s="35"/>
-      <c r="G20" s="35"/>
-      <c r="H20" s="35"/>
-      <c r="I20" s="36"/>
+      <c r="B20" s="35"/>
+      <c r="C20" s="36"/>
+      <c r="D20" s="36"/>
+      <c r="E20" s="36"/>
+      <c r="F20" s="36"/>
+      <c r="G20" s="36"/>
+      <c r="H20" s="36"/>
+      <c r="I20" s="37"/>
     </row>
     <row r="21" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B21" s="34"/>
-      <c r="C21" s="35"/>
-      <c r="D21" s="35"/>
-      <c r="E21" s="35"/>
-      <c r="F21" s="35"/>
-      <c r="G21" s="35"/>
-      <c r="H21" s="35"/>
-      <c r="I21" s="36"/>
+      <c r="B21" s="35"/>
+      <c r="C21" s="36"/>
+      <c r="D21" s="36"/>
+      <c r="E21" s="36"/>
+      <c r="F21" s="36"/>
+      <c r="G21" s="36"/>
+      <c r="H21" s="36"/>
+      <c r="I21" s="37"/>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B22" s="34"/>
-      <c r="C22" s="35"/>
-      <c r="D22" s="35"/>
-      <c r="E22" s="35"/>
-      <c r="F22" s="35"/>
-      <c r="G22" s="35"/>
-      <c r="H22" s="35"/>
-      <c r="I22" s="36"/>
+      <c r="B22" s="35"/>
+      <c r="C22" s="36"/>
+      <c r="D22" s="36"/>
+      <c r="E22" s="36"/>
+      <c r="F22" s="36"/>
+      <c r="G22" s="36"/>
+      <c r="H22" s="36"/>
+      <c r="I22" s="37"/>
     </row>
-    <row r="23" spans="2:9" ht="67.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B23" s="37"/>
-      <c r="C23" s="38"/>
-      <c r="D23" s="38"/>
-      <c r="E23" s="38"/>
-      <c r="F23" s="38"/>
-      <c r="G23" s="38"/>
-      <c r="H23" s="38"/>
-      <c r="I23" s="39"/>
+    <row r="23" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B23" s="35"/>
+      <c r="C23" s="36"/>
+      <c r="D23" s="36"/>
+      <c r="E23" s="36"/>
+      <c r="F23" s="36"/>
+      <c r="G23" s="36"/>
+      <c r="H23" s="36"/>
+      <c r="I23" s="37"/>
+    </row>
+    <row r="24" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B24" s="35"/>
+      <c r="C24" s="36"/>
+      <c r="D24" s="36"/>
+      <c r="E24" s="36"/>
+      <c r="F24" s="36"/>
+      <c r="G24" s="36"/>
+      <c r="H24" s="36"/>
+      <c r="I24" s="37"/>
+    </row>
+    <row r="25" spans="2:9" ht="67.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B25" s="38"/>
+      <c r="C25" s="39"/>
+      <c r="D25" s="39"/>
+      <c r="E25" s="39"/>
+      <c r="F25" s="39"/>
+      <c r="G25" s="39"/>
+      <c r="H25" s="39"/>
+      <c r="I25" s="40"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="B14:I23"/>
+    <mergeCell ref="B16:I25"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -20380,9 +23134,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6FB0C85-64F4-4D82-8FA2-89FE65C5C7BA}">
-  <dimension ref="A1:H23"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="2.81640625" bestFit="1" customWidth="1"/>
@@ -20707,102 +23461,160 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="14" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="31" t="s">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B13" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C13" s="4">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="D13" s="4">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="E13" s="4">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F13" s="4">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="G13" s="4">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="H13" s="4">
+        <f>VLOOKUP($A$1,[10]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[10]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B14" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C14" s="4">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(C$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="D14" s="4">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(D$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="E14" s="4">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(E$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="F14" s="4">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(F$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="G14" s="4">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(G$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="H14" s="4">
+        <f>VLOOKUP($A$1,[11]resultados_integracion_partido_!$A$1:$AA$29,MATCH(H$2,[11]resultados_integracion_partido_!$A$1:$AA$1,0),FALSE)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="16" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B16" s="32" t="s">
         <v>64</v>
       </c>
-      <c r="C14" s="32"/>
-      <c r="D14" s="32"/>
-      <c r="E14" s="32"/>
-      <c r="F14" s="32"/>
-      <c r="G14" s="32"/>
-      <c r="H14" s="33"/>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="B15" s="34"/>
-      <c r="C15" s="35"/>
-      <c r="D15" s="35"/>
-      <c r="E15" s="35"/>
-      <c r="F15" s="35"/>
-      <c r="G15" s="35"/>
-      <c r="H15" s="36"/>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="B16" s="34"/>
-      <c r="C16" s="35"/>
-      <c r="D16" s="35"/>
-      <c r="E16" s="35"/>
-      <c r="F16" s="35"/>
-      <c r="G16" s="35"/>
-      <c r="H16" s="36"/>
+      <c r="C16" s="33"/>
+      <c r="D16" s="33"/>
+      <c r="E16" s="33"/>
+      <c r="F16" s="33"/>
+      <c r="G16" s="33"/>
+      <c r="H16" s="34"/>
     </row>
     <row r="17" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B17" s="34"/>
-      <c r="C17" s="35"/>
-      <c r="D17" s="35"/>
-      <c r="E17" s="35"/>
-      <c r="F17" s="35"/>
-      <c r="G17" s="35"/>
-      <c r="H17" s="36"/>
+      <c r="B17" s="35"/>
+      <c r="C17" s="36"/>
+      <c r="D17" s="36"/>
+      <c r="E17" s="36"/>
+      <c r="F17" s="36"/>
+      <c r="G17" s="36"/>
+      <c r="H17" s="37"/>
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B18" s="34"/>
-      <c r="C18" s="35"/>
-      <c r="D18" s="35"/>
-      <c r="E18" s="35"/>
-      <c r="F18" s="35"/>
-      <c r="G18" s="35"/>
-      <c r="H18" s="36"/>
+      <c r="B18" s="35"/>
+      <c r="C18" s="36"/>
+      <c r="D18" s="36"/>
+      <c r="E18" s="36"/>
+      <c r="F18" s="36"/>
+      <c r="G18" s="36"/>
+      <c r="H18" s="37"/>
     </row>
     <row r="19" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B19" s="34"/>
-      <c r="C19" s="35"/>
-      <c r="D19" s="35"/>
-      <c r="E19" s="35"/>
-      <c r="F19" s="35"/>
-      <c r="G19" s="35"/>
-      <c r="H19" s="36"/>
+      <c r="B19" s="35"/>
+      <c r="C19" s="36"/>
+      <c r="D19" s="36"/>
+      <c r="E19" s="36"/>
+      <c r="F19" s="36"/>
+      <c r="G19" s="36"/>
+      <c r="H19" s="37"/>
     </row>
-    <row r="20" spans="2:8" ht="74" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B20" s="34"/>
-      <c r="C20" s="35"/>
-      <c r="D20" s="35"/>
-      <c r="E20" s="35"/>
-      <c r="F20" s="35"/>
-      <c r="G20" s="35"/>
-      <c r="H20" s="36"/>
+    <row r="20" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B20" s="35"/>
+      <c r="C20" s="36"/>
+      <c r="D20" s="36"/>
+      <c r="E20" s="36"/>
+      <c r="F20" s="36"/>
+      <c r="G20" s="36"/>
+      <c r="H20" s="37"/>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B21" s="34"/>
-      <c r="C21" s="35"/>
-      <c r="D21" s="35"/>
-      <c r="E21" s="35"/>
-      <c r="F21" s="35"/>
-      <c r="G21" s="35"/>
-      <c r="H21" s="36"/>
+      <c r="B21" s="35"/>
+      <c r="C21" s="36"/>
+      <c r="D21" s="36"/>
+      <c r="E21" s="36"/>
+      <c r="F21" s="36"/>
+      <c r="G21" s="36"/>
+      <c r="H21" s="37"/>
     </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B22" s="34"/>
-      <c r="C22" s="35"/>
-      <c r="D22" s="35"/>
-      <c r="E22" s="35"/>
-      <c r="F22" s="35"/>
-      <c r="G22" s="35"/>
-      <c r="H22" s="36"/>
+    <row r="22" spans="2:8" ht="74" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B22" s="35"/>
+      <c r="C22" s="36"/>
+      <c r="D22" s="36"/>
+      <c r="E22" s="36"/>
+      <c r="F22" s="36"/>
+      <c r="G22" s="36"/>
+      <c r="H22" s="37"/>
     </row>
-    <row r="23" spans="2:8" ht="10.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B23" s="37"/>
-      <c r="C23" s="38"/>
-      <c r="D23" s="38"/>
-      <c r="E23" s="38"/>
-      <c r="F23" s="38"/>
-      <c r="G23" s="38"/>
-      <c r="H23" s="39"/>
+    <row r="23" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B23" s="35"/>
+      <c r="C23" s="36"/>
+      <c r="D23" s="36"/>
+      <c r="E23" s="36"/>
+      <c r="F23" s="36"/>
+      <c r="G23" s="36"/>
+      <c r="H23" s="37"/>
+    </row>
+    <row r="24" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B24" s="35"/>
+      <c r="C24" s="36"/>
+      <c r="D24" s="36"/>
+      <c r="E24" s="36"/>
+      <c r="F24" s="36"/>
+      <c r="G24" s="36"/>
+      <c r="H24" s="37"/>
+    </row>
+    <row r="25" spans="2:8" ht="10.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B25" s="38"/>
+      <c r="C25" s="39"/>
+      <c r="D25" s="39"/>
+      <c r="E25" s="39"/>
+      <c r="F25" s="39"/>
+      <c r="G25" s="39"/>
+      <c r="H25" s="40"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="B14:H23"/>
+    <mergeCell ref="B16:H25"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
